--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>8671</v>
+        <v>8662</v>
       </c>
       <c r="C9" s="1" t="n"/>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="n"/>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="n"/>
     </row>
@@ -3174,7 +3174,6 @@
 MK-PL-F-050 — Never lets balance fall below 0.
 MK-PL-F-050 — Never lets off fall below 0.
 MK-PL-F-050 — Never lets required withdrawal tax rate fall below 0.
-MK-PL-F-050 — Rounds the answer to a whole number.
 MK-PL-F-050 — The tax on pre-tax withdrawals is the rate the caller passes, capped at 60%; when no rate is passed NO tax is applied and the result says so — never a built-in 22% (G7, founder 2026-09-12).
 MK-PL-F-050 — Turns a monthly figure into a year by multiplying by twelve.
 MK-PL-F-050 — Uses a built-in successes of 0.
@@ -3185,7 +3184,7 @@
 MK-PL-F-055 — Uses a built-in need of 0.
 MK-PL-F-060 — If statement monthly is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-PL-F-065 — Never lets the answer fall below 5% or rise above 20%.
-MK-PL-F-066 — Rounds the answer to a whole number.
+MK-PL-F-066 — Rounds the answer to 6 decimal places.
 MK-PL-F-067 — If monthly is missing it uses 0.
 MK-PL-F-067 — If salary growth is missing it uses 0.
 MK-PL-F-067 — If social security claim age is missing it uses 67.
@@ -3205,7 +3204,7 @@
 [Founder] Each stream grows on its own rule: Social Security rises with inflation, a fixed pension stays flat. They are never inflated together (fix B1).
 [Founder] One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.
 [Founder] The recommended nest egg is 25× the yearly expenses not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.
-[Founder] brief Q-50 (2026-08-20): inflation defaults to the 30-year average of consumer prices — 2.5% a year (Bureau of Labor Statistics CPI-U, 1996–2025), fixed and date</t>
+[Founder] brief Q-50 (2026-08-20): inflation defaults to the 30-year average of consumer prices — 2.5% a year (Bureau of Labor Statistics CPI-U, 1996–2025), fixed and dated, stated on screen, and the person can change it</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -3598,7 +3597,6 @@
 MK-PL-F-050 — Never lets balance fall below 0.
 MK-PL-F-050 — Never lets off fall below 0.
 MK-PL-F-050 — Never lets required withdrawal tax rate fall below 0.
-MK-PL-F-050 — Rounds the answer to a whole number.
 MK-PL-F-050 — The tax on pre-tax withdrawals is the rate the caller passes, capped at 60%; when no rate is passed NO tax is applied and the result says so — never a built-in 22% (G7, founder 2026-09-12).
 MK-PL-F-050 — Turns a monthly figure into a year by multiplying by twelve.
 MK-PL-F-050 — Uses a built-in successes of 0.
@@ -4558,7 +4556,7 @@
 MK-XS-F-179 — G9 (founder, 2026-09-12): birthday-aware when the birth month is known (the onboarding asks for it), the year-attained age when only the year is known, nothing when the birth year is unknown — never a stand-in month or age. Limits use the year-attained age instead (G1).
 MK-XS-F-179 — Uses today's date from the device clock, so the answer changes by itself overnight.
 No function on record — assumptions unknown
-… and 41 more, on the functions tab</t>
+… and 40 more, on the functions tab</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -7163,7 +7161,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>26 rows on the master · 30 places in the code print a dollar figure · 5 of them have no row · 10 rows not found on screen</t>
+          <t>26 rows on the master · 30 places in the code print a dollar figure · 6 of them have no row · 10 rows not found on screen</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -7478,7 +7476,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>10 rows on the master · 19 places in the code print a dollar figure · 3 of them have no row · 4 rows not found on screen</t>
+          <t>10 rows on the master · 19 places in the code print a dollar figure · 4 of them have no row · 4 rows not found on screen</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -8922,7 +8920,7 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>Connected · read-only | What is Where this number came from?</t>
+          <t>Linked · read-only | What is Where this number came from?</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
@@ -9767,7 +9765,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>🔗 | connected · updated yesterday | $#</t>
+          <t>🔗 | linked | $#</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -10849,7 +10847,7 @@
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>: ~ | $20,210</t>
+          <t>: ~ | $20,125</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
@@ -11150,7 +11148,7 @@
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>ⓘ | $1,300</t>
+          <t>ⓘ | $1,295</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
@@ -12264,7 +12262,7 @@
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>$4,800 | this month</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
@@ -12350,7 +12348,7 @@
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>. | Surplus in Sep: an estimate. $4,800</t>
+          <t>. | Surplus in Sep: an estimate. $4,795</t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
@@ -12393,7 +12391,7 @@
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>ⓘ | $1,300</t>
+          <t>ⓘ | $1,295</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
@@ -14146,7 +14144,7 @@
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t>No big bills this month. | = Surplus: $4,800</t>
+          <t>No big bills this month. | = Surplus: $4,795</t>
         </is>
       </c>
       <c r="H178" s="1" t="inlineStr">
@@ -14188,7 +14186,7 @@
         </is>
       </c>
       <c r="G179" s="1">
-        <f> In | $4,800</f>
+        <f> In | $4,795</f>
         <v/>
       </c>
       <c r="H179" s="1" t="inlineStr">
@@ -14231,7 +14229,7 @@
       </c>
       <c r="G180" s="1" t="inlineStr">
         <is>
-          <t>$1,300 | Draw from savings: $1,300</t>
+          <t>$1,300 | Draw from savings: $1,295</t>
         </is>
       </c>
       <c r="H180" s="1" t="inlineStr">
@@ -14446,7 +14444,7 @@
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t>SURPLUS · AS OF TODAY | $4,800</t>
+          <t>SURPLUS · AS OF TODAY | $4,795</t>
         </is>
       </c>
       <c r="H185" s="1" t="inlineStr">
@@ -14617,7 +14615,7 @@
         </is>
       </c>
       <c r="G189" s="1">
-        <f> Surplus | $4,800</f>
+        <f> Surplus | $4,795</f>
         <v/>
       </c>
       <c r="H189" s="1" t="inlineStr">
@@ -15133,7 +15131,7 @@
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t>Every month is its own real month — a pension that lands in December shows up in December, a property tax in November dents November. This year: | $480</t>
+          <t>Every month is its own real month — a pension that lands in December shows up in December, a property tax in November dents November. This year: | $420</t>
         </is>
       </c>
       <c r="H201" s="1" t="inlineStr">
@@ -15176,7 +15174,7 @@
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t>(calculated). | Sep: surplus $340</t>
+          <t>(calculated). | Sep: surplus $335</t>
         </is>
       </c>
       <c r="H202" s="1" t="inlineStr">
@@ -15219,7 +15217,7 @@
       </c>
       <c r="G203" s="1" t="inlineStr">
         <is>
-          <t>$340 | Dec: surplus $340</t>
+          <t>$335 | Dec: surplus $335</t>
         </is>
       </c>
       <c r="H203" s="1" t="inlineStr">
@@ -15262,7 +15260,7 @@
       </c>
       <c r="G204" s="1" t="inlineStr">
         <is>
-          <t>$420 | Oct: surplus $340</t>
+          <t>$420 | Oct: surplus $335</t>
         </is>
       </c>
       <c r="H204" s="1" t="inlineStr">
@@ -15305,7 +15303,7 @@
       </c>
       <c r="G205" s="1" t="inlineStr">
         <is>
-          <t>$340 | Aug ’27: surplus $340</t>
+          <t>$335 | Aug ’27: surplus $335</t>
         </is>
       </c>
       <c r="H205" s="1" t="inlineStr">
@@ -15348,7 +15346,7 @@
       </c>
       <c r="G206" s="1" t="inlineStr">
         <is>
-          <t>$340 | Jan ’27: surplus $340</t>
+          <t>$335 | Jan ’27: surplus $335</t>
         </is>
       </c>
       <c r="H206" s="1" t="inlineStr">
@@ -15391,7 +15389,7 @@
       </c>
       <c r="G207" s="1" t="inlineStr">
         <is>
-          <t>$4,800 | May ’27: surplus $4,800</t>
+          <t>$4,795 | May ’27: surplus $4,795</t>
         </is>
       </c>
       <c r="H207" s="1" t="inlineStr">
@@ -15434,7 +15432,7 @@
       </c>
       <c r="G208" s="1" t="inlineStr">
         <is>
-          <t>$340 | Mar ’27: surplus $340</t>
+          <t>$335 | Mar ’27: surplus $335</t>
         </is>
       </c>
       <c r="H208" s="1" t="inlineStr">
@@ -15477,7 +15475,7 @@
       </c>
       <c r="G209" s="1" t="inlineStr">
         <is>
-          <t>$4,800 | Jun ’27: surplus $2,400, lower — big bill this month</t>
+          <t>$4,795 | Jun ’27: surplus $2,395, lower — big bill this month</t>
         </is>
       </c>
       <c r="H209" s="1" t="inlineStr">
@@ -15520,7 +15518,7 @@
       </c>
       <c r="G210" s="1" t="inlineStr">
         <is>
-          <t>$340 | Apr ’27: surplus -$3,260, lower — big bill this month</t>
+          <t>$335 | Apr ’27: surplus -$3,265, lower — big bill this month</t>
         </is>
       </c>
       <c r="H210" s="1" t="inlineStr">
@@ -15605,7 +15603,7 @@
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t>Draw from savings | $340</t>
+          <t>Draw from savings | $335</t>
         </is>
       </c>
       <c r="H212" s="1" t="inlineStr">
@@ -15691,7 +15689,7 @@
       </c>
       <c r="G214" s="1" t="inlineStr">
         <is>
-          <t>Sep | $4,800</t>
+          <t>Sep | $4,795</t>
         </is>
       </c>
       <c r="H214" s="1" t="inlineStr">
@@ -15734,7 +15732,7 @@
       </c>
       <c r="G215" s="1" t="inlineStr">
         <is>
-          <t>$340 | Big bills this month</t>
+          <t>$335 | Big bills this month</t>
         </is>
       </c>
       <c r="H215" s="1" t="inlineStr">
@@ -15820,7 +15818,7 @@
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t>$340 | Inflow (income (take-home))</t>
+          <t>$335 | Inflow (income (take-home))</t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
@@ -15905,7 +15903,7 @@
         </is>
       </c>
       <c r="G219" s="1">
-        <f> Surplus | $340</f>
+        <f> Surplus | $335</f>
         <v/>
       </c>
       <c r="H219" s="1" t="inlineStr">
@@ -15947,7 +15945,7 @@
         </is>
       </c>
       <c r="G220" s="1">
-        <f> Surplus | $4,800</f>
+        <f> Surplus | $4,795</f>
         <v/>
       </c>
       <c r="H220" s="1" t="inlineStr">
@@ -15989,7 +15987,7 @@
         </is>
       </c>
       <c r="G221" s="1">
-        <f> Surplus | $1,520</f>
+        <f> Surplus | $1,495</f>
         <v/>
       </c>
       <c r="H221" s="1" t="inlineStr">
@@ -17146,7 +17144,7 @@
       </c>
       <c r="G248" s="1" t="inlineStr">
         <is>
-          <t>past age 95 | in most futures — 95out of 100 simulated futures</t>
+          <t>past age 95 | in most futures — 99.4out of 100 simulated futures</t>
         </is>
       </c>
       <c r="H248" s="1" t="inlineStr">
@@ -19765,7 +19763,7 @@
       </c>
       <c r="G309" s="1" t="inlineStr">
         <is>
-          <t>✓ Saved — Home, Plan and this screen all use these same answers. | Estimates at age 65: nest egg $4,977,392 becomes $5,734,057; the chance your money lasts 95 p</t>
+          <t>✓ Saved — Home, Plan and this screen all use these same answers. | Estimates at age 65: nest egg $4,977,392 becomes $5,734,057; the chance your money lasts 93 p</t>
         </is>
       </c>
       <c r="H309" s="1" t="inlineStr">
@@ -22340,7 +22338,7 @@
       </c>
       <c r="G385" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H385" s="1" t="inlineStr">
@@ -22383,7 +22381,7 @@
       </c>
       <c r="G386" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H386" s="1" t="inlineStr">
@@ -22459,7 +22457,7 @@
       </c>
       <c r="E388" s="1" t="inlineStr">
         <is>
-          <t>$4,800 … (14 renders)</t>
+          <t>$4,795 … (14 renders)</t>
         </is>
       </c>
       <c r="F388" s="1" t="inlineStr">
@@ -22512,7 +22510,7 @@
       </c>
       <c r="G389" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H389" s="1" t="inlineStr">
@@ -22555,7 +22553,7 @@
       </c>
       <c r="G390" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-009 YOUR SOURCES — Stock vesting (equity)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H390" s="1" t="inlineStr">
@@ -22568,7 +22566,7 @@
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B391" s="1" t="inlineStr">
@@ -22588,7 +22586,7 @@
       </c>
       <c r="E391" s="1" t="inlineStr">
         <is>
-          <t>$1,300 … (7 renders)</t>
+          <t>$1,295 … (7 renders)</t>
         </is>
       </c>
       <c r="F391" s="1" t="inlineStr">
@@ -22598,12 +22596,12 @@
       </c>
       <c r="G391" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H391" s="1" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I391" s="1" t="n"/>
@@ -22631,7 +22629,7 @@
       </c>
       <c r="E392" s="1" t="inlineStr">
         <is>
-          <t>$55,200 … (7 renders)</t>
+          <t>$55,140 … (7 renders)</t>
         </is>
       </c>
       <c r="F392" s="1" t="inlineStr">
@@ -23286,7 +23284,7 @@
       </c>
       <c r="G407" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-027 Yield on today's value</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value</t>
         </is>
       </c>
       <c r="H407" s="1" t="inlineStr">
@@ -23372,7 +23370,7 @@
       </c>
       <c r="G409" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-023 Face value, MK-NW-M-027 Yield on today's value</t>
+          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-023 Face value, MK-NW-M-018 Market value</t>
         </is>
       </c>
       <c r="H409" s="1" t="inlineStr">
@@ -23415,7 +23413,7 @@
       </c>
       <c r="G410" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-027 Yield on today's value, MK-NW-M-026 Yield if held to maturity</t>
+          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value, MK-NW-M-026 Yield if held to maturity</t>
         </is>
       </c>
       <c r="H410" s="1" t="inlineStr">
@@ -23458,7 +23456,7 @@
       </c>
       <c r="G411" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-027 Yield on today's value</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value</t>
         </is>
       </c>
       <c r="H411" s="1" t="inlineStr">
@@ -24447,7 +24445,7 @@
       </c>
       <c r="G434" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
         </is>
       </c>
       <c r="H434" s="1" t="inlineStr">
@@ -24490,7 +24488,7 @@
       </c>
       <c r="G435" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H435" s="1" t="inlineStr">
@@ -24533,7 +24531,7 @@
       </c>
       <c r="G436" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-009 YOUR SOURCES — Stock vesting (equity), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-010 YOUR SOURCES — Rental property</t>
         </is>
       </c>
       <c r="H436" s="1" t="inlineStr">
@@ -24738,7 +24736,7 @@
       </c>
       <c r="E441" s="1" t="inlineStr">
         <is>
-          <t>$0, $4,800 … (20 renders)</t>
+          <t>$0, $4,795 … (20 renders)</t>
         </is>
       </c>
       <c r="F441" s="1" t="inlineStr">
@@ -24791,7 +24789,7 @@
       </c>
       <c r="G442" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-005 = Surplus, MK-CF-M-003 = Planned surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
+          <t>MK-CF-M-003 = Planned surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-005 = Surplus</t>
         </is>
       </c>
       <c r="H442" s="1" t="inlineStr">
@@ -24834,7 +24832,7 @@
       </c>
       <c r="G443" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
         </is>
       </c>
       <c r="H443" s="1" t="inlineStr">
@@ -24877,7 +24875,7 @@
       </c>
       <c r="G444" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H444" s="1" t="inlineStr">
@@ -24953,7 +24951,7 @@
       </c>
       <c r="E446" s="1" t="inlineStr">
         <is>
-          <t>$20,210, $35,130 … (30 renders)</t>
+          <t>$20,125, $35,095 … (30 renders)</t>
         </is>
       </c>
       <c r="F446" s="1" t="inlineStr">
@@ -24963,7 +24961,7 @@
       </c>
       <c r="G446" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X / m</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X / m</t>
         </is>
       </c>
       <c r="H446" s="1" t="inlineStr">
@@ -25436,7 +25434,7 @@
       </c>
       <c r="G457" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H457" s="1" t="inlineStr">
@@ -25522,7 +25520,7 @@
       </c>
       <c r="G459" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H459" s="1" t="inlineStr">
@@ -25565,7 +25563,7 @@
       </c>
       <c r="G460" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H460" s="1" t="inlineStr">
@@ -25780,7 +25778,7 @@
       </c>
       <c r="G465" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H465" s="1" t="inlineStr">
@@ -26339,7 +26337,7 @@
       </c>
       <c r="G478" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H478" s="1" t="inlineStr">
@@ -26382,7 +26380,7 @@
       </c>
       <c r="G479" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H479" s="1" t="inlineStr">
@@ -26425,7 +26423,7 @@
       </c>
       <c r="G480" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H480" s="1" t="inlineStr">
@@ -26511,7 +26509,7 @@
       </c>
       <c r="G482" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H482" s="1" t="inlineStr">
@@ -26898,7 +26896,7 @@
       </c>
       <c r="G491" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H491" s="1" t="inlineStr">
@@ -26984,7 +26982,7 @@
       </c>
       <c r="G493" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H493" s="1" t="inlineStr">
@@ -27533,7 +27531,7 @@
       </c>
       <c r="E506" s="1" t="inlineStr">
         <is>
-          <t>$2,980, $1,200, $4,800, $0 … (8 renders)</t>
+          <t>$2,980, $1,200, $4,795, $0 … (8 renders)</t>
         </is>
       </c>
       <c r="F506" s="1" t="inlineStr">
@@ -27619,7 +27617,7 @@
       </c>
       <c r="E508" s="1" t="inlineStr">
         <is>
-          <t>$1,300</t>
+          <t>$1,295</t>
         </is>
       </c>
       <c r="F508" s="1" t="inlineStr">
@@ -27662,7 +27660,7 @@
       </c>
       <c r="E509" s="1" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$4,795</t>
         </is>
       </c>
       <c r="F509" s="1" t="inlineStr">
@@ -27748,7 +27746,7 @@
       </c>
       <c r="E511" s="1" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$4,795</t>
         </is>
       </c>
       <c r="F511" s="1" t="inlineStr">
@@ -28082,7 +28080,7 @@
       </c>
       <c r="C519" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:317 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:318 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D519" s="1" t="inlineStr">
@@ -28125,7 +28123,7 @@
       </c>
       <c r="C520" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:332 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:333 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D520" s="1" t="inlineStr">
@@ -28168,7 +28166,7 @@
       </c>
       <c r="C521" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:523 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:524 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D521" s="1" t="inlineStr">
@@ -28211,7 +28209,7 @@
       </c>
       <c r="C522" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:544 (+3 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:545 (+3 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D522" s="1" t="inlineStr">
@@ -28254,7 +28252,7 @@
       </c>
       <c r="C523" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:576</t>
+          <t>src/screens/NetWorthScreen.tsx:570</t>
         </is>
       </c>
       <c r="D523" s="1" t="inlineStr">
@@ -28297,7 +28295,7 @@
       </c>
       <c r="C524" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:705 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:700 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D524" s="1" t="inlineStr">
@@ -28340,7 +28338,7 @@
       </c>
       <c r="C525" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:714</t>
+          <t>src/screens/NetWorthScreen.tsx:709</t>
         </is>
       </c>
       <c r="D525" s="1" t="inlineStr">
@@ -28383,7 +28381,7 @@
       </c>
       <c r="C526" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:803</t>
+          <t>src/screens/NetWorthScreen.tsx:798</t>
         </is>
       </c>
       <c r="D526" s="1" t="inlineStr">
@@ -28426,7 +28424,7 @@
       </c>
       <c r="C527" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:830 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:825 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D527" s="1" t="inlineStr">
@@ -28469,7 +28467,7 @@
       </c>
       <c r="C528" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:837 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:832 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D528" s="1" t="inlineStr">
@@ -28512,7 +28510,7 @@
       </c>
       <c r="C529" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:866 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:861 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D529" s="1" t="inlineStr">
@@ -28555,7 +28553,7 @@
       </c>
       <c r="C530" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:884</t>
+          <t>src/screens/NetWorthScreen.tsx:879</t>
         </is>
       </c>
       <c r="D530" s="1" t="inlineStr">
@@ -28598,7 +28596,7 @@
       </c>
       <c r="C531" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:892</t>
+          <t>src/screens/NetWorthScreen.tsx:887</t>
         </is>
       </c>
       <c r="D531" s="1" t="inlineStr">
@@ -28641,7 +28639,7 @@
       </c>
       <c r="C532" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:903 (+1 spoken/visible twin)</t>
+          <t>src/screens/NetWorthScreen.tsx:898 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D532" s="1" t="inlineStr">
@@ -28684,7 +28682,7 @@
       </c>
       <c r="C533" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:940</t>
+          <t>src/screens/NetWorthScreen.tsx:935</t>
         </is>
       </c>
       <c r="D533" s="1" t="inlineStr">
@@ -28780,7 +28778,7 @@
       </c>
       <c r="E535" s="1" t="inlineStr">
         <is>
-          <t>$480, $14,640, $55,200, $0</t>
+          <t>$420, $14,340, $55,140, $0</t>
         </is>
       </c>
       <c r="F535" s="1" t="inlineStr">
@@ -28823,7 +28821,7 @@
       </c>
       <c r="E536" s="1" t="inlineStr">
         <is>
-          <t>$340, -$3,260, $1,520, -$2,080 … (96 renders)</t>
+          <t>$335, -$3,265, $1,495, -$2,105 … (96 renders)</t>
         </is>
       </c>
       <c r="F536" s="1" t="inlineStr">
@@ -28909,7 +28907,7 @@
       </c>
       <c r="E538" s="1" t="inlineStr">
         <is>
-          <t>$340, $1,520, $1,300, $0</t>
+          <t>$335, $1,495, $1,295, $0</t>
         </is>
       </c>
       <c r="F538" s="1" t="inlineStr">
@@ -28952,7 +28950,7 @@
       </c>
       <c r="E539" s="1" t="inlineStr">
         <is>
-          <t>$340, $1,520, $4,800, $0 … (8 renders)</t>
+          <t>$335, $1,495, $4,795, $0 … (8 renders)</t>
         </is>
       </c>
       <c r="F539" s="1" t="inlineStr">
@@ -29607,7 +29605,7 @@
       </c>
       <c r="G554" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return </t>
+          <t>MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return , MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H554" s="1" t="inlineStr">
@@ -29650,7 +29648,7 @@
       </c>
       <c r="G555" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return </t>
+          <t>MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return , MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H555" s="1" t="inlineStr">
@@ -29812,7 +29810,7 @@
       </c>
       <c r="E559" s="1" t="inlineStr">
         <is>
-          <t>$3,500, $1,300, $4,800 … (6 renders)</t>
+          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
         </is>
       </c>
       <c r="F559" s="1" t="inlineStr">
@@ -29865,7 +29863,7 @@
       </c>
       <c r="G560" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H560" s="1" t="inlineStr">
@@ -29908,7 +29906,7 @@
       </c>
       <c r="G561" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H561" s="1" t="inlineStr">
@@ -29941,7 +29939,7 @@
       </c>
       <c r="E562" s="1" t="inlineStr">
         <is>
-          <t>$1,300 … (4 renders)</t>
+          <t>$1,295 … (4 renders)</t>
         </is>
       </c>
       <c r="F562" s="1" t="inlineStr">
@@ -29951,7 +29949,7 @@
       </c>
       <c r="G562" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H562" s="1" t="inlineStr">
@@ -29984,7 +29982,7 @@
       </c>
       <c r="E563" s="1" t="inlineStr">
         <is>
-          <t>$4,800 … (2 renders)</t>
+          <t>$4,795 … (2 renders)</t>
         </is>
       </c>
       <c r="F563" s="1" t="inlineStr">
@@ -29994,7 +29992,7 @@
       </c>
       <c r="G563" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H563" s="1" t="inlineStr">
@@ -31112,7 +31110,7 @@
       </c>
       <c r="G589" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H589" s="1" t="inlineStr">
@@ -31155,7 +31153,7 @@
       </c>
       <c r="G590" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H590" s="1" t="inlineStr">
@@ -31198,7 +31196,7 @@
       </c>
       <c r="G591" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H591" s="1" t="inlineStr">
@@ -31241,7 +31239,7 @@
       </c>
       <c r="G592" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H592" s="1" t="inlineStr">
@@ -31327,7 +31325,7 @@
       </c>
       <c r="G594" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H594" s="1" t="inlineStr">
@@ -31370,7 +31368,7 @@
       </c>
       <c r="G595" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H595" s="1" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -17144,7 +17144,7 @@
       </c>
       <c r="G248" s="1" t="inlineStr">
         <is>
-          <t>past age 95 | in most futures — 99.4out of 100 simulated futures</t>
+          <t>past age 95 | in most futures — 99.4 out of 100 simulated futures</t>
         </is>
       </c>
       <c r="H248" s="1" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>covers your expenses | past age # | in most futures — #out of # simulated futures | .</t>
+          <t>covers your expenses | past age # | in most futures — # out of # simulated futures | .</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="G385" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H385" s="1" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="G386" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H386" s="1" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="G388" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-005 = Surplus, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT</t>
+          <t>MK-CF-M-005 = Surplus, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H388" s="1" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="G389" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H389" s="1" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="G390" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-008 YOUR SOURCES — Bonus</t>
         </is>
       </c>
       <c r="H390" s="1" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="G407" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-026 Yield if held to maturity</t>
         </is>
       </c>
       <c r="H407" s="1" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="G409" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-023 Face value, MK-NW-M-018 Market value</t>
+          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-023 Face value, MK-NW-M-026 Yield if held to maturity</t>
         </is>
       </c>
       <c r="H409" s="1" t="inlineStr">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="G410" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value, MK-NW-M-026 Yield if held to maturity</t>
+          <t>MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-026 Yield if held to maturity, MK-NW-M-027 Yield on today's value</t>
         </is>
       </c>
       <c r="H410" s="1" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="G411" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-018 Market value</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y, MK-NW-M-026 Yield if held to maturity</t>
         </is>
       </c>
       <c r="H411" s="1" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="G422" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-045 each bond — face, coupon, yield, MK-NW-M-041 total value of your bonds, MK-NW-M-042 n bonds · face $X</t>
+          <t>MK-NW-M-045 each bond — face, coupon, yield, MK-NW-M-042 n bonds · face $X, MK-NW-M-041 total value of your bonds</t>
         </is>
       </c>
       <c r="H422" s="1" t="inlineStr">
@@ -24101,7 +24101,7 @@
       </c>
       <c r="G426" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H426" s="1" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="G427" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H427" s="1" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="G429" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H429" s="1" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="G430" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H430" s="1" t="inlineStr">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="G431" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H431" s="1" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="G432" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H432" s="1" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="G433" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-015 BY CATEGORY VS PLAN — $X of $Y</t>
+          <t>MK-CF-M-015 BY CATEGORY VS PLAN — $X of $Y, MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
         </is>
       </c>
       <c r="H433" s="1" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="G434" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
         </is>
       </c>
       <c r="H434" s="1" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="G435" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H435" s="1" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="G436" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-010 YOUR SOURCES — Rental property</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-008 YOUR SOURCES — Bonus, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H436" s="1" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="G437" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H437" s="1" t="inlineStr">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="G438" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H438" s="1" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="G439" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H439" s="1" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="G441" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H441" s="1" t="inlineStr">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="G442" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-003 = Planned surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-005 = Surplus</t>
+          <t>MK-CF-M-005 = Surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-003 = Planned surplus</t>
         </is>
       </c>
       <c r="H442" s="1" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="G443" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
         </is>
       </c>
       <c r="H443" s="1" t="inlineStr">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="G444" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H444" s="1" t="inlineStr">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G445" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H445" s="1" t="inlineStr">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="G446" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X / m</t>
+          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·</t>
         </is>
       </c>
       <c r="H446" s="1" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="G469" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average)</t>
+          <t>MK-NW-M-032 Price paid (average), MK-NW-M-031 Quantity — n shares</t>
         </is>
       </c>
       <c r="H469" s="1" t="inlineStr">
@@ -26036,7 +26036,7 @@
       </c>
       <c r="G471" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average)</t>
+          <t>MK-NW-M-032 Price paid (average), MK-NW-M-031 Quantity — n shares</t>
         </is>
       </c>
       <c r="H471" s="1" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="G476" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H476" s="1" t="inlineStr">
@@ -26294,7 +26294,7 @@
       </c>
       <c r="G477" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H477" s="1" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="G478" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H478" s="1" t="inlineStr">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="G479" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H479" s="1" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="G480" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H480" s="1" t="inlineStr">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="G481" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H481" s="1" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="G482" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H482" s="1" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="G491" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H491" s="1" t="inlineStr">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="G493" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H493" s="1" t="inlineStr">
@@ -29863,7 +29863,7 @@
       </c>
       <c r="G560" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H560" s="1" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="G561" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H561" s="1" t="inlineStr">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="G562" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H562" s="1" t="inlineStr">
@@ -29992,7 +29992,7 @@
       </c>
       <c r="G563" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H563" s="1" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="G589" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H589" s="1" t="inlineStr">
@@ -31153,7 +31153,7 @@
       </c>
       <c r="G590" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H590" s="1" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="G591" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H591" s="1" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="G592" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H592" s="1" t="inlineStr">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="G594" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H594" s="1" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="G595" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H595" s="1" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -22545,7 +22545,7 @@
       </c>
       <c r="G386" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H386" s="1" t="inlineStr">
@@ -22588,7 +22588,7 @@
       </c>
       <c r="G387" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H387" s="1" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="G389" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-005 = Surplus, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-CF-M-005 = Surplus, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT</t>
         </is>
       </c>
       <c r="H389" s="1" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="G390" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H390" s="1" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="G391" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·</t>
         </is>
       </c>
       <c r="H391" s="1" t="inlineStr">
@@ -23577,7 +23577,7 @@
       </c>
       <c r="G410" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-026 Yield if held to maturity, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-026 Yield if held to maturity, MK-NW-M-027 Yield on today's value</t>
         </is>
       </c>
       <c r="H410" s="1" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="G414" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-023 Face value, MK-NW-M-026 Yield if held to maturity, MK-NW-M-028 Rates rise 1% → value roughly $X–$Y</t>
+          <t>MK-NW-M-023 Face value, MK-NW-M-026 Yield if held to maturity, MK-NW-M-027 Yield on today's value</t>
         </is>
       </c>
       <c r="H414" s="1" t="inlineStr">
@@ -24222,7 +24222,7 @@
       </c>
       <c r="G425" s="1" t="inlineStr">
         <is>
-          <t>MK-NW-M-045 each bond — face, coupon, yield, MK-NW-M-042 n bonds · face $X, MK-NW-M-041 total value of your bonds</t>
+          <t>MK-NW-M-041 total value of your bonds, MK-NW-M-042 n bonds · face $X, MK-NW-M-045 each bond — face, coupon, yield</t>
         </is>
       </c>
       <c r="H425" s="1" t="inlineStr">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="G429" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H429" s="1" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="G430" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H430" s="1" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="G435" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H435" s="1" t="inlineStr">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="G437" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
         </is>
       </c>
       <c r="H437" s="1" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="G439" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-007 YOUR SOURCES — Self-employment</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-008 YOUR SOURCES — Bonus</t>
         </is>
       </c>
       <c r="H439" s="1" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="G440" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H440" s="1" t="inlineStr">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="G441" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H441" s="1" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G442" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H442" s="1" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="G444" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H444" s="1" t="inlineStr">
@@ -25082,7 +25082,7 @@
       </c>
       <c r="G445" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-003 = Planned surplus, MK-CF-M-005 = Surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
+          <t>MK-CF-M-005 = Surplus, MK-CF-M-003 = Planned surplus, MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
         </is>
       </c>
       <c r="H445" s="1" t="inlineStr">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="G446" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-003 = Planned surplus</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-005 = Surplus</t>
         </is>
       </c>
       <c r="H446" s="1" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="G448" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H448" s="1" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="G449" s="1" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H449" s="1" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="G460" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H460" s="1" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="G462" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H462" s="1" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="G463" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H463" s="1" t="inlineStr">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="G468" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H468" s="1" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="G481" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H481" s="1" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="G482" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H482" s="1" t="inlineStr">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="G483" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H483" s="1" t="inlineStr">
@@ -26802,7 +26802,7 @@
       </c>
       <c r="G485" s="1" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H485" s="1" t="inlineStr">
@@ -27189,7 +27189,7 @@
       </c>
       <c r="G494" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H494" s="1" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="G496" s="1" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H496" s="1" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="C536" s="1" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx:935</t>
+          <t>src/screens/NetWorthScreen.tsx:936</t>
         </is>
       </c>
       <c r="D536" s="1" t="inlineStr">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="C544" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:292 (+1 spoken/visible twin)</t>
+          <t>src/screens/PerformanceScreen.tsx:303 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D544" s="1" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="C545" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:308 (+1 spoken/visible twin)</t>
+          <t>src/screens/PerformanceScreen.tsx:319 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D545" s="1" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="C546" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:345</t>
+          <t>src/screens/PerformanceScreen.tsx:357</t>
         </is>
       </c>
       <c r="D546" s="1" t="inlineStr">
@@ -29425,7 +29425,7 @@
       </c>
       <c r="G546" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return </t>
+          <t>MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H546" s="1" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="C547" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:346</t>
+          <t>src/screens/PerformanceScreen.tsx:358</t>
         </is>
       </c>
       <c r="D547" s="1" t="inlineStr">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="C548" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:373</t>
+          <t>src/screens/PerformanceScreen.tsx:387</t>
         </is>
       </c>
       <c r="D548" s="1" t="inlineStr">
@@ -29511,7 +29511,7 @@
       </c>
       <c r="G548" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return </t>
+          <t>MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H548" s="1" t="inlineStr">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="C549" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:386</t>
+          <t>src/screens/PerformanceScreen.tsx:400</t>
         </is>
       </c>
       <c r="D549" s="1" t="inlineStr">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="C550" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:392</t>
+          <t>src/screens/PerformanceScreen.tsx:406</t>
         </is>
       </c>
       <c r="D550" s="1" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="G550" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-XS-M-004 ▲ up/▼ down $X (Y%) this month · Return </t>
+          <t>MK-PF-M-001 Ending value, MK-PF-M-003 HOW $X BECAME $Y · ALL ACCOUNTS, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H550" s="1" t="inlineStr">
@@ -29620,7 +29620,7 @@
       </c>
       <c r="C551" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:449 (+1 spoken/visible twin)</t>
+          <t>src/screens/PerformanceScreen.tsx:463 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D551" s="1" t="inlineStr">
@@ -29663,7 +29663,7 @@
       </c>
       <c r="C552" s="1" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx:457</t>
+          <t>src/screens/PerformanceScreen.tsx:471</t>
         </is>
       </c>
       <c r="D552" s="1" t="inlineStr">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="G555" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H555" s="1" t="inlineStr">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="G556" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H556" s="1" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="G557" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H557" s="1" t="inlineStr">
@@ -29941,7 +29941,7 @@
       </c>
       <c r="G558" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H558" s="1" t="inlineStr">
@@ -29984,7 +29984,7 @@
       </c>
       <c r="G559" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H559" s="1" t="inlineStr">
@@ -31102,7 +31102,7 @@
       </c>
       <c r="G585" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H585" s="1" t="inlineStr">
@@ -31145,7 +31145,7 @@
       </c>
       <c r="G586" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H586" s="1" t="inlineStr">
@@ -31188,7 +31188,7 @@
       </c>
       <c r="G587" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H587" s="1" t="inlineStr">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="G588" s="1" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H588" s="1" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9209</v>
+        <v>9334</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -1361,6 +1361,7 @@
 MK-XS-F-018 yearsToRetirement
 MK-XS-F-019 retirementHorizonYears
 MK-XS-F-020 toReadModel
+MK-XS-F-025 tabOrder
 MK-XS-F-026 profileFromOnboarding
 MK-XS-F-028 surplusByMonth
 MK-XS-F-029 monthlySavings
@@ -2017,6 +2018,8 @@
 MK-ST-F-065 isoLocalDate
 MK-ST-F-075 agoLabel
 MK-ST-F-077 isStale
+MK-XS-F-024 resolveLens
+MK-XS-F-025 tabOrder
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-082 priceFreshness
@@ -8982,6 +8985,7 @@
 MK-XS-F-009 readHistory
 MK-XS-F-010 investableChangePct
 MK-XS-F-024 resolveLens
+MK-XS-F-025 tabOrder
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-083 fetchPriceSeries
@@ -26593,7 +26597,7 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -26636,7 +26640,7 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -26765,7 +26769,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26808,7 +26812,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-010 YOUR SOURCES — Rental property</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-008 YOUR SOURCES — Bonus</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27883,7 +27887,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -27926,7 +27930,7 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -27969,7 +27973,7 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -28012,7 +28016,7 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -28055,7 +28059,7 @@
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -28098,7 +28102,7 @@
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
@@ -28141,7 +28145,7 @@
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-001 Expenses, MK-CF-M-015 BY CATEGORY VS PLAN — $X of $Y, MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
+          <t>MK-CF-M-001 Expenses, MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-015 BY CATEGORY VS PLAN — $X of $Y</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
@@ -28184,7 +28188,7 @@
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
@@ -28227,7 +28231,7 @@
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -28270,7 +28274,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-010 YOUR SOURCES — Rental property, MK-CF-M-009 YOUR SOURCES — Stock vesting (equity)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-008 YOUR SOURCES — Bonus, MK-CF-M-006 YOUR SOURCES — Base salary</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -28313,7 +28317,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -28399,7 +28403,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -28485,7 +28489,7 @@
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -28528,7 +28532,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28571,7 +28575,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-001 Expenses</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-001 Expenses</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28614,7 +28618,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28657,7 +28661,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28700,7 +28704,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29818,7 +29822,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29861,7 +29865,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -29904,7 +29908,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29947,7 +29951,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -29990,7 +29994,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30377,7 +30381,7 @@
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
@@ -30506,7 +30510,7 @@
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
@@ -32312,7 +32316,7 @@
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
@@ -32355,7 +32359,7 @@
       </c>
       <c r="G573" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H573" s="2" t="inlineStr">
@@ -32441,7 +32445,7 @@
       </c>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
@@ -33774,7 +33778,7 @@
       </c>
       <c r="G606" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H606" s="2" t="inlineStr">
@@ -33817,7 +33821,7 @@
       </c>
       <c r="G607" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H607" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9334</v>
+        <v>9360</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -17628,7 +17628,11 @@
           <t>visible</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Settings | </t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -26822,7 +26826,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -26865,7 +26869,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -26994,7 +26998,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -27037,7 +27041,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-008 YOUR SOURCES — Bonus</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -28112,7 +28116,7 @@
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
@@ -28155,7 +28159,7 @@
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
@@ -28198,7 +28202,7 @@
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -28241,7 +28245,7 @@
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -28284,7 +28288,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -28327,7 +28331,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -28413,7 +28417,7 @@
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-021 &lt;goal&gt; · from your Plan</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
@@ -28456,7 +28460,7 @@
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -28499,7 +28503,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-008 YOUR SOURCES — Bonus, MK-CF-M-011 YOUR SOURCES — Social Security · pension</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-007 YOUR SOURCES — Self-employment</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28542,7 +28546,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28628,7 +28632,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28714,7 +28718,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28757,7 +28761,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -28800,7 +28804,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-001 Expenses</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-001 Expenses</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -28843,7 +28847,7 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-021 &lt;goal&gt; · from your Plan, MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
@@ -28886,7 +28890,7 @@
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-018 THIS MONTH — In (take-home)</t>
+          <t>MK-CF-M-013 &lt;MONTH&gt; · $X SPENT, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-019 THIS MONTH — Out (bills + debt)</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
@@ -28929,7 +28933,7 @@
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-019 THIS MONTH — Out (bills + debt), MK-CF-M-018 THIS MONTH — In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
@@ -29402,7 +29406,7 @@
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
@@ -29488,7 +29492,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -29531,7 +29535,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -29746,7 +29750,7 @@
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -29961,7 +29965,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30004,7 +30008,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30047,7 +30051,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30219,7 +30223,7 @@
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">
@@ -30606,7 +30610,7 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
@@ -30735,7 +30739,7 @@
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
@@ -32154,7 +32158,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -32197,7 +32201,7 @@
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr">
@@ -32240,7 +32244,7 @@
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
@@ -32283,7 +32287,7 @@
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
@@ -33401,7 +33405,7 @@
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H598" s="2" t="inlineStr">
@@ -33444,7 +33448,7 @@
       </c>
       <c r="G599" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H599" s="2" t="inlineStr">
@@ -33487,7 +33491,7 @@
       </c>
       <c r="G600" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H600" s="2" t="inlineStr">
@@ -33530,7 +33534,7 @@
       </c>
       <c r="G601" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H601" s="2" t="inlineStr">
@@ -33616,7 +33620,7 @@
       </c>
       <c r="G603" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H603" s="2" t="inlineStr">
@@ -33659,7 +33663,7 @@
       </c>
       <c r="G604" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H604" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9561</v>
+        <v>9611</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>SURPLUS · AS OF TODAY | $2,980</t>
+          <t>ⓘ | $2,980</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>SURPLUS · AS OF TODAY | $4,795</t>
+          <t>ⓘ | $4,795</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>no regular bills recorded. | so far this month: | $#</t>
+          <t>log your expenses › | so far this month: | $#</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>REGULAR BILLS | Including everyday expenses.</t>
+          <t>Nothing entered yet. Log your expenses › | Nothing entered yet.</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>surplus · as of today | $#</t>
+          <t>what is surplus? | ⓘ | $#</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>› | Surplus in October 2026: $2,980 a month. As of today.</t>
+          <t>Surplus in October 2026: $2,980 a month. As of today. | SURPLUS · AS OF TODAY</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -18768,12 +18768,12 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>draw from savings | $#</t>
+          <t>add your guaranteed income › | draw from savings | $#</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new, rich, worker</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Pension | $1,300</t>
+          <t>Nothing entered yet. Add your guaranteed income › | Nothing entered yet.</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>inflow (social security + pension) | social security | $#</t>
+          <t>draw from savings | $#</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Oct | $4,795</t>
+          <t>Pension | $1,300</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>no big bills this month | = surplus | $#</t>
+          <t>inflow (social security + pension) | social security | $#</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>$335 | Big bills this month</t>
+          <t>Oct | $4,795</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -18897,22 +18897,22 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>no big bills this month | = surplus | $# | &lt;month&gt;: surplus $# a month</t>
+          <t>no big bills this month | = surplus | $#</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>$0 | Big bills this month</t>
+          <t>$335 | Big bills this month</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -18940,22 +18940,22 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>no guaranteed income entered yet | draw from savings | $#</t>
+          <t>no big bills this month | = surplus | $# | &lt;month&gt;: surplus $# a month</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>new, rich, worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>$335 | Inflow (income (take-home))</t>
+          <t>$0 | Big bills this month</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -26637,7 +26637,7 @@
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="I437" s="2" t="n"/>
     </row>
-    <row r="438" ht="45" customHeight="1">
+    <row r="438" ht="60" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26680,7 +26680,7 @@
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-006 YOUR SOURCES — Base salary</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-CF-M-008 YOUR SOURCES — Bonus</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -28443,7 +28443,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
@@ -28615,7 +28615,7 @@
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -28787,7 +28787,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29647,7 +29647,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="G542" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H542" s="2" t="inlineStr">
@@ -31195,7 +31195,7 @@
       </c>
       <c r="G543" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H543" s="2" t="inlineStr">
@@ -32965,7 +32965,7 @@
           <t>a function with a row — becomes a dependent of its question's orchestrator</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G33"/>

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-03</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-04</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9117</v>
+        <v>9115</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2" t="n"/>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="2" t="n"/>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
@@ -4565,9 +4565,9 @@
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-075
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-076
-MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
+MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092, MK-CF-O-004
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092, MK-XS-F-004
-MK-XS-I-060 how </t>
+MK-</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6474,6 +6474,7 @@
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
+MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092, MK-CF-O-004
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
@@ -6505,6 +6506,7 @@
 MK-CF-F-088 — Never lets t fall below 0.
 MK-CF-F-088 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-089 — Uses today's date from the device clock, so the answer changes by itself overnight.
+MK-CF-F-092 — Never lets earned before401k fall below 0.
 MK-CF-F-092 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-098 — Never lets g fall below 0.
 MK-CF-F-098 — Never lets state rate fall below 0.
@@ -6532,18 +6534,16 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 41 more, on the functions tab</t>
+… and 42 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>MK-CF-M-027 each income source and its amount
 MK-CF-M-031 Take-home
-MK-CF-M-038 each source of take-home
 MK-CF-M-039 its own month, never spread
 MK-CF-M-040 is not here — it is reinvested where it is earned
 MK-CF-M-042 each taxed source
-MK-CF-M-044 Calculated federal tax
 MK-CF-M-046 Medicare 1.45% of everything, 0.9% more above</t>
         </is>
       </c>
@@ -7073,6 +7073,7 @@
 MK-CF-F-088 — Never lets t fall below 0.
 MK-CF-F-088 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-089 — Uses today's date from the device clock, so the answer changes by itself overnight.
+MK-CF-F-092 — Never lets earned before401k fall below 0.
 MK-CF-F-092 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-098 — Never lets g fall below 0.
 MK-CF-F-098 — Never lets state rate fall below 0.
@@ -7091,8 +7092,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 41 more, on the functions tab
-… and 42 more, on the functions tab</t>
+… and 42 more, on the functions tab
+… and 43 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9811,7 +9812,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0 rows on the master · 7 places in the code print a dollar figure · 1 of them have no row · 4 rows not found on screen</t>
+          <t>0 rows on the master · 7 places in the code print a dollar figure · 1 of them have no row · 3 rows not found on screen</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -9916,7 +9917,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 3 rows not found on screen</t>
+          <t>8 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 2 rows not found on screen</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -16234,14 +16235,13 @@
           <t>src/screens/IncomeSummaryScreen.tsx</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>your rate, #% (edit on your base pay screen) | $#/year</t>
-        </is>
+      <c r="D174" s="2">
+        <f> inflow (income (take-home)) | $#</f>
+        <v/>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>12% | Tax</t>
+          <t>after tax and 401(k) | $6,400</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -16269,17 +16269,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>/insights</t>
+          <t>/income-summary</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx</t>
+          <t>src/screens/IncomeSummaryScreen.tsx</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>🎯 | concentrated in one account | $# (#%) of your invested money sits in a single account — spreading across accounts lowers risk.</t>
+          <t>your rate, #% (edit on your base pay screen) | $#/year</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>› | Concentrated in one account</t>
+          <t>12% | Tax</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -16322,12 +16322,12 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>💼 | room left in your #(k) | about $# of this year's tax-advantaged room looks unused — an estimate from what you entered you contribute, no</t>
+          <t>🎯 | concentrated in one account | $# (#%) of your invested money sits in a single account — spreading across accounts lowers risk.</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>⚙️ OPTIMIZE | Room left in your 401(k)</t>
+          <t>› | Concentrated in one account</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -16365,12 +16365,12 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>📈 | nudge up your investing | you're investing about #% of your gross income toward retirement — even +#% compounds over time.</t>
+          <t>💼 | room left in your #(k) | about $# of this year's tax-advantaged room looks unused — an estimate from what you entered you contribute, no</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>📈 GROW | Nudge up your investing</t>
+          <t>⚙️ OPTIMIZE | Room left in your 401(k)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -16408,12 +16408,12 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>🔥 | tackle high-interest debt first | &lt;name&gt; is at #% &lt;month&gt; — paying it down beats almost any investment return.</t>
+          <t>📈 | nudge up your investing | you're investing about #% of your gross income toward retirement — even +#% compounds over time.</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -16423,7 +16423,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>🛡️ PROTECT | Tackle high-interest debt first</t>
+          <t>📈 GROW | Nudge up your investing</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -16451,12 +16451,12 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>🛟 | build your emergency fund | you have no cash set aside for emergencies — most planners use #–# months of expenses as the range (&lt;name&gt; a</t>
+          <t>🔥 | tackle high-interest debt first | &lt;name&gt; is at #% &lt;month&gt; — paying it down beats almost any investment return.</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>🛡️ PROTECT | Build your emergency fund</t>
+          <t>🛡️ PROTECT | Tackle high-interest debt first</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -16484,22 +16484,22 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/insights</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx</t>
+          <t>src/screens/InsightsScreen.tsx</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>$ | additional coverage to consider | $#</t>
+          <t>🛟 | build your emergency fund | you have no cash set aside for emergencies — most planners use #–# months of expenses as the range (&lt;name&gt; a</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>$ | Coverage you already have</t>
+          <t>🛡️ PROTECT | Build your emergency fund</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>gap | $#</t>
+          <t>$ | additional coverage to consider | $#</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>− | $165,000</t>
+          <t>$ | Coverage you already have</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -16570,17 +16570,17 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>/invest</t>
+          <t>/insurance</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PerformanceScreen.tsx</t>
+          <t>src/screens/InsuranceScreen.tsx</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>change in investment value | $#</t>
+          <t>gap | $#</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Interest | $0</t>
+          <t>− | $165,000</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -16623,22 +16623,22 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>every line fills in as days pass — the structure never changes. | &lt;name&gt; &lt;name&gt;, $#</t>
+          <t>change in investment value | $#</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>) | $709,800</t>
+          <t>Interest | $0</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>every line fills in as days pass — the structure never changes. | &lt;name&gt;, $#</t>
+          <t>every line fills in as days pass — the structure never changes. | &lt;name&gt; &lt;name&gt;, $#</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -16681,7 +16681,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>) | $165,000</t>
+          <t>) | $709,800</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -16709,12 +16709,12 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>open &lt;name&gt; &lt;name&gt; — this account's own page | &lt;name&gt; &lt;name&gt; | $#</t>
+          <t>every line fills in as days pass — the structure never changes. | &lt;name&gt;, $#</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Every line fills in as days pass — the structure never changes. | Vanguard Brokerage, $300,000.</t>
+          <t>) | $165,000</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>open &lt;name&gt; — this account's own page | &lt;name&gt; | $#</t>
+          <t>open &lt;name&gt; &lt;name&gt; — this account's own page | &lt;name&gt; &lt;name&gt; | $#</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Every line fills in as days pass — the structure never changes. | Retirement (Traditional), $120,000.</t>
+          <t>Every line fills in as days pass — the structure never changes. | Vanguard Brokerage, $300,000.</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -16795,22 +16795,22 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>🔗 | linked · # days old</t>
+          <t>open &lt;name&gt; — this account's own page | &lt;name&gt; | $#</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Brokerage | $300,000</t>
+          <t>Every line fills in as days pass — the structure never changes. | Retirement (Traditional), $120,000.</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -16828,22 +16828,22 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>/itemize</t>
+          <t>/invest</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ItemizeScreen.tsx</t>
+          <t>src/screens/PerformanceScreen.tsx</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>. | unallocated | $# | $#</t>
+          <t>🔗 | linked · # days old</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>— any leftover stays as cash in | Retirement (Traditional)</t>
+          <t>Vanguard Brokerage | $300,000</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>of | $#</t>
+          <t>. | unallocated | $# | $#</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>$120,000 | $0</t>
+          <t>— any leftover stays as cash in | Retirement (Traditional)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -16914,32 +16914,32 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>/jobsafety</t>
+          <t>/itemize</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx</t>
+          <t>src/screens/ItemizeScreen.tsx</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t># | mo | # months of emergency fund</t>
+          <t>of | $#</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Essential monthly expenses, editable | 3 months of emergency fund</t>
+          <t>$120,000 | $0</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t># | mo | # months of emergency fund | #</t>
+          <t># | mo | # months of emergency fund</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>6 months of emergency fund | ✓</t>
+          <t>Essential monthly expenses, editable | 3 months of emergency fund</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -17010,22 +17010,22 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>/month — | # month average</t>
+          <t># | mo | # months of emergency fund | #</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Using | $600</t>
+          <t>6 months of emergency fund | ✓</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>income could stop within a year | still needed for your emergency fund | $# | #</t>
+          <t>/month — | # month average</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>Worried — income could stop within a year | Worried</t>
+          <t>Using | $600</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>of it. | using | $#</t>
+          <t>income could stop within a year | still needed for your emergency fund | $# | #</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>cover | $0</t>
+          <t>Worried — income could stop within a year | Worried</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>of your logged expenses — type your own if a typical month differs. | essential monthly expenses, editable | # months of emergency fund | #</t>
+          <t>of it. | using | $#</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>/month — | 1 month average</t>
+          <t>cover | $0</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>savings | cover | $#</t>
+          <t>of your logged expenses — type your own if a typical month differs. | essential monthly expenses, editable | # months of emergency fund | #</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -17192,12 +17192,12 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>$600 | /month) — your</t>
+          <t>/month — | 1 month average</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -17225,22 +17225,22 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">what do your essential expenses come to in a typical month? (rent, food, utilities — the must-pays) | essential monthly expenses | # months </t>
+          <t>savings | cover | $#</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>income could stop within a year | STILL NEEDED FOR YOUR EMERGENCY FUND</t>
+          <t>$600 | /month) — your</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -17268,22 +17268,22 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>what would close it | setting aside | $#</t>
+          <t xml:space="preserve">what do your essential expenses come to in a typical month? (rent, food, utilities — the must-pays) | essential monthly expenses | # months </t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Count Savings + investments | Savings + investments</t>
+          <t>income could stop within a year | STILL NEEDED FOR YOUR EMERGENCY FUND</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -17301,32 +17301,32 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>/look-back</t>
+          <t>/jobsafety</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>src/screens/LookBackScreen.tsx</t>
+          <t>src/screens/JobSafetyScreen.tsx</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>aor | when | # months ago | # months ago | # years ago | # years ago | # years ago | # years ago</t>
+          <t>what would close it | setting aside | $#</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>BTC | To AOR</t>
+          <t>Count Savings + investments | Savings + investments</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>facts about the past only | what if i'd moved money | # months ago</t>
+          <t>aor | when | # months ago | # months ago | # years ago | # years ago | # years ago | # years ago</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -17364,12 +17364,12 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Settings | </t>
+          <t>BTC | To AOR</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -17387,22 +17387,22 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>/multi-goal</t>
+          <t>/look-back</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>src/screens/MultiGoalScreen.tsx</t>
+          <t>src/screens/LookBackScreen.tsx</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t># → # | will my money last? | #% → #%</t>
+          <t>facts about the past only | what if i'd moved money | # months ago</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>EFFECT ON RETIREMENT | Earliest retire age</t>
+          <t>Settings | </t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>where the money goes | ▾ | effect on retirement: will-it-last # percent to # percent. estimate, not a promise.</t>
+          <t># → # | will my money last? | #% → #%</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -17450,12 +17450,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Short $500/month | Where the money goes</t>
+          <t>EFFECT ON RETIREMENT | Earliest retire age</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -17483,22 +17483,22 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>your regular bills, including the &lt;name&gt;, are already counted. | covered — $#/month to spare</t>
+          <t>where the money goes | ▾ | effect on retirement: will-it-last # percent to # percent. estimate, not a promise.</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Can you do it all? Covered, with $1,380 a month to spare | CAN YOU DO IT ALL?</t>
+          <t>Short $500/month | Where the money goes</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -17526,12 +17526,12 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>your regular bills, including the &lt;name&gt;, are already counted. | short $#/month</t>
+          <t>your regular bills, including the &lt;name&gt;, are already counted. | covered — $#/month to spare</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Can you do it all? Short $400 a month | CAN YOU DO IT ALL?</t>
+          <t>Can you do it all? Covered, with $1,380 a month to spare | CAN YOU DO IT ALL?</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -17559,22 +17559,22 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/multi-goal</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx</t>
+          <t>src/screens/MultiGoalScreen.tsx</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t># | fact | $#</t>
+          <t>your regular bills, including the &lt;name&gt;, are already counted. | short $#/month</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>new, retiree, rich</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>New roof | ,</t>
+          <t>Can you do it all? Short $400 a month | CAN YOU DO IT ALL?</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>$ | your target nest egg | $#</t>
+          <t># | fact | $#</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>, from your loan. | What's your target nest egg?</t>
+          <t>New roof | ,</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -17655,22 +17655,22 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>+ | you'd spend | $#</t>
+          <t>$ | your target nest egg | $#</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>$0 | Spend more extra</t>
+          <t>, from your loan. | What's your target nest egg?</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>/month expenses | — on course to last past # ~$# to spare | .</t>
+          <t>+ | you'd spend | $#</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Your | $3,800</t>
+          <t>$0 | Spend more extra</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>/month expenses. you're drawing | $#</t>
+          <t>/month expenses | — on course to last past # ~$# to spare | .</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>✓ covers your | $3,800</t>
+          <t>Your | $3,800</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -17784,22 +17784,22 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>add something by hand › | big one-time costs | $# | &lt;name&gt;, #: $#</t>
+          <t>/month expenses. you're drawing | $#</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Add something by hand | ✍️</t>
+          <t>✓ covers your | $3,800</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>everything you own counts, except the home you live in and the car you drive. tap any row to change it. | &lt;name&gt; &lt;name&gt;, $# counts toward re</t>
+          <t>add something by hand › | big one-time costs | $# | &lt;name&gt;, #: $#</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -17842,7 +17842,7 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>WHAT COUNTS TOWARD RETIREMENT | $729,800</t>
+          <t>Add something by hand | ✍️</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -17870,12 +17870,12 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>everything you own counts, except the home you live in and the car you drive. tap any row to change it. | &lt;name&gt;, $# counts toward retiremen</t>
+          <t>everything you own counts, except the home you live in and the car you drive. tap any row to change it. | &lt;name&gt; &lt;name&gt;, $# counts toward re</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>WHAT COUNTS TOWARD RETIREMENT | $165,000</t>
+          <t>WHAT COUNTS TOWARD RETIREMENT | $729,800</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -17913,12 +17913,12 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>lower extra saving each month | − | +$#</t>
+          <t>everything you own counts, except the home you live in and the car you drive. tap any row to change it. | &lt;name&gt;, $# counts toward retiremen</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>Extra saving each month | DRAFT</t>
+          <t>WHAT COUNTS TOWARD RETIREMENT | $165,000</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -17956,22 +17956,22 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>s | , | $#</t>
+          <t>lower extra saving each month | − | +$#</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>connected | account</t>
+          <t>Extra saving each month | DRAFT</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -17999,22 +17999,22 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>spend less extra | − | $# more in expenses each month | $#</t>
+          <t>s | , | $#</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Not without it changing how long your money lasts. | Spend extra</t>
+          <t>connected | account</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -18042,22 +18042,22 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>— our starting figure, not yours. change it to your own number. | what counts toward retirement | $#</t>
+          <t>spend less extra | − | $# more in expenses each month | $#</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>Your target nest egg | $1,080,000</t>
+          <t>Not without it changing how long your money lasts. | Spend extra</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -18085,12 +18085,12 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; &lt;name&gt; | $#</t>
+          <t>— our starting figure, not yours. change it to your own number. | what counts toward retirement | $#</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>$400,000 | TreasuryDirect Treasury note, $9,800. Counts toward retirement. Tap to change.</t>
+          <t>Your target nest egg | $1,080,000</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; &lt;name&gt; | $# | &lt;name&gt; &lt;name&gt;, $# counts toward retirement. tap to change.</t>
+          <t>✓ | &lt;name&gt; &lt;name&gt; | $#</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -18138,12 +18138,12 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>$20,000 | Fidelity Traditional IRA, $400,000. Counts toward retirement. Tap to change.</t>
+          <t>$400,000 | TreasuryDirect Treasury note, $9,800. Counts toward retirement. Tap to change.</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; &lt;name&gt; | $# | &lt;name&gt;, $# counts toward retirement. tap to change.</t>
+          <t>✓ | &lt;name&gt; &lt;name&gt; | $# | &lt;name&gt; &lt;name&gt;, $# counts toward retirement. tap to change.</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Everything you own counts, except the home you live in and the car you drive. Tap any row to change it. | Vanguard Brokerage, $300,000. Counts toward retirement</t>
+          <t>$20,000 | Fidelity Traditional IRA, $400,000. Counts toward retirement. Tap to change.</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -18214,22 +18214,22 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; | $#</t>
+          <t>✓ | &lt;name&gt; &lt;name&gt; | $# | &lt;name&gt;, $# counts toward retirement. tap to change.</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>$120,000 | Investments, $45,000. Counts toward retirement. Tap to change.</t>
+          <t>Everything you own counts, except the home you live in and the car you drive. Tap any row to change it. | Vanguard Brokerage, $300,000. Counts toward retirement</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -18257,22 +18257,22 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; | $# | &lt;name&gt; &lt;name&gt;, $# counts toward retirement. tap to change.</t>
+          <t>✓ | &lt;name&gt; | $#</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>$300,000 | Ally Savings, $20,000. Counts toward retirement. Tap to change.</t>
+          <t>$120,000 | Investments, $45,000. Counts toward retirement. Tap to change.</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -18300,12 +18300,12 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>✓ | &lt;name&gt; | $# | &lt;name&gt;, $# counts toward retirement. tap to change.</t>
+          <t>✓ | &lt;name&gt; | $# | &lt;name&gt; &lt;name&gt;, $# counts toward retirement. tap to change.</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>Everything you own counts, except the home you live in and the car you drive. Tap any row to change it. | Retirement (Traditional), $120,000. Counts toward reti</t>
+          <t>$300,000 | Ally Savings, $20,000. Counts toward retirement. Tap to change.</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -18333,32 +18333,32 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>/required-withdrawals</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx</t>
+          <t>src/screens/PlanHubScreen.tsx</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t># | ~ | $#</t>
+          <t>✓ | &lt;name&gt; | $# | &lt;name&gt;, $# counts toward retirement. tap to change.</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>2073 | ·</t>
+          <t>Everything you own counts, except the home you live in and the car you drive. Tap any row to change it. | Retirement (Traditional), $120,000. Counts toward reti</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t># | ~ | $# | # age #: about $# | #</t>
+          <t># | ~ | $#</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>2066 | ·</t>
+          <t>2073 | ·</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>). estimated first withdrawal: | ~ | $#</t>
+          <t># | ~ | $# | # age #: about $# | #</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -18439,12 +18439,12 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>(age | 75</t>
+          <t>2066 | ·</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -18462,17 +18462,17 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t># | if your | $#k</t>
+          <t>). estimated first withdrawal: | ~ | $#</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>$2.03M | by</t>
+          <t>(age | 75</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>#(k) | · | $#k</t>
+          <t># | if your | $#k</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>BENCHMARK | Retirement (Traditional)</t>
+          <t>$2.03M | by</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -18558,12 +18558,12 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>% | &lt;name&gt; | $#k</t>
+          <t>#(k) | · | $#k</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>+ Add | 2.4</t>
+          <t>BENCHMARK | Retirement (Traditional)</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>) | you plan to spend | $#</t>
+          <t>% | &lt;name&gt; | $#k</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>In retirement (from | 65</t>
+          <t>+ Add | 2.4</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -18644,12 +18644,12 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>. | each year you spend | $# | : social security / pension covers $# and you take $# from savings</t>
+          <t>) | you plan to spend | $#</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>past age 95 | in most futures — 99.4 out of 100 simulated futures</t>
+          <t>In retirement (from | 65</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -18687,12 +18687,12 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>. | what you have | $#</t>
+          <t>. | each year you spend | $# | : social security / pension covers $# and you take $# from savings</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>▸ Everything below assumes your plan: retire at | 65</t>
+          <t>past age 95 | in most futures — 99.4 out of 100 simulated futures</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -18730,22 +18730,22 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>. | what you have | retirement nest egg $#k, by account type: &lt;name&gt; $# retirement $# | $#k</t>
+          <t>. | what you have | $#</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>65 | , keep saving $2,000/month</t>
+          <t>▸ Everything below assumes your plan: retire at | 65</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -18773,12 +18773,12 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>. | what you have | retirement nest egg $#k, by account type: cash $# &lt;name&gt; $# retirement $# | $#k</t>
+          <t>. | what you have | retirement nest egg $#k, by account type: &lt;name&gt; $# retirement $# | $#k</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -18816,22 +18816,22 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>. | 🏦 you can also contribute up to | $#</t>
+          <t>. | what you have | retirement nest egg $#k, by account type: cash $# &lt;name&gt; $# retirement $# | $#k</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>new, rich, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>— up to | $24,500</t>
+          <t>65 | , keep saving $2,000/month</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>/month | in today's dollars → about | $#k</t>
+          <t>. | 🏦 you can also contribute up to | $#</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>new, rich, worker</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>You plan to spend | $5,000</t>
+          <t>— up to | $24,500</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -18902,12 +18902,12 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | $#k</t>
+          <t>/month | in today's dollars → about | $#k</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Cash | $20K</t>
+          <t>You plan to spend | $5,000</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -18945,12 +18945,12 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | · | $#k</t>
+          <t>&lt;name&gt; | $#k</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, rich</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>BENCHMARK | Fidelity</t>
+          <t>Cash | $20K</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -18988,12 +18988,12 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>add your accounts in the net worth tab to build your nest egg. | your plan · | assumes age #</t>
+          <t>&lt;name&gt; | · | $#k</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>WHAT YOU HAVE | $0</t>
+          <t>BENCHMARK | Fidelity</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>assumed return on your remaining nest egg | benchmark | #%</t>
+          <t>add your accounts in the net worth tab to build your nest egg. | your plan · | assumes age #</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>YOUR PLAN · | in retirement</t>
+          <t>WHAT YOU HAVE | $0</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -19074,12 +19074,12 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>at your target, | # | $# | #% odds it lasts to #</t>
+          <t>assumed return on your remaining nest egg | benchmark | #%</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>6.0 | %/year</t>
+          <t>YOUR PLAN · | in retirement</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -19117,12 +19117,12 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>at your target, | # | $#m | #% odds it lasts to #</t>
+          <t>at your target, | # | $# | #% odds it lasts to #</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -19132,7 +19132,7 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>8.6 | %/year</t>
+          <t>6.0 | %/year</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -19160,12 +19160,12 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>covers your expenses | past age # | in most futures — # out of # simulated futures | .</t>
+          <t>at your target, | # | $#m | #% odds it lasts to #</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Your | $250K</t>
+          <t>8.6 | %/year</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -19203,12 +19203,12 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>grow my nest egg using | benchmark | #%</t>
+          <t>covers your expenses | past age # | in most futures — # out of # simulated futures | .</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>new, rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>YOUR PLAN · | assumes age 65</t>
+          <t>Your | $250K</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -19246,12 +19246,12 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>growth | = | $#m</t>
+          <t>grow my nest egg using | benchmark | #%</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>new, rich, worker</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>+ | $1.38M</t>
+          <t>YOUR PLAN · | assumes age 65</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -19289,12 +19289,12 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>if you never save again | keep saving | today's $# alone doesn't get there — even by #</t>
+          <t>growth | = | $#m</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>RETIREMENT · WHERE YOU STAND</t>
+          <t>+ | $1.38M</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -19332,12 +19332,12 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>if you never save again | retire # | today's $#k alone gets there by #</t>
+          <t>if you never save again | keep saving | today's $# alone doesn't get there — even by #</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -19375,12 +19375,12 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>nest egg | &lt;name&gt; | $#k</t>
+          <t>if you never save again | retire # | today's $#k alone gets there by #</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Retirement nest egg $165K, by account type: Investments $45,000, Retirement $120,000 | $165K</t>
+          <t>RETIREMENT · WHERE YOU STAND</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -19418,12 +19418,12 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>nest egg | cash | $#k</t>
+          <t>nest egg | &lt;name&gt; | $#k</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Retirement nest egg $730K, by account type: Cash $20,000, Investments $309,800, Retirement $400,000 | $730K</t>
+          <t>Retirement nest egg $165K, by account type: Investments $45,000, Retirement $120,000 | $165K</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -19461,12 +19461,12 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>nest egg | nest egg | $#k</t>
+          <t>nest egg | cash | $#k</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>RETIREMENT · WHERE YOU STAND | $250K</t>
+          <t>Retirement nest egg $730K, by account type: Cash $20,000, Investments $309,800, Retirement $400,000 | $730K</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -19504,12 +19504,12 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>now | + | $#k</t>
+          <t>nest egg | nest egg | $#k</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>. | $165K</t>
+          <t>RETIREMENT · WHERE YOU STAND | $250K</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>projected nest egg | $#m</t>
+          <t>now | + | $#k</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Scenario | 8.6%</t>
+          <t>. | $165K</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>retirement | $#k</t>
+          <t>projected nest egg | $#m</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Investments | $45K</t>
+          <t>Scenario | 8.6%</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -19633,12 +19633,12 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>retirement · where you stand | $#k</t>
+          <t>retirement | $#k</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -19646,7 +19646,11 @@
           <t>visible</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Investments | $45K</t>
+        </is>
+      </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -19672,12 +19676,12 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>savings | · | $#k</t>
+          <t>retirement · where you stand | $#k</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -19685,11 +19689,7 @@
           <t>visible</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>% | Ally</t>
-        </is>
-      </c>
+      <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -19715,12 +19715,12 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>stocks / funds | · | $#k</t>
+          <t>savings | · | $#k</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>% | Investments</t>
+          <t>% | Ally</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>the blended benchmark | ) | and you keep saving $#/month | . | $#k</t>
+          <t>stocks / funds | · | $#k</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>8.6 | % (</t>
+          <t>% | Investments</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -19801,12 +19801,12 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>to your #(k) this year | — up to | $# | .</t>
+          <t>the blended benchmark | ) | and you keep saving $#/month | . | $#k</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>new, rich, worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>💼 You can still add | $14,900</t>
+          <t>8.6 | % (</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -19844,22 +19844,22 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>what is guaranteed income? | ⓘ | $#/month · today's $ · from your setup</t>
+          <t>to your #(k) this year | — up to | $# | .</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new, rich, worker</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>🏛️ | Social Security &amp; pension</t>
+          <t>💼 You can still add | $14,900</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -19887,22 +19887,22 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>you add | + | $#m</t>
+          <t>what is guaranteed income? | ⓘ | $#/month · today's $ · from your setup</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>+ | $480K</t>
+          <t>🏛️ | Social Security &amp; pension</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -19930,12 +19930,12 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>— add | scenario | #%</t>
+          <t>you add | + | $#m</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Your 12-mo | ⚠</t>
+          <t>+ | $480K</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -19973,12 +19973,12 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>ⓘ | 💼 you can still add | $#</t>
+          <t>— add | scenario | #%</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>new, rich, worker</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
@@ -19988,7 +19988,7 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Tax-smart moves | What is Required withdrawals (RMD)?</t>
+          <t>Your 12-mo | ⚠</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -20016,12 +20016,12 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>▸ everything below assumes your plan: retire at | # | , keep saving $#/month | .</t>
+          <t>ⓘ | 💼 you can still add | $#</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>new, rich, worker</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>8.6 | %/year</t>
+          <t>Tax-smart moves | What is Required withdrawals (RMD)?</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -20059,12 +20059,12 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>✅ looking good | your | $#k</t>
+          <t>▸ everything below assumes your plan: retire at | # | , keep saving $#/month | .</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>⚙︎ Edit what counts toward retirement › | WILL YOUR MONEY LAST?</t>
+          <t>8.6 | %/year</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -20102,12 +20102,12 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>📈 track live performance vs benchmark › | your plan · | assumes age #</t>
+          <t>✅ looking good | your | $#k</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>% | Add your actual 12-month return on each holding to see how you compare to the benchmark.</t>
+          <t>⚙︎ Edit what counts toward retirement › | WILL YOUR MONEY LAST?</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -20135,22 +20135,22 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>/rewards</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RewardsScreen.tsx</t>
+          <t>src/screens/RetirementCockpit.tsx</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>locked | 💰 | $#k saved</t>
+          <t>📈 track live performance vs benchmark › | your plan · | assumes age #</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>🦸 | Debt free</t>
+          <t>% | Add your actual 12-month return on each holding to see how you compare to the benchmark.</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -20178,32 +20178,32 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/rewards</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RothScreen.tsx</t>
+          <t>src/screens/RewardsScreen.tsx</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>set $# | $# | set $# | $#</t>
+          <t>locked | 💰 | $#k saved</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Set $10,000 | $10,000</t>
+          <t>🦸 | Debt free</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -20221,17 +20221,17 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/roth</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx</t>
+          <t>src/screens/RothScreen.tsx</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>you can claim any time from | #-# | (age #) to age # — no deadline.</t>
+          <t>set $# | $# | set $# | $#</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -20241,12 +20241,12 @@
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>＋ | Your assumption, not our prediction.</t>
+          <t>Set $10,000 | $10,000</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -20264,22 +20264,22 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>/stress-test</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx</t>
+          <t>src/screens/SsTimingScreen.tsx</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>if you lost your income | your essential expenses come to | $#</t>
+          <t>you can claim any time from | #-# | (age #) to age # — no deadline.</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Nothing entered yet. | Add your accounts ›</t>
+          <t>＋ | Your assumption, not our prediction.</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -20317,12 +20317,12 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>months your cash would last | covering your | $#</t>
+          <t>if you lost your income | your essential expenses come to | $#</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>If you lost your income | 0.0</t>
+          <t>Nothing entered yet. | Add your accounts ›</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -20360,12 +20360,12 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>🦷 dental | 💻 new laptop | ⚠ a $# hit would put you $# in the red | you'd need $# more to absorb it without borrowing.</t>
+          <t>months your cash would last | covering your | $#</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, worker</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>🩺 Medical bill | 🚗 Car repair</t>
+          <t>If you lost your income | 0.0</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -20393,22 +20393,22 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>/tax-organizer</t>
+          <t>/stress-test</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx</t>
+          <t>src/screens/StressTestScreen.tsx</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | #k | $#</t>
+          <t>🦷 dental | 💻 new laptop | ⚠ a $# hit would put you $# in the red | you'd need $# more to absorb it without borrowing.</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>new, retiree, worker</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>$6,000 | ACCOUNTS (year-end)</t>
+          <t>🩺 Medical bill | 🚗 Car repair</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -20446,12 +20446,12 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | &lt;name&gt; | $#</t>
+          <t>&lt;name&gt; | #k | $#</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | bond | $#</t>
+          <t>&lt;name&gt; | &lt;name&gt; | $#</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>trad_ira | $400,000</t>
+          <t>$6,000 | ACCOUNTS (year-end)</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | savings | $#</t>
+          <t>&lt;name&gt; | bond | $#</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>brokerage | $300,000</t>
+          <t>trad_ira | $400,000</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -20575,12 +20575,12 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | stocks_etf | $#</t>
+          <t>&lt;name&gt; | savings | $#</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>retiree, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>401k | $120,000</t>
+          <t>brokerage | $300,000</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -20618,12 +20618,12 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | trad_ira | $#</t>
+          <t>&lt;name&gt; | stocks_etf | $#</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>retiree, worker</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>savings | $20,000</t>
+          <t>401k | $120,000</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -20661,12 +20661,12 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>income | retirement income (ss / pension / withdrawals) | $#</t>
+          <t>&lt;name&gt; | trad_ira | $#</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>State income tax percent, optional | These tune every tax estimate in the app — withholding, Roth conversions, capital gains, required-withdrawal taxes. Estimat</t>
+          <t>savings | $20,000</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -20704,12 +20704,12 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>income | wages (w-#) | $#</t>
+          <t>income | retirement income (ss / pension / withdrawals) | $#</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>rich, worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -20747,12 +20747,12 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>interest &amp; dividends | $#</t>
+          <t>income | wages (w-#) | $#</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>rich, worker</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Wages (W-2) | $108,000</t>
+          <t>State income tax percent, optional | These tune every tax estimate in the app — withholding, Roth conversions, capital gains, required-withdrawal taxes. Estimat</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>/tips</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TipsScreen.tsx</t>
+          <t>src/screens/TaxOrganizerScreen.tsx</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>actual expenses | $#</t>
+          <t>interest &amp; dividends | $#</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>new, retiree, rich, worker</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Income | $0</t>
+          <t>Wages (W-2) | $108,000</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>budget remaining | $#</t>
+          <t>actual expenses | $#</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Actual expenses | $0</t>
+          <t>Income | $0</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>from what you've logged this month — not your full income or budget. | income | $#</t>
+          <t>budget remaining | $#</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>This month at a glance</t>
+          <t>Actual expenses | $0</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -20909,32 +20909,32 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/tips</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx</t>
+          <t>src/screens/TipsScreen.tsx</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t># | ✓ saved — home, plan and this screen all use these same answers. | estimates at age #: nest egg $# becomes $#; the chance your money las</t>
+          <t>from what you've logged this month — not your full income or budget. | income | $#</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich, worker</t>
+          <t>new, retiree, rich, worker</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>65 | 50</t>
+          <t>This month at a glance</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>/month | raise the extra monthly amount by $#</t>
+          <t># | ✓ saved — home, plan and this screen all use these same answers. | estimates at age #: nest egg $# becomes $#; the chance your money las</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -20977,7 +20977,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>+ | $500</t>
+          <t>65 | 50</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>at # (estimates) | + | $#</t>
+          <t>/month | raise the extra monthly amount by $#</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -21015,12 +21015,12 @@
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>✓ Saved — Home, Plan and this screen all use these same answers. | Estimates at age 65: nest egg $4,977,392 becomes $5,734,057; the chance your money lasts 93 p</t>
+          <t>+ | $500</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>trying it out — nothing changes until you tap use as my plan. | if you save more each month | lower the extra monthly amount by $#</t>
+          <t>at # (estimates) | + | $#</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -21058,12 +21058,12 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>What if I save more?</t>
+          <t>✓ Saved — Home, Plan and this screen all use these same answers. | Estimates at age 65: nest egg $4,977,392 becomes $5,734,057; the chance your money lasts 93 p</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>what is how we calculate your odds? | ⓘ | $# → $#</t>
+          <t>trying it out — nothing changes until you tap use as my plan. | if you save more each month | lower the extra monthly amount by $#</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>— an estimate | Projected nest egg</t>
+          <t>What if I save more?</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -21134,7 +21134,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>will my money last? | #% → #%</t>
+          <t>what is how we calculate your odds? | ⓘ | $# → $#</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>ⓘ | $4,977,392 → $5,734,057</t>
+          <t>— an estimate | Projected nest egg</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -21177,7 +21177,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>− | + | $#</t>
+          <t>will my money last? | #% → #%</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -21192,7 +21192,7 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>IF YOU SAVE MORE EACH MONTH | Lower the extra monthly amount by $100</t>
+          <t>ⓘ | $4,977,392 → $5,734,057</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -21210,22 +21210,22 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx</t>
+          <t>src/screens/WhatIfScreen.tsx</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>inflation assumed | from economic data | #%</t>
+          <t>− | + | $#</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>retiree, rich, worker</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>› | Inflation assumed: 2.5%, from economic data. Opens where you can change it.</t>
+          <t>IF YOU SAVE MORE EACH MONTH | Lower the extra monthly amount by $100</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>we play out hundreds of possible &lt;month&gt; futures — some kind, some rough — using the numbers below. in | # | out of # simulated futures, you</t>
+          <t>inflation assumed | from economic data | #%</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -21278,7 +21278,7 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>estimate | WHAT THIS MEANS</t>
+          <t>› | Inflation assumed: 2.5%, from economic data. Opens where you can change it.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>will my money last to #: # percent, an estimate.</t>
+          <t>we play out hundreds of possible &lt;month&gt; futures — some kind, some rough — using the numbers below. in | # | out of # simulated futures, you</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -21316,10 +21316,14 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>spoken</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr"/>
+          <t>visible</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>estimate | WHAT THIS MEANS</t>
+        </is>
+      </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -21345,7 +21349,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>› | inflation assumed: #%, from economic data. opens where you can change it.</t>
+          <t>will my money last to #: # percent, an estimate.</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -21355,14 +21359,10 @@
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>the blended benchmark for your mix | 10.4%</t>
-        </is>
-      </c>
+          <t>spoken</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr"/>
       <c r="H293" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -21373,30 +21373,42 @@
     <row r="294" ht="60" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>row not seen on its screen</t>
+          <t>figure no row claims</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
-        </is>
-      </c>
-      <c r="C294" s="2" t="inlineStr"/>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/WillItLastScreen.tsx</t>
+        </is>
+      </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-002 — Your net worth just crossed X</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr"/>
-      <c r="F294" s="2" t="inlineStr"/>
+          <t>› | inflation assumed: #%, from economic data. opens where you can change it.</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>retiree</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>spoken, visible</t>
+        </is>
+      </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>words looked for: net worth just crossed</t>
+          <t>the blended benchmark for your mix | 10.4%</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>The master file has a row for this figure, but the words on the row were not found on the screen. Either the words on the row are out of date, or the figure only appears after a tap the census cannot make. Claude reads each one and fixes the row or the census; nothing for you to decide yet.</t>
+          <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
         </is>
       </c>
       <c r="I294" s="2" t="n"/>
@@ -21409,20 +21421,20 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>/home · /analytics</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr"/>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-001 — Net worth</t>
+          <t>MK-HM-M-002 — Your net worth just crossed X</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr"/>
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>words looked for: net worth</t>
+          <t>words looked for: net worth just crossed</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -21446,14 +21458,14 @@
       <c r="C296" s="2" t="inlineStr"/>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-003 — YOUR INVESTMENTS</t>
+          <t>MK-XS-M-001 — Net worth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr"/>
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>words looked for: investments</t>
+          <t>words looked for: net worth</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -21471,20 +21483,20 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>/invest · /home</t>
+          <t>/home · /analytics</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr"/>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
+          <t>MK-XS-M-003 — YOUR INVESTMENTS</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr"/>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>words looked for: down month / return / return</t>
+          <t>words looked for: investments</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -21502,20 +21514,20 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>/networth</t>
+          <t>/invest · /home</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr"/>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-001 — Change in net worth +$X</t>
+          <t>MK-XS-M-004 — ▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr"/>
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>words looked for: change net worth</t>
+          <t>words looked for: down month / return / return</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -21533,20 +21545,20 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/networth</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr"/>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-002 — Return on cash + investments</t>
+          <t>MK-NW-M-001 — Change in net worth +$X</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr"/>
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>words looked for: return cash investments</t>
+          <t>words looked for: change net worth</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -21564,20 +21576,20 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /insights</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr"/>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-005 — CASH</t>
+          <t>MK-NW-M-002 — Return on cash + investments</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr"/>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>words looked for: cash</t>
+          <t>words looked for: return cash investments</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -21595,20 +21607,20 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>/networth</t>
+          <t>/analytics · /insights</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr"/>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
+          <t>MK-NW-M-005 — CASH</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr"/>
       <c r="F301" s="2" t="inlineStr"/>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>words looked for: personal property</t>
+          <t>words looked for: cash</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -21626,20 +21638,20 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/networth</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr"/>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-011 — minimum monthly payment on a debt</t>
+          <t>MK-NW-M-006 — 🏠 PERSONAL PROPERTY</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr"/>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>words looked for: minimum monthly payment debt</t>
+          <t>words looked for: personal property</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -21657,20 +21669,20 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /home</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr"/>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-012 — Monthly debt payments</t>
+          <t>MK-NW-M-011 — minimum monthly payment on a debt</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr"/>
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>words looked for: monthly debt payments</t>
+          <t>words looked for: minimum monthly payment debt</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -21688,20 +21700,20 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /jobsafety</t>
+          <t>/analytics · /home</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr"/>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-013 — EMERGENCY FUND — X.X months</t>
+          <t>MK-NW-M-012 — Monthly debt payments</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr"/>
       <c r="F304" s="2" t="inlineStr"/>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>words looked for: emergency fund / months</t>
+          <t>words looked for: monthly debt payments</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -21719,20 +21731,20 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>/networth</t>
+          <t>/analytics · /jobsafety</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr"/>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+          <t>MK-NW-M-013 — EMERGENCY FUND — X.X months</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>words looked for: retirement plan / track age</t>
+          <t>words looked for: emergency fund / months</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -21756,14 +21768,14 @@
       <c r="C306" s="2" t="inlineStr"/>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-016 — Net worth so far (setup)</t>
+          <t>MK-NW-M-015 — YOUR RETIREMENT PLAN — on track for $X by age Y</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>words looked for: net worth setup</t>
+          <t>words looked for: retirement plan / track age</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -21781,20 +21793,20 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/networth</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr"/>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-017 — Assets $X − Debts $Y = Net worth $Z</t>
+          <t>MK-NW-M-016 — Net worth so far (setup)</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>words looked for: assets debts net worth</t>
+          <t>words looked for: net worth setup</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -21812,20 +21824,20 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>/account-detail · /invest</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr"/>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-018 — Market value</t>
+          <t>MK-NW-M-017 — Assets $X − Debts $Y = Net worth $Z</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr"/>
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>words looked for: market value</t>
+          <t>words looked for: assets debts net worth</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -21843,20 +21855,20 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>/account-detail</t>
+          <t>/account-detail · /invest</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr"/>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-021 — Income: &lt;amount&gt; on a holding row</t>
+          <t>MK-NW-M-018 — Market value</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr"/>
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>words looked for: income holding row</t>
+          <t>words looked for: market value</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -21874,20 +21886,20 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail · /invest</t>
+          <t>/account-detail</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr"/>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-033 — Total paid</t>
+          <t>MK-NW-M-021 — Income: &lt;amount&gt; on a holding row</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr"/>
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>words looked for: total paid</t>
+          <t>words looked for: income holding row</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -21905,20 +21917,20 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
+          <t>/holding-detail · /invest</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr"/>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
+          <t>MK-NW-M-033 — Total paid</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr"/>
       <c r="F311" s="2" t="inlineStr"/>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>words looked for: dividends received</t>
+          <t>words looked for: total paid</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -21942,14 +21954,14 @@
       <c r="C312" s="2" t="inlineStr"/>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
+          <t>MK-NW-M-034 — Dividends received (12 mo)</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr"/>
       <c r="F312" s="2" t="inlineStr"/>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>words looked for: realized gain buys sells</t>
+          <t>words looked for: dividends received</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -21973,14 +21985,14 @@
       <c r="C313" s="2" t="inlineStr"/>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
+          <t>MK-NW-M-035 — Realized gain from your buys and sells</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr"/>
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>words looked for: gain / long term held over</t>
+          <t>words looked for: realized gain buys sells</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -22004,14 +22016,14 @@
       <c r="C314" s="2" t="inlineStr"/>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-037 — Gain — short-term (under 1 yr)</t>
+          <t>MK-NW-M-036 — Gain — long-term (held over 1 yr)</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
       <c r="F314" s="2" t="inlineStr"/>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>words looked for: gain / short term under</t>
+          <t>words looked for: gain / long term held over</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -22029,20 +22041,20 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /insights</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr"/>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-047 — Both include $X/month of debt payments you cannot stop</t>
+          <t>MK-NW-M-037 — Gain — short-term (under 1 yr)</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr"/>
       <c r="F315" s="2" t="inlineStr"/>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>words looked for: both include month debt payments cannot stop</t>
+          <t>words looked for: gain / short term under</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -22066,14 +22078,14 @@
       <c r="C316" s="2" t="inlineStr"/>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-048 — cash ÷ planned spend</t>
+          <t>MK-NW-M-047 — Both include $X/month of debt payments you cannot stop</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr"/>
       <c r="F316" s="2" t="inlineStr"/>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>words looked for: cash planned spend</t>
+          <t>words looked for: both include month debt payments cannot stop</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -22091,20 +22103,20 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>/other-investments</t>
+          <t>/analytics · /insights</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr"/>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-050 — EST. GROWTH /year</t>
+          <t>MK-NW-M-048 — cash ÷ planned spend</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr"/>
       <c r="F317" s="2" t="inlineStr"/>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>words looked for: est growth year</t>
+          <t>words looked for: cash planned spend</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -22128,14 +22140,14 @@
       <c r="C318" s="2" t="inlineStr"/>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-051 — EXP. RETURN</t>
+          <t>MK-NW-M-050 — EST. GROWTH /year</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr"/>
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>words looked for: exp return</t>
+          <t>words looked for: est growth year</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -22153,20 +22165,20 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
+          <t>/other-investments</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr"/>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-059 — Change since purchase</t>
+          <t>MK-NW-M-051 — EXP. RETURN</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr"/>
       <c r="F319" s="2" t="inlineStr"/>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>words looked for: change since purchase</t>
+          <t>words looked for: exp return</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -22190,14 +22202,14 @@
       <c r="C320" s="2" t="inlineStr"/>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-060 — up</t>
+          <t>MK-NW-M-059 — Change since purchase</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">words looked for: </t>
+          <t>words looked for: change since purchase</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -22215,13 +22227,13 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail · /invest</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr"/>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-061 — sh @</t>
+          <t>MK-NW-M-060 — up</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr"/>
@@ -22246,20 +22258,20 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>/account-detail · /invest</t>
+          <t>/holding-detail · /invest</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr"/>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-062 — what one record moved</t>
+          <t>MK-NW-M-061 — sh @</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr"/>
       <c r="F322" s="2" t="inlineStr"/>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>words looked for: one record moved</t>
+          <t xml:space="preserve">words looked for: </t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -22277,20 +22289,20 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>/analytics</t>
+          <t>/account-detail · /invest</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr"/>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-063 — what is inside this institution</t>
+          <t>MK-NW-M-062 — what one record moved</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr"/>
       <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>words looked for: inside institution</t>
+          <t>words looked for: one record moved</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -22308,20 +22320,20 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>/invest · /account-detail</t>
+          <t>/analytics</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr"/>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-004 — Ending market value (per account)</t>
+          <t>MK-NW-M-063 — what is inside this institution</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr"/>
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>words looked for: ending market value per account</t>
+          <t>words looked for: inside institution</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -22339,20 +22351,20 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/invest · /account-detail</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr"/>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-008 — market +X%</t>
+          <t>MK-PF-M-004 — Ending market value (per account)</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr"/>
       <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>words looked for: market</t>
+          <t>words looked for: ending market value per account</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -22370,20 +22382,20 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>/look-back</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr"/>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-010 — Left in &lt;fund&gt; it became $X (up/down $Y, Z%)</t>
+          <t>MK-PF-M-008 — market +X%</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr"/>
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>words looked for: left became down</t>
+          <t>words looked for: market</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -22407,14 +22419,14 @@
       <c r="C327" s="2" t="inlineStr"/>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-011 — Moved to &lt;fund&gt; it would be $X</t>
+          <t>MK-PF-M-010 — Left in &lt;fund&gt; it became $X (up/down $Y, Z%)</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr"/>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>words looked for: moved would</t>
+          <t>words looked for: left became down</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -22438,14 +22450,14 @@
       <c r="C328" s="2" t="inlineStr"/>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-012 — Difference: $X more/less if you had moved</t>
+          <t>MK-PF-M-011 — Moved to &lt;fund&gt; it would be $X</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr"/>
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>words looked for: difference more less had moved</t>
+          <t>words looked for: moved would</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -22463,20 +22475,20 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>/account-detail · /invest</t>
+          <t>/look-back</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr"/>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-013 — Beginning market value</t>
+          <t>MK-PF-M-012 — Difference: $X more/less if you had moved</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr"/>
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>words looked for: beginning market value</t>
+          <t>words looked for: difference more less had moved</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -22500,14 +22512,14 @@
       <c r="C330" s="2" t="inlineStr"/>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-015 — one line of the walk</t>
+          <t>MK-PF-M-013 — Beginning market value</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr"/>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>words looked for: one line walk</t>
+          <t>words looked for: beginning market value</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -22531,14 +22543,14 @@
       <c r="C331" s="2" t="inlineStr"/>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-016 — Return</t>
+          <t>MK-PF-M-015 — one line of the walk</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr"/>
       <c r="F331" s="2" t="inlineStr"/>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>words looked for: return</t>
+          <t>words looked for: one line walk</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -22556,20 +22568,20 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>/invest</t>
+          <t>/account-detail · /invest</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr"/>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-019 — one line of the walk</t>
+          <t>MK-PF-M-016 — Return</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr"/>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>words looked for: one line walk</t>
+          <t>words looked for: return</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -22593,14 +22605,14 @@
       <c r="C333" s="2" t="inlineStr"/>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-020 — Available cash</t>
+          <t>MK-PF-M-019 — one line of the walk</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr"/>
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>words looked for: available cash</t>
+          <t>words looked for: one line walk</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -22618,20 +22630,20 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/invest</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr"/>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-007 — SAVED SCENARIOS (n)</t>
+          <t>MK-PF-M-020 — Available cash</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr"/>
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>words looked for: saved scenarios</t>
+          <t>words looked for: available cash</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -22649,20 +22661,20 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr"/>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-011 — Monthly saving until then</t>
+          <t>MK-PL-M-007 — SAVED SCENARIOS (n)</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr"/>
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>words looked for: monthly saving until then</t>
+          <t>words looked for: saved scenarios</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -22680,20 +22692,20 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>/required-withdrawals</t>
+          <t>/will-it-last</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr"/>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-014 — Taken so far $X · still to take</t>
+          <t>MK-PL-M-011 — Monthly saving until then</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr"/>
       <c r="F336" s="2" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>words looked for: taken / still take</t>
+          <t>words looked for: monthly saving until then</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -22711,20 +22723,20 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr"/>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-017 — Monthly check (today's dollars)</t>
+          <t>MK-PL-M-014 — Taken so far $X · still to take</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr"/>
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>words looked for: monthly check today dollars</t>
+          <t>words looked for: taken / still take</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -22742,20 +22754,20 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr"/>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-023 — Extra tax next April (calculated) — about $X</t>
+          <t>MK-PL-M-017 — Monthly check (today's dollars)</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr"/>
       <c r="F338" s="2" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>words looked for: extra tax next april calculated / about</t>
+          <t>words looked for: monthly check today dollars</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -22773,20 +22785,20 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/roth</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr"/>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-025 — +$X/mo (the saving dial)</t>
+          <t>MK-PL-M-023 — Extra tax next April (calculated) — about $X</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr"/>
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>words looked for: saving dial</t>
+          <t>words looked for: extra tax next april calculated / about</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -22810,14 +22822,14 @@
       <c r="C340" s="2" t="inlineStr"/>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-026 — $X → $Y (nest egg before and after)</t>
+          <t>MK-PL-M-025 — +$X/mo (the saving dial)</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr"/>
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>words looked for: nest egg before after</t>
+          <t>words looked for: saving dial</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -22841,14 +22853,14 @@
       <c r="C341" s="2" t="inlineStr"/>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-027 — the difference the change makes</t>
+          <t>MK-PL-M-026 — $X → $Y (nest egg before and after)</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr"/>
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>words looked for: difference change makes</t>
+          <t>words looked for: nest egg before after</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -22866,20 +22878,20 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>/multi-goal</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr"/>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-031 — paid off &lt;month&gt; · saves $X</t>
+          <t>MK-PL-M-027 — the difference the change makes</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr"/>
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>words looked for: paid off / saves</t>
+          <t>words looked for: difference change makes</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -22897,20 +22909,20 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/multi-goal</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr"/>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-033 — your $X grows to $Y by age N at Z%/yr</t>
+          <t>MK-PL-M-031 — paid off &lt;month&gt; · saves $X</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr"/>
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>words looked for: grows age</t>
+          <t>words looked for: paid off / saves</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -22934,14 +22946,14 @@
       <c r="C344" s="2" t="inlineStr"/>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-034 — At Z% return, your money lasts past age N</t>
+          <t>MK-PL-M-033 — your $X grows to $Y by age N at Z%/yr</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr"/>
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>words looked for: return money lasts past age</t>
+          <t>words looked for: grows age</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -22965,14 +22977,14 @@
       <c r="C345" s="2" t="inlineStr"/>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-035 — Retire at age (the dial)</t>
+          <t>MK-PL-M-034 — At Z% return, your money lasts past age N</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr"/>
       <c r="F345" s="2" t="inlineStr"/>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>words looked for: retire age dial</t>
+          <t>words looked for: return money lasts past age</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -22990,20 +23002,20 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr"/>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-036 — the future total cost of school</t>
+          <t>MK-PL-M-035 — Retire at age (the dial)</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
       <c r="F346" s="2" t="inlineStr"/>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>words looked for: future total cost school</t>
+          <t>words looked for: retire age dial</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -23021,20 +23033,20 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /home</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr"/>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-002 — = Planned surplus</t>
+          <t>MK-PL-M-036 — the future total cost of school</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr"/>
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>words looked for: planned surplus</t>
+          <t>words looked for: future total cost school</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -23052,20 +23064,20 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /income-manager</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr"/>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-012 — RECEIVED · &lt;month&gt; — each payment</t>
+          <t>MK-CF-M-002 — = Planned surplus</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr"/>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>words looked for: received / payment</t>
+          <t>words looked for: planned surplus</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -23083,20 +23095,20 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /bill-calendar</t>
+          <t>/cashflow · /income-manager</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr"/>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-016 — BIG-TICKET RADAR — &lt;bill&gt; · due &lt;month&gt;</t>
+          <t>MK-CF-M-012 — RECEIVED · &lt;month&gt; — each payment</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr"/>
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>words looked for: big ticket radar / due</t>
+          <t>words looked for: received / payment</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -23114,20 +23126,20 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/base-pay · /cashflow</t>
+          <t>/cashflow · /bill-calendar</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr"/>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-031 — Take-home</t>
+          <t>MK-CF-M-016 — BIG-TICKET RADAR — &lt;bill&gt; · due &lt;month&gt;</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr"/>
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>words looked for: take home</t>
+          <t>words looked for: big ticket radar / due</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -23145,20 +23157,20 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/income-summary</t>
+          <t>/base-pay · /cashflow</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr"/>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-039 — its own month, never spread</t>
+          <t>MK-CF-M-031 — Take-home</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr"/>
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>words looked for: own month never spread</t>
+          <t>words looked for: take home</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -23182,14 +23194,14 @@
       <c r="C352" s="2" t="inlineStr"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-040 — is not here — it is reinvested where it is earned</t>
+          <t>MK-CF-M-039 — its own month, never spread</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr"/>
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>words looked for: not here / reinvested where earned</t>
+          <t>words looked for: own month never spread</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -23213,14 +23225,14 @@
       <c r="C353" s="2" t="inlineStr"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-044 — Calculated federal tax</t>
+          <t>MK-CF-M-040 — is not here — it is reinvested where it is earned</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr"/>
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>words looked for: calculated federal tax</t>
+          <t>words looked for: not here / reinvested where earned</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -24684,7 +24696,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -24813,7 +24825,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -24856,7 +24868,7 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -24899,7 +24911,7 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -24909,7 +24921,7 @@
       </c>
       <c r="I399" s="2" t="n"/>
     </row>
-    <row r="400" ht="45" customHeight="1">
+    <row r="400" ht="60" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -24942,7 +24954,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -24985,7 +24997,7 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -25028,7 +25040,7 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -26705,7 +26717,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -26748,7 +26760,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -26791,7 +26803,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26877,7 +26889,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27049,7 +27061,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -27178,7 +27190,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -27952,7 +27964,7 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -27995,7 +28007,7 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -29414,7 +29426,7 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -29457,7 +29469,7 @@
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -24825,7 +24825,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -24921,7 +24921,7 @@
       </c>
       <c r="I399" s="2" t="n"/>
     </row>
-    <row r="400" ht="60" customHeight="1">
+    <row r="400" ht="45" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -26760,7 +26760,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -29469,7 +29469,7 @@
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -15463,22 +15463,22 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -15506,22 +15506,22 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -26760,7 +26760,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -26889,7 +26889,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -29211,7 +29211,7 @@
       </c>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
@@ -29340,7 +29340,7 @@
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -29469,7 +29469,7 @@
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-04</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-05</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -1196,11 +1196,14 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-077 isStale
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-024 resolveLens
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
@@ -1217,7 +1220,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1288,8 @@
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-094 ledgerGroups
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1298,11 +1302,7 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-015 topHoldingConcentration
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -1353,8 +1353,8 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-076 ageLabel
+MK-ST-F-078 dateShown
 MK-XS-F-002 dataGaps
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-011 buildChangeWalk
@@ -1469,15 +1469,17 @@
 A GENUINE NEGATIVE IS SHOWN, never floored at zero — someone early in a mortgage really does owe more than they own.
 A month and its own days live in one series, sorted by their date text — "2026-04" sorts before "2026-04-30", which is what makes plain text sorting safe.
 An account with no institution recorded groups under "No institution set" rather than being dropped.
+CASH EARNS ONLY INTEREST. A paycheck arriving or a bill being paid is money moving, counted on the day the record first shows it.
+EVERY RETURN IS TIME-WEIGHTED (owner, 2026-10-04, DEC-1669): "All return should be True Weighted Return and not Dietz return." It was a change in balance, so money paid in read as money earned.
 FOUNDER RULING G19 (2026-09-08): one payment rule, the larger of the stated minimum and the payment set — the same words in both formula columns.
 IT IS COMPUTED EACH TIME AND NEVER STORED as a third number that could disagree with its own two halves (his ruling).
 IT IS READ FROM THE RECORD, never back-solved: the months we actually saved and the daily points after them.
 Insights took these its own way before 2026-09-27; his ruling on Q-NW-1 made all three screens read one answer.
 MK-HM-F-003 — Uses a built-in floor of 0.
 NONE RECORDED — the declaration names none.
-No recorded day on or after the baseline → no figure. A movement from a day nobody recorded is not a movement.
 None found anywhere in this chain
 REAL ESTATE IS ITS OWN BAND: a house is not a vehicle, and mixing them hides both.
+THE DAY COMPARED FROM MUST BE ON RECORD. A comparison from before the record begins gives no figure — never one quietly measured from a later day.
 THE SAME ACCOUNTS GROUP TWO WAYS — by class and by institution — and both ways add to the same total, so switching the view can never change what you own.
 The line is drawn only from days we hold a record for; today’s balances are never priced at past dates.
 The mix is ordered biggest first, so the largest thing inside an institution is the first thing read.
@@ -1705,7 +1707,8 @@
 MK-NW-F-084 categoryEarnings
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1720,13 +1723,10 @@
 MK-PF-F-012 earliestPurchaseDate
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-014 buildPerformance
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PL-F-012 waterfall
+MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
 MK-ST-F-036 reconcile
@@ -1742,11 +1742,14 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-065 isoLocalDate
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
 MK-ST-F-078 dateShown
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
@@ -2265,7 +2268,8 @@
 MK-NW-F-084 categoryEarnings
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2280,15 +2284,12 @@
 MK-PF-F-012 earliestPurchaseDate
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-014 buildPerformance
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PL-F-012 waterfall
 MK-ST-F-013 personalFlowTotals
 MK-ST-F-021 toNumber
+MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-030 record
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
@@ -2305,10 +2306,13 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
 MK-ST-F-078 dateShown
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
@@ -2709,12 +2713,15 @@
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-002 dataGaps
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -2852,7 +2859,7 @@
       </c>
       <c r="U6" s="2" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Q-PF-1</t>
@@ -2898,8 +2905,73 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-132 map
+          <t>MK-CF-F-003 categoryMonthly
+MK-CF-F-004 spendBuckets
+MK-CF-F-005 actualMonthFlow
+MK-CF-F-008 spendByMonth
+MK-CF-F-011 savingsByMonth
+MK-CF-F-021 defaultPaymentType
+MK-CF-F-022 paymentShape
+MK-CF-F-023 requiredPayment
+MK-CF-F-060 salaryGrossByMonth
+MK-CF-F-062 equityRowValue
+MK-CF-F-063 rowVestYear
+MK-CF-F-065 equityVestWeights
+MK-CF-F-066 rsuAnnual
+MK-CF-F-067 rentalList
+MK-CF-F-068 rentalNetAnnual
+MK-CF-F-069 benefitActiveMonths
+MK-CF-F-070 benefitAnnual
+MK-CF-F-071 extraIncome
+MK-CF-F-072 currentRetirementIncomeMonthly
+MK-CF-F-073 otherIncomeMonth
+MK-CF-F-074 tipsAnnual
+MK-CF-F-075 retirementIncomeMonthly
+MK-CF-F-077 scholarshipByCalendarMonth
+MK-CF-F-081 salaryActiveMonths
+MK-CF-F-082 salaryAnnual
+MK-CF-F-084 taxableAnnual
+MK-CF-F-085 filingStatusOf
+MK-CF-F-086 stateRateOf
+MK-CF-F-087 monthlyTaxRates
+MK-CF-F-088 taxableByCalendarMonth
+MK-CF-F-089 over65CountOf
+MK-CF-F-090 effectiveRate
+MK-CF-F-092 incomeMonthlyGrid
+MK-CF-F-099 deductionFor
+MK-CF-F-100 taxableIncomeFor
+MK-CF-F-101 taxOwedFor
+MK-CF-F-120 pctBaseMonthly
+MK-CF-F-130 enteredMonthlyRaw
+MK-CF-F-132 map
+MK-CF-F-148 inMonth
+MK-CF-F-149 recurringDebtPayments
+MK-CF-F-150 debtPaymentsCountedAsExpenses
+MK-CF-F-151 actualSpending
+MK-CF-F-152 isRadarItem
+MK-CF-F-153 radar
 MK-CF-F-155 cash
+MK-CF-F-156 plannedMonthFlow
+MK-CF-F-157 debtPaymentsByDebt
+MK-CF-F-165 salaryMonths
+MK-CF-F-166 hasMonthlySalaryTable
+MK-CF-F-167 salaryCalendarYear
+MK-CF-F-172 hasWage
+MK-CF-F-173 earnerWages
+MK-CF-F-176 sumMonthsOverEarners
+MK-CF-F-177 wageGrossByMonth
+MK-CF-F-180 enteredLandsAnnual
+MK-CF-F-181 rateInForce
+MK-CF-F-187 seniorDeductionFor
+MK-CF-F-191 ym
+MK-CF-F-192 inflowLabel
+MK-CF-F-193 inflowSourceWord
+MK-CF-F-203 MONTH
+MK-CF-F-204 line
+MK-CF-F-206 householdK401ByMonth
+MK-CF-O-002 expenses
+MK-CF-O-003 thisMonth
+MK-CF-O-010 theMonth
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
 MK-NW-F-055 isBond
@@ -2916,32 +2988,39 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
-MK-PF-F-030 npv
+MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
 MK-ST-F-021 toNumber
 MK-ST-F-027 accountId
+MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-030 record
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
+MK-ST-F-036 reconcile
 MK-ST-F-038 windowBounds
 MK-ST-F-039 on
 MK-ST-F-047 activeCurrency
 MK-ST-F-048 currencySymbol
 MK-ST-F-049 formatMoney
+MK-ST-F-052 toNum
 MK-ST-F-053 money
 MK-ST-F-056 has
+MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-065 isoLocalDate
+MK-ST-F-078 dateShown
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-011 buildChangeWalk
+MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
 MK-XS-F-122 n
@@ -2950,22 +3029,14 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
 MK-CF-F-002 plannedMonthlySpend
-MK-CF-F-003 categoryMonthly
-MK-CF-F-004 spendBuckets
-MK-CF-F-005 actualMonthFlow
-MK-CF-F-008 spendByMonth
-MK-CF-F-011 savingsByMonth
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
-MK-CF-F-021 defaultPaymentType
-MK-CF-F-022 paymentShape
-MK-CF-F-023 requiredPayment
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
@@ -2977,40 +3048,12 @@
 MK-CF-F-046 employerMatchAnnual
 MK-CF-F-048 effectiveTaxRate
 MK-CF-F-049 buildIncomeState
-MK-CF-F-060 salaryGrossByMonth
-MK-CF-F-062 equityRowValue
-MK-CF-F-063 rowVestYear
-MK-CF-F-065 equityVestWeights
-MK-CF-F-066 rsuAnnual
-MK-CF-F-067 rentalList
-MK-CF-F-068 rentalNetAnnual
-MK-CF-F-069 benefitActiveMonths
-MK-CF-F-070 benefitAnnual
-MK-CF-F-071 extraIncome
-MK-CF-F-072 currentRetirementIncomeMonthly
-MK-CF-F-073 otherIncomeMonth
-MK-CF-F-074 tipsAnnual
-MK-CF-F-075 retirementIncomeMonthly
 MK-CF-F-076 guaranteedOutsideStreams
-MK-CF-F-077 scholarshipByCalendarMonth
 MK-CF-F-078 employerMatchMonthly
 MK-CF-F-079 incomeFromOnboarding
-MK-CF-F-081 salaryActiveMonths
-MK-CF-F-082 salaryAnnual
 MK-CF-F-083 totalGrossAnnual
-MK-CF-F-084 taxableAnnual
-MK-CF-F-085 filingStatusOf
-MK-CF-F-086 stateRateOf
-MK-CF-F-087 monthlyTaxRates
-MK-CF-F-088 taxableByCalendarMonth
-MK-CF-F-089 over65CountOf
-MK-CF-F-090 effectiveRate
-MK-CF-F-092 incomeMonthlyGrid
 MK-CF-F-097 grossFromNet
 MK-CF-F-098 progressiveMonthlyTax
-MK-CF-F-099 deductionFor
-MK-CF-F-100 taxableIncomeFor
-MK-CF-F-101 taxOwedFor
 MK-CF-F-102 effectiveRateOnGrossFor
 MK-CF-F-103 marginalBracketFor
 MK-CF-F-108 isMoneyOut
@@ -3023,11 +3066,9 @@
 MK-CF-F-116 inverseOf
 MK-CF-F-117 txnLabel
 MK-CF-F-118 cashEffect
-MK-CF-F-120 pctBaseMonthly
 MK-CF-F-127 isRental
 MK-CF-F-128 grossByMonth
 MK-CF-F-129 round4
-MK-CF-F-130 enteredMonthlyRaw
 MK-CF-F-131 normPayee
 MK-CF-F-133 cashOf
 MK-CF-F-134 usesSleeve
@@ -3042,47 +3083,20 @@
 MK-CF-F-144 takeHomeAsEntered
 MK-CF-F-145 deductionsFromPay
 MK-CF-F-146 payFiguresAgree
-MK-CF-F-148 inMonth
-MK-CF-F-149 recurringDebtPayments
-MK-CF-F-150 debtPaymentsCountedAsExpenses
-MK-CF-F-151 actualSpending
-MK-CF-F-152 isRadarItem
-MK-CF-F-153 radar
-MK-CF-F-156 plannedMonthFlow
-MK-CF-F-157 debtPaymentsByDebt
 MK-CF-F-161 monthlyGrossOfSource
 MK-CF-F-162 daysApart
-MK-CF-F-165 salaryMonths
-MK-CF-F-166 hasMonthlySalaryTable
-MK-CF-F-167 salaryCalendarYear
 MK-CF-F-171 earnerPay
-MK-CF-F-172 hasWage
-MK-CF-F-173 earnerWages
 MK-CF-F-175 sumOverEarners
-MK-CF-F-176 sumMonthsOverEarners
-MK-CF-F-177 wageGrossByMonth
 MK-CF-F-178 wageMatchMonthly
 MK-CF-F-179 entryFromWage
-MK-CF-F-180 enteredLandsAnnual
-MK-CF-F-181 rateInForce
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
-MK-CF-F-187 seniorDeductionFor
-MK-CF-F-191 ym
-MK-CF-F-192 inflowLabel
-MK-CF-F-193 inflowSourceWord
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-198 payrollTaxWithheld
 MK-CF-F-201 INCOME
-MK-CF-F-203 MONTH
-MK-CF-F-204 line
-MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
 MK-CF-O-001 basePay
-MK-CF-O-002 expenses
-MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
-MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
@@ -3148,7 +3162,6 @@
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-011 buildGoalsState
-MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-024 oddsLine
 MK-PL-F-025 sampleOddsLine
@@ -3174,17 +3187,13 @@
 MK-PL-F-085 oddsTail
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
-MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-034 firstDate
 MK-ST-F-035 covers
-MK-ST-F-036 reconcile
 MK-ST-F-043 newEntityId
 MK-ST-F-044 setMoneyFormat
 MK-ST-F-050 formatMoneyCents
 MK-ST-F-051 moneyCompact
-MK-ST-F-052 toNum
 MK-ST-F-055 round2
-MK-ST-F-060 verdict
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
 MK-ST-F-068 stepDay
@@ -3197,7 +3206,6 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
-MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
 MK-XS-F-002 dataGaps
 MK-XS-F-005 trendPoints
@@ -3205,14 +3213,12 @@
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
 MK-XS-F-019 retirementHorizonYears
 MK-XS-F-020 toReadModel
 MK-XS-F-024 resolveLens
 MK-XS-F-026 profileFromOnboarding
-MK-XS-F-027 takeHomeMonthly
 MK-XS-F-030 effectiveAnnualContribution
 MK-XS-F-031 buildSnapshot
 MK-XS-F-033 resolveNetWorthRows
@@ -3250,29 +3256,53 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
-MK-XS-I-004 holding quantity (shares) — read by MK-PF-F-024, MK-ST-F-027
+MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
+MK-XS-I-005 holding price — read by MK-ST-F-027, MK-ST-F-028
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-008 transaction amount — read by MK-NW-F-102, MK-NW-O-008, MK-PF-F-024
-MK-XS-I-009 transaction date — read by MK-NW-F-102, MK-NW-O-008, MK-PF-F-024
+MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027, MK-ST-F-028
+MK-XS-I-009 transaction date — read by MK-NW-O-008
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
-MK-XS-I-024 logged expenses — read by MK-NW-F-102, MK-NW-O-008, MK-PF-F-024, MK-PF-F-025, MK-PF-F-026
+MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
+MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
+MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
+MK-XS-I-017 birth year — read by MK-CF-F-089
+MK-XS-I-020 Social Security monthly amount — read by MK-CF-F-072, MK-CF-F-075
+MK-XS-I-022 pension monthly amount — read by MK-CF-F-072, MK-CF-F-075
+MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-084, MK-CF-F-088, MK-CF-F-092, MK-CF-F-165, MK
+MK-XS-I-024 logged expenses — read by MK-CF-F-005, MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK
+MK-XS-I-027 goals (target, saved, date) — read by MK-CF-F-204, MK-PL-F-012
 MK-XS-I-028 assumed return — read by MK-NW-O-001
-MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-030, MK-ST-F-031
-MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-031
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
+MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK-CF-F-187
+MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-031, MK-ST-F-036, MK-ST-F-083
+MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-031, MK-ST-F-083
+MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
+MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062
+MK-XS-I-035 annuity income — read by MK-CF-F-072, MK-CF-F-075
+MK-XS-I-036 other guaranteed income — read by MK-CF-F-072, MK-CF-F-075
+MK-XS-I-037 required-withdrawal income stream (ri_rmd) — read by MK-CF-F-075
+MK-XS-I-038 withdrawal income stream (ri_withdrawals) — read by MK-CF-F-075
+MK-XS-I-039 how often each income arrives — read by MK-CF-F-071, MK-CF-F-072, MK-CF-F-074, MK-CF-F-075, MK-CF-F-130
+MK-XS-I-040 whether a stream is already being received — read by MK-CF-F-072
+MK-XS-I-041 the payment the person chose to make on a debt — read by MK-CF-F-023
+MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
+MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027, MK-ST-F-028, MK-ST-F-060
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-NW-F-078
+MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
+MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
+MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -3283,7 +3313,7 @@
 A class that received nothing is not shown at all; where nothing was received the table does not appear.
 A class with no holding we can price shows an em-dash, never a 0% — a zero reads as "it returned nothing", which is a different claim.
 A record with no ticker is classed by what it IS — a dividend comes from a fund, interest from a bond.
-IT REFUSES WHEN TIMING WOULD DRIVE IT: where money moved in or out in amounts large enough that WHEN it moved decides the percentage, the screen shows the dollar walk instead.
+IT IS TIME-WEIGHTED (owner, 2026-10-04, DEC-1669): "All return should be True Weighted Return and not Dietz return." Where a piece cannot be measured it shows nothing, and never another method.
 LEDGER ONLY: what was actually RECEIVED, never a rate applied to a balance.
 MOVED OFF THE SCREEN 2026-09-30: this was calculated inside PerformanceScreen, so it had no row, no example and nothing able to check it (his rule: a screen computes nothing).
 NONE RECORDED — the declaration names none.
@@ -3322,7 +3352,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Nothing for you. 2 functions, and they nest: theBonds inside thePerformance. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
+          <t>Nothing for you. 5 functions, and they nest: expenses inside thisMonth, expenses inside theMonth, expenses inside thePerformance, thisMonth inside theMonth, thisMonth inside thePerformance, theMonth inside thisMonth, theMonth inside thePerformance, theBonds inside thisMonth, theBonds inside theMonth and theBonds inside thePerformance. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3731,11 +3761,14 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
 MK-XS-F-027 takeHomeMonthly
@@ -3752,7 +3785,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3852,8 @@
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-094 ledgerGroups
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -3830,11 +3864,7 @@
 MK-PF-F-012 earliestPurchaseDate
 MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PL-F-002 withdrawalPlan
 MK-PL-F-003 depletionAge
 MK-PL-F-004 withdrawalOrder
@@ -3887,10 +3917,10 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-XS-F-002 dataGaps
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-007 makeMonthlySnapshot
@@ -6285,7 +6315,8 @@
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6301,11 +6332,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
@@ -6356,7 +6383,6 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
 MK-ST-F-068 stepDay
@@ -6368,14 +6394,18 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
@@ -6864,7 +6894,8 @@
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6880,11 +6911,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
@@ -6937,7 +6964,6 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
 MK-ST-F-068 stepDay
@@ -6949,14 +6975,18 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
@@ -7786,7 +7816,8 @@
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -7803,11 +7834,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
@@ -7863,9 +7890,9 @@
 MK-ST-F-053 money
 MK-ST-F-055 round2
 MK-ST-F-056 has
+MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-065 isoLocalDate
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
@@ -7878,13 +7905,17 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
@@ -8637,7 +8668,8 @@
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
-MK-NW-F-102 rateWhereItRefuses
+MK-NW-F-104 closedWith
+MK-NW-F-105 whyNoReturn
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -8656,11 +8688,7 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-015 topHoldingConcentration
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-024 userFlows
-MK-PF-F-025 historyIsComplete
-MK-PF-F-026 moneyWeightedReturn
 MK-PF-F-029 closeAsOf
-MK-PF-F-030 npv
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
@@ -8725,7 +8753,6 @@
 MK-ST-F-060 verdict
 MK-ST-F-062 toUtc
 MK-ST-F-063 shiftDay
-MK-ST-F-064 modifiedDietzOverWindow
 MK-ST-F-065 isoLocalDate
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
@@ -8738,13 +8765,17 @@
 MK-ST-F-075 agoLabel
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
@@ -9065,11 +9096,14 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-080 isDay
+MK-ST-F-081 timeWeightedReturn
+MK-ST-F-082 movementsOf
+MK-ST-F-083 accountValuesOn
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
 MK-XS-F-009 readHistory
-MK-XS-F-010 investableChangePct
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
 MK-XS-F-027 takeHomeMonthly
@@ -11726,7 +11760,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>SUMMARY · SINCE TODAY | What is Your money-weighted return?</t>
+          <t>SUMMARY · SINCE TODAY | What is Your time-weighted return?</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -15513,22 +15547,22 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -15556,22 +15590,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -25228,7 +25262,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -25314,7 +25348,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25400,7 +25434,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25443,7 +25477,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25486,7 +25520,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25572,7 +25606,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -27100,7 +27134,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:295 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:296 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -27143,7 +27177,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:409 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:410 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -27186,7 +27220,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:494</t>
+          <t>src/screens/HomeScreen.tsx:495</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -27206,7 +27240,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -27229,7 +27263,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:507 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:508 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -27249,7 +27283,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27272,7 +27306,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:508</t>
+          <t>src/screens/HomeScreen.tsx:509</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -27292,7 +27326,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27335,7 +27369,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27378,7 +27412,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27421,7 +27455,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27464,7 +27498,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27636,7 +27670,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -27765,7 +27799,7 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -28496,7 +28530,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28539,7 +28573,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28582,7 +28616,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28625,7 +28659,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28668,7 +28702,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29786,7 +29820,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29829,7 +29863,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -29872,7 +29906,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29915,7 +29949,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25262,7 +25262,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25477,7 +25477,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27025,7 +27025,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27455,7 +27455,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27498,7 +27498,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27670,7 +27670,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -27799,7 +27799,7 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -28573,7 +28573,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28616,7 +28616,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28702,7 +28702,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29820,7 +29820,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29863,7 +29863,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30035,7 +30035,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30078,7 +30078,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1200,6 +1200,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -1220,7 +1221,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1409,7 +1410,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-006 price fetched at — read by MK-XS-F-082
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK-XS-F-174, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073
@@ -1872,7 +1873,7 @@
 MK-NW-M-034 Dividends received (12 mo)
 MK-NW-M-035 Realized gain from your buys and sells
 MK-NW-M-036 Gain — long-term (held over 1 yr)
-MK-NW-M-037 Gain — short-term (under 1 yr)</t>
+MK-NW-M-037 Gain — short-term (held 1 yr or less)</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2073,7 +2074,7 @@
 MK-NW-M-034 Dividends received (12 mo)
 MK-NW-M-035 Realized gain from your buys and sells
 MK-NW-M-036 Gain — long-term (held over 1 yr)
-MK-NW-M-037 Gain — short-term (under 1 yr)</t>
+MK-NW-M-037 Gain — short-term (held 1 yr or less)</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -2352,7 +2353,7 @@
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -2717,6 +2718,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-002 dataGaps
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
@@ -2807,7 +2809,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3207,6 +3209,7 @@
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-002 dataGaps
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
@@ -3260,7 +3263,7 @@
 MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
-MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028
+MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028, MK-ST-F-082
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027, MK-ST-F-028
@@ -3303,7 +3306,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3765,6 +3768,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -3785,7 +3789,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3984,7 @@
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-PF-F-009, MK-PF-F-034, MK-ST-F-027, MK-ST-F-028, MK-ST-F-073, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK-XS-F-174, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073
@@ -4488,6 +4492,7 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -4832,6 +4837,7 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -5228,6 +5234,7 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -5608,6 +5615,7 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-006 pruneDaily
 MK-XS-F-024 resolveLens
@@ -6400,6 +6408,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
@@ -6500,7 +6509,7 @@
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -6558,7 +6567,7 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 43 more, on the functions tab</t>
+… and 44 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6981,6 +6990,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
@@ -7070,7 +7080,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 NONE — no function in this chain reads a stored input the sweep knows
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -7120,8 +7130,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 43 more, on the functions tab
-… and 44 more, on the functions tab</t>
+… and 44 more, on the functions tab
+… and 45 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7457,6 +7467,7 @@
 MK-ST-F-072 undo
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
@@ -7526,7 +7537,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-019, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -7911,6 +7922,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
@@ -8405,7 +8417,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -8771,6 +8783,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
@@ -9100,6 +9113,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-084 fillBetweenObservations
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -22388,14 +22402,14 @@
       <c r="C322" s="2" t="inlineStr"/>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-037 — Gain — short-term (under 1 yr)</t>
+          <t>MK-NW-M-037 — Gain — short-term (held 1 yr or less)</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr"/>
       <c r="F322" s="2" t="inlineStr"/>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>words looked for: gain / short term under</t>
+          <t>words looked for: gain / short term held less</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -25262,7 +25276,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -25348,7 +25362,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25434,7 +25448,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25477,7 +25491,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25520,7 +25534,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25530,7 +25544,7 @@
       </c>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="45" customHeight="1">
+    <row r="415" ht="60" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25563,7 +25577,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25606,7 +25620,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25649,7 +25663,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27240,7 +27254,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -27283,7 +27297,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27326,7 +27340,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27369,7 +27383,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27412,7 +27426,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27455,7 +27469,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27498,7 +27512,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27670,7 +27684,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -27799,7 +27813,7 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -28530,7 +28544,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28573,7 +28587,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28616,7 +28630,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28659,7 +28673,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28702,7 +28716,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29820,7 +29834,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29863,7 +29877,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -29906,7 +29920,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29949,7 +29963,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30035,7 +30049,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30078,7 +30092,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25276,7 +25276,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25448,7 +25448,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25276,7 +25276,7 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25448,7 +25448,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25544,7 +25544,7 @@
       </c>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="60" customHeight="1">
+    <row r="415" ht="45" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -27254,7 +27254,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27426,7 +27426,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25500,7 +25500,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25629,7 +25629,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -26833,7 +26833,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -26876,7 +26876,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27736,7 +27736,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -27865,7 +27865,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28682,7 +28682,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -29929,7 +29929,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30015,7 +30015,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30101,7 +30101,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Map'!$A$1:$U$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$536</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$537</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conflicts'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9215</v>
+        <v>9217</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="n"/>
     </row>
@@ -1258,6 +1258,7 @@
 MK-CF-F-189 essentialsFromLoggedSpending
 MK-CF-F-190 essentialsMonthly
 MK-CF-F-197 ageAttainedInYear
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-001 buildInsights
 MK-HM-F-002 milestoneLabel
 MK-NW-F-001 isAlternative
@@ -1292,6 +1293,7 @@
 MK-NW-F-094 ledgerGroups
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-107 propertyUses
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1391,6 +1393,7 @@
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -1414,7 +1417,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
-MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073
+MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-027, MK-NW-F-054, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
@@ -1461,7 +1464,7 @@
 MK-XS-I-044 the person’s own plan overrides — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-ST-F-027, MK-ST-F-028, MK-ST-F-073, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
-MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-</t>
+MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2614,6 +2617,7 @@
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
@@ -2653,6 +2657,7 @@
 MK-NW-F-068 prettyDay
 MK-NW-F-094 ledgerGroups
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
@@ -2751,6 +2756,7 @@
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund</t>
@@ -3839,6 +3845,7 @@
 MK-CF-F-212 receivedInMonth
 MK-CF-O-008 whatsComing
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -3862,6 +3869,7 @@
 MK-NW-F-094 ledgerGroups
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-107 propertyUses
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -3965,6 +3973,7 @@
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -3991,7 +4000,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
-MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073
+MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-027, MK-NW-F-054, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
@@ -4041,7 +4050,7 @@
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-027
 MK-XS-I-035 annuity income — read by MK-CF-F-072, MK-CF-F-075
-MK-XS-I-035 annuity income —</t>
+MK-XS-I-035 ann</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4404,6 +4413,7 @@
 MK-CF-F-212 receivedInMonth
 MK-CF-O-008 whatsComing
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-009 maturityClass
@@ -4420,6 +4430,8 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -4523,6 +4535,7 @@
 MK-CF-O-008 whatsComing
 MK-CF-O-010 theMonth
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds</t>
         </is>
       </c>
@@ -5567,12 +5580,15 @@
 MK-CF-O-008 whatsComing
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-009 maturityClass
 MK-NW-F-040 assetsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5645,6 +5661,7 @@
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds</t>
         </is>
       </c>
@@ -6295,6 +6312,7 @@
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
 MK-CF-O-019 theIncomeManager
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -6330,6 +6348,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6457,6 +6476,7 @@
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
 MK-CF-O-019 theIncomeManager
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance</t>
@@ -6876,6 +6896,7 @@
 MK-CF-O-008 whatsComing
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -6911,6 +6932,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7038,6 +7060,7 @@
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance</t>
@@ -7398,6 +7421,7 @@
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
@@ -7417,6 +7441,8 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -7499,6 +7525,7 @@
 MK-CF-O-008 whatsComing
 MK-CF-O-010 theMonth
 MK-CF-O-017 futurePaycheck
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds</t>
         </is>
       </c>
@@ -8638,6 +8665,7 @@
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-001 buildInsights
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
@@ -8690,6 +8718,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -8838,6 +8867,7 @@
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9203,7 +9233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12155,12 +12185,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; is not on a property. a &lt;name&gt; is always on a property — open it and say which one. | emergency fund | # months</t>
+          <t>&lt;name&gt; | − | $#</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution</t>
+          <t>rich, rich|By institution, worker, worker|By institution</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -12170,7 +12200,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>› | Mortgage is not on a property. A mortgage is always on a property — open it and say which one. Opens that mortgage.</t>
+          <t>Car loan, you owe $14,000. Opens the editor. | 🚗</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -12198,22 +12228,22 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt; | − | $#</t>
+          <t>&lt;name&gt;, $# # account. collapses them.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution, worker, worker|By institution</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Car loan, you owe $14,000. Opens the editor. | 🚗</t>
+          <t>100 | %</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -12241,22 +12271,22 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>&lt;name&gt;, $# # account. collapses them.</t>
+          <t>add your accounts › | your retirement plan | sample: #% odds of lasting to age #</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>new, new|By institution</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>spoken</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>100 | %</t>
+          <t>Nothing entered yet. Add your accounts › | Nothing entered yet.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -12284,24 +12314,20 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>add your accounts › | your retirement plan | sample: #% odds of lasting to age #</t>
+          <t>net worth $# by asset class: stocks / funds # percent.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>new, new|By institution</t>
+          <t>retiree, retiree|By institution</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Nothing entered yet. Add your accounts › | Nothing entered yet.</t>
-        </is>
-      </c>
+          <t>spoken</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -12327,12 +12353,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>net worth $# by asset class: stocks / funds # percent.</t>
+          <t>net worth $# by asset class: unclassified # percent, stocks / funds # percent, cash # percent, bonds &amp; cds # percent.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>retiree, retiree|By institution</t>
+          <t>rich, rich|By institution</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -12366,12 +12392,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>net worth $# by asset class: unclassified # percent, stocks / funds # percent, cash # percent, bonds &amp; cds # percent.</t>
+          <t>net worth $# by asset class: unclassified # percent, stocks / funds # percent.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution</t>
+          <t>worker, worker|By institution</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12405,12 +12431,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>net worth $# by asset class: unclassified # percent, stocks / funds # percent.</t>
+          <t>no institution, $# # account. collapses them.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>worker, worker|By institution</t>
+          <t>retiree|By institution</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12418,7 +12444,11 @@
           <t>spoken</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>100 | %</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>The screen shows this number, but no row on the master file describes it. A number with no row has no formula, no inputs and no test, so nobody can check it. Say whether it gets its own row, or belongs to a row that already exists.</t>
@@ -12444,12 +12474,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>no institution, $# # account. collapses them.</t>
+          <t>no institution, $# # accounts. collapses them.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>retiree|By institution</t>
+          <t>worker|By institution</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12487,22 +12517,22 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>no institution, $# # accounts. collapses them.</t>
+          <t>of debt payments you cannot stop. | #–# months is the usual guide</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>worker|By institution</t>
+          <t>rich, rich|By institution, worker, worker|By institution</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>spoken</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>100 | %</t>
+          <t>Both include | $420/month</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -12530,12 +12560,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>of debt payments you cannot stop. | #–# months is the usual guide</t>
+          <t>pay first | − | $#</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution, worker, worker|By institution</t>
+          <t>rich, rich|By institution</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -12545,7 +12575,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Both include | $420/month</t>
+          <t>🧾 | Chase Sapphire</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -12573,22 +12603,22 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>pay first | − | $#</t>
+          <t>tracking starts today — change shows as history builds | your retirement plan: on course to last past # ~$# to spare. opens the plan tab.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution</t>
+          <t>retiree, retiree|By institution</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>🧾 | Chase Sapphire</t>
+          <t>$0 | $250,000</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -12616,22 +12646,22 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>tracking starts today — change shows as history builds | your retirement plan: on course to last past # ~$# to spare. opens the plan tab.</t>
+          <t>what you owe: &lt;name&gt; # percent, &lt;name&gt; # percent.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>retiree, retiree|By institution</t>
+          <t>rich, rich|By institution</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>spoken</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>$0 | $250,000</t>
+          <t>ⓘ | −$284,200</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -12659,12 +12689,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>what you owe: &lt;name&gt; # percent, &lt;name&gt; # percent.</t>
+          <t>what you owe: &lt;name&gt; # percent.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>rich, rich|By institution</t>
+          <t>worker, worker|By institution</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -12674,7 +12704,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>ⓘ | −$284,200</t>
+          <t>ⓘ | −$14,000</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -12702,22 +12732,22 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>what you owe: &lt;name&gt; # percent.</t>
+          <t>you entered | # months</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>worker, worker|By institution</t>
+          <t>retiree, retiree|By institution, rich, rich|By institution</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>spoken</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>ⓘ | −$14,000</t>
+          <t>essentials | —</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -12745,12 +12775,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>you entered | # months</t>
+          <t>your &lt;name&gt; “&lt;name&gt;” is not on a property. a &lt;name&gt; is always on a property — open it and say which one. | emergency fund | # months</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>retiree, retiree|By institution, rich, rich|By institution</t>
+          <t>rich, rich|By institution</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -12760,7 +12790,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>essentials | —</t>
+          <t>› | Your mortgage “Mortgage” is not on a property. A mortgage is always on a property — open it and say which one. Opens that mortgage.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -15656,7 +15686,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -25298,123 +25328,119 @@
     <row r="409" ht="60" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
         <is>
+          <t>orchestrator orphan</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>/plan · /cashflow</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/budget-counted.ts</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>MK-CF-O-020 theBudgetCounted</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>named by 0 row(s)</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>imported by 2 screen(s)</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr"/>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="n"/>
+    </row>
+    <row r="410" ht="60" customHeight="1">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B409" s="2" t="inlineStr">
+      <c r="B410" s="2" t="inlineStr">
         <is>
           <t>/account-detail · /analytics · /base-pay · /bill-calendar · /bonds · /cashflow · /holding-detail · /home · /income-manager · /income-summary · /insights · /invest · /itemize · /monthly-income · /other-investments</t>
         </is>
       </c>
-      <c r="C409" s="2" t="inlineStr">
+      <c r="C410" s="2" t="inlineStr">
         <is>
           <t>MoneyKeel/functions/_figure-spec.ts:71</t>
         </is>
       </c>
-      <c r="D409" s="2" t="inlineStr">
+      <c r="D410" s="2" t="inlineStr">
         <is>
           <t>spec.unit === 'money' ? formatMoney(value)</t>
         </is>
       </c>
-      <c r="E409" s="2" t="inlineStr">
+      <c r="E410" s="2" t="inlineStr">
         <is>
           <t>$420, $600, $151,000, $165,000 … (1257 renders)</t>
         </is>
       </c>
-      <c r="F409" s="2" t="inlineStr">
+      <c r="F410" s="2" t="inlineStr">
         <is>
           <t>inside writeFigure</t>
         </is>
       </c>
-      <c r="G409" s="2" t="inlineStr">
+      <c r="G410" s="2" t="inlineStr">
         <is>
           <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
-      <c r="H409" s="2" t="inlineStr">
+      <c r="H410" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
-      <c r="I409" s="2" t="n"/>
-    </row>
-    <row r="410" ht="45" customHeight="1">
-      <c r="A410" s="2" t="inlineStr">
+      <c r="I410" s="2" t="n"/>
+    </row>
+    <row r="411" ht="45" customHeight="1">
+      <c r="A411" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B410" s="2" t="inlineStr">
+      <c r="B411" s="2" t="inlineStr">
         <is>
           <t>/holding-detail</t>
         </is>
       </c>
-      <c r="C410" s="2" t="inlineStr">
+      <c r="C411" s="2" t="inlineStr">
         <is>
           <t>MoneyKeel/functions/_figure-spec.ts:73</t>
         </is>
       </c>
-      <c r="D410" s="2" t="inlineStr">
+      <c r="D411" s="2" t="inlineStr">
         <is>
           <t>: spec.unit === 'money-cents' ? formatMoneyCents(value)</t>
         </is>
       </c>
-      <c r="E410" s="2" t="inlineStr">
+      <c r="E411" s="2" t="inlineStr">
         <is>
           <t>$90.00 … (3 renders)</t>
         </is>
       </c>
-      <c r="F410" s="2" t="inlineStr">
+      <c r="F411" s="2" t="inlineStr">
         <is>
           <t>inside writeFigure</t>
         </is>
       </c>
-      <c r="G410" s="2" t="inlineStr">
+      <c r="G411" s="2" t="inlineStr">
         <is>
           <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average), MK-NW-M-029 CURRENT PRICE · LIVE</t>
-        </is>
-      </c>
-      <c r="H410" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I410" s="2" t="n"/>
-    </row>
-    <row r="411" ht="60" customHeight="1">
-      <c r="A411" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B411" s="2" t="inlineStr">
-        <is>
-          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
-        </is>
-      </c>
-      <c r="C411" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
-        </is>
-      </c>
-      <c r="D411" s="2" t="inlineStr">
-        <is>
-          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
-        </is>
-      </c>
-      <c r="E411" s="2" t="inlineStr">
-        <is>
-          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
-        </is>
-      </c>
-      <c r="F411" s="2" t="inlineStr">
-        <is>
-          <t>inside basePay</t>
-        </is>
-      </c>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25427,42 +25453,42 @@
     <row r="412" ht="60" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>src/components/DrawSteerSheet.tsx:136 (+1 spoken/visible twin)</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
+          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>$250,000 … (10 renders)</t>
+          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>inside DrawSteerSheet</t>
+          <t>inside basePay</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I412" s="2" t="n"/>
@@ -25470,42 +25496,42 @@
     <row r="413" ht="60" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:285</t>
+          <t>src/components/DrawSteerSheet.tsx:136 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>$0 … (14 renders)</t>
+          <t>$250,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>inside AllocateSavings</t>
+          <t>inside DrawSteerSheet</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I413" s="2" t="n"/>
@@ -25523,17 +25549,17 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:324</t>
+          <t>src/components/MoneySheets.tsx:285</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
+          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>$0 … (7 renders)</t>
+          <t>$0 … (14 renders)</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -25543,7 +25569,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25561,75 +25587,75 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>src/components/MoneySheets.tsx:324</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (7 renders)</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>inside AllocateSavings</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="n"/>
+    </row>
+    <row r="416" ht="60" customHeight="1">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
           <t>/cashflow</t>
         </is>
       </c>
-      <c r="C415" s="2" t="inlineStr">
+      <c r="C416" s="2" t="inlineStr">
         <is>
           <t>src/components/MortgageRateCompare.tsx:56 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D415" s="2" t="inlineStr">
+      <c r="D416" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">accessibilityLabel={`${rates} A dollar into your mortgage saves you ${c.direction === 'paying-down-wins' ? 'more' : 'less'} than the same dollar would earn in Treasuries, about ${spokenMoney(yearly)} </t>
         </is>
       </c>
-      <c r="E415" s="2" t="inlineStr">
+      <c r="E416" s="2" t="inlineStr">
         <is>
           <t>$5,320 … (4 renders)</t>
         </is>
       </c>
-      <c r="F415" s="2" t="inlineStr">
+      <c r="F416" s="2" t="inlineStr">
         <is>
           <t>inside MortgageRateCompare</t>
         </is>
       </c>
-      <c r="G415" s="2" t="inlineStr">
+      <c r="G416" s="2" t="inlineStr">
         <is>
           <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
-        </is>
-      </c>
-      <c r="H415" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="n"/>
-    </row>
-    <row r="416" ht="45" customHeight="1">
-      <c r="A416" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B416" s="2" t="inlineStr">
-        <is>
-          <t>/cashflow · /home</t>
-        </is>
-      </c>
-      <c r="C416" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D416" s="2" t="inlineStr">
-        <is>
-          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="inlineStr">
-        <is>
-          <t>$4,795 … (14 renders)</t>
-        </is>
-      </c>
-      <c r="F416" s="2" t="inlineStr">
-        <is>
-          <t>inside PaycheckCard</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25652,17 +25678,17 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:49</t>
+          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row key={i} label={g.source + (g.day ? ` (day ${g.day})` : '')} value={maskedMoney(g.amount)} /&gt;</t>
+          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>$2,200, $1,300 … (14 renders)</t>
+          <t>$4,795 … (14 renders)</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
@@ -25672,7 +25698,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25695,204 +25721,204 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
+          <t>src/components/PaycheckCard.tsx:49</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Row key={i} label={g.source + (g.day ? ` (day ${g.day})` : '')} value={maskedMoney(g.amount)} /&gt;</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>$2,200, $1,300 … (14 renders)</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>inside PaycheckCard</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="n"/>
+    </row>
+    <row r="419" ht="60" customHeight="1">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow · /home</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
           <t>src/components/PaycheckCard.tsx:54</t>
         </is>
       </c>
-      <c r="D418" s="2" t="inlineStr">
+      <c r="D419" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={[styles.rowValue, { fontWeight: '800' }]}&gt;{maskedMoney(m.guaranteedTotal)}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E418" s="2" t="inlineStr">
+      <c r="E419" s="2" t="inlineStr">
         <is>
           <t>$3,500 … (7 renders)</t>
         </is>
       </c>
-      <c r="F418" s="2" t="inlineStr">
+      <c r="F419" s="2" t="inlineStr">
         <is>
           <t>inside PaycheckCard</t>
         </is>
       </c>
-      <c r="G418" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
-        </is>
-      </c>
-      <c r="H418" s="2" t="inlineStr">
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
-      <c r="I418" s="2" t="n"/>
-    </row>
-    <row r="419" ht="30" customHeight="1">
-      <c r="A419" s="2" t="inlineStr">
+      <c r="I419" s="2" t="n"/>
+    </row>
+    <row r="420" ht="30" customHeight="1">
+      <c r="A420" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B419" s="2" t="inlineStr">
+      <c r="B420" s="2" t="inlineStr">
         <is>
           <t>/cashflow · /home</t>
         </is>
       </c>
-      <c r="C419" s="2" t="inlineStr">
+      <c r="C420" s="2" t="inlineStr">
         <is>
           <t>src/components/PaycheckCard.tsx:59</t>
         </is>
       </c>
-      <c r="D419" s="2" t="inlineStr">
+      <c r="D420" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.rowValue}&gt;{maskedMoney(m.safeDraw)}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E419" s="2" t="inlineStr">
+      <c r="E420" s="2" t="inlineStr">
         <is>
           <t>$1,295 … (7 renders)</t>
         </is>
       </c>
-      <c r="F419" s="2" t="inlineStr">
+      <c r="F420" s="2" t="inlineStr">
         <is>
           <t>inside PaycheckCard</t>
         </is>
       </c>
-      <c r="G419" s="2" t="inlineStr">
+      <c r="G420" s="2" t="inlineStr">
         <is>
           <t>MK-CF-M-055 Draw from savings</t>
         </is>
       </c>
-      <c r="H419" s="2" t="inlineStr">
+      <c r="H420" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I419" s="2" t="n"/>
-    </row>
-    <row r="420" ht="60" customHeight="1">
-      <c r="A420" s="2" t="inlineStr">
+      <c r="I420" s="2" t="n"/>
+    </row>
+    <row r="421" ht="60" customHeight="1">
+      <c r="A421" s="2" t="inlineStr">
         <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B420" s="2" t="inlineStr">
+      <c r="B421" s="2" t="inlineStr">
         <is>
           <t>/cashflow · /home</t>
         </is>
       </c>
-      <c r="C420" s="2" t="inlineStr">
+      <c r="C421" s="2" t="inlineStr">
         <is>
           <t>src/components/PaycheckCard.tsx:65</t>
         </is>
       </c>
-      <c r="D420" s="2" t="inlineStr">
+      <c r="D421" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.year}&gt;This year ~{maskedMoney(year.thisYear)} &lt;EstimateTag /&gt; &lt;Text style={styles.yearNote}&gt;— varies month to month&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E420" s="2" t="inlineStr">
+      <c r="E421" s="2" t="inlineStr">
         <is>
           <t>$55,140 … (7 renders)</t>
         </is>
       </c>
-      <c r="F420" s="2" t="inlineStr">
+      <c r="F421" s="2" t="inlineStr">
         <is>
           <t>inside PaycheckCard</t>
         </is>
       </c>
-      <c r="G420" s="2" t="inlineStr">
+      <c r="G421" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H420" s="2" t="inlineStr">
+      <c r="H421" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I420" s="2" t="n"/>
-    </row>
-    <row r="421" ht="45" customHeight="1">
-      <c r="A421" s="2" t="inlineStr">
+      <c r="I421" s="2" t="n"/>
+    </row>
+    <row r="422" ht="45" customHeight="1">
+      <c r="A422" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B421" s="2" t="inlineStr">
+      <c r="B422" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C421" s="2" t="inlineStr">
+      <c r="C422" s="2" t="inlineStr">
         <is>
           <t>src/components/PlanInputs.tsx:118</t>
         </is>
       </c>
-      <c r="D421" s="2" t="inlineStr">
+      <c r="D422" s="2" t="inlineStr">
         <is>
           <t>We're including your {maskedMoney(mortgageMonthly)}/month mortgage until it's paid off in {mortgagePayoffYear}, from your loan.</t>
         </is>
       </c>
-      <c r="E421" s="2" t="inlineStr">
+      <c r="E422" s="2" t="inlineStr">
         <is>
           <t>$1,900</t>
         </is>
       </c>
-      <c r="F421" s="2" t="inlineStr">
+      <c r="F422" s="2" t="inlineStr">
         <is>
           <t>inside PlanInputs</t>
         </is>
       </c>
-      <c r="G421" s="2" t="inlineStr">
+      <c r="G422" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
         </is>
       </c>
-      <c r="H421" s="2" t="inlineStr">
+      <c r="H422" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I421" s="2" t="n"/>
-    </row>
-    <row r="422" ht="60" customHeight="1">
-      <c r="A422" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B422" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C422" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PlanInputs.tsx:140</t>
-        </is>
-      </c>
-      <c r="D422" s="2" t="inlineStr">
-        <is>
-          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr">
-        <is>
-          <t>$1,080,000, $1,160,000, $110,000 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F422" s="2" t="inlineStr">
-        <is>
-          <t>inside PlanInputs</t>
-        </is>
-      </c>
-      <c r="G422" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H422" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I422" s="2" t="n"/>
@@ -25910,17 +25936,17 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:147</t>
+          <t>src/components/PlanInputs.tsx:140</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
+          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
+          <t>$1,080,000, $1,160,000, $110,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -25953,17 +25979,17 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:153 (+1 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:147</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
+          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
+          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
@@ -25996,17 +26022,17 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:171 (+2 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:153 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
+          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>$25,000 … (3 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
@@ -26039,22 +26065,22 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:241</t>
+          <t>src/components/PlanInputs.tsx:171 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
+          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>$0 … (5 renders)</t>
+          <t>$25,000 … (3 renders)</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>inside Stepper</t>
+          <t>inside PlanInputs</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -26082,118 +26108,118 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
+          <t>src/components/PlanInputs.tsx:241</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (5 renders)</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>inside Stepper</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="n"/>
+    </row>
+    <row r="428" ht="60" customHeight="1">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
           <t>src/components/SpendMoreControl.tsx:61</t>
         </is>
       </c>
-      <c r="D427" s="2" t="inlineStr">
+      <c r="D428" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.amt} accessibilityLabel={`${spokenMoney(extra)} more in expenses each month`}&gt;{maskedMoney(extra)}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E427" s="2" t="inlineStr">
+      <c r="E428" s="2" t="inlineStr">
         <is>
           <t>$0 … (4 renders)</t>
         </is>
       </c>
-      <c r="F427" s="2" t="inlineStr">
+      <c r="F428" s="2" t="inlineStr">
         <is>
           <t>inside SpendMoreControl</t>
         </is>
       </c>
-      <c r="G427" s="2" t="inlineStr">
+      <c r="G428" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H427" s="2" t="inlineStr">
+      <c r="H428" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I427" s="2" t="n"/>
-    </row>
-    <row r="428" ht="45" customHeight="1">
-      <c r="A428" s="2" t="inlineStr">
+      <c r="I428" s="2" t="n"/>
+    </row>
+    <row r="429" ht="45" customHeight="1">
+      <c r="A429" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B428" s="2" t="inlineStr">
+      <c r="B429" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C428" s="2" t="inlineStr">
+      <c r="C429" s="2" t="inlineStr">
         <is>
           <t>src/components/SpendMoreControl.tsx:73</t>
         </is>
       </c>
-      <c r="D428" s="2" t="inlineStr">
+      <c r="D429" s="2" t="inlineStr">
         <is>
           <t>? &lt;&gt;You'd spend &lt;Text style={s.b}&gt;{maskedMoney(total)}&lt;/Text&gt;/month — the same as now.&lt;/&gt;</t>
         </is>
       </c>
-      <c r="E428" s="2" t="inlineStr">
+      <c r="E429" s="2" t="inlineStr">
         <is>
           <t>$3,800 … (2 renders)</t>
         </is>
       </c>
-      <c r="F428" s="2" t="inlineStr">
+      <c r="F429" s="2" t="inlineStr">
         <is>
           <t>inside SpendMoreControl</t>
         </is>
       </c>
-      <c r="G428" s="2" t="inlineStr">
+      <c r="G429" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
-      <c r="H428" s="2" t="inlineStr">
+      <c r="H429" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I428" s="2" t="n"/>
-    </row>
-    <row r="429" ht="60" customHeight="1">
-      <c r="A429" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B429" s="2" t="inlineStr">
-        <is>
-          <t>/tips</t>
-        </is>
-      </c>
-      <c r="C429" s="2" t="inlineStr">
-        <is>
-          <t>src/components/UI.tsx:179</t>
-        </is>
-      </c>
-      <c r="D429" s="2" t="inlineStr">
-        <is>
-          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
-        </is>
-      </c>
-      <c r="E429" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F429" s="2" t="inlineStr">
-        <is>
-          <t>inside AmountText</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H429" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I429" s="2" t="n"/>
@@ -26206,27 +26232,27 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>/income-detail · /tax-organizer</t>
+          <t>/tips</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>src/domain/income/from-accounts.ts:176</t>
+          <t>src/components/UI.tsx:179</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
+          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>$10,000 … (2 renders)</t>
+          <t>$0 … (12 renders)</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>inside incomeFromAccounts</t>
+          <t>inside AmountText</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -26249,27 +26275,27 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /plan</t>
+          <t>/income-detail · /tax-organizer</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:354</t>
+          <t>src/domain/income/from-accounts.ts:176</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
+          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>$1,031,000 … (10 renders)</t>
+          <t>$10,000 … (2 renders)</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>inside onCourseSentence</t>
+          <t>inside incomeFromAccounts</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
@@ -26292,27 +26318,27 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/big-costs</t>
+          <t>/analytics · /plan</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>src/screens/BigCostsScreen.tsx:46</t>
+          <t>src/domain/planning/hub.ts:354</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
+          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>$0 … (3 renders)</t>
+          <t>$1,031,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>inside BigCostsScreen</t>
+          <t>inside onCourseSentence</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
@@ -26340,204 +26366,204 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
+          <t>src/screens/BigCostsScreen.tsx:46</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (3 renders)</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>inside BigCostsScreen</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="n"/>
+    </row>
+    <row r="434" ht="60" customHeight="1">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>/big-costs</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
           <t>src/screens/BigCostsScreen.tsx:61 (+2 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D433" s="2" t="inlineStr">
+      <c r="D434" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`${c.label}, ${spokenMoney(c.amount)} in ${c.year}. Opens the editor.`}</t>
         </is>
       </c>
-      <c r="E433" s="2" t="inlineStr">
+      <c r="E434" s="2" t="inlineStr">
         <is>
           <t>$25,000 … (3 renders)</t>
         </is>
       </c>
-      <c r="F433" s="2" t="inlineStr">
+      <c r="F434" s="2" t="inlineStr">
         <is>
           <t>inside BigCostsScreen</t>
         </is>
       </c>
-      <c r="G433" s="2" t="inlineStr">
+      <c r="G434" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H433" s="2" t="inlineStr">
+      <c r="H434" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I433" s="2" t="n"/>
-    </row>
-    <row r="434" ht="45" customHeight="1">
-      <c r="A434" s="2" t="inlineStr">
+      <c r="I434" s="2" t="n"/>
+    </row>
+    <row r="435" ht="45" customHeight="1">
+      <c r="A435" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B434" s="2" t="inlineStr">
+      <c r="B435" s="2" t="inlineStr">
         <is>
           <t>/contribution-room</t>
         </is>
       </c>
-      <c r="C434" s="2" t="inlineStr">
+      <c r="C435" s="2" t="inlineStr">
         <is>
           <t>src/screens/ContributionRoomScreen.tsx:30</t>
         </is>
       </c>
-      <c r="D434" s="2" t="inlineStr">
+      <c r="D435" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.room}&gt;{knownUsed ? `${money(room)} left` : `up to ${money(limit)}`}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E434" s="2" t="inlineStr">
+      <c r="E435" s="2" t="inlineStr">
         <is>
           <t>$14,900, $1,500, $4,400, $32,500 … (12 renders)</t>
         </is>
       </c>
-      <c r="F434" s="2" t="inlineStr">
+      <c r="F435" s="2" t="inlineStr">
         <is>
           <t>inside RoomCard</t>
         </is>
       </c>
-      <c r="G434" s="2" t="inlineStr">
+      <c r="G435" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
-      <c r="H434" s="2" t="inlineStr">
+      <c r="H435" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I434" s="2" t="n"/>
-    </row>
-    <row r="435" ht="60" customHeight="1">
-      <c r="A435" s="2" t="inlineStr">
+      <c r="I435" s="2" t="n"/>
+    </row>
+    <row r="436" ht="60" customHeight="1">
+      <c r="A436" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B435" s="2" t="inlineStr">
+      <c r="B436" s="2" t="inlineStr">
         <is>
           <t>/contribution-room</t>
         </is>
       </c>
-      <c r="C435" s="2" t="inlineStr">
+      <c r="C436" s="2" t="inlineStr">
         <is>
           <t>src/screens/ContributionRoomScreen.tsx:34</t>
         </is>
       </c>
-      <c r="D435" s="2" t="inlineStr">
+      <c r="D436" s="2" t="inlineStr">
         <is>
           <t>{knownUsed ? `That is about ${money(used)} of the ${money(limit)} limit — calculated from what you entered you contribute each month, not from your payroll, so check it against your latest statement.`</t>
         </is>
       </c>
-      <c r="E435" s="2" t="inlineStr">
+      <c r="E436" s="2" t="inlineStr">
         <is>
           <t>$9,600, $24,500, $6,000, $7,500 … (18 renders)</t>
         </is>
       </c>
-      <c r="F435" s="2" t="inlineStr">
+      <c r="F436" s="2" t="inlineStr">
         <is>
           <t>inside RoomCard</t>
         </is>
       </c>
-      <c r="G435" s="2" t="inlineStr">
+      <c r="G436" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
-      <c r="H435" s="2" t="inlineStr">
+      <c r="H436" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I435" s="2" t="n"/>
-    </row>
-    <row r="436" ht="45" customHeight="1">
-      <c r="A436" s="2" t="inlineStr">
+      <c r="I436" s="2" t="n"/>
+    </row>
+    <row r="437" ht="45" customHeight="1">
+      <c r="A437" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
+      <c r="B437" s="2" t="inlineStr">
         <is>
           <t>/contribution-room</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
+      <c r="C437" s="2" t="inlineStr">
         <is>
           <t>src/screens/ContributionRoomScreen.tsx:74 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D436" s="2" t="inlineStr">
+      <c r="D437" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`Try it in a what-if: about ${money(perMonth)} a month for the rest of the year`}&gt;</t>
         </is>
       </c>
-      <c r="E436" s="2" t="inlineStr">
+      <c r="E437" s="2" t="inlineStr">
         <is>
           <t>$5,000, $10,800, $8,200 … (8 renders)</t>
         </is>
       </c>
-      <c r="F436" s="2" t="inlineStr">
+      <c r="F437" s="2" t="inlineStr">
         <is>
           <t>inside ContributionRoomScreen</t>
         </is>
       </c>
-      <c r="G436" s="2" t="inlineStr">
+      <c r="G437" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-005 about $X for the rest of the year, MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
-      <c r="H436" s="2" t="inlineStr">
+      <c r="H437" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I436" s="2" t="n"/>
-    </row>
-    <row r="437" ht="60" customHeight="1">
-      <c r="A437" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B437" s="2" t="inlineStr">
-        <is>
-          <t>/education</t>
-        </is>
-      </c>
-      <c r="C437" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D437" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>$210,622 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F437" s="2" t="inlineStr">
-        <is>
-          <t>inside EducationScreen</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I437" s="2" t="n"/>
@@ -26555,17 +26581,17 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>src/screens/EducationScreen.tsx:74</t>
+          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>$1,285 … (4 renders)</t>
+          <t>$210,622 … (8 renders)</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
@@ -26593,27 +26619,27 @@
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>/expense</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ExpenseScreen.tsx:225</t>
+          <t>src/screens/EducationScreen.tsx:74</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>$60.00, $120.00</t>
+          <t>$1,285 … (4 renders)</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>inside ExpenseScreen</t>
+          <t>inside EducationScreen</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
@@ -26636,27 +26662,27 @@
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>/goals</t>
+          <t>/expense</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:91</t>
+          <t>src/screens/ExpenseScreen.tsx:225</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>$1,880, $100 … (4 renders)</t>
+          <t>$60.00, $120.00</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>inside GoalsScreen</t>
+          <t>inside ExpenseScreen</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
@@ -26674,128 +26700,128 @@
     <row r="441" ht="60" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:91</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>$1,880, $100 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>inside GoalsScreen</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="n"/>
+    </row>
+    <row r="442" ht="60" customHeight="1">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B441" s="2" t="inlineStr">
+      <c r="B442" s="2" t="inlineStr">
         <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C441" s="2" t="inlineStr">
+      <c r="C442" s="2" t="inlineStr">
         <is>
           <t>src/screens/GoalsScreen.tsx:92</t>
         </is>
       </c>
-      <c r="D441" s="2" t="inlineStr">
+      <c r="D442" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.capLab}&gt;typical free cash to save{capacity.lumpy ? ` · ranges ${money(capacity.min)}–${money(capacity.max)} (some months free up more)` : ''}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E441" s="2" t="inlineStr">
+      <c r="E442" s="2" t="inlineStr">
         <is>
           <t>-$1,420, $2,180, -$3,200, $400 … (8 renders)</t>
         </is>
       </c>
-      <c r="F441" s="2" t="inlineStr">
+      <c r="F442" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G441" s="2" t="inlineStr">
+      <c r="G442" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-008 typical free cash to save $X/mo</t>
         </is>
       </c>
-      <c r="H441" s="2" t="inlineStr">
+      <c r="H442" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I441" s="2" t="n"/>
-    </row>
-    <row r="442" ht="45" customHeight="1">
-      <c r="A442" s="2" t="inlineStr">
+      <c r="I442" s="2" t="n"/>
+    </row>
+    <row r="443" ht="45" customHeight="1">
+      <c r="A443" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B442" s="2" t="inlineStr">
+      <c r="B443" s="2" t="inlineStr">
         <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C442" s="2" t="inlineStr">
+      <c r="C443" s="2" t="inlineStr">
         <is>
           <t>src/screens/GoalsScreen.tsx:100</t>
         </is>
       </c>
-      <c r="D442" s="2" t="inlineStr">
+      <c r="D443" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget comes to {money(0)}/year.&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E442" s="2" t="inlineStr">
+      <c r="E443" s="2" t="inlineStr">
         <is>
           <t>$0 … (2 renders)</t>
         </is>
       </c>
-      <c r="F442" s="2" t="inlineStr">
+      <c r="F443" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G442" s="2" t="inlineStr">
+      <c r="G443" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
-      <c r="H442" s="2" t="inlineStr">
+      <c r="H443" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I442" s="2" t="n"/>
-    </row>
-    <row r="443" ht="60" customHeight="1">
-      <c r="A443" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B443" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C443" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:107</t>
-        </is>
-      </c>
-      <c r="D443" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget{sinkBasis.allPct ? ` (${sinkBasis.pct}% of take-home pay)` : ''} comes to ~{money(sink.annual)}/year. Set aside {money(sink.monthly)}/month so n</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr">
-        <is>
-          <t>$3,600, $300, $2,400, $200 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F443" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-010 your non-monthly budget</t>
-        </is>
-      </c>
-      <c r="H443" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I443" s="2" t="n"/>
@@ -26803,128 +26829,128 @@
     <row r="444" ht="60" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:107</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget{sinkBasis.allPct ? ` (${sinkBasis.pct}% of take-home pay)` : ''} comes to ~{money(sink.annual)}/year. Set aside {money(sink.monthly)}/month so n</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>$3,600, $300, $2,400, $200 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>inside GoalsScreen</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010 your non-monthly budget</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="n"/>
+    </row>
+    <row r="445" ht="60" customHeight="1">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B444" s="2" t="inlineStr">
+      <c r="B445" s="2" t="inlineStr">
         <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C444" s="2" t="inlineStr">
+      <c r="C445" s="2" t="inlineStr">
         <is>
           <t>src/screens/GoalsScreen.tsx:141</t>
         </is>
       </c>
-      <c r="D444" s="2" t="inlineStr">
+      <c r="D445" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.goalSub}&gt;{money(g.saved)} of {money(g.target)} · {money(remaining)} to go{perMonth &gt; 0 ? ` · need ~${money(perMonth)}/month${mo &gt; 0 ? ` for ${mo} mo` : ''}` : ''}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E444" s="2" t="inlineStr">
+      <c r="E445" s="2" t="inlineStr">
         <is>
           <t>$0, $60,000, $1,538, $20,000 … (16 renders)</t>
         </is>
       </c>
-      <c r="F444" s="2" t="inlineStr">
+      <c r="F445" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G444" s="2" t="inlineStr">
+      <c r="G445" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
-      <c r="H444" s="2" t="inlineStr">
+      <c r="H445" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
-      <c r="I444" s="2" t="n"/>
-    </row>
-    <row r="445" ht="45" customHeight="1">
-      <c r="A445" s="2" t="inlineStr">
+      <c r="I445" s="2" t="n"/>
+    </row>
+    <row r="446" ht="45" customHeight="1">
+      <c r="A446" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B445" s="2" t="inlineStr">
+      <c r="B446" s="2" t="inlineStr">
         <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C445" s="2" t="inlineStr">
+      <c r="C446" s="2" t="inlineStr">
         <is>
           <t>src/screens/GoalsScreen.tsx:144</t>
         </is>
       </c>
-      <c r="D445" s="2" t="inlineStr">
+      <c r="D446" s="2" t="inlineStr">
         <is>
           <t>This month: funded {money(fundedMo)} of {money(perMonth)}/month{behind ? ' — allocate more to catch up.' : ' ✓'}</t>
         </is>
       </c>
-      <c r="E445" s="2" t="inlineStr">
+      <c r="E446" s="2" t="inlineStr">
         <is>
           <t>$0, $1,538, $1,333 … (8 renders)</t>
         </is>
       </c>
-      <c r="F445" s="2" t="inlineStr">
+      <c r="F446" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G445" s="2" t="inlineStr">
+      <c r="G446" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
-      <c r="H445" s="2" t="inlineStr">
+      <c r="H446" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="n"/>
-    </row>
-    <row r="446" ht="60" customHeight="1">
-      <c r="A446" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B446" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C446" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:150</t>
-        </is>
-      </c>
-      <c r="D446" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>$7,200 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F446" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H446" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I446" s="2" t="n"/>
@@ -26942,17 +26968,17 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:206</t>
+          <t>src/screens/GoalsScreen.tsx:150</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>$420, $9,000, $2,200 … (8 renders)</t>
+          <t>$7,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr">
@@ -26985,17 +27011,17 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:233</t>
+          <t>src/screens/GoalsScreen.tsx:206</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {liabilities.length} debt{liabilities.length &gt; 1 ? 's' : ''}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>$14,000, $284,200 … (4 renders)</t>
+          <t>$420, $9,000, $2,200 … (8 renders)</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
@@ -27028,17 +27054,17 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:234</t>
+          <t>src/screens/GoalsScreen.tsx:233</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {liabilities.length} debt{liabilities.length &gt; 1 ? 's' : ''}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>$1,228, $236,683 … (4 renders)</t>
+          <t>$14,000, $284,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
@@ -27061,7 +27087,7 @@
     <row r="450" ht="60" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -27071,17 +27097,17 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:302</t>
+          <t>src/screens/GoalsScreen.tsx:234</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500, $0 … (8 renders)</t>
+          <t>$1,228, $236,683 … (4 renders)</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -27091,12 +27117,12 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I450" s="2" t="n"/>
@@ -27104,7 +27130,7 @@
     <row r="451" ht="60" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -27114,17 +27140,17 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:304</t>
+          <t>src/screens/GoalsScreen.tsx:302</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
+          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (12 renders)</t>
+          <t>$7,200, $3,500, $0 … (8 renders)</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
@@ -27134,12 +27160,12 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I451" s="2" t="n"/>
@@ -27152,27 +27178,27 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/goals</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:135</t>
+          <t>src/screens/GoalsScreen.tsx:304</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
+          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>$1,900</t>
+          <t>$7,200, $3,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>inside HomeScreen</t>
+          <t>inside GoalsScreen</t>
         </is>
       </c>
       <c r="G452" s="2" t="inlineStr">
@@ -27190,7 +27216,7 @@
     <row r="453" ht="60" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -27200,17 +27226,17 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:296 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:135</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
+          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $709,800 … (10 renders)</t>
+          <t>$1,900</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
@@ -27220,12 +27246,12 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
@@ -27233,7 +27259,7 @@
     <row r="454" ht="60" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -27243,17 +27269,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:410 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:296 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
+          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
+          <t>$165,000, $709,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -27263,12 +27289,12 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I454" s="2" t="n"/>
@@ -27276,7 +27302,7 @@
     <row r="455" ht="60" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -27286,17 +27312,17 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:495</t>
+          <t>src/screens/HomeScreen.tsx:410 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
+          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $0, $3,500 … (21 renders)</t>
+          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
@@ -27306,12 +27332,12 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
@@ -27329,17 +27355,17 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:508 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:495</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
+          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (14 renders)</t>
+          <t>$7,200, $0, $3,500 … (21 renders)</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
@@ -27372,70 +27398,70 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
+          <t>src/screens/HomeScreen.tsx:508 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>$7,200, $3,500 … (14 renders)</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>inside HomeScreen</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="n"/>
+    </row>
+    <row r="458" ht="60" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
           <t>src/screens/HomeScreen.tsx:509</t>
         </is>
       </c>
-      <c r="D457" s="2" t="inlineStr">
+      <c r="D458" s="2" t="inlineStr">
         <is>
           <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Actual expenses so far&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(bva.spent_total))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
-      <c r="E457" s="2" t="inlineStr">
+      <c r="E458" s="2" t="inlineStr">
         <is>
           <t>$0 … (7 renders)</t>
         </is>
       </c>
-      <c r="F457" s="2" t="inlineStr">
+      <c r="F458" s="2" t="inlineStr">
         <is>
           <t>inside HomeScreen</t>
         </is>
       </c>
-      <c r="G457" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
-        </is>
-      </c>
-      <c r="H457" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I457" s="2" t="n"/>
-    </row>
-    <row r="458" ht="45" customHeight="1">
-      <c r="A458" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B458" s="2" t="inlineStr">
-        <is>
-          <t>/income-detail</t>
-        </is>
-      </c>
-      <c r="C458" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/IncomeDetailScreen.tsx:68</t>
-        </is>
-      </c>
-      <c r="D458" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E458" s="2" t="inlineStr">
-        <is>
-          <t>$86,400, $86,720, $42,000</t>
-        </is>
-      </c>
-      <c r="F458" s="2" t="inlineStr">
-        <is>
-          <t>inside IncomeDetailScreen</t>
-        </is>
-      </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27458,17 +27484,17 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:69</t>
+          <t>src/screens/IncomeDetailScreen.tsx:68</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
+          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>$108,000, $108,400, $42,000</t>
+          <t>$86,400, $86,720, $42,000</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
@@ -27501,17 +27527,17 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:72</t>
+          <t>src/screens/IncomeDetailScreen.tsx:69</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
+          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $7,227, $3,500</t>
+          <t>$108,000, $108,400, $42,000</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -27521,7 +27547,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27544,17 +27570,17 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:73</t>
+          <t>src/screens/IncomeDetailScreen.tsx:72</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
+          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>$4,800 … (2 renders)</t>
+          <t>$7,200, $7,227, $3,500</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -27564,7 +27590,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27587,75 +27613,75 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
+          <t>src/screens/IncomeDetailScreen.tsx:73</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>$4,800 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>inside IncomeDetailScreen</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="n"/>
+    </row>
+    <row r="463" ht="45" customHeight="1">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
           <t>src/screens/IncomeDetailScreen.tsx:85</t>
         </is>
       </c>
-      <c r="D462" s="2" t="inlineStr">
+      <c r="D463" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.srcAmt}&gt;{money(src.gross_amount)}&lt;Text style={styles.per}&gt;{CADENCE[src.frequency]}&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E462" s="2" t="inlineStr">
+      <c r="E463" s="2" t="inlineStr">
         <is>
           <t>$9,000, $400, $3,500 … (4 renders)</t>
         </is>
       </c>
-      <c r="F462" s="2" t="inlineStr">
+      <c r="F463" s="2" t="inlineStr">
         <is>
           <t>inside IncomeDetailScreen</t>
         </is>
       </c>
-      <c r="G462" s="2" t="inlineStr">
+      <c r="G463" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
-      <c r="H462" s="2" t="inlineStr">
+      <c r="H463" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I462" s="2" t="n"/>
-    </row>
-    <row r="463" ht="60" customHeight="1">
-      <c r="A463" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B463" s="2" t="inlineStr">
-        <is>
-          <t>/home · /insights</t>
-        </is>
-      </c>
-      <c r="C463" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/InsightsScreen.tsx:76</t>
-        </is>
-      </c>
-      <c r="D463" s="2" t="inlineStr">
-        <is>
-          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="inlineStr">
-        <is>
-          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
-        </is>
-      </c>
-      <c r="F463" s="2" t="inlineStr">
-        <is>
-          <t>inside useInsights</t>
-        </is>
-      </c>
-      <c r="G463" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
-        </is>
-      </c>
-      <c r="H463" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I463" s="2" t="n"/>
@@ -27663,7 +27689,7 @@
     <row r="464" ht="60" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -27673,17 +27699,17 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:155</t>
+          <t>src/screens/InsightsScreen.tsx:76</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
+          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
+          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -27693,12 +27719,12 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I464" s="2" t="n"/>
@@ -27706,7 +27732,7 @@
     <row r="465" ht="60" customHeight="1">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -27716,17 +27742,17 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:161</t>
+          <t>src/screens/InsightsScreen.tsx:155</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
+          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>$0 … (6 renders)</t>
+          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -27736,12 +27762,12 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I465" s="2" t="n"/>
@@ -27749,7 +27775,7 @@
     <row r="466" ht="60" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -27759,17 +27785,17 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:162</t>
+          <t>src/screens/InsightsScreen.tsx:161</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
+          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>$4,520, $3,800 … (6 renders)</t>
+          <t>$0 … (6 renders)</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -27779,12 +27805,12 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I466" s="2" t="n"/>
@@ -27792,7 +27818,7 @@
     <row r="467" ht="60" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -27802,17 +27828,17 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:172</t>
+          <t>src/screens/InsightsScreen.tsx:162</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
+          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
+          <t>$4,520, $3,800 … (6 renders)</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
@@ -27822,12 +27848,12 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I467" s="2" t="n"/>
@@ -27835,7 +27861,7 @@
     <row r="468" ht="60" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -27845,17 +27871,17 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:175</t>
+          <t>src/screens/InsightsScreen.tsx:172</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>'invest-rate': () =&gt; [{ label: 'Annual contributions', value: money(monthlyContributionsFromOnboarding(op) * 12) }, { label: 'Gross income', value: money(gross) },</t>
+          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>$0, $42,000 … (6 renders)</t>
+          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -27865,12 +27891,12 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I468" s="2" t="n"/>
@@ -27878,7 +27904,7 @@
     <row r="469" ht="60" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -27888,17 +27914,17 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:177</t>
+          <t>src/screens/InsightsScreen.tsx:175</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
+          <t>'invest-rate': () =&gt; [{ label: 'Annual contributions', value: money(monthlyContributionsFromOnboarding(op) * 12) }, { label: 'Gross income', value: money(gross) },</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>$4,200 … (2 renders)</t>
+          <t>$0, $42,000 … (6 renders)</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
@@ -27908,12 +27934,12 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I469" s="2" t="n"/>
@@ -27921,42 +27947,42 @@
     <row r="470" ht="60" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/home · /insights</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
+          <t>src/screens/InsightsScreen.tsx:177</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
+          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
+          <t>$4,200 … (2 renders)</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>inside InsuranceScreen</t>
+          <t>inside useInsights</t>
         </is>
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>—</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I470" s="2" t="n"/>
@@ -27974,17 +28000,17 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:70</t>
+          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
+          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
@@ -27994,7 +28020,7 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -28017,17 +28043,17 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:71</t>
+          <t>src/screens/InsuranceScreen.tsx:70</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
+          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
@@ -28037,7 +28063,7 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>MK-MN-M-018 Income replacement (N yrs)</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -28060,17 +28086,17 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:72</t>
+          <t>src/screens/InsuranceScreen.tsx:71</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
+          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
@@ -28103,103 +28129,103 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
+          <t>src/screens/InsuranceScreen.tsx:72</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>inside InsuranceScreen</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="n"/>
+    </row>
+    <row r="475" ht="60" customHeight="1">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>/insurance</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
           <t>src/screens/InsuranceScreen.tsx:73</t>
         </is>
       </c>
-      <c r="D474" s="2" t="inlineStr">
+      <c r="D475" s="2" t="inlineStr">
         <is>
           <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;− Savings &amp; existing coverage&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;−{money(need.covered)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
-      <c r="E474" s="2" t="inlineStr">
+      <c r="E475" s="2" t="inlineStr">
         <is>
           <t>$165,000, $729,800, $250,000, $0</t>
         </is>
       </c>
-      <c r="F474" s="2" t="inlineStr">
+      <c r="F475" s="2" t="inlineStr">
         <is>
           <t>inside InsuranceScreen</t>
         </is>
       </c>
-      <c r="G474" s="2" t="inlineStr">
+      <c r="G475" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-018 Income replacement (N yrs)</t>
         </is>
       </c>
-      <c r="H474" s="2" t="inlineStr">
+      <c r="H475" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I474" s="2" t="n"/>
-    </row>
-    <row r="475" ht="45" customHeight="1">
-      <c r="A475" s="2" t="inlineStr">
+      <c r="I475" s="2" t="n"/>
+    </row>
+    <row r="476" ht="45" customHeight="1">
+      <c r="A476" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B475" s="2" t="inlineStr">
+      <c r="B476" s="2" t="inlineStr">
         <is>
           <t>/jobsafety</t>
         </is>
       </c>
-      <c r="C475" s="2" t="inlineStr">
+      <c r="C476" s="2" t="inlineStr">
         <is>
           <t>src/screens/JobSafetyScreen.tsx:115</t>
         </is>
       </c>
-      <c r="D475" s="2" t="inlineStr">
+      <c r="D476" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={[s.hero, { color: covered ? Colors.gainText : Colors.amber }]}&gt;{covered ? '✓ Covered' : money(gap)}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E475" s="2" t="inlineStr">
-        <is>
-          <t>$3,600, $21,000, $18,600</t>
-        </is>
-      </c>
-      <c r="F475" s="2" t="inlineStr">
-        <is>
-          <t>inside JobSafetyScreen</t>
-        </is>
-      </c>
-      <c r="G475" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
-        </is>
-      </c>
-      <c r="H475" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I475" s="2" t="n"/>
-    </row>
-    <row r="476" ht="60" customHeight="1">
-      <c r="A476" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B476" s="2" t="inlineStr">
-        <is>
-          <t>/jobsafety</t>
-        </is>
-      </c>
-      <c r="C476" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/JobSafetyScreen.tsx:117</t>
-        </is>
-      </c>
-      <c r="D476" s="2" t="inlineStr">
-        <is>
-          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
-        </is>
-      </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>$3,600, $600, $0, $21,000 … (9 renders)</t>
+          <t>$3,600, $31,320, $18,600</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -28232,17 +28258,17 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:120</t>
+          <t>src/screens/JobSafetyScreen.tsx:117</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
+          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>$600, $3,500, $3,100</t>
+          <t>$3,600, $600, $0, $31,320 … (9 renders)</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
@@ -28265,85 +28291,85 @@
     <row r="478" ht="60" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>/jobsafety</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/JobSafetyScreen.tsx:120</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>$600, $5,220, $3,100</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>inside JobSafetyScreen</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="n"/>
+    </row>
+    <row r="479" ht="60" customHeight="1">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B478" s="2" t="inlineStr">
+      <c r="B479" s="2" t="inlineStr">
         <is>
           <t>/jobsafety</t>
         </is>
       </c>
-      <c r="C478" s="2" t="inlineStr">
+      <c r="C479" s="2" t="inlineStr">
         <is>
           <t>src/screens/JobSafetyScreen.tsx:163</t>
         </is>
       </c>
-      <c r="D478" s="2" t="inlineStr">
+      <c r="D479" s="2" t="inlineStr">
         <is>
           <t>Setting aside &lt;Text style={s.bold}&gt;{money(EXAMPLE_PACE)}/month&lt;/Text&gt; closes the gap in &lt;Text style={s.bold}&gt;{monthsToClose} months&lt;/Text&gt; — an example pace, set your own.</t>
         </is>
       </c>
-      <c r="E478" s="2" t="inlineStr">
+      <c r="E479" s="2" t="inlineStr">
         <is>
           <t>$300 … (3 renders)</t>
         </is>
       </c>
-      <c r="F478" s="2" t="inlineStr">
+      <c r="F479" s="2" t="inlineStr">
         <is>
           <t>inside JobSafetyScreen</t>
         </is>
       </c>
-      <c r="G478" s="2" t="inlineStr">
+      <c r="G479" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H478" s="2" t="inlineStr">
+      <c r="H479" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
-      <c r="I478" s="2" t="n"/>
-    </row>
-    <row r="479" ht="45" customHeight="1">
-      <c r="A479" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B479" s="2" t="inlineStr">
-        <is>
-          <t>/multi-goal</t>
-        </is>
-      </c>
-      <c r="C479" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/MultiGoalScreen.tsx:79</t>
-        </is>
-      </c>
-      <c r="D479" s="2" t="inlineStr">
-        <is>
-          <t>{ label: 'Retirement saving', from: `${maskedMoney(A.contribMonthly ?? 0)}/month`, to: `${maskedMoney(retirementMonthly)}/month` },</t>
-        </is>
-      </c>
-      <c r="E479" s="2" t="inlineStr">
-        <is>
-          <t>$0, $500 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F479" s="2" t="inlineStr">
-        <is>
-          <t>inside MultiGoalScreen</t>
-        </is>
-      </c>
-      <c r="G479" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo, MK-PL-M-030 Extra on debt $X/mo</t>
-        </is>
-      </c>
-      <c r="H479" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I479" s="2" t="n"/>
@@ -28351,214 +28377,214 @@
     <row r="480" ht="45" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>/multi-goal</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/MultiGoalScreen.tsx:79</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>{ label: 'Retirement saving', from: `${maskedMoney(A.contribMonthly ?? 0)}/month`, to: `${maskedMoney(retirementMonthly)}/month` },</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>$0, $500 … (8 renders)</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>inside MultiGoalScreen</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo, MK-PL-M-030 Extra on debt $X/mo</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="n"/>
+    </row>
+    <row r="481" ht="45" customHeight="1">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B480" s="2" t="inlineStr">
+      <c r="B481" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C480" s="2" t="inlineStr">
+      <c r="C481" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:131 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D480" s="2" t="inlineStr">
+      <c r="D481" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`Extra on debt at ${spokenMoney(extraDebt)} a month`} /&gt;</t>
         </is>
       </c>
-      <c r="E480" s="2" t="inlineStr">
+      <c r="E481" s="2" t="inlineStr">
         <is>
           <t>$0 … (4 renders)</t>
         </is>
       </c>
-      <c r="F480" s="2" t="inlineStr">
+      <c r="F481" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G480" s="2" t="inlineStr">
+      <c r="G481" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-030 Extra on debt $X/mo</t>
         </is>
       </c>
-      <c r="H480" s="2" t="inlineStr">
+      <c r="H481" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I480" s="2" t="n"/>
-    </row>
-    <row r="481" ht="30" customHeight="1">
-      <c r="A481" s="2" t="inlineStr">
+      <c r="I481" s="2" t="n"/>
+    </row>
+    <row r="482" ht="30" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B481" s="2" t="inlineStr">
+      <c r="B482" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr">
+      <c r="C482" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:151</t>
         </is>
       </c>
-      <c r="D481" s="2" t="inlineStr">
+      <c r="D482" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.dialAmt}&gt;{maskedMoney(retirementMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E481" s="2" t="inlineStr">
+      <c r="E482" s="2" t="inlineStr">
         <is>
           <t>$500 … (4 renders)</t>
         </is>
       </c>
-      <c r="F481" s="2" t="inlineStr">
+      <c r="F482" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G481" s="2" t="inlineStr">
+      <c r="G482" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
         </is>
       </c>
-      <c r="H481" s="2" t="inlineStr">
+      <c r="H482" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I481" s="2" t="n"/>
-    </row>
-    <row r="482" ht="60" customHeight="1">
-      <c r="A482" s="2" t="inlineStr">
+      <c r="I482" s="2" t="n"/>
+    </row>
+    <row r="483" ht="60" customHeight="1">
+      <c r="A483" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B482" s="2" t="inlineStr">
+      <c r="B483" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C482" s="2" t="inlineStr">
+      <c r="C483" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:164 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D482" s="2" t="inlineStr">
+      <c r="D483" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`Can you do it all? ${weighed.covered ? `Covered, with ${spokenMoney(weighed.spare)} a month to spare` : `Short ${spokenMoney(Math.abs(weighed.spare))} a month`}`}&gt;</t>
         </is>
       </c>
-      <c r="E482" s="2" t="inlineStr">
+      <c r="E483" s="2" t="inlineStr">
         <is>
           <t>$1,380, $400, $500 … (8 renders)</t>
         </is>
       </c>
-      <c r="F482" s="2" t="inlineStr">
+      <c r="F483" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr">
+      <c r="G483" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
         </is>
       </c>
-      <c r="H482" s="2" t="inlineStr">
+      <c r="H483" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I482" s="2" t="n"/>
-    </row>
-    <row r="483" ht="45" customHeight="1">
-      <c r="A483" s="2" t="inlineStr">
+      <c r="I483" s="2" t="n"/>
+    </row>
+    <row r="484" ht="45" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B483" s="2" t="inlineStr">
+      <c r="B484" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C483" s="2" t="inlineStr">
+      <c r="C484" s="2" t="inlineStr">
         <is>
           <t>src/screens/PlanHubScreen.tsx:233</t>
         </is>
       </c>
-      <c r="D483" s="2" t="inlineStr">
+      <c r="D484" s="2" t="inlineStr">
         <is>
           <t>Your {maskedMoney(planSpend)}/month expenses{onCourse ? ` — ${onCourse}` : ` — ${oddsLine(lens, wil.chance!, wil.horizonAge)}`}.</t>
         </is>
       </c>
-      <c r="E483" s="2" t="inlineStr">
+      <c r="E484" s="2" t="inlineStr">
         <is>
           <t>$3,800 … (2 renders)</t>
         </is>
       </c>
-      <c r="F483" s="2" t="inlineStr">
+      <c r="F484" s="2" t="inlineStr">
         <is>
           <t>inside PlanHubScreen</t>
         </is>
       </c>
-      <c r="G483" s="2" t="inlineStr">
+      <c r="G484" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
-      <c r="H483" s="2" t="inlineStr">
+      <c r="H484" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="n"/>
-    </row>
-    <row r="484" ht="60" customHeight="1">
-      <c r="A484" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B484" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C484" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/PlanHubScreen.tsx:273</t>
-        </is>
-      </c>
-      <c r="D484" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {door.credit.accounts} {accounts.some((a: any) =&gt; a.source === 'connected') ? 'connected ' : ''}account{door.credit.accounts === 1 ? '' : </t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>$165,000, $729,800</t>
-        </is>
-      </c>
-      <c r="F484" s="2" t="inlineStr">
-        <is>
-          <t>inside PlanHubScreen</t>
-        </is>
-      </c>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H484" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I484" s="2" t="n"/>
@@ -28566,7 +28592,7 @@
     <row r="485" ht="60" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -28576,17 +28602,17 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:308</t>
+          <t>src/screens/PlanHubScreen.tsx:273</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
+          <t xml:space="preserve">&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {door.credit.accounts} {accounts.some((a: any) =&gt; a.source === 'connected') ? 'connected ' : ''}account{door.credit.accounts === 1 ? '' : </t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
+          <t>$165,000, $729,800</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -28596,12 +28622,12 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I485" s="2" t="n"/>
@@ -28619,17 +28645,17 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:314</t>
+          <t>src/screens/PlanHubScreen.tsx:308</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>$2,200, $1,300 … (4 renders)</t>
+          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
@@ -28639,7 +28665,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28662,17 +28688,17 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:316</t>
+          <t>src/screens/PlanHubScreen.tsx:314</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
+          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$2,200, $1,300 … (4 renders)</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
@@ -28682,7 +28708,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28705,17 +28731,17 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:317 (+1 spoken/visible twin)</t>
+          <t>src/screens/PlanHubScreen.tsx:316</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
+          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>$1,295 … (4 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
@@ -28725,7 +28751,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -28748,113 +28774,113 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
+          <t>src/screens/PlanHubScreen.tsx:317 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>$1,295 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>inside PlanHubScreen</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="n"/>
+    </row>
+    <row r="490" ht="60" customHeight="1">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
           <t>src/screens/PlanHubScreen.tsx:318</t>
         </is>
       </c>
-      <c r="D489" s="2" t="inlineStr">
+      <c r="D490" s="2" t="inlineStr">
         <is>
           <t>&lt;View style={[styles.payRow, styles.payTotal]}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;Your paycheck&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(paycheckTotal))}/</t>
         </is>
       </c>
-      <c r="E489" s="2" t="inlineStr">
+      <c r="E490" s="2" t="inlineStr">
         <is>
           <t>$4,795 … (2 renders)</t>
         </is>
       </c>
-      <c r="F489" s="2" t="inlineStr">
+      <c r="F490" s="2" t="inlineStr">
         <is>
           <t>inside PlanHubScreen</t>
         </is>
       </c>
-      <c r="G489" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
-        </is>
-      </c>
-      <c r="H489" s="2" t="inlineStr">
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
-      <c r="I489" s="2" t="n"/>
-    </row>
-    <row r="490" ht="45" customHeight="1">
-      <c r="A490" s="2" t="inlineStr">
+      <c r="I490" s="2" t="n"/>
+    </row>
+    <row r="491" ht="45" customHeight="1">
+      <c r="A491" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B490" s="2" t="inlineStr">
+      <c r="B491" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C490" s="2" t="inlineStr">
+      <c r="C491" s="2" t="inlineStr">
         <is>
           <t>src/screens/PlanHubScreen.tsx:327</t>
         </is>
       </c>
-      <c r="D490" s="2" t="inlineStr">
+      <c r="D491" s="2" t="inlineStr">
         <is>
           <t>✓ covers your {maskedMoney(planSpend)}/month expenses. You're drawing {maskedMoney(Math.round(drawUsed))}/month</t>
         </is>
       </c>
-      <c r="E490" s="2" t="inlineStr">
+      <c r="E491" s="2" t="inlineStr">
         <is>
           <t>$3,800, $300 … (4 renders)</t>
         </is>
       </c>
-      <c r="F490" s="2" t="inlineStr">
+      <c r="F491" s="2" t="inlineStr">
         <is>
           <t>inside PlanHubScreen</t>
         </is>
       </c>
-      <c r="G490" s="2" t="inlineStr">
+      <c r="G491" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
-        </is>
-      </c>
-      <c r="H490" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I490" s="2" t="n"/>
-    </row>
-    <row r="491" ht="60" customHeight="1">
-      <c r="A491" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B491" s="2" t="inlineStr">
-        <is>
-          <t>/required-withdrawals</t>
-        </is>
-      </c>
-      <c r="C491" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:101</t>
-        </is>
-      </c>
-      <c r="D491" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.line}&gt;Yours starts in &lt;Text style={s.strong}&gt;{startYear}&lt;/Text&gt; (age {rmdStartAgeFor(age)}). Estimated first withdrawal: &lt;Text style={s.strong}&gt;~{maskedMoney(Math.round(schedule[0]?.amo</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>$41,528, $138,428</t>
-        </is>
-      </c>
-      <c r="F491" s="2" t="inlineStr">
-        <is>
-          <t>inside RequiredWithdrawalsScreen</t>
-        </is>
-      </c>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -28877,118 +28903,118 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:101</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.line}&gt;Yours starts in &lt;Text style={s.strong}&gt;{startYear}&lt;/Text&gt; (age {rmdStartAgeFor(age)}). Estimated first withdrawal: &lt;Text style={s.strong}&gt;~{maskedMoney(Math.round(schedule[0]?.amo</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>$41,528, $138,428</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>inside RequiredWithdrawalsScreen</t>
+        </is>
+      </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="n"/>
+    </row>
+    <row r="493" ht="60" customHeight="1">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
           <t>src/screens/RequiredWithdrawalsScreen.tsx:186 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
+      <c r="D493" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`${r.year}, age ${r.age}: about ${spokenMoney(Math.round(r.amount))}${r.isCurrent ? ', this year' : ''}`}&gt;</t>
         </is>
       </c>
-      <c r="E492" s="2" t="inlineStr">
+      <c r="E493" s="2" t="inlineStr">
         <is>
           <t>$41,528, $43,628, $45,625, $47,916 … (32 renders)</t>
         </is>
       </c>
-      <c r="F492" s="2" t="inlineStr">
+      <c r="F493" s="2" t="inlineStr">
         <is>
           <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
-      <c r="G492" s="2" t="inlineStr">
+      <c r="G493" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
         </is>
       </c>
-      <c r="H492" s="2" t="inlineStr">
+      <c r="H493" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I492" s="2" t="n"/>
-    </row>
-    <row r="493" ht="45" customHeight="1">
-      <c r="A493" s="2" t="inlineStr">
+      <c r="I493" s="2" t="n"/>
+    </row>
+    <row r="494" ht="45" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B493" s="2" t="inlineStr">
+      <c r="B494" s="2" t="inlineStr">
         <is>
           <t>/required-withdrawals</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr">
+      <c r="C494" s="2" t="inlineStr">
         <is>
           <t>src/screens/RequiredWithdrawalsScreen.tsx:202 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D493" s="2" t="inlineStr">
+      <c r="D494" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`${a.label}, ${spokenMoney(Math.round(a.balance || 0))}, marked pre-tax. Opens its page to edit.`}&gt;</t>
         </is>
       </c>
-      <c r="E493" s="2" t="inlineStr">
+      <c r="E494" s="2" t="inlineStr">
         <is>
           <t>$120,000, $400,000 … (4 renders)</t>
         </is>
       </c>
-      <c r="F493" s="2" t="inlineStr">
+      <c r="F494" s="2" t="inlineStr">
         <is>
           <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
-      <c r="G493" s="2" t="inlineStr">
+      <c r="G494" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-016 BASED ON THESE ACCOUNTS — each balance</t>
         </is>
       </c>
-      <c r="H493" s="2" t="inlineStr">
+      <c r="H494" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I493" s="2" t="n"/>
-    </row>
-    <row r="494" ht="60" customHeight="1">
-      <c r="A494" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B494" s="2" t="inlineStr">
-        <is>
-          <t>/retirement</t>
-        </is>
-      </c>
-      <c r="C494" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RetirementCockpit.tsx:37</t>
-        </is>
-      </c>
-      <c r="D494" s="2" t="inlineStr">
-        <is>
-          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
-        </is>
-      </c>
-      <c r="F494" s="2" t="inlineStr">
-        <is>
-          <t>inside big</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H494" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I494" s="2" t="n"/>
@@ -29006,22 +29032,22 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:491</t>
+          <t>src/screens/RetirementCockpit.tsx:37</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>$250K … (2 renders)</t>
+          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
-          <t>inside RetirementCockpit</t>
+          <t>inside big</t>
         </is>
       </c>
       <c r="G495" s="2" t="inlineStr">
@@ -29049,17 +29075,17 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:520</t>
+          <t>src/screens/RetirementCockpit.tsx:491</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
+          <t>$250K … (2 renders)</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -29092,17 +29118,17 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:555</t>
+          <t>src/screens/RetirementCockpit.tsx:520</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
@@ -29135,17 +29161,17 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:630</t>
+          <t>src/screens/RetirementCockpit.tsx:555</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
+          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -29178,17 +29204,17 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:639</t>
+          <t>src/screens/RetirementCockpit.tsx:630</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
+          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
@@ -29221,17 +29247,17 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:648</t>
+          <t>src/screens/RetirementCockpit.tsx:639</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>$0 … (2 renders)</t>
+          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -29264,17 +29290,17 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:672</t>
+          <t>src/screens/RetirementCockpit.tsx:648</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>$10K … (2 renders)</t>
+          <t>$0 … (2 renders)</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -29307,17 +29333,17 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:673</t>
+          <t>src/screens/RetirementCockpit.tsx:672</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a), 'M')}{simple ? '' : ` · ${info.source} · ${info.period}${info.estimate ? ' · est.' : ''}</t>
+          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $400K, $300K … (12 renders)</t>
+          <t>$10K … (2 renders)</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -29350,17 +29376,17 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:734</t>
+          <t>src/screens/RetirementCockpit.tsx:673</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
+          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a), 'M')}{simple ? '' : ` · ${info.source} · ${info.period}${info.estimate ? ' · est.' : ''}</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$120K, $45K, $400K, $300K … (12 renders)</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -29393,17 +29419,17 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:751</t>
+          <t>src/screens/RetirementCockpit.tsx:734</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
+          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>$5,000, $3,800 … (8 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -29436,17 +29462,17 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:773</t>
+          <t>src/screens/RetirementCockpit.tsx:751</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>$14,900, $24,500 … (12 renders)</t>
+          <t>$5,000, $3,800 … (8 renders)</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -29479,17 +29505,17 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:775</t>
+          <t>src/screens/RetirementCockpit.tsx:773</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
+          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>$7,500 … (6 renders)</t>
+          <t>$14,900, $24,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
@@ -29522,17 +29548,17 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:790</t>
+          <t>src/screens/RetirementCockpit.tsx:775</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
+          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$7,500 … (6 renders)</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -29565,22 +29591,22 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:954</t>
+          <t>src/screens/RetirementCockpit.tsx:790</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
+          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>inside EarmarkSheet</t>
+          <t>inside RetirementCockpit</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
@@ -29608,17 +29634,17 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:959</t>
+          <t>src/screens/RetirementCockpit.tsx:954</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a), 'M')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -29646,27 +29672,27 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RothScreen.tsx:84 (+1 spoken/visible twin)</t>
+          <t>src/screens/RetirementCockpit.tsx:959</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
+          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a), 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>$0 … (12 renders)</t>
+          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>inside RothScreen</t>
+          <t>inside EarmarkSheet</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
@@ -29684,214 +29710,214 @@
     <row r="511" ht="60" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
         <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:84 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>inside RothScreen</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="n"/>
+    </row>
+    <row r="512" ht="60" customHeight="1">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B511" s="2" t="inlineStr">
+      <c r="B512" s="2" t="inlineStr">
         <is>
           <t>/roth</t>
         </is>
       </c>
-      <c r="C511" s="2" t="inlineStr">
+      <c r="C512" s="2" t="inlineStr">
         <is>
           <t>src/screens/RothScreen.tsx:132</t>
         </is>
       </c>
-      <c r="D511" s="2" t="inlineStr">
+      <c r="D512" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.note}&gt;from your pre-tax {maskedMoney(Math.round(preTax))}{num(amount) &gt; preTax ? ' — capped at your balance' : ''}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E511" s="2" t="inlineStr">
+      <c r="E512" s="2" t="inlineStr">
         <is>
           <t>$120,000, $400,000</t>
         </is>
       </c>
-      <c r="F511" s="2" t="inlineStr">
+      <c r="F512" s="2" t="inlineStr">
         <is>
           <t>inside RothScreen</t>
         </is>
       </c>
-      <c r="G511" s="2" t="inlineStr">
+      <c r="G512" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-024 from your pre-tax $X</t>
         </is>
       </c>
-      <c r="H511" s="2" t="inlineStr">
+      <c r="H512" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I511" s="2" t="n"/>
-    </row>
-    <row r="512" ht="45" customHeight="1">
-      <c r="A512" s="2" t="inlineStr">
+      <c r="I512" s="2" t="n"/>
+    </row>
+    <row r="513" ht="45" customHeight="1">
+      <c r="A513" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B512" s="2" t="inlineStr">
+      <c r="B513" s="2" t="inlineStr">
         <is>
           <t>/roth</t>
         </is>
       </c>
-      <c r="C512" s="2" t="inlineStr">
+      <c r="C513" s="2" t="inlineStr">
         <is>
           <t>src/screens/RothScreen.tsx:137 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D512" s="2" t="inlineStr">
+      <c r="D513" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`Set ${spokenMoney(v)}`}&gt;</t>
         </is>
       </c>
-      <c r="E512" s="2" t="inlineStr">
+      <c r="E513" s="2" t="inlineStr">
         <is>
           <t>$10,000, $25,000, $50,000 … (12 renders)</t>
         </is>
       </c>
-      <c r="F512" s="2" t="inlineStr">
+      <c r="F513" s="2" t="inlineStr">
         <is>
           <t>inside RothScreen</t>
         </is>
       </c>
-      <c r="G512" s="2" t="inlineStr">
+      <c r="G513" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-024 from your pre-tax $X</t>
         </is>
       </c>
-      <c r="H512" s="2" t="inlineStr">
+      <c r="H513" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I512" s="2" t="n"/>
-    </row>
-    <row r="513" ht="60" customHeight="1">
-      <c r="A513" s="2" t="inlineStr">
+      <c r="I513" s="2" t="n"/>
+    </row>
+    <row r="514" ht="60" customHeight="1">
+      <c r="A514" s="2" t="inlineStr">
         <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B513" s="2" t="inlineStr">
+      <c r="B514" s="2" t="inlineStr">
         <is>
           <t>/roth</t>
         </is>
       </c>
-      <c r="C513" s="2" t="inlineStr">
+      <c r="C514" s="2" t="inlineStr">
         <is>
           <t>src/screens/RothScreen.tsx:190</t>
         </is>
       </c>
-      <c r="D513" s="2" t="inlineStr">
+      <c r="D514" s="2" t="inlineStr">
         <is>
           <t>title={`Convert ${maskedMoney(amt)} to Roth this year`}</t>
         </is>
       </c>
-      <c r="E513" s="2" t="inlineStr">
+      <c r="E514" s="2" t="inlineStr">
         <is>
           <t>$0 … (2 renders)</t>
         </is>
       </c>
-      <c r="F513" s="2" t="inlineStr">
+      <c r="F514" s="2" t="inlineStr">
         <is>
           <t>inside RothScreen</t>
         </is>
       </c>
-      <c r="G513" s="2" t="inlineStr">
+      <c r="G514" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H513" s="2" t="inlineStr">
+      <c r="H514" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I513" s="2" t="n"/>
-    </row>
-    <row r="514" ht="30" customHeight="1">
-      <c r="A514" s="2" t="inlineStr">
+      <c r="I514" s="2" t="n"/>
+    </row>
+    <row r="515" ht="30" customHeight="1">
+      <c r="A515" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B514" s="2" t="inlineStr">
+      <c r="B515" s="2" t="inlineStr">
         <is>
           <t>/ss-timing</t>
         </is>
       </c>
-      <c r="C514" s="2" t="inlineStr">
+      <c r="C515" s="2" t="inlineStr">
         <is>
           <t>src/screens/SsTimingScreen.tsx:102</t>
         </is>
       </c>
-      <c r="D514" s="2" t="inlineStr">
+      <c r="D515" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.receiveHead}&gt;You receive {maskedMoney(num(op.ri_ss))}/month ✓&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E514" s="2" t="inlineStr">
+      <c r="E515" s="2" t="inlineStr">
         <is>
           <t>$2,200</t>
         </is>
       </c>
-      <c r="F514" s="2" t="inlineStr">
+      <c r="F515" s="2" t="inlineStr">
         <is>
           <t>inside SsTimingScreen</t>
         </is>
       </c>
-      <c r="G514" s="2" t="inlineStr">
+      <c r="G515" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-018 You receive $X/mo ✓</t>
         </is>
       </c>
-      <c r="H514" s="2" t="inlineStr">
+      <c r="H515" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I514" s="2" t="n"/>
-    </row>
-    <row r="515" ht="60" customHeight="1">
-      <c r="A515" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B515" s="2" t="inlineStr">
-        <is>
-          <t>/ss-timing</t>
-        </is>
-      </c>
-      <c r="C515" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/SsTimingScreen.tsx:134</t>
-        </is>
-      </c>
-      <c r="D515" s="2" t="inlineStr">
-        <is>
-          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
-        </is>
-      </c>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>$2,600 … (3 renders)</t>
-        </is>
-      </c>
-      <c r="F515" s="2" t="inlineStr">
-        <is>
-          <t>inside SsTimingScreen</t>
-        </is>
-      </c>
-      <c r="G515" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
-        </is>
-      </c>
-      <c r="H515" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I515" s="2" t="n"/>
@@ -29909,17 +29935,17 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:148</t>
+          <t>src/screens/SsTimingScreen.tsx:134</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
+          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
+          <t>$2,600 … (3 renders)</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
@@ -29952,17 +29978,17 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:150</t>
+          <t>src/screens/SsTimingScreen.tsx:148</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
+          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
+          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -29995,17 +30021,17 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:151</t>
+          <t>src/screens/SsTimingScreen.tsx:150</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
+          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -30015,7 +30041,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30028,42 +30054,42 @@
     <row r="519" ht="60" customHeight="1">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>/stress-test</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:72 (+1 spoken/visible twin)</t>
+          <t>src/screens/SsTimingScreen.tsx:151</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
+          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>$3,000 … (10 renders)</t>
+          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>inside StressTestScreen</t>
+          <t>inside SsTimingScreen</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I519" s="2" t="n"/>
@@ -30071,7 +30097,7 @@
     <row r="520" ht="60" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -30081,17 +30107,17 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:76</t>
+          <t>src/screens/StressTestScreen.tsx:72 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
+          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>$17,000, $3,500</t>
+          <t>$3,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -30101,12 +30127,12 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I520" s="2" t="n"/>
@@ -30124,17 +30150,17 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:93</t>
+          <t>src/screens/StressTestScreen.tsx:76</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
+          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>$600, $3,500, $3,100</t>
+          <t>$17,000, $5,220</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
@@ -30144,7 +30170,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30157,7 +30183,7 @@
     <row r="522" ht="60" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -30167,17 +30193,17 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:97</t>
+          <t>src/screens/StressTestScreen.tsx:93</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$600, $5,220, $3,100</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -30187,12 +30213,12 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I522" s="2" t="n"/>
@@ -30200,113 +30226,113 @@
     <row r="523" ht="60" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>/stress-test</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/StressTestScreen.tsx:97</t>
+        </is>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>inside StressTestScreen</t>
+        </is>
+      </c>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="n"/>
+    </row>
+    <row r="524" ht="60" customHeight="1">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B523" s="2" t="inlineStr">
+      <c r="B524" s="2" t="inlineStr">
         <is>
           <t>/stress-test</t>
         </is>
       </c>
-      <c r="C523" s="2" t="inlineStr">
+      <c r="C524" s="2" t="inlineStr">
         <is>
           <t>src/screens/StressTestScreen.tsx:107</t>
         </is>
       </c>
-      <c r="D523" s="2" t="inlineStr">
+      <c r="D524" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.fundTxt}&gt;3 months of essentials{rent &gt; 0 ? ', less the rent that keeps arriving,' : ''} is &lt;Text style={styles.bold}&gt;{money(r.recommendedFund)}&lt;/Text&gt;. You're &lt;Text style={[styles.</t>
         </is>
       </c>
-      <c r="E523" s="2" t="inlineStr">
+      <c r="E524" s="2" t="inlineStr">
         <is>
           <t>$1,800, $9,300 … (4 renders)</t>
         </is>
       </c>
-      <c r="F523" s="2" t="inlineStr">
+      <c r="F524" s="2" t="inlineStr">
         <is>
           <t>inside StressTestScreen</t>
         </is>
       </c>
-      <c r="G523" s="2" t="inlineStr">
+      <c r="G524" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
-      <c r="H523" s="2" t="inlineStr">
+      <c r="H524" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I523" s="2" t="n"/>
-    </row>
-    <row r="524" ht="45" customHeight="1">
-      <c r="A524" s="2" t="inlineStr">
+      <c r="I524" s="2" t="n"/>
+    </row>
+    <row r="525" ht="45" customHeight="1">
+      <c r="A525" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B524" s="2" t="inlineStr">
+      <c r="B525" s="2" t="inlineStr">
         <is>
           <t>/tax-organizer</t>
         </is>
       </c>
-      <c r="C524" s="2" t="inlineStr">
+      <c r="C525" s="2" t="inlineStr">
         <is>
           <t>src/screens/TaxOrganizerScreen.tsx:90</t>
         </is>
       </c>
-      <c r="D524" s="2" t="inlineStr">
+      <c r="D525" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.rowV}&gt;{money(l.amount)}&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E524" s="2" t="inlineStr">
+      <c r="E525" s="2" t="inlineStr">
         <is>
           <t>$108,000, $400, $42,000 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F524" s="2" t="inlineStr">
-        <is>
-          <t>inside TaxOrganizerScreen</t>
-        </is>
-      </c>
-      <c r="G524" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
-        </is>
-      </c>
-      <c r="H524" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I524" s="2" t="n"/>
-    </row>
-    <row r="525" ht="60" customHeight="1">
-      <c r="A525" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B525" s="2" t="inlineStr">
-        <is>
-          <t>/tax-organizer</t>
-        </is>
-      </c>
-      <c r="C525" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
-        </is>
-      </c>
-      <c r="D525" s="2" t="inlineStr">
-        <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
-        </is>
-      </c>
-      <c r="E525" s="2" t="inlineStr">
-        <is>
-          <t>$108,000, $108,400, $42,000, $0</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -30339,17 +30365,17 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $0 … (4 renders)</t>
+          <t>$108,000, $108,400, $42,000, $0</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
@@ -30382,17 +30408,17 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
         <is>
-          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
+          <t>$9,600, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F527" s="2" t="inlineStr">
@@ -30425,17 +30451,17 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>$66,200, $66,600, $17,850, $0</t>
+          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
@@ -30468,17 +30494,17 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $6,000 … (4 renders)</t>
+          <t>$66,200, $66,600, $17,850, $0</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
@@ -30501,7 +30527,7 @@
     <row r="530" ht="60" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -30511,17 +30537,17 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
+          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000</t>
+          <t>$9,600, $6,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
@@ -30531,12 +30557,12 @@
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I530" s="2" t="n"/>
@@ -30549,27 +30575,27 @@
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:102</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
+          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>$500 … (3 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>inside WhatIfScreen</t>
+          <t>inside TaxOrganizerScreen</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
@@ -30597,17 +30623,17 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:143 (+1 spoken/visible twin)</t>
+          <t>src/screens/WhatIfScreen.tsx:102</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
+          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
+          <t>$500 … (3 renders)</t>
         </is>
       </c>
       <c r="F532" s="2" t="inlineStr">
@@ -30640,17 +30666,17 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:147</t>
+          <t>src/screens/WhatIfScreen.tsx:143 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>$756,665, $651,067, $6,000</t>
+          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
@@ -30673,42 +30699,42 @@
     <row r="534" ht="60" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:50</t>
+          <t>src/screens/WhatIfScreen.tsx:147</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
+          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>$250,000</t>
+          <t>$756,665, $651,067, $6,000</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>inside WillItLastScreen</t>
+          <t>inside WhatIfScreen</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-008 What you have (nest egg)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I534" s="2" t="n"/>
@@ -30726,17 +30752,17 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:51</t>
+          <t>src/screens/WillItLastScreen.tsx:50</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
+          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$250,000</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -30746,7 +30772,7 @@
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-009 Monthly expenses in retirement</t>
+          <t>MK-PL-M-008 What you have (nest egg)</t>
         </is>
       </c>
       <c r="H535" s="2" t="inlineStr">
@@ -30769,38 +30795,81 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
+          <t>src/screens/WillItLastScreen.tsx:51</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>$3,800</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>inside WillItLastScreen</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-009 Monthly expenses in retirement</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="n"/>
+    </row>
+    <row r="537" ht="60" customHeight="1">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
           <t>src/screens/WillItLastScreen.tsx:52</t>
         </is>
       </c>
-      <c r="D536" s="2" t="inlineStr">
+      <c r="D537" s="2" t="inlineStr">
         <is>
           <t>{ label: 'Guaranteed income', value: `${maskedMoney(inp.guaranteed_monthly_income)}/month from age ${inp.guaranteed_start_age ?? inp.retire_age}`, source: A.ssMonthly != null || A.ssClaimAge != null ?</t>
         </is>
       </c>
-      <c r="E536" s="2" t="inlineStr">
+      <c r="E537" s="2" t="inlineStr">
         <is>
           <t>$3,500</t>
         </is>
       </c>
-      <c r="F536" s="2" t="inlineStr">
+      <c r="F537" s="2" t="inlineStr">
         <is>
           <t>inside WillItLastScreen</t>
         </is>
       </c>
-      <c r="G536" s="2" t="inlineStr">
+      <c r="G537" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-010 Guaranteed income — $X/mo from age Y</t>
         </is>
       </c>
-      <c r="H536" s="2" t="inlineStr">
+      <c r="H537" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I536" s="2" t="n"/>
+      <c r="I537" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I536"/>
+  <autoFilter ref="A1:I537"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1462,7 +1462,7 @@
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-179, MK-CF-F-181, MK-CF-F-206
 MK-XS-I-044 the person’s own plan overrides — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-ST-F-027, MK-ST-F-028, MK-ST-F-073, MK
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-NW-O-003, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-</t>
         </is>
@@ -1791,6 +1791,7 @@
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-NW-F-027
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-ST-F-027
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-027
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -2814,6 +2815,7 @@
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-027
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
@@ -15643,22 +15645,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15686,22 +15688,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25483,7 +25485,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25569,7 +25571,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25612,7 +25614,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25655,7 +25657,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25741,7 +25743,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26816,7 +26818,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26902,7 +26904,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -26945,7 +26947,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -27160,7 +27162,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -27375,7 +27377,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27418,7 +27420,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27461,7 +27463,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27504,7 +27506,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27547,7 +27549,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27590,7 +27592,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27633,7 +27635,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -27805,7 +27807,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -27934,7 +27936,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -28708,7 +28710,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28794,7 +28796,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28837,7 +28839,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29955,7 +29957,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -29998,7 +30000,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30041,7 +30043,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30084,7 +30086,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30170,7 +30172,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30213,7 +30215,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1132,6 +1132,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -1156,6 +1157,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -1222,7 +1224,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1405,7 +1407,7 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-040, MK-NW-F-054, MK-NW-O-001, MK
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-111, MK-CF-F-116, MK-CF-F-138, MK-CF-F-139, MK-CF-F-201, MK
@@ -1418,7 +1420,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-027, MK-NW-F-054, MK-XS-F-174, MK-XS-F-175
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
@@ -1462,7 +1464,7 @@
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-179, MK-CF-F-181, MK-CF-F-206
 MK-XS-I-044 the person’s own plan overrides — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-NW-O-003, MK-ST-F-027, MK-ST-F-028, MK
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-054, MK-NW-F-109, MK-NW-O-003, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-</t>
         </is>
@@ -1595,6 +1597,7 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-109 holdingClassOf
 MK-NW-O-002 theAccount
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
@@ -1609,7 +1612,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -1682,11 +1685,16 @@
 MK-NW-F-003 valueFreshness
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
+MK-NW-F-013 realEstateUseOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
+MK-NW-F-030 earmarkDefault
+MK-NW-F-031 primaryCarIdOf
+MK-NW-F-032 earmarkedAmount
 MK-NW-F-034 benchmarkReturn
+MK-NW-F-037 blendedReturn
 MK-NW-F-045 sourceWording
 MK-NW-F-046 historyCoverage
 MK-NW-F-049 itemizedTotal
@@ -1714,6 +1722,7 @@
 MK-NW-F-091 pricedGainOf
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-108 taxWordsOf
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1778,20 +1787,20 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-027, MK-NW-O-002, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-118, MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-118, MK-NW-O-002
 MK-XS-I-009 transaction date — read by MK-NW-O-002
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-027, MK-ST-F-013
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109, MK-ST-F-013
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-024 logged expenses — read by MK-NW-O-002
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-030
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-NW-F-027
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-ST-F-027
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-109, MK-ST-F-027
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
-MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-027
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -2260,12 +2269,17 @@
 MK-NW-F-003 valueFreshness
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
+MK-NW-F-013 realEstateUseOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-030 earmarkDefault
+MK-NW-F-031 primaryCarIdOf
+MK-NW-F-032 earmarkedAmount
 MK-NW-F-034 benchmarkReturn
+MK-NW-F-037 blendedReturn
 MK-NW-F-045 sourceWording
 MK-NW-F-046 historyCoverage
 MK-NW-F-068 prettyDay
@@ -2276,6 +2290,8 @@
 MK-NW-F-091 pricedGainOf
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-108 taxWordsOf
+MK-NW-F-109 holdingClassOf
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2525,6 +2541,7 @@
 MK-NW-F-011 assetClassOf
 MK-NW-F-016 cashTotal
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-055 isBond
 MK-NW-F-056 bondInfo
 MK-NW-F-057 annualCoupon
@@ -2539,6 +2556,7 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -2561,7 +2579,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -2629,13 +2647,13 @@
 MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
 MK-NW-F-028 classPortionLabel
-MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -2765,9 +2783,9 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-NW-F-016, MK-NW-F-027, MK-ST-F-027
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-016, MK-NW-F-027, MK-NW-F-029, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
@@ -2775,7 +2793,7 @@
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-027
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
@@ -2809,13 +2827,13 @@
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-027, MK-ST-F-027
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-109, MK-ST-F-027
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
-MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-027
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
@@ -3156,6 +3174,7 @@
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-109 holdingClassOf
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -3270,7 +3289,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027, MK-ST-F-028
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-NW-O-008, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
@@ -3684,6 +3703,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -3716,6 +3736,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -3801,7 +3822,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -3988,7 +4009,7 @@
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-032, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-040, MK-NW-F-054, MK-NW-O-001, MK
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-NW-F-035, MK-NW-F-037, MK-PL-F-001
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-PL-F-001
@@ -4003,7 +4024,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-027, MK-NW-F-054, MK-XS-F-174, MK-XS-F-175
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
@@ -5033,6 +5054,10 @@
         <is>
           <t>MK-NW-F-003 — Turns a monthly figure into a year by multiplying by twelve.
 MK-NW-F-003 — Uses today's date from the device clock, so the answer changes by itself overnight.
+MK-NW-F-031 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
+MK-NW-F-032 — Caps percent at 100.
+MK-NW-F-032 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
+MK-NW-F-034 — If return is missing it uses 6%.
 No function on record — assumptions unknown
 [Founder] G8, 2026-09-08: the year's figure stands on last 31 December's balance when the person enters it; until then today's balance, stated in those words on the screen.
 [Founder] One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).
@@ -5981,7 +6006,9 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-022 investableAssets
+MK-NW-F-027 accountClassBreakdown
 MK-NW-F-066 sumWhere
+MK-NW-F-109 holdingClassOf
 MK-PL-F-034 lifeInsuranceNeed
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -6325,6 +6352,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -6351,6 +6379,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6911,6 +6940,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -6935,6 +6965,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7432,6 +7463,7 @@
 MK-NW-F-013 realEstateUseOf
 MK-NW-F-016 cashTotal
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -7445,6 +7477,7 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -7828,6 +7861,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -7865,6 +7899,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8683,6 +8718,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -8721,6 +8757,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9078,6 +9115,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
+MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -9107,6 +9145,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-109 holdingClassOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -25571,7 +25610,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25614,7 +25653,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25743,7 +25782,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -25786,7 +25825,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -27271,7 +27310,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:296 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:299 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -27314,7 +27353,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:410 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:413 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -27357,7 +27396,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:495</t>
+          <t>src/screens/HomeScreen.tsx:498</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -27377,7 +27416,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27400,7 +27439,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:508 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:511 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -27420,7 +27459,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27443,7 +27482,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:509</t>
+          <t>src/screens/HomeScreen.tsx:512</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -27463,7 +27502,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27506,7 +27545,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27549,7 +27588,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27592,7 +27631,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27635,7 +27674,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -27807,7 +27846,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -27936,7 +27975,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -28667,7 +28706,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28710,7 +28749,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28753,7 +28792,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -28796,7 +28835,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -30172,7 +30211,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30215,7 +30254,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25524,7 +25524,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25696,7 +25696,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -25825,7 +25825,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30039,7 +30039,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30082,7 +30082,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-05</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-06</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25524,7 +25524,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30039,7 +30039,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30082,7 +30082,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-06</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-07</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -15684,22 +15684,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15727,22 +15727,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25524,7 +25524,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -25696,7 +25696,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30039,7 +30039,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30082,7 +30082,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25438,7 +25438,7 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -26943,7 +26943,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -28878,7 +28878,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -30211,7 +30211,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1269,7 +1269,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
@@ -1296,6 +1295,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-107 propertyUses
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1685,7 +1685,6 @@
 MK-NW-F-003 valueFreshness
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
@@ -1724,6 +1723,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-108 taxWordsOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2270,7 +2270,6 @@
 MK-NW-F-003 valueFreshness
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
@@ -2294,6 +2293,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-108 taxWordsOf
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2647,7 +2647,6 @@
 MK-NW-F-009 maturityClass
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-021 investmentsTotal
@@ -2680,6 +2679,7 @@
 MK-NW-F-094 ledgerGroups
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
@@ -3144,7 +3144,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-009 maturityClass
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -3180,6 +3179,7 @@
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -3705,7 +3705,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -3743,6 +3742,7 @@
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -4341,7 +4341,6 @@
 MK-HM-F-006 money0
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -4360,6 +4359,7 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4815,7 +4815,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -4827,6 +4826,7 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-110 primaryHomeIdOf
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5014,11 +5014,11 @@
 MK-CF-F-155 cash
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
 MK-NW-F-035 blendedVolatility
+MK-NW-F-110 primaryHomeIdOf
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-008 rmdSchedule
@@ -5213,7 +5213,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -5225,6 +5224,7 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-110 primaryHomeIdOf
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5478,7 +5478,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -5501,6 +5500,7 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -6357,7 +6357,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-009 maturityClass
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -6390,6 +6389,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6947,7 +6947,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-009 maturityClass
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -6977,6 +6976,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7472,7 +7472,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-009 maturityClass
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-016 cashTotal
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -7490,6 +7489,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -7869,7 +7869,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -7912,6 +7911,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8726,7 +8726,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -8770,6 +8769,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9123,7 +9123,6 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-013 realEstateUseOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -9158,6 +9157,7 @@
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
+MK-NW-F-110 primaryHomeIdOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -25407,7 +25407,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25675,7 +25675,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="45" customHeight="1">
+    <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25708,7 +25708,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:118</t>
+          <t>src/components/PlanInputs.tsx:119</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:140</t>
+          <t>src/components/PlanInputs.tsx:141</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -25989,7 +25989,7 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:147</t>
+          <t>src/components/PlanInputs.tsx:148</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:153 (+1 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:154 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -26075,7 +26075,7 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:171 (+2 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:172 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:241</t>
+          <t>src/components/PlanInputs.tsx:242</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28761,7 +28761,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29965,7 +29965,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -15696,22 +15696,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15739,22 +15739,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28675,7 +28675,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28761,7 +28761,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29922,7 +29922,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29965,7 +29965,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30051,7 +30051,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9209</v>
+        <v>9208</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -1152,12 +1152,12 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -1409,7 +1409,7 @@
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-111, MK-CF-F-116, MK-CF-F-138, MK-CF-F-139, MK-CF-F-201, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-201, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-PF-F-009, MK-PF-F-034, MK-ST-F-027, MK-ST-F-028, MK-ST-F-073, MK
@@ -1422,7 +1422,7 @@
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
@@ -1712,7 +1712,6 @@
 MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-073 itemising
 MK-NW-F-077 ALL
@@ -1724,6 +1723,7 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-108 taxWordsOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1997,10 +1997,10 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -2182,8 +2182,8 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -2361,13 +2361,13 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-011 bond face value — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-112, MK-NW-O-001
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-064
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069
@@ -2375,8 +2375,9 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -2554,11 +2555,11 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-109 holdingClassOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -2790,7 +2791,7 @@
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
@@ -2798,7 +2799,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
@@ -2834,13 +2835,13 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
 MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3017,12 +3018,12 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PL-F-012 waterfall
@@ -3297,7 +3298,7 @@
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-NW-O-008, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028, MK-ST-F-082
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
@@ -3307,7 +3308,7 @@
 MK-XS-I-009 transaction date — read by MK-NW-O-008
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -3337,11 +3338,11 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3736,13 +3737,13 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -4018,7 +4019,7 @@
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-PL-F-001
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-PL-F-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-111, MK-CF-F-116, MK-CF-F-138, MK-CF-F-139, MK-CF-F-201, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
@@ -4031,7 +4032,7 @@
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
@@ -4355,11 +4356,11 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4572,12 +4573,12 @@
           <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010, MK-XS-F-004
@@ -4635,9 +4636,9 @@
 MK-XS-I-053 the month a debt is first paid — read by MK-XS-F-004
 MK-XS-I-054 the date a debt is due to be paid off in full — read by MK-XS-F-004
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-076, MK-CF-F-107, MK-CF-F-156, MK-NW-F-011, MK
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-075
-MK-XS-I-055 the wrapper an account</t>
+MK-XS-I-055 the wrapp</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5496,11 +5497,11 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -5706,12 +5707,12 @@
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-PL-F-001
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-034
@@ -6248,10 +6249,10 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6527,12 +6528,12 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -6569,13 +6570,13 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092, MK-CF-O-004
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -6633,7 +6634,7 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 44 more, on the functions tab</t>
+… and 50 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6830,10 +6831,10 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7114,12 +7115,12 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -7149,11 +7150,11 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 NONE — no function in this chain reads a stored input the sweep knows
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -7203,8 +7204,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 44 more, on the functions tab
-… and 45 more, on the functions tab</t>
+… and 50 more, on the functions tab
+… and 51 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,10 +7382,10 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7580,12 +7581,12 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-019, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -7613,11 +7614,11 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-019, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -7900,7 +7901,6 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
@@ -7912,6 +7912,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8417,10 +8418,10 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -8463,12 +8464,12 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-031, MK-CF-O-006, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-071, MK-NW-F-072, MK-NW-F-078, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -8496,11 +8497,11 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -8757,7 +8758,6 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
@@ -8770,6 +8770,7 @@
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9151,13 +9152,13 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
-MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -10920,7 +10921,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>(down about | $430</t>
+          <t>(down about | $420</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -11393,7 +11394,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>– | $10,340</t>
+          <t>– | $10,350</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -25407,7 +25408,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25493,7 +25494,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25579,7 +25580,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25622,7 +25623,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25675,7 +25676,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25708,7 +25709,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25751,7 +25752,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25794,7 +25795,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27385,7 +27386,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27428,7 +27429,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27471,7 +27472,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27514,7 +27515,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27557,7 +27558,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27643,7 +27644,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27815,7 +27816,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28632,7 +28633,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28675,7 +28676,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28761,7 +28762,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28804,7 +28805,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29922,7 +29923,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29965,7 +29966,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30008,7 +30009,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30051,7 +30052,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30137,7 +30138,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30180,7 +30181,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25408,7 +25408,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29923,7 +29923,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30009,7 +30009,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30181,7 +30181,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25494,7 +25494,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29923,7 +29923,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30009,7 +30009,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30181,7 +30181,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1236,6 +1236,7 @@
 MK-CF-F-014 budgetVsActual
 MK-CF-F-029 monthsToClear
 MK-CF-F-030 paymentToClearBy
+MK-CF-F-031 creditUtilization
 MK-CF-F-035 debtKind
 MK-CF-F-044 annualNet
 MK-CF-F-045 grossAnnualBaseline
@@ -1260,6 +1261,8 @@
 MK-CF-F-189 essentialsFromLoggedSpending
 MK-CF-F-190 essentialsMonthly
 MK-CF-F-197 ageAttainedInYear
+MK-CF-F-200 LINE
+MK-CF-O-006 theCreditLine
 MK-CF-O-020 theBudgetCounted
 MK-HM-F-001 buildInsights
 MK-HM-F-002 milestoneLabel
@@ -1296,6 +1299,11 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-107 propertyUses
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-113 altPartsOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1393,6 +1401,7 @@
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
+MK-CF-O-006 theCreditLine
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-CF-O-020 theBudgetCounted
@@ -1416,7 +1425,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-006 price fetched at — read by MK-XS-F-082
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-NW-F-027, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
@@ -1724,6 +1733,10 @@
 MK-NW-F-108 taxWordsOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1791,7 +1804,7 @@
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-118, MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
-MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
+MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-118, MK-NW-O-002
 MK-XS-I-009 transaction date — read by MK-NW-O-002
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109, MK-ST-F-013
@@ -1800,7 +1813,7 @@
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-030
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-NW-F-027
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-109, MK-ST-F-027
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-109
 MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -2067,6 +2080,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-003
 MK-XS-I-009 transaction date — read by MK-NW-O-006, MK-PF-F-028
 MK-XS-I-024 logged expenses — read by MK-NW-O-006, MK-PF-F-028
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-O-006
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-PF-F-031
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-031
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-PF-F-002, MK-PF-F-003, MK-PF-F-031
@@ -2294,6 +2308,10 @@
 MK-NW-F-108 taxWordsOf
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2681,6 +2699,10 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
@@ -2796,6 +2818,7 @@
 MK-XS-I-004 holding quantity (shares) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
+MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
@@ -2836,7 +2859,7 @@
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-109
 MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
@@ -3181,6 +3204,10 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -3744,6 +3771,10 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -3829,7 +3860,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4057,7 @@
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-PF-F-009, MK-PF-F-034, MK-ST-F-027, MK-ST-F-028, MK-ST-F-073, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-NW-F-027, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
@@ -4058,8 +4089,9 @@
 MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-083, MK-CF-F-165, MK-CF-F-172
 MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-084, MK-CF-F-088, MK-CF-F-092, MK-CF-F-165, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-005, MK-CF-F-067, MK-CF-F-068, MK-CF-F-109, MK-CF-F-150, MK-CF-F-151, MK
-MK-XS-I-024 logged expenses — read by MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002
+MK-XS-I-024 logged expenses — read by MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002
+MK-XS-I-024 logged expenses — read by MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002, MK-NW-F-115
 MK-XS-I-026 big costs (amount and year) — read by MK-PL-F-065, MK-PL-F-067
 MK-XS-I-026 big costs (amount and year) — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-027 goals (target, saved, date) — read by MK-CF-F-204, MK-HM-F-006, MK-PL-F-012, MK-PL-F-013, MK-XS-F-174, MK-XS-F-175
@@ -4077,9 +4109,7 @@
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-036
 MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062
-MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-027
-MK-XS-I-035 annuity income — read by MK-CF-F-072, MK-CF-F-075
-MK-XS-I-035 annuity income — read by MK-C</t>
+MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4361,6 +4391,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4393,7 +4427,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -4828,6 +4862,10 @@
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5011,8 +5049,19 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-132 map
+          <t>MK-CF-F-021 defaultPaymentType
+MK-CF-F-022 paymentShape
+MK-CF-F-023 requiredPayment
+MK-CF-F-132 map
+MK-CF-F-148 inMonth
+MK-CF-F-149 recurringDebtPayments
+MK-CF-F-150 debtPaymentsCountedAsExpenses
+MK-CF-F-151 actualSpending
+MK-CF-F-152 isRadarItem
+MK-CF-F-153 radar
 MK-CF-F-155 cash
+MK-CF-F-191 ym
+MK-CF-O-002 expenses
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
 MK-NW-F-030 earmarkDefault
@@ -5020,6 +5069,10 @@
 MK-NW-F-032 earmarkedAmount
 MK-NW-F-035 blendedVolatility
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-008 rmdSchedule
@@ -5035,6 +5088,7 @@
 MK-ST-F-048 currencySymbol
 MK-ST-F-049 formatMoney
 MK-ST-F-051 moneyCompact
+MK-ST-F-052 toNum
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
 MK-XS-F-064 currentIdToken
@@ -5047,7 +5101,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>none — every figure reached through inner parts</t>
+          <t>MK-CF-O-002 expenses</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -5059,7 +5113,9 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-F-003 — Turns a monthly figure into a year by multiplying by twelve.
+          <t>MK-CF-F-023 — If monthly payment is missing it uses 0.
+MK-CF-F-150 — Uses a built-in s h o w f i r s t of 5.
+MK-NW-F-003 — Turns a monthly figure into a year by multiplying by twelve.
 MK-NW-F-003 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-NW-F-031 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-NW-F-032 — Caps percent at 100.
@@ -5226,6 +5282,10 @@
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5502,6 +5562,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -5548,7 +5612,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -5703,7 +5767,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-ST-F-027
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-PL-F-001
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
@@ -5734,7 +5798,7 @@
 MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-083, MK-CF-F-165, MK-CF-F-172
 MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-084, MK-CF-F-088, MK-CF-F-092, MK-CF-F-165, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-005, MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK
-MK-XS-I-024 logged expenses — read by MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002
+MK-XS-I-024 logged expenses — read by MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002, MK
 MK-XS-I-026 big costs (amount and year) — read by MK-PL-F-065, MK-PL-F-067
 MK-XS-I-027 goals (target, saved, date) — read by MK-PL-F-012
 MK-XS-I-027 goals (target, saved, date) — read by MK-PL-F-018, MK-PL-F-019, MK-PL-F-020, MK-PL-F-023
@@ -5770,7 +5834,7 @@
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-050 the share of an account earmarked for retirement — read by MK-NW-F-032
 MK-XS-I-051 what an account actually returned over the last twelve months — read by MK-NW-F-004
-MK-XS-I-052 the day of the month a debt </t>
+MK-XS-I-052 the day of the month a d</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6391,6 +6455,10 @@
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6978,6 +7046,10 @@
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7491,6 +7563,10 @@
 MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -7913,6 +7989,10 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8771,6 +8851,10 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9018,6 +9102,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-031 creditUtilization
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -9105,6 +9190,7 @@
 MK-CF-F-192 inflowLabel
 MK-CF-F-193 inflowSourceWord
 MK-CF-F-198 payrollTaxWithheld
+MK-CF-F-200 LINE
 MK-CF-F-201 INCOME
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
@@ -9114,6 +9200,7 @@
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
+MK-CF-O-006 theCreditLine
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-HM-F-005 pctTxt
@@ -9159,6 +9246,11 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-113 altPartsOf
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -9233,6 +9325,7 @@
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
+MK-CF-O-006 theCreditLine
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
 MK-NW-O-001 theBonds
@@ -25580,7 +25673,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25623,7 +25716,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25666,7 +25759,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -27280,7 +27373,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:299 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:301 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -27323,7 +27416,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:413 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:415 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -27366,7 +27459,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:498</t>
+          <t>src/screens/HomeScreen.tsx:500</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -27386,7 +27479,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27409,7 +27502,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:511 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:513 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -27429,7 +27522,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27452,7 +27545,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:512</t>
+          <t>src/screens/HomeScreen.tsx:514</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -27472,7 +27565,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27515,7 +27608,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27558,7 +27651,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27644,7 +27737,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27816,7 +27909,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28633,7 +28726,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28676,7 +28769,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28719,7 +28812,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28762,7 +28855,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29923,7 +30016,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -29966,7 +30059,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30009,7 +30102,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30052,7 +30145,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30138,7 +30231,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30181,7 +30274,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-07</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -15790,22 +15790,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15833,22 +15833,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -26920,7 +26920,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27006,7 +27006,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28769,7 +28769,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28855,7 +28855,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30059,7 +30059,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30102,7 +30102,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30145,7 +30145,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -9217,6 +9217,7 @@
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-028 classPortionLabel
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
@@ -9237,6 +9238,7 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
+MK-NW-F-067 plural
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -9309,6 +9311,7 @@
 MK-XS-F-064 currentIdToken
 MK-XS-F-083 fetchPriceSeries
 MK-XS-F-112 relayUrl
+MK-XS-F-120 nameOf
 MK-XS-F-121 isYm
 MK-XS-F-122 n
 MK-XS-F-147 call
@@ -25501,7 +25504,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25673,7 +25676,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25716,7 +25719,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25845,7 +25848,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26920,7 +26923,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27006,7 +27009,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27049,7 +27052,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27264,7 +27267,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27565,7 +27568,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27737,7 +27740,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27909,7 +27912,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28726,7 +28729,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28769,7 +28772,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28812,7 +28815,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28855,7 +28858,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28898,7 +28901,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25590,7 +25590,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -15836,7 +15836,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25676,7 +25676,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="45" customHeight="1">
+    <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27376,7 +27376,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:301 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:304 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -27419,7 +27419,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:415 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:418 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:500</t>
+          <t>src/screens/HomeScreen.tsx:503</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:513 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:516 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -27525,7 +27525,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:514</t>
+          <t>src/screens/HomeScreen.tsx:517</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28901,7 +28901,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1134,6 +1134,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-039 buildAssetsState
@@ -1224,7 +1225,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1272,7 +1273,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
@@ -1431,7 +1431,7 @@
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
@@ -1737,6 +1737,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-118 itemizeMissingCount
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2385,8 +2386,8 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-011 bond face value — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-112, MK-NW-O-001
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-064
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069
 MK-XS-I-028 assumed return — read by MK-NW-O-001
@@ -2394,8 +2395,7 @@
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -2822,7 +2822,7 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
@@ -2864,7 +2864,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3335,7 +3335,7 @@
 MK-XS-I-009 transaction date — read by MK-NW-O-008
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -3369,7 +3369,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3738,6 +3738,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -3860,7 +3861,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -3911,7 +3912,6 @@
 MK-HM-F-004 milestoneCrossed
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
-MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
@@ -4063,7 +4063,7 @@
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
@@ -4612,7 +4612,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010, MK-XS-F-004
@@ -5776,7 +5776,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-034
@@ -6079,6 +6079,7 @@
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-066 sumWhere
 MK-NW-F-109 holdingClassOf
@@ -6427,6 +6428,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -6601,7 +6603,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -6644,7 +6646,7 @@
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -6702,7 +6704,7 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 50 more, on the functions tab</t>
+… and 47 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7021,6 +7023,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -7192,7 +7195,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -7226,7 +7229,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 NONE — no function in this chain reads a stored input the sweep knows
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -7276,8 +7279,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 50 more, on the functions tab
-… and 51 more, on the functions tab</t>
+… and 47 more, on the functions tab
+… and 48 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7662,7 +7665,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -7694,7 +7697,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-019, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -7951,6 +7954,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -8549,7 +8553,7 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-064, MK-NW-F-072, MK-NW-F-078, MK-NW-F-112, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -8581,7 +8585,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -8812,6 +8816,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -9216,6 +9221,7 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
+MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-028 classPortionLabel
 MK-NW-F-029 assetAllocation
@@ -11017,7 +11023,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>(down about | $420</t>
+          <t>(down about | $380</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -11490,7 +11496,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>– | $10,350</t>
+          <t>– | $10,310</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -25504,7 +25510,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25590,7 +25596,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25676,7 +25682,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25719,7 +25725,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25762,7 +25768,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25772,7 +25778,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25805,7 +25811,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25848,7 +25854,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26923,7 +26929,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27009,7 +27015,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27052,7 +27058,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27267,7 +27273,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27568,7 +27574,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27611,7 +27617,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27654,7 +27660,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27697,7 +27703,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27740,7 +27746,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27912,7 +27918,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28729,7 +28735,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28772,7 +28778,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28815,7 +28821,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28858,7 +28864,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28901,7 +28907,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25510,7 +25510,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="45" customHeight="1">
+    <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27058,7 +27058,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27617,7 +27617,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27660,7 +27660,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28778,7 +28778,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28821,7 +28821,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30025,7 +30025,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30154,7 +30154,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-08</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-09</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -1159,6 +1159,7 @@
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -1225,7 +1226,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1738,6 +1739,7 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-118 itemizeMissingCount
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2015,6 +2017,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -2199,6 +2202,7 @@
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -2211,7 +2215,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -2385,17 +2389,18 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-011 bond face value — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
+MK-XS-I-011 bond face value — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-119
 MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069
+MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069, MK-NW-F-119
 MK-XS-I-028 assumed return — read by MK-NW-O-001
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069
+MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -2578,6 +2583,7 @@
 MK-NW-F-078 ONE
 MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -2600,7 +2606,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -2864,7 +2870,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3047,6 +3053,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PL-F-012 waterfall
@@ -3086,7 +3093,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3369,7 +3376,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -3776,6 +3783,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -3861,7 +3869,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4395,6 +4403,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4427,7 +4436,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -5566,6 +5575,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -5612,7 +5622,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -6318,6 +6328,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6342,7 +6353,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -6646,7 +6657,7 @@
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -6704,7 +6715,7 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 47 more, on the functions tab</t>
+… and 50 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6905,6 +6916,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6927,7 +6939,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -7229,7 +7241,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 NONE — no function in this chain reads a stored input the sweep knows
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -7279,8 +7291,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 47 more, on the functions tab
-… and 48 more, on the functions tab</t>
+… and 50 more, on the functions tab
+… and 51 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7461,6 +7473,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7483,7 +7496,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -7697,7 +7710,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-019, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -7997,6 +8010,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8506,6 +8520,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -8528,7 +8543,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -8585,7 +8600,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
-MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-059, MK-NW-F-061, MK-NW-F-070, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
       </c>
@@ -8860,6 +8875,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9259,6 +9275,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -11023,7 +11040,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>(down about | $380</t>
+          <t>(down about | $390</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -11496,7 +11513,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>– | $10,310</t>
+          <t>– | $10,320</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -25510,7 +25527,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25596,7 +25613,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25682,7 +25699,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25725,7 +25742,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25768,7 +25785,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25778,7 +25795,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25811,7 +25828,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -27488,7 +27505,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27531,7 +27548,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27574,7 +27591,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27617,7 +27634,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27660,7 +27677,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27703,7 +27720,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27746,7 +27763,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27918,7 +27935,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28735,7 +28752,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28778,7 +28795,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28821,7 +28838,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28864,7 +28881,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28907,7 +28924,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30025,7 +30042,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30068,7 +30085,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30111,7 +30128,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30154,7 +30171,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30240,7 +30257,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30283,7 +30300,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25613,7 +25613,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25785,7 +25785,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26946,7 +26946,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27032,7 +27032,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27075,7 +27075,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28752,7 +28752,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28795,7 +28795,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -15816,22 +15816,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15859,22 +15859,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28795,7 +28795,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30085,7 +30085,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30128,7 +30128,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30171,7 +30171,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25527,7 +25527,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25795,7 +25795,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="45" customHeight="1">
+    <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25828,7 +25828,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27720,7 +27720,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28752,7 +28752,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28795,7 +28795,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30257,7 +30257,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1127,7 +1127,6 @@
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -1160,6 +1159,13 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -1226,7 +1232,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1272,6 +1278,7 @@
 MK-NW-F-002 alternativesSummary
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
+MK-NW-F-009 maturityClass
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-024 accountLastFour
@@ -1418,7 +1425,7 @@
           <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-111, MK-CF-F-116, MK-CF-F-138, MK-CF-F-139, MK-CF-F-201, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-201, MK-ST-F-027
@@ -1430,11 +1437,10 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-123, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
@@ -1474,9 +1480,11 @@
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-179, MK-CF-F-181, MK-CF-F-206
 MK-XS-I-044 the person’s own plan overrides — read by MK-XS-F-174, MK-XS-F-175
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-054, MK-NW-F-109, MK-NW-O-003, MK-ST-F-027, MK-ST-F-028, MK
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-NW-O-003, MK-ST-F-027, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
-MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-</t>
+MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
+MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
+MK-XS-I-055 the wra</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1607,7 +1615,13 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-109 holdingClassOf
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-O-002 theAccount
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
@@ -1622,7 +1636,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -1740,6 +1754,9 @@
 MK-NW-F-117 propertyUseMap
 MK-NW-F-118 itemizeMissingCount
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1804,20 +1821,20 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-027, MK-NW-O-002, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-NW-F-120
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-118, MK-NW-F-027, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-118, MK-NW-O-002
 MK-XS-I-009 transaction date — read by MK-NW-O-002
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109, MK-ST-F-013
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-123, MK-ST-F-013
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
 MK-XS-I-024 logged expenses — read by MK-NW-O-002
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-030
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-NW-F-027
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-109, MK-ST-F-027
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-109
-MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-ST-F-027
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-NW-F-120
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-053, MK-NW-F-054, MK-NW-F-109
 No function on record — nothing to read from
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -2018,6 +2035,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -2203,6 +2224,10 @@
 MK-NW-F-072 rowOf
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -2215,7 +2240,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -2301,6 +2326,8 @@
 MK-NW-F-037 blendedReturn
 MK-NW-F-045 sourceWording
 MK-NW-F-046 historyCoverage
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
 MK-NW-F-077 ALL
@@ -2317,6 +2344,9 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2383,7 +2413,7 @@
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
@@ -2392,13 +2422,13 @@
 MK-XS-I-011 bond face value — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-119
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069, MK-NW-F-119
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069, MK-NW-F-119, MK-NW-F-124
 MK-XS-I-028 assumed return — read by MK-NW-O-001
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -2568,6 +2598,8 @@
 MK-NW-F-016 cashTotal
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-055 isBond
 MK-NW-F-056 bondInfo
 MK-NW-F-057 annualCoupon
@@ -2584,6 +2616,13 @@
 MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -2606,7 +2645,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -2695,8 +2734,6 @@
 MK-NW-F-046 historyCoverage
 MK-NW-F-047 uberGroupOf
 MK-NW-F-048 uberGroupRows
-MK-NW-F-053 correctClassOf
-MK-NW-F-054 reclassifyAccounts
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
@@ -2817,8 +2854,8 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-016, MK-NW-F-027, MK-NW-F-029, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-027, MK-NW-F-054, MK-NW-F-120
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-NW-F-027, MK-ST-F-027
@@ -2826,11 +2863,11 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-027, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-109
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-123
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
@@ -2860,13 +2897,13 @@
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-109, MK-ST-F-027
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-ST-F-027
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-109
-MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-109
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-NW-F-120
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-053, MK-NW-F-054, MK-NW-F-109
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-009, MK-NW-F-078
@@ -3054,6 +3091,10 @@
 MK-NW-F-105 whyNoReturn
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PL-F-012 waterfall
@@ -3093,7 +3134,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3173,7 +3214,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-005 accountAllowsTicker
 MK-NW-F-007 assetKind
-MK-NW-F-009 maturityClass
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -3215,6 +3255,9 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -3331,7 +3374,7 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-NW-O-008, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028, MK-ST-F-082
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
@@ -3343,7 +3386,7 @@
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -3372,7 +3415,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
@@ -3738,7 +3781,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -3784,6 +3826,13 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -3869,7 +3918,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -3918,6 +3967,7 @@
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
+MK-NW-F-009 maturityClass
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-024 accountLastFour
@@ -4050,14 +4100,13 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
+          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-ST-F-027
-MK-XS-I-001 account balance — read by MK-NW-F-032, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-PL-F-001
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-PL-F-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-NW-F-120, MK-PL-F-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-PL-F-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-CF-F-111, MK-CF-F-116, MK-CF-F-138, MK-CF-F-139, MK-CF-F-201, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
@@ -4069,11 +4118,11 @@
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-054, MK-NW-F-109, MK-XS-F-174, MK-XS-F-175
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-123, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
 MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
@@ -4117,7 +4166,8 @@
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-036
 MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062
-MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-0</t>
+MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-027
+MK-XS-I-035 annuity income — read </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4404,6 +4454,10 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4436,7 +4490,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -4488,7 +4542,6 @@
 MK-CF-O-020 theBudgetCounted
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
-MK-NW-F-009 maturityClass
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
@@ -4504,6 +4557,9 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -4615,14 +4671,14 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010, MK-XS-F-004
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -4679,9 +4735,9 @@
 MK-XS-I-053 the month a debt is first paid — read by MK-XS-F-004
 MK-XS-I-054 the date a debt is due to be paid off in full — read by MK-XS-F-004
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-076, MK-CF-F-107, MK-CF-F-156, MK-NW-F-011, MK
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-075
-MK-XS-I-055 the wrapp</t>
+MK-X</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4857,7 +4913,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
@@ -4875,6 +4930,10 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5082,6 +5141,7 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-120 classEvidenceOf
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-008 rmdSchedule
@@ -5277,7 +5337,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
@@ -5295,6 +5354,10 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5576,6 +5639,10 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -5622,7 +5689,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -5693,12 +5760,14 @@
 MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
-MK-NW-F-009 maturityClass
 MK-NW-F-040 assetsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5779,16 +5848,16 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-PL-F-001
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-NW-F-120, MK-PL-F-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-034
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-034
@@ -5844,7 +5913,7 @@
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-050 the share of an account earmarked for retirement — read by MK-NW-F-032
 MK-XS-I-051 what an account actually returned over the last twelve months — read by MK-NW-F-004
-MK-XS-I-052 the day of the month a d</t>
+MK-XS-I-05</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6091,8 +6160,14 @@
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
 MK-NW-F-027 accountClassBreakdown
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-066 sumWhere
 MK-NW-F-109 holdingClassOf
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PL-F-034 lifeInsuranceNeed
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -6329,6 +6404,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6353,7 +6432,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -6433,7 +6512,6 @@
 MK-HM-F-004 milestoneCrossed
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
-MK-NW-F-009 maturityClass
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -6472,6 +6550,9 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -6608,14 +6689,14 @@
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -6651,7 +6732,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092, MK-CF-O-004
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
@@ -6715,7 +6796,7 @@
 The employer’s match is not counted here — it is not taken out of take-home (MK-CF-D-003).
 The household figure is the sum of the earners’, so a total and its parts cannot disagree (rule 2).
 When it is ours it assumes the standard deduction and is federal only (MK-CF-D-002).
-… and 50 more, on the functions tab</t>
+… and 51 more, on the functions tab</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6917,6 +6998,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6939,7 +7024,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -7029,7 +7114,6 @@
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
-MK-NW-F-009 maturityClass
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
@@ -7065,6 +7149,9 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7201,14 +7288,14 @@
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -7237,7 +7324,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-NW-F-078
@@ -7291,8 +7378,8 @@
 Nothing is assumed to have arrived; a source counts only once it is recorded (founder, 2026-08-28).
 One line on This month, and the Expenses tab is its detail — not a second answer to the same question (his correction, 2026-09-28).
 [Founder] 2026-08-27 worked example (his cash-flow screen sheet): Planned — In (take-home) 5,000 · mortgage 2,000 · car 250 · expenses 2,000 · HELOC (from the big-ticket radar) 200 · credit-card payment (entered by hand) 200 → surplus 750. Actual — 5,000 · mortgage paid 2,000 · car paid 0 · expenses entered 500 · expenses imported from the card 1,200 · HELOC 200 · card payment 200 → surplus 1,300. A credit-card PAYMENT is not an expense (the card's imported transactions already are); a HELOC payment is counted as an expense; recurring debt is never a radar item, a card or HELOC payment always is (the rule in MK-CF-O-002).
-… and 50 more, on the functions tab
-… and 51 more, on the functions tab</t>
+… and 51 more, on the functions tab
+… and 52 more, on the functions tab</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7474,6 +7561,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7496,7 +7587,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -7560,7 +7651,6 @@
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
-MK-NW-F-009 maturityClass
 MK-NW-F-016 cashTotal
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
@@ -7583,6 +7673,9 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -7672,14 +7765,14 @@
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-019, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -7706,7 +7799,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-019, MK-NW-F-078
@@ -7960,7 +8053,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -8011,6 +8103,13 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8312,6 +8411,7 @@
 MK-CF-O-007 theTaxOrganizer
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
+MK-NW-F-120 classEvidenceOf
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
 MK-ST-F-047 activeCurrency
@@ -8521,6 +8621,10 @@
 MK-NW-F-078 ONE
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -8543,7 +8647,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -8562,14 +8666,14 @@
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-031, MK-CF-O-006, MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -8596,7 +8700,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
@@ -8824,7 +8928,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -8876,6 +8979,13 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9230,7 +9340,6 @@
 MK-NW-F-002 alternativesSummary
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
-MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
@@ -9276,6 +9385,13 @@
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
+MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -25527,7 +25643,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25613,7 +25729,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25699,7 +25815,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25742,7 +25858,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25871,7 +25987,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -25914,7 +26030,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26946,7 +27062,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27032,7 +27148,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27075,7 +27191,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27290,7 +27406,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27591,7 +27707,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27634,7 +27750,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27677,7 +27793,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27720,7 +27836,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27763,7 +27879,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -27935,7 +28051,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28752,7 +28868,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28795,7 +28911,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28838,7 +28954,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28881,7 +28997,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -28924,7 +29040,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29162,7 +29278,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:491</t>
+          <t>src/screens/RetirementCockpit.tsx:495</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
@@ -29205,7 +29321,7 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:520</t>
+          <t>src/screens/RetirementCockpit.tsx:524</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -29248,7 +29364,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:555</t>
+          <t>src/screens/RetirementCockpit.tsx:559</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -29291,7 +29407,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:630</t>
+          <t>src/screens/RetirementCockpit.tsx:634</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -29334,7 +29450,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:639</t>
+          <t>src/screens/RetirementCockpit.tsx:643</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -29377,7 +29493,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:648</t>
+          <t>src/screens/RetirementCockpit.tsx:652</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
@@ -29420,12 +29536,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:672</t>
+          <t>src/screens/RetirementCockpit.tsx:676</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
+          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -29463,12 +29579,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:673</t>
+          <t>src/screens/RetirementCockpit.tsx:677</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a), 'M')}{simple ? '' : ` · ${info.source} · ${info.period}${info.estimate ? ' · est.' : ''}</t>
+          <t xml:space="preserve">: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source} · ${info.period}${info.estimate ? </t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -29506,7 +29622,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:734</t>
+          <t>src/screens/RetirementCockpit.tsx:738</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -29549,7 +29665,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:751</t>
+          <t>src/screens/RetirementCockpit.tsx:755</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
@@ -29592,7 +29708,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:773</t>
+          <t>src/screens/RetirementCockpit.tsx:777</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -29635,7 +29751,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:775</t>
+          <t>src/screens/RetirementCockpit.tsx:779</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -29678,7 +29794,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:790</t>
+          <t>src/screens/RetirementCockpit.tsx:794</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -29721,7 +29837,7 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:954</t>
+          <t>src/screens/RetirementCockpit.tsx:960</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
@@ -29764,12 +29880,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:959</t>
+          <t>src/screens/RetirementCockpit.tsx:965</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a), 'M')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -30257,7 +30373,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30300,7 +30416,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-09</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-10</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -15932,22 +15932,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -15975,22 +15975,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -25944,7 +25944,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28997,7 +28997,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1299,6 +1299,7 @@
 MK-NW-F-048 uberGroupRows
 MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
@@ -1312,6 +1313,10 @@
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1736,6 +1741,7 @@
 MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-073 itemising
 MK-NW-F-077 ALL
@@ -1757,6 +1763,10 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2330,6 +2340,7 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-084 categoryEarnings
@@ -2347,6 +2358,10 @@
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3074,6 +3089,11 @@
 MK-CF-O-010 theMonth
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
+MK-NW-F-012 taxTreatmentOf
+MK-NW-F-023 wrapperWord
+MK-NW-F-024 accountLastFour
+MK-NW-F-025 accountDisplayName
+MK-NW-F-026 accountDisplayNames
 MK-NW-F-055 isBond
 MK-NW-F-056 bondInfo
 MK-NW-F-057 annualCoupon
@@ -3084,9 +3104,11 @@
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-091 pricedGainOf
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-112 yearlyInterest
@@ -3095,8 +3117,26 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
+MK-PF-F-001 totalShares
+MK-PF-F-002 costBasis
+MK-PF-F-004 marketValue
+MK-PF-F-005 unrealizedGain
+MK-PF-F-007 totalROI
+MK-PF-F-008 startDateFor
+MK-PF-F-009 latestClose
+MK-PF-F-010 periodReturn
+MK-PF-F-011 periodReturnSince
+MK-PF-F-012 earliestPurchaseDate
+MK-PF-F-013 benchmarkTicker
+MK-PF-F-014 buildPerformance
+MK-PF-F-029 closeAsOf
+MK-PF-F-031 contractMultiplier
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
@@ -3134,7 +3174,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3214,16 +3254,11 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-005 accountAllowsTicker
 MK-NW-F-007 assetKind
-MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
-MK-NW-F-023 wrapperWord
-MK-NW-F-024 accountLastFour
-MK-NW-F-025 accountDisplayName
-MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -3245,7 +3280,6 @@
 MK-NW-F-068 prettyDay
 MK-NW-F-084 categoryEarnings
 MK-NW-F-090 windowStartKey
-MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
@@ -3259,21 +3293,7 @@
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
 MK-NW-O-003 theNetWorth
-MK-PF-F-001 totalShares
-MK-PF-F-002 costBasis
-MK-PF-F-004 marketValue
-MK-PF-F-005 unrealizedGain
-MK-PF-F-007 totalROI
-MK-PF-F-008 startDateFor
-MK-PF-F-009 latestClose
-MK-PF-F-010 periodReturn
-MK-PF-F-011 periodReturnSince
-MK-PF-F-012 earliestPurchaseDate
-MK-PF-F-013 benchmarkTicker
-MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-029 closeAsOf
-MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-011 buildGoalsState
@@ -3374,19 +3394,19 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-NW-O-008, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
-MK-XS-I-003 institution name — read by MK-NW-F-056, MK-NW-F-072, MK-NW-O-001
-MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-ST-F-027, MK-ST-F-028, MK-ST-F-082
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-012, MK-NW-F-025, MK-NW-F-120, MK-NW-O-001
+MK-XS-I-003 institution name — read by MK-NW-F-025, MK-NW-F-026, MK-NW-F-056, MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
+MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-NW-F-091, MK-NW-F-128, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
+MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-009, MK-PF-F-010, MK-PF-F-011, MK-PF-F-014, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
-MK-XS-I-005 holding price — read by MK-ST-F-027, MK-ST-F-028
+MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK-PF-F-014, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027, MK-ST-F-028
 MK-XS-I-009 transaction date — read by MK-NW-O-008
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
-MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
+MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-071, MK
+MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-071, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
@@ -3415,9 +3435,10 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-012, MK-NW-F-023, MK
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
+MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -3981,6 +4002,7 @@
 MK-NW-F-048 uberGroupRows
 MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
@@ -3988,6 +4010,10 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-107 propertyUses
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -6512,12 +6538,16 @@
 MK-HM-F-004 milestoneCrossed
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
+MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
+MK-NW-F-024 accountLastFour
+MK-NW-F-025 accountDisplayName
+MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -6537,6 +6567,7 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
@@ -6553,6 +6584,10 @@
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7114,12 +7149,16 @@
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
+MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
+MK-NW-F-024 accountLastFour
+MK-NW-F-025 accountDisplayName
+MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -7136,6 +7175,7 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-092 investmentAccountIdsOf
@@ -7152,6 +7192,10 @@
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -8054,12 +8098,16 @@
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
+MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
+MK-NW-F-024 accountLastFour
+MK-NW-F-025 accountDisplayName
+MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -8086,6 +8134,7 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
@@ -8110,6 +8159,10 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8929,12 +8982,16 @@
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-011 assetClassOf
+MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
 MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
+MK-NW-F-024 accountLastFour
+MK-NW-F-025 accountDisplayName
+MK-NW-F-026 accountDisplayNames
 MK-NW-F-027 accountClassBreakdown
 MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
@@ -8961,6 +9018,7 @@
 MK-NW-F-066 sumWhere
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
@@ -8986,6 +9044,10 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-127 gainOfRow
+MK-NW-F-128 heldValueOf
+MK-NW-F-129 gainRowName
+MK-NW-F-130 cannotWorkBackSentence
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -25643,7 +25705,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25729,7 +25791,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25987,7 +26049,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26030,7 +26092,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27062,7 +27124,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27148,7 +27210,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27191,7 +27253,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27406,7 +27468,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27750,7 +27812,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27793,7 +27855,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27879,7 +27941,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28868,7 +28930,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28911,7 +28973,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -28954,7 +29016,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -28997,7 +29059,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1212,6 +1212,7 @@
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -1232,7 +1233,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1808,6 +1809,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-085 rentFigure
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
@@ -2084,6 +2086,7 @@
 MK-ST-F-065 isoLocalDate
 MK-ST-F-075 agoLabel
 MK-ST-F-077 isStale
+MK-ST-F-085 rentFigure
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
 MK-XS-F-027 takeHomeMonthly
@@ -2405,6 +2408,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-085 rentFigure
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
@@ -2651,6 +2655,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
@@ -2660,7 +2665,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -3164,6 +3169,7 @@
 MK-ST-F-081 timeWeightedReturn
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
+MK-ST-F-085 rentFigure
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
@@ -3174,7 +3180,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3919,6 +3925,7 @@
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -3939,7 +3946,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4506,6 +4513,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-004 buildDatedGrid
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
@@ -4516,7 +4524,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -5017,6 +5025,7 @@
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -5186,6 +5195,7 @@
 MK-ST-F-052 toNum
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-064 currentIdToken
 MK-XS-F-084 requestNotificationPermission
 MK-XS-F-087 scheduleRmdReminder
@@ -5445,6 +5455,7 @@
 MK-ST-F-073 rebuildDays
 MK-ST-F-079 dailyWindowStart
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
@@ -5704,6 +5715,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-017 currentAge
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
@@ -5715,7 +5727,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -6201,6 +6213,7 @@
 MK-ST-F-039 on
 MK-ST-F-052 toNum
 MK-ST-F-056 has
+MK-ST-F-085 rentFigure
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
 MK-XS-F-122 n
@@ -6449,6 +6462,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
@@ -6458,7 +6472,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -7050,6 +7064,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
@@ -7059,7 +7074,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -7622,6 +7637,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
@@ -7631,7 +7647,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -8257,6 +8273,7 @@
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
@@ -8449,11 +8466,12 @@
 MK-ST-F-039 on
 MK-ST-F-052 toNum
 MK-ST-F-056 has
+MK-ST-F-085 rentFigure
 MK-XS-F-122 n</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -8691,6 +8709,7 @@
 MK-ST-F-053 money
 MK-ST-F-056 has
 MK-ST-F-065 isoLocalDate
+MK-ST-F-085 rentFigure
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-112 relayUrl
@@ -8700,7 +8719,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -9150,6 +9169,7 @@
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
@@ -9502,6 +9522,7 @@
 MK-ST-F-082 movementsOf
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
+MK-ST-F-085 rentFigure
 MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-008 normalizeSnapshot
@@ -16037,7 +16058,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -25791,7 +25812,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25877,7 +25898,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25920,7 +25941,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -27769,7 +27790,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27941,7 +27962,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28113,7 +28134,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28930,7 +28951,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -28973,7 +28994,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -29016,7 +29037,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -29059,7 +29080,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29102,7 +29123,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30220,7 +30241,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30263,7 +30284,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30306,7 +30327,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30349,7 +30370,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1166,6 +1166,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -1233,7 +1234,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1768,6 +1769,7 @@
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
 MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2051,6 +2053,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -2241,6 +2244,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -2253,7 +2257,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2450,7 @@
 MK-XS-I-028 assumed return — read by MK-NW-O-001
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119
+MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119, MK-NW-F-131
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
@@ -2457,7 +2461,8 @@
         <is>
           <t>An approximation, and labelled an estimate on screen.
 An estimate, and it wears the estimate label.
-FOUNDER 2026-09-27: a CD gets no estimate. It is not traded, so its value does not move with rates; the screen says that instead. KEEP — the app does not ask whether a CD is a bank one or a brokered one.
+DEC-3837, 2026-10-10: a CD bought through a broker trades, so it gets the estimate like a bond. A CD whose answer was never given is read as bought from the bank.
+FOUNDER 2026-09-27: a CD bought from the bank gets no estimate. It is not traded, so its value does not move with rates; the screen says that instead.
 NONE RECORDED — the declaration names none.</t>
         </is>
       </c>
@@ -2642,6 +2647,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -2665,7 +2671,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -3126,6 +3132,7 @@
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
 MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3180,7 +3187,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3860,6 +3867,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-PF-F-001 totalShares
@@ -3946,7 +3954,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4491,6 +4499,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-PL-F-050 simulate
@@ -4524,7 +4533,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -5680,6 +5689,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
@@ -5727,7 +5737,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -6447,6 +6457,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -6472,7 +6483,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -7051,6 +7062,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7074,7 +7086,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -7624,6 +7636,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -7647,7 +7660,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -8179,6 +8192,7 @@
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
 MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -8696,6 +8710,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
@@ -8719,7 +8734,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -9067,6 +9082,7 @@
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
 MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9474,6 +9490,7 @@
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-005 theAlternativesOutlook
@@ -10209,7 +10226,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8 rows on the master · 21 places in the code print a dollar figure · 6 of them have no row · 11 rows not found on screen</t>
+          <t>8 rows on the master · 21 places in the code print a dollar figure · 6 of them have no row · 12 rows not found on screen</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10419,7 +10436,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2 rows on the master · 8 places in the code print a dollar figure · 3 of them have no row · 5 rows not found on screen</t>
+          <t>2 rows on the master · 8 places in the code print a dollar figure · 3 of them have no row · 6 rows not found on screen</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11014,7 +11031,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3 rows on the master · 6 places in the code print a dollar figure · 1 of them have no row · 1 rows not found on screen</t>
+          <t>3 rows on the master · 6 places in the code print a dollar figure · 1 of them have no row · 2 rows not found on screen</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -16015,22 +16032,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16058,22 +16075,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -22497,7 +22514,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /jobsafety</t>
+          <t>/analytics · /jobsafety · /stress-test · /insights · /home</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr"/>
@@ -25812,7 +25829,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25898,7 +25915,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25941,7 +25958,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -25994,7 +26011,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="45" customHeight="1">
+    <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26027,7 +26044,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26070,7 +26087,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26113,7 +26130,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27145,7 +27162,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27231,7 +27248,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27274,7 +27291,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27489,7 +27506,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27684,7 +27701,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:503</t>
+          <t>src/screens/HomeScreen.tsx:505</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -27704,7 +27721,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27727,7 +27744,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:516 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:518 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -27747,7 +27764,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27770,7 +27787,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:517</t>
+          <t>src/screens/HomeScreen.tsx:519</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -27790,7 +27807,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27962,7 +27979,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28134,7 +28151,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28501,7 +28518,7 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:115</t>
+          <t>src/screens/JobSafetyScreen.tsx:117</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -28544,7 +28561,7 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:117</t>
+          <t>src/screens/JobSafetyScreen.tsx:119</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -28587,7 +28604,7 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:120</t>
+          <t>src/screens/JobSafetyScreen.tsx:132</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
@@ -28630,7 +28647,7 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:163</t>
+          <t>src/screens/JobSafetyScreen.tsx:175</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -28994,7 +29011,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -29037,7 +29054,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -29080,7 +29097,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29123,7 +29140,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30241,7 +30258,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30284,7 +30301,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30327,7 +30344,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30370,7 +30387,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30393,7 +30410,7 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:72 (+1 spoken/visible twin)</t>
+          <t>src/screens/StressTestScreen.tsx:74 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
@@ -30436,7 +30453,7 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:76</t>
+          <t>src/screens/StressTestScreen.tsx:78</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
@@ -30456,7 +30473,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30479,7 +30496,7 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:93</t>
+          <t>src/screens/StressTestScreen.tsx:104</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
@@ -30499,7 +30516,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30522,7 +30539,7 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:97</t>
+          <t>src/screens/StressTestScreen.tsx:108</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
@@ -30565,7 +30582,7 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:107</t>
+          <t>src/screens/StressTestScreen.tsx:118</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -25829,7 +25829,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26011,7 +26011,7 @@
       </c>
       <c r="I415" s="2" t="n"/>
     </row>
-    <row r="416" ht="60" customHeight="1">
+    <row r="416" ht="45" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27721,7 +27721,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29140,7 +29140,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-10</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-11</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -16032,22 +16032,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16075,22 +16075,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -25829,7 +25829,7 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -25915,7 +25915,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -25958,7 +25958,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -29011,7 +29011,7 @@
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -29054,7 +29054,7 @@
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -29140,7 +29140,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
@@ -30301,7 +30301,7 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30387,7 +30387,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1024,6 +1024,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -1179,6 +1180,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-074 median
@@ -1237,7 +1239,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1335,6 +1337,15 @@
 MK-PF-F-015 topHoldingConcentration
 MK-PF-F-020 portfolioBenchReturn
 MK-PF-F-029 closeAsOf
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -1447,13 +1458,13 @@
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-NW-F-027, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
+MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072, MK-ST-F-082
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-123, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
+MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
@@ -1496,7 +1507,7 @@
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-I-055 the wrapper an accou</t>
+MK-XS-</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1795,6 +1806,15 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
+MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
 MK-PL-F-012 waterfall
 MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-031 valueOn
@@ -1967,11 +1987,13 @@
 MK-PF-F-006 capGains
 MK-PF-F-028 realizedFromLedger
 MK-PF-F-031 contractMultiplier
+MK-PF-F-035 unknownFigure
+MK-ST-F-027 accountId
 MK-XS-F-122 n</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -2079,12 +2101,18 @@
 MK-PF-F-029 closeAsOf
 MK-PF-F-032 quantityUnit
 MK-PF-F-033 quantityWithUnit
+MK-PF-F-034 closeOnOrBefore
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
 MK-PL-F-012 waterfall
 MK-ST-F-002 monthWords
 MK-ST-F-003 dayWords
 MK-ST-F-004 coverageFor
 MK-ST-F-010 nameEvidence
-MK-ST-F-027 accountId
 MK-ST-F-030 record
 MK-ST-F-034 firstDate
 MK-ST-F-036 reconcile
@@ -2126,16 +2154,18 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-004 holding quantity (shares) — read by MK-NW-O-006, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-028
+          <t>MK-XS-I-001 account balance — read by MK-ST-F-027
+MK-XS-I-004 holding quantity (shares) — read by MK-NW-O-006, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-028, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-PF-F-001, MK-PF-F-002, MK-PF-F-003
-MK-XS-I-005 holding price — read by MK-NW-O-006
-MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-006
+MK-XS-I-005 holding price — read by MK-NW-O-006, MK-ST-F-027
+MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-006, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-003
 MK-XS-I-009 transaction date — read by MK-NW-O-006, MK-PF-F-028
 MK-XS-I-024 logged expenses — read by MK-NW-O-006, MK-PF-F-028
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-O-006
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-O-006, MK-ST-F-027
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-PF-F-028, MK-PF-F-031
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-PF-F-031
-MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-031
+MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-028, MK-PF-F-031
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-PF-F-002, MK-PF-F-003, MK-PF-F-031
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-NW-O-006
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -2401,6 +2431,15 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
+MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
 MK-PL-F-012 waterfall
 MK-ST-F-013 personalFlowTotals
 MK-ST-F-021 toNumber
@@ -2697,6 +2736,7 @@
           <t>MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-029 monthsToClear
 MK-CF-F-030 paymentToClearBy
 MK-CF-F-035 debtKind
@@ -2799,6 +2839,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-024 oddsLine
@@ -3143,6 +3184,7 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
@@ -3173,6 +3215,15 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
+MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
@@ -3211,7 +3262,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3222,6 +3273,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -3313,7 +3365,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-084 categoryEarnings
-MK-NW-F-090 windowStartKey
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
@@ -3330,7 +3381,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-O-003 theNetWorth
 MK-PF-F-020 portfolioBenchReturn
-MK-PF-F-034 closeOnOrBefore
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-011 buildGoalsState
 MK-PL-F-013 goalsFromOnboarding
@@ -3436,10 +3488,11 @@
 MK-XS-I-003 institution name — read by MK-NW-F-025, MK-NW-F-026, MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-NW-F-091, MK-NW-F-128, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
-MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-009, MK-PF-F-010, MK-PF-F-011, MK-PF-F-014, MK
+MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-009, MK-PF-F-011, MK-PF-F-014, MK-PF-F-029, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK-PF-F-014, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
+MK-XS-I-008 transaction amount — read by MK-ST-F-082
 MK-XS-I-009 transaction date — read by MK-NW-O-008
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
@@ -3469,14 +3522,15 @@
 MK-XS-I-041 the payment the person chose to make on a debt — read by MK-CF-F-023
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027, MK-ST-F-028, MK-ST-F-060
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK-ST-F-060
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-012, MK-NW-F-023, MK
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-PF-F-013
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
-MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
+MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -3497,7 +3551,7 @@
 ONE MEANING OF RETURN (B-97, 2026-09-25): dividends and interest are part of this, so the return beside it counts them too.
 OVER A YEAR IT IS A YEARLY RATE and the screen says so (his ruling, 2026-08-18, restated 2026-09-25).
 The benchmark runs over the SAME DATES as your return — including where your window is cut short at your own purchase date. Comparing your three months against the market's twelve is not a comparison.
-Weighted by what each holding is worth, so the blend answers "the market, matched to my mix" rather than a plain average of indices.
+Weighted by what each holding was worth when the window began, so the blend answers "the market, matched to my mix" rather than a plain average of indices — and a holding that grew does not grow its yardstick's weight (outside review Claude Performance, 2026-10-11, DEC-1669, DEC-3035b).
 Whatever the records cannot explain lands in the change-in-value line rather than being silently dropped.</t>
         </is>
       </c>
@@ -3578,11 +3632,12 @@
           <t>MK-NW-O-007 theLookBack
 MK-PF-F-022 factorOverMonths
 MK-PF-F-023 lookBack
+MK-PF-F-036 monthsBefore
 MK-ST-F-065 isoLocalDate</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -3730,6 +3785,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -3912,6 +3968,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
@@ -3991,7 +4048,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4072,6 +4129,15 @@
 MK-PF-F-014 buildPerformance
 MK-PF-F-020 portfolioBenchReturn
 MK-PF-F-029 closeAsOf
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-002 withdrawalPlan
 MK-PL-F-003 depletionAge
 MK-PL-F-004 withdrawalOrder
@@ -4173,7 +4239,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
+          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
@@ -4191,14 +4257,14 @@
 MK-XS-I-006 price fetched at — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-007 purchase price and date (per lot) — read by MK-CF-F-138, MK-CF-F-139, MK-NW-F-027, MK-PF-F-002, MK-PF-F-013, MK-ST-F-027, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072
+MK-XS-I-008 transaction amount — read by MK-CF-F-109, MK-CF-F-111, MK-ST-F-072, MK-ST-F-082
 MK-XS-I-009 transaction date — read by MK-CF-F-109, MK-CF-F-138, MK-ST-F-071, MK-ST-F-073, MK-XS-F-175
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-CF-F-109, MK-NW-F-123, MK-XS-F-174, MK-XS-F-175
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
-MK-XS-I-014 debt balance — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
+MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
 MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-025, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
@@ -4240,7 +4306,7 @@
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-035, MK-ST-F-036, MK-ST-F-072, MK-ST-F-073, MK
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-036
 MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
-MK-XS-I-034 option positions — contrac</t>
+MK-XS-I-034 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4650,6 +4716,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-002 withdrawalPlan
 MK-PL-F-003 depletionAge
@@ -5036,6 +5103,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-047 colFactor
@@ -5488,6 +5556,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -5915,6 +5984,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -6594,6 +6664,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -6729,6 +6800,16 @@
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
@@ -7200,6 +7281,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -7346,6 +7428,16 @@
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
@@ -7873,6 +7965,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
@@ -8116,6 +8209,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -8336,6 +8430,16 @@
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-011 buildGoalsState
 MK-PL-F-012 waterfall
@@ -9015,6 +9119,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
 MK-CF-F-038 debtsFromOnboarding
@@ -9240,6 +9345,16 @@
 MK-PF-F-029 closeAsOf
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
+MK-PF-F-036 monthsBefore
+MK-PF-F-037 dayBefore
+MK-PF-F-038 periodTotalReturn
+MK-PF-F-039 periodReturnParts
+MK-PF-F-040 returnSincePurchases
+MK-PF-F-041 isoDay
+MK-PF-F-042 windowTotal
+MK-PF-F-043 windowTotalOfRow
+MK-PF-F-044 startValues
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -9469,6 +9584,7 @@
 MK-CF-F-024 totalDebtMonthly
 MK-CF-F-025 minimumDebtService
 MK-CF-F-026 actualDebtPayment
+MK-CF-F-027 totalDebtBalance
 MK-CF-F-031 creditUtilization
 MK-CF-F-036 buildDebtState
 MK-CF-F-037 inferDebtType
@@ -9645,6 +9761,7 @@
 MK-PF-F-013 benchmarkTicker
 MK-PF-F-031 contractMultiplier
 MK-PF-F-034 closeOnOrBefore
+MK-PF-F-035 unknownFigure
 MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-074 median
@@ -26102,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26188,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26231,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26284,7 +26401,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" ht="45" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26317,7 +26434,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26360,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26403,7 +26520,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27994,7 +28111,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28037,7 +28154,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28080,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28123,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28166,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28252,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28424,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29241,7 +29358,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29284,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29327,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29370,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -30746,7 +30863,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30789,7 +30906,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26133,7 +26133,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-11</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-12</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9205</v>
+        <v>9207</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -14749,7 +14749,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>−$# | -$#</t>
+          <t>−$# | −$#</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -26123,7 +26123,7 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>$420, $600, $151,000, $165,000 … (1257 renders)</t>
+          <t>$420, $600, $151,000, $165,000 … (1260 renders)</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -16336,7 +16336,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:72</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:74</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:74</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:76</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="45" customHeight="1">
+    <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26434,7 +26434,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" ht="45" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26434,7 +26434,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26219,7 +26219,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="45" customHeight="1">
+    <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26434,7 +26434,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30648,7 +30648,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1815,10 +1815,15 @@
 MK-PF-F-040 returnSincePurchases
 MK-PF-F-041 isoDay
 MK-PF-F-042 windowTotal
+MK-PF-F-045 priceHistoryShortSentence
 MK-PL-F-012 waterfall
+MK-ST-F-002 monthWords
+MK-ST-F-003 dayWords
+MK-ST-F-004 coverageFor
 MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
+MK-ST-F-034 firstDate
 MK-ST-F-036 reconcile
 MK-ST-F-038 windowBounds
 MK-ST-F-039 on
@@ -1972,8 +1977,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-O-006 theHolding
-MK-PF-F-003 avgCost</t>
+          <t>MK-NW-O-006 theHolding</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1982,7 +1986,6 @@
 MK-NW-O-006 theHolding
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
-MK-PF-F-003 avgCost
 MK-PF-F-004 marketValue
 MK-PF-F-006 capGains
 MK-PF-F-028 realizedFromLedger
@@ -1993,7 +1996,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -2081,6 +2084,7 @@
 MK-NW-F-072 rowOf
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
+MK-NW-F-090 windowStartKey
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
@@ -2108,6 +2112,8 @@
 MK-PF-F-039 periodReturnParts
 MK-PF-F-040 returnSincePurchases
 MK-PF-F-041 isoDay
+MK-PF-F-045 priceHistoryShortSentence
+MK-PF-F-046 saleShortOfPurchasesSentence
 MK-PL-F-012 waterfall
 MK-ST-F-002 monthWords
 MK-ST-F-003 dayWords
@@ -2129,6 +2135,7 @@
 MK-ST-F-065 isoLocalDate
 MK-ST-F-075 agoLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-085 rentFigure
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
@@ -2156,17 +2163,13 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-004 holding quantity (shares) — read by MK-NW-O-006, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-028, MK
-MK-XS-I-004 holding quantity (shares) — read by MK-PF-F-001, MK-PF-F-002, MK-PF-F-003
 MK-XS-I-005 holding price — read by MK-NW-O-006, MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-006, MK-ST-F-027
-MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-003
 MK-XS-I-009 transaction date — read by MK-NW-O-006, MK-PF-F-028
 MK-XS-I-024 logged expenses — read by MK-NW-O-006, MK-PF-F-028
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-O-006, MK-ST-F-027
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-PF-F-028, MK-PF-F-031
-MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-PF-F-031
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-O-006, MK-PF-F-002, MK-PF-F-004, MK-PF-F-006, MK-PF-F-028, MK-PF-F-031
-MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-PF-F-002, MK-PF-F-003, MK-PF-F-031
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-NW-O-006
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -2440,13 +2443,18 @@
 MK-PF-F-040 returnSincePurchases
 MK-PF-F-041 isoDay
 MK-PF-F-042 windowTotal
+MK-PF-F-045 priceHistoryShortSentence
 MK-PL-F-012 waterfall
+MK-ST-F-002 monthWords
+MK-ST-F-003 dayWords
+MK-ST-F-004 coverageFor
 MK-ST-F-013 personalFlowTotals
 MK-ST-F-021 toNumber
 MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-030 record
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
+MK-ST-F-034 firstDate
 MK-ST-F-036 reconcile
 MK-ST-F-038 windowBounds
 MK-ST-F-039 on
@@ -3550,6 +3558,7 @@
 ONE MEANING OF RETURN (B-97, 2026-09-25): dividends and interest are in it, because "Wealth generated" beside it counts them.
 ONE MEANING OF RETURN (B-97, 2026-09-25): dividends and interest are part of this, so the return beside it counts them too.
 OVER A YEAR IT IS A YEARLY RATE and the screen says so (his ruling, 2026-08-18, restated 2026-09-25).
+THE MARKET INCLUDES ITS DIVIDENDS AND INTEREST (DEC-4645, 2026-10-12): SPY and AGG are read through the same dividend-adjusted closes as every holding (src/services/marketData.ts, adjclose).
 The benchmark runs over the SAME DATES as your return — including where your window is cut short at your own purchase date. Comparing your three months against the market's twelve is not a comparison.
 Weighted by what each holding was worth when the window began, so the blend answers "the market, matched to my mix" rather than a plain average of indices — and a holding that grew does not grow its yardstick's weight (outside review Claude Performance, 2026-10-11, DEC-1669, DEC-3035b).
 Whatever the records cannot explain lands in the change-in-value line rather than being silently dropped.</t>
@@ -3673,8 +3682,8 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>A road not taken, priced from real history — never a projection forward.
-NONE RECORDED — the declaration names none.
-Price changes only — dividends are not in it, and the screen says so.</t>
+Dividends and distributions are in it: the closes it reads are adjusted for them (corrected 2026-10-12; it said price changes only).
+NONE RECORDED — the declaration names none.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -26133,7 +26142,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26219,7 +26228,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26391,7 +26400,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -27552,7 +27561,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27638,7 +27647,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27681,7 +27690,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27896,7 +27905,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28005,7 +28014,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:304 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:306 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -28048,7 +28057,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:418 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:421 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -28091,7 +28100,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:505</t>
+          <t>src/screens/HomeScreen.tsx:508</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -28134,7 +28143,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:518 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:521 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -28177,7 +28186,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:519</t>
+          <t>src/screens/HomeScreen.tsx:522</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -28240,7 +28249,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28283,7 +28292,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28369,7 +28378,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -29358,7 +29367,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29401,7 +29410,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29444,7 +29453,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29487,7 +29496,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29530,7 +29539,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30648,7 +30657,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30691,7 +30700,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30734,7 +30743,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30777,7 +30786,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30863,7 +30872,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30906,7 +30915,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-12</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-13</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26357,7 +26357,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28163,7 +28163,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28335,7 +28335,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -30657,7 +30657,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30786,7 +30786,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30915,7 +30915,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9207</v>
+        <v>9219</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>🔗 | linked · # days old</t>
+          <t>› | 🔗 | linked · # days old</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Brokerage | $300,000</t>
+          <t>$300,000 | Open Vanguard Brokerage — this account's own page</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26400,7 +26400,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30657,7 +30657,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30786,7 +30786,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30915,7 +30915,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1131,7 +1131,6 @@
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -1239,7 +1238,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1445,7 +1444,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
+          <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-016, MK-NW-F-027, MK
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
@@ -2804,7 +2803,6 @@
 MK-NW-F-010 wrapperAccount
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
@@ -3351,7 +3349,6 @@
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-005 accountAllowsTicker
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -3910,7 +3907,6 @@
 MK-NW-F-011 assetClassOf
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -4057,7 +4053,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4244,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-015, MK-NW-F-016, MK
+          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-016, MK-NW-F-027, MK
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
@@ -6376,20 +6372,11 @@
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
-MK-NW-F-027 accountClassBreakdown
-MK-NW-F-053 correctClassOf
-MK-NW-F-054 reclassifyAccounts
 MK-NW-F-066 sumWhere
-MK-NW-F-067 plural
 MK-NW-F-068 prettyDay
-MK-NW-F-109 holdingClassOf
 MK-NW-F-120 classEvidenceOf
-MK-NW-F-121 holdingTagClass
-MK-NW-F-122 holdingTagFor
-MK-NW-F-123 holdingNameEvidence
 MK-PL-F-034 lifeInsuranceNeed
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -6743,7 +6730,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -7372,7 +7358,6 @@
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -8352,7 +8337,6 @@
 MK-NW-F-011 assetClassOf
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -9264,7 +9248,6 @@
 MK-NW-F-011 assetClassOf
 MK-NW-F-012 taxTreatmentOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -9704,7 +9687,6 @@
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-014 isRealAsset
-MK-NW-F-015 totalAssets
 MK-NW-F-016 cashTotal
 MK-NW-F-021 investmentsTotal
 MK-NW-F-022 investableAssets
@@ -16345,7 +16327,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -26142,7 +26124,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26314,7 +26296,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26357,7 +26339,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26400,7 +26382,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26410,7 +26392,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" ht="45" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26443,7 +26425,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26486,7 +26468,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26529,7 +26511,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28206,7 +28188,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28249,7 +28231,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28292,7 +28274,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28335,7 +28317,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28378,7 +28360,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28550,7 +28532,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29410,7 +29392,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29453,7 +29435,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29496,7 +29478,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29539,7 +29521,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30083,7 +30065,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source} · ${info.period}${info.estimate ? </t>
+          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source}${info.period ? ` · ${info.period}`</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -30657,7 +30639,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30700,7 +30682,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30743,7 +30725,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30786,7 +30768,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30872,7 +30854,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30915,7 +30897,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -16284,22 +16284,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16327,22 +16327,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26296,7 +26296,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="45" customHeight="1">
+    <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26425,7 +26425,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26468,7 +26468,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26620,7 +26620,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:122</t>
+          <t>src/components/PlanInputs.tsx:124</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -26663,7 +26663,7 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:144</t>
+          <t>src/components/PlanInputs.tsx:146</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:151</t>
+          <t>src/components/PlanInputs.tsx:153</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -26749,7 +26749,7 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:163 (+1 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:165 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:181 (+2 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:183 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:251</t>
+          <t>src/components/PlanInputs.tsx:253</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:354</t>
+          <t>src/domain/planning/hub.ts:355</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27629,7 +27629,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27887,7 +27887,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28188,7 +28188,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29435,7 +29435,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -29759,7 +29759,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:501</t>
+          <t>src/screens/RetirementCockpit.tsx:503</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -29802,7 +29802,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:531</t>
+          <t>src/screens/RetirementCockpit.tsx:533</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -29845,7 +29845,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:566</t>
+          <t>src/screens/RetirementCockpit.tsx:568</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:643</t>
+          <t>src/screens/RetirementCockpit.tsx:645</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:652</t>
+          <t>src/screens/RetirementCockpit.tsx:654</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:662</t>
+          <t>src/screens/RetirementCockpit.tsx:664</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -30017,7 +30017,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:686</t>
+          <t>src/screens/RetirementCockpit.tsx:688</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
@@ -30060,7 +30060,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:687</t>
+          <t>src/screens/RetirementCockpit.tsx:689</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -30103,7 +30103,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:748</t>
+          <t>src/screens/RetirementCockpit.tsx:750</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:765</t>
+          <t>src/screens/RetirementCockpit.tsx:767</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:787</t>
+          <t>src/screens/RetirementCockpit.tsx:789</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
@@ -30232,7 +30232,7 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:789</t>
+          <t>src/screens/RetirementCockpit.tsx:791</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:804</t>
+          <t>src/screens/RetirementCockpit.tsx:806</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:975</t>
+          <t>src/screens/RetirementCockpit.tsx:979</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:980</t>
+          <t>src/screens/RetirementCockpit.tsx:984</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30897,7 +30897,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -1152,7 +1152,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -1238,7 +1237,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -1302,6 +1301,7 @@
 MK-NW-F-046 historyCoverage
 MK-NW-F-047 uberGroupOf
 MK-NW-F-048 uberGroupRows
+MK-NW-F-068 prettyDay
 MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
@@ -1641,12 +1641,12 @@
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-109 holdingClassOf
 MK-NW-F-120 classEvidenceOf
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
 MK-NW-O-002 theAccount
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
@@ -1758,6 +1758,7 @@
 MK-NW-F-060 approxYTM
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
+MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-071 isCertificateOfDeposit
@@ -1779,7 +1780,6 @@
 MK-NW-F-117 propertyUseMap
 MK-NW-F-118 itemizeMissingCount
 MK-NW-F-119 estimatedAccrued
-MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
 MK-NW-F-127 gainOfRow
@@ -1875,7 +1875,7 @@
 MK-XS-I-008 transaction amount — read by MK-CF-F-118, MK-NW-O-002
 MK-XS-I-009 transaction date — read by MK-NW-O-002
 MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-123, MK-ST-F-013
-MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-NW-F-124, MK-ST-F-010
 MK-XS-I-024 logged expenses — read by MK-NW-O-002
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-030
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-NW-F-027
@@ -2077,7 +2077,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -2281,7 +2280,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -2304,7 +2302,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -2393,6 +2391,7 @@
 MK-NW-F-046 historyCoverage
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-068 prettyDay
 MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
@@ -2498,6 +2497,8 @@
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-O-001, MK-ST-F-027
+MK-XS-I-001 account balance — read by MK-ST-F-027
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
@@ -2508,12 +2509,13 @@
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-119
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069, MK-NW-F-119, MK-NW-F-124
+MK-XS-I-013 bond maturity date — read by MK-NW-F-058, MK-NW-F-060, MK-NW-F-069, MK-NW-F-119, MK-NW-F-120, MK-NW-F-124, MK
 MK-XS-I-028 assumed return — read by MK-NW-O-001
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-069, MK-NW-F-119, MK-NW-F-131
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-056, MK-NW-F-120, MK-NW-O-001
+MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-NW-F-011, MK-NW-F-120
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-060
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -2696,7 +2698,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -2736,7 +2737,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -2826,6 +2827,7 @@
 MK-NW-F-048 uberGroupRows
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
+MK-NW-F-068 prettyDay
 MK-NW-F-094 ledgerGroups
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
@@ -2960,7 +2962,7 @@
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-NW-F-124, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
@@ -3183,7 +3185,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-071 isCertificateOfDeposit
@@ -3268,7 +3269,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3369,6 +3370,7 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
+MK-NW-F-068 prettyDay
 MK-NW-F-084 categoryEarnings
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-103 investmentRecordDates
@@ -3939,7 +3941,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -4053,7 +4054,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -4109,6 +4110,7 @@
 MK-NW-F-046 historyCoverage
 MK-NW-F-047 uberGroupOf
 MK-NW-F-048 uberGroupRows
+MK-NW-F-068 prettyDay
 MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
@@ -4244,7 +4246,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-016, MK-NW-F-027, MK
+          <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-016, MK-NW-F-027, MK
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
@@ -4268,7 +4270,7 @@
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-NW-F-124, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
 MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
@@ -4310,8 +4312,7 @@
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK-CF-F-102, MK
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-035, MK-ST-F-036, MK-ST-F-072, MK-ST-F-073, MK
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-036
-MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
-MK-XS-I-034 </t>
+MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4589,7 +4590,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -5089,7 +5089,6 @@
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
@@ -5099,6 +5098,7 @@
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-PF-F-001 totalShares
@@ -5315,13 +5315,13 @@
 MK-NW-F-032 earmarkedAmount
 MK-NW-F-033 retirementEarmarkedValue
 MK-NW-F-035 blendedVolatility
-MK-NW-F-068 prettyDay
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
 MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-PL-F-001 taxBucketSplit
@@ -5542,7 +5542,6 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
-MK-NW-F-068 prettyDay
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
@@ -5552,6 +5551,7 @@
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-F-124 maturityParts
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-PF-F-001 totalShares
@@ -5834,7 +5834,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -5903,7 +5902,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -6073,7 +6072,7 @@
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-ST-F-010
+MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-NW-F-124, MK-ST-F-010
 MK-XS-I-014 debt balance — read by MK-CF-F-034
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
 MK-XS-I-015 debt interest rate — read by MK-CF-F-034
@@ -6127,8 +6126,7 @@
 MK-XS-I-047 money to leave behind — read by MK-PL-F-067
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-050 the share of an account earmarked for retirement — read by MK-NW-F-032
-MK-</t>
+MK-XS-I-050 the share of an account earmarked for retirement — read by MK</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6375,8 +6373,8 @@
 MK-NW-F-022 investableAssets
 MK-NW-F-023 wrapperWord
 MK-NW-F-066 sumWhere
-MK-NW-F-068 prettyDay
 MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
 MK-PL-F-034 lifeInsuranceNeed
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
@@ -6609,7 +6607,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -6647,7 +6644,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -6754,6 +6751,7 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
+MK-NW-F-068 prettyDay
 MK-NW-F-071 isCertificateOfDeposit
 MK-NW-F-090 windowStartKey
 MK-NW-F-091 pricedGainOf
@@ -7229,7 +7227,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -7265,7 +7262,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -7820,7 +7817,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -7856,7 +7852,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -8369,7 +8365,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-071 isCertificateOfDeposit
@@ -8720,8 +8715,8 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
-MK-NW-F-068 prettyDay
 MK-NW-F-120 classEvidenceOf
+MK-NW-F-124 maturityParts
 MK-ST-F-010 nameEvidence
 MK-ST-F-027 accountId
 MK-ST-F-047 activeCurrency
@@ -8926,7 +8921,6 @@
 MK-NW-F-061 bondSummary
 MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -8962,7 +8956,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -9280,7 +9274,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-071 isCertificateOfDeposit
@@ -9715,7 +9708,6 @@
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-067 plural
-MK-NW-F-068 prettyDay
 MK-NW-F-069 priceAtYield
 MK-NW-F-070 accruedInterestCaveat
 MK-NW-F-072 rowOf
@@ -26124,7 +26116,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26296,7 +26288,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26339,7 +26331,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26382,7 +26374,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26511,7 +26503,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28102,7 +28094,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28145,7 +28137,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28188,7 +28180,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28231,7 +28223,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28274,7 +28266,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28317,7 +28309,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28360,7 +28352,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28532,7 +28524,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29349,7 +29341,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29392,7 +29384,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29435,7 +29427,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29478,7 +29470,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29521,7 +29513,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30854,7 +30846,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30897,7 +30889,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26288,7 +26288,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26374,7 +26374,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28137,7 +28137,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28180,7 +28180,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29384,7 +29384,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29427,7 +29427,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29513,7 +29513,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30846,7 +30846,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9219</v>
+        <v>9215</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -1319,10 +1319,11 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-132 notClassifiedWords
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
@@ -1785,10 +1786,11 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-131 pricedLikeBond
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2413,9 +2415,10 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3204,8 +3207,9 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-131 pricedLikeBond
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3269,7 +3273,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -4122,9 +4126,10 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-135 earmarkLeavesOut
 MK-NW-F-136 earmarkLeavesOutWords
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -6772,9 +6777,10 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -7398,9 +7404,10 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -8395,10 +8402,11 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-131 pricedLikeBond
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-008 thePerformance
@@ -9305,10 +9313,11 @@
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
-MK-NW-F-130 cannotWorkBackSentence
+MK-NW-F-130 notIncludedSentence
 MK-NW-F-131 pricedLikeBond
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -26106,7 +26115,7 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>$420, $600, $151,000, $165,000 … (1260 renders)</t>
+          <t>$420, $600, $151,000, $165,000 … (1279 renders)</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -26202,7 +26211,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26288,7 +26297,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26331,7 +26340,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26384,7 +26393,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" ht="45" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26417,7 +26426,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26460,7 +26469,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26503,7 +26512,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27535,7 +27544,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27621,7 +27630,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27664,7 +27673,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27879,7 +27888,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28180,7 +28189,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28223,7 +28232,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28266,7 +28275,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28352,7 +28361,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28524,7 +28533,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29341,7 +29350,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29384,7 +29393,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29427,7 +29436,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29470,7 +29479,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29513,7 +29522,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30631,7 +30640,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30674,7 +30683,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30717,7 +30726,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30760,7 +30769,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30846,7 +30855,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30889,7 +30898,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26211,7 +26211,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26383,7 +26383,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="45" customHeight="1">
+    <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:306 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:309 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:421 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:426 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:508</t>
+          <t>src/screens/HomeScreen.tsx:513</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:521 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:526 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:522</t>
+          <t>src/screens/HomeScreen.tsx:527</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28533,7 +28533,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-13</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
 MK-XS-I-041 the payment the person chose to make on a debt — read by MK-CF-F-023
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK-ST-F-060
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-091, MK-NW-F-127, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
@@ -26125,7 +26125,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-017 Return, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-017 Return</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="60" customHeight="1">
+    <row r="419" ht="45" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27673,7 +27673,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28146,7 +28146,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28533,7 +28533,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30640,7 +30640,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30726,7 +30726,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -30769,7 +30769,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-14</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-19</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9215</v>
+        <v>9213</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -985,7 +985,6 @@
 MK-HM-M-002 Your net worth just crossed X
 MK-NW-M-001 Change in net worth +$X
 MK-NW-M-002 Return on cash + investments
-MK-NW-M-003 the trend line
 MK-NW-M-004 WHAT YOU OWN
 MK-NW-M-005 CASH
 MK-NW-M-006 🏠 PERSONAL PROPERTY
@@ -1001,7 +1000,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1013,10 +1012,13 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-003 categoryMonthly
+          <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-003 categoryMonthly
 MK-CF-F-004 spendBuckets
 MK-CF-F-005 actualMonthFlow
 MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-011 savingsByMonth
 MK-CF-F-021 defaultPaymentType
 MK-CF-F-022 paymentShape
@@ -1108,6 +1110,8 @@
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
 MK-CF-F-192 inflowLabel
 MK-CF-F-193 inflowSourceWord
@@ -1117,12 +1121,16 @@
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
 MK-HM-F-005 pctTxt
@@ -1158,8 +1166,13 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
+MK-NW-F-114 rentAmount
+MK-NW-F-115 liveRent
+MK-NW-F-116 rentedIdsOf
+MK-NW-F-117 propertyUseMap
 MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
 MK-NW-F-121 holdingTagClass
@@ -1171,6 +1184,7 @@
 MK-NW-F-131 pricedLikeBond
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -1217,17 +1231,13 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-ST-F-085 rentFigure
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
-MK-XS-F-008 normalizeSnapshot
-MK-XS-F-009 readHistory
 MK-XS-F-024 resolveLens
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-082 priceFreshness
 MK-XS-F-083 fetchPriceSeries
 MK-XS-F-112 relayUrl
-MK-XS-F-121 isYm
 MK-XS-F-122 n
 MK-XS-F-147 call
 MK-XS-F-170 daysSince
@@ -1237,14 +1247,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
-MK-CF-F-002 plannedMonthlySpend
-MK-CF-F-009 monthlyEssentials
-MK-CF-F-010 emergencyTest
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
 MK-CF-F-029 monthsToClear
@@ -1271,12 +1278,9 @@
 MK-CF-F-164 monthWindow
 MK-CF-F-175 sumOverEarners
 MK-CF-F-178 wageMatchMonthly
-MK-CF-F-189 essentialsFromLoggedSpending
-MK-CF-F-190 essentialsMonthly
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-200 LINE
 MK-CF-O-006 theCreditLine
-MK-CF-O-020 theBudgetCounted
 MK-HM-F-001 buildInsights
 MK-HM-F-002 milestoneLabel
 MK-NW-F-001 isAlternative
@@ -1309,13 +1313,8 @@
 MK-NW-F-094 ledgerGroups
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
-MK-NW-F-107 propertyUses
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-113 altPartsOf
-MK-NW-F-114 rentAmount
-MK-NW-F-115 liveRent
-MK-NW-F-116 rentedIdsOf
-MK-NW-F-117 propertyUseMap
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
@@ -1324,7 +1323,6 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
-MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -1401,7 +1399,10 @@
 MK-ST-F-076 ageLabel
 MK-ST-F-078 dateShown
 MK-XS-F-002 dataGaps
+MK-XS-F-005 trendPoints
 MK-XS-F-007 makeMonthlySnapshot
+MK-XS-F-008 normalizeSnapshot
+MK-XS-F-009 readHistory
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-017 currentAge
 MK-XS-F-018 yearsToRetirement
@@ -1420,6 +1421,7 @@
 MK-XS-F-118 prettyDate
 MK-XS-F-119 namesFor
 MK-XS-F-120 nameOf
+MK-XS-F-121 isYm
 MK-XS-F-131 toInt
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
@@ -1464,11 +1466,11 @@
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
-MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
+MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003, MK
 MK-XS-I-014 debt balance — read by MK-CF-F-157, MK-CF-O-010
-MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
+MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-004
 MK-XS-I-015 debt interest rate — read by MK-CF-F-157, MK-CF-O-010
-MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-025, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
+MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-025, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-004
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-157, MK-CF-O-010
 MK-XS-I-017 birth year — read by MK-CF-F-089
 MK-XS-I-018 retirement age — read by MK-XS-F-174, MK-XS-F-175
@@ -1479,10 +1481,11 @@
 MK-XS-I-023 salary and other income — read by MK-CF-F-074, MK-CF-F-082, MK-CF-F-084, MK-CF-F-088, MK-CF-F-092, MK-CF-F-165, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-005, MK-CF-F-067, MK-CF-F-068, MK-CF-F-109, MK-CF-F-150, MK-CF-F-151, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-005, MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK
+MK-XS-I-025 typical monthly essentials — read by MK-CF-F-009, MK-CF-F-010, MK-NW-O-004
 MK-XS-I-026 big costs (amount and year) — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-027 goals (target, saved, date) — read by MK-CF-F-204, MK-HM-F-006, MK-PL-F-012
 MK-XS-I-027 goals (target, saved, date) — read by MK-CF-F-204, MK-HM-F-006, MK-PL-F-012, MK-PL-F-013, MK-XS-F-174, MK-XS-F-175
-MK-XS-I-028 assumed return — read by MK-NW-F-039, MK-NW-F-040, MK-NW-O-001
+MK-XS-I-028 assumed return — read by MK-NW-F-039, MK-NW-F-040, MK-NW-O-001, MK-NW-O-004
 MK-XS-I-028 assumed return — read by MK-NW-O-001
 MK-XS-I-029 inflation rate — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-097, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK
@@ -1490,6 +1493,7 @@
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-035, MK-ST-F-036, MK-ST-F-072, MK-ST-F-073, MK
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-035, MK-ST-F-036
 MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008
+MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008, MK-CF-F-009, MK-CF-O-020, MK-NW-O-004
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062
 MK-XS-I-034 option positions — contracts, strike, expiry, put or call — read by MK-CF-F-062, MK-NW-F-027
 MK-XS-I-035 annuity income — read by MK-CF-F-072, MK-CF-F-075
@@ -1504,16 +1508,12 @@
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-179, MK-CF-F-181, MK-CF-F-206
 MK-XS-I-044 the person’s own plan overrides — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-040, MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-NW-O-003, MK
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
-MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
-MK-XS-</t>
+MK-XS-I-048 the person’s own asset-class answer — read by</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>A CD and a money-market fund are NOT cash: they are bonds and funds, because they pay interest and dividends that must be measured (founder, 2026-08-04).
-A DAY THAT IS NOT A REAL DATE IS DROPPED, and a month whose figures do not add up is dropped — never drawn as a guess.
 A GENUINE NEGATIVE IS SHOWN, never floored at zero — someone early in a mortgage really does owe more than they own.
 A month and its own days live in one series, sorted by their date text — "2026-04" sorts before "2026-04-30", which is what makes plain text sorting safe.
 An account with no institution recorded groups under "No institution set" rather than being dropped.
@@ -1529,7 +1529,6 @@
 REAL ESTATE IS ITS OWN BAND: a house is not a vehicle, and mixing them hides both.
 THE DAY COMPARED FROM MUST BE ON RECORD. A comparison from before the record begins gives no figure — never one quietly measured from a later day.
 THE SAME ACCOUNTS GROUP TWO WAYS — by class and by institution — and both ways add to the same total, so switching the view can never change what you own.
-The line is drawn only from days we hold a record for; today’s balances are never priced at past dates.
 The mix is ordered biggest first, so the largest thing inside an institution is the first thing read.
 UNDER AN INSTITUTION’S NAME, the class mix inside it is named too — a Fidelity holding a fund and a Treasury reads as a roll-up, not a flat lump.</t>
         </is>
@@ -1541,7 +1540,6 @@
 MK-HM-M-002 Your net worth just crossed X
 MK-NW-M-001 Change in net worth +$X
 MK-NW-M-002 Return on cash + investments
-MK-NW-M-003 the trend line
 MK-NW-M-005 CASH
 MK-NW-M-006 🏠 PERSONAL PROPERTY
 MK-NW-M-007 class rows — by class, institution or type
@@ -1578,7 +1576,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Nothing for you. 8 functions, and they nest: basePay inside incomeSummary, basePay inside theNetWorth, expenses inside basePay, expenses inside thisMonth, expenses inside incomeSummary, expenses inside theMonth, expenses inside incomeSources, expenses inside theNetWorth, thisMonth inside basePay, thisMonth inside incomeSummary, thisMonth inside theMonth, thisMonth inside theNetWorth, incomeSummary inside theNetWorth, theMonth inside basePay, theMonth inside thisMonth, theMonth inside incomeSummary, theMonth inside theNetWorth, incomeSources inside theNetWorth, theBonds inside basePay, theBonds inside thisMonth, theBonds inside incomeSummary, theBonds inside theMonth and theBonds inside theNetWorth. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
+          <t>Nothing for you. 10 functions, and they nest: basePay inside incomeSummary, basePay inside theNetWorth, basePay inside theEmergencyFund, expenses inside basePay, expenses inside thisMonth, expenses inside incomeSummary, expenses inside theMonth, expenses inside incomeSources, expenses inside theBudgetCounted, expenses inside theNetWorth, expenses inside theEmergencyFund, thisMonth inside basePay, thisMonth inside incomeSummary, thisMonth inside theMonth, thisMonth inside theNetWorth, thisMonth inside theEmergencyFund, incomeSummary inside theNetWorth, incomeSummary inside theEmergencyFund, theMonth inside basePay, theMonth inside thisMonth, theMonth inside incomeSummary, theMonth inside theNetWorth, theMonth inside theEmergencyFund, incomeSources inside theNetWorth, theBudgetCounted inside theNetWorth, theBudgetCounted inside theEmergencyFund, theBonds inside basePay, theBonds inside thisMonth, theBonds inside incomeSummary, theBonds inside theMonth, theBonds inside theNetWorth, theBonds inside theEmergencyFund and theEmergencyFund inside theNetWorth. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -1635,6 +1633,7 @@
           <t>MK-CF-F-118 cashEffect
 MK-CF-F-132 map
 MK-CF-F-155 cash
+MK-CF-F-216 typed
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
@@ -1662,7 +1661,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -2064,6 +2063,7 @@
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-010 theMonth
@@ -2270,6 +2270,7 @@
         <is>
           <t>MK-CF-F-132 map
 MK-CF-F-155 cash
+MK-CF-F-216 typed
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
@@ -2304,7 +2305,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -2681,6 +2682,7 @@
 MK-CF-F-193 inflowSourceWord
 MK-CF-F-203 MONTH
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-010 theMonth
@@ -2740,7 +2742,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -2796,6 +2798,8 @@
 MK-CF-F-201 INCOME
 MK-CF-F-204 line
 MK-CF-F-207 SOURCE
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-016 incomeSources
@@ -3167,6 +3171,7 @@
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-010 theMonth
@@ -3273,12 +3278,14 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
 MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
 MK-CF-F-024 totalDebtMonthly
@@ -3337,13 +3344,18 @@
 MK-CF-F-179 entryFromWage
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-198 payrollTaxWithheld
 MK-CF-F-201 INCOME
 MK-CF-F-207 SOURCE
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -3379,6 +3391,7 @@
 MK-NW-F-092 investmentAccountIdsOf
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-114 rentAmount
@@ -3391,6 +3404,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-020 portfolioBenchReturn
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
@@ -3445,7 +3459,6 @@
 MK-ST-F-079 dailyWindowStart
 MK-ST-F-084 fillBetweenObservations
 MK-XS-F-002 dataGaps
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
@@ -3486,8 +3499,10 @@
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance</t>
         </is>
       </c>
@@ -3786,10 +3801,13 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-003 categoryMonthly
+          <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-003 categoryMonthly
 MK-CF-F-004 spendBuckets
 MK-CF-F-005 actualMonthFlow
 MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-011 savingsByMonth
 MK-CF-F-021 defaultPaymentType
 MK-CF-F-022 paymentShape
@@ -3888,6 +3906,8 @@
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
 MK-CF-F-192 inflowLabel
 MK-CF-F-193 inflowSourceWord
@@ -3898,12 +3918,16 @@
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-004 incomeSummary
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
@@ -3951,6 +3975,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
@@ -3971,6 +3996,7 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -4038,17 +4064,13 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-ST-F-085 rentFigure
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
-MK-XS-F-008 normalizeSnapshot
-MK-XS-F-009 readHistory
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
 MK-XS-F-027 takeHomeMonthly
 MK-XS-F-064 currentIdToken
 MK-XS-F-083 fetchPriceSeries
 MK-XS-F-112 relayUrl
-MK-XS-F-121 isYm
 MK-XS-F-122 n
 MK-XS-F-147 call
 MK-XS-F-174 recomputeBalances
@@ -4058,14 +4080,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
-MK-CF-F-002 plannedMonthlySpend
-MK-CF-F-009 monthlyEssentials
-MK-CF-F-010 emergencyTest
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
 MK-CF-F-018 equityByMonth
@@ -4096,14 +4115,11 @@
 MK-CF-F-129 round4
 MK-CF-F-160 daysBetweenDates
 MK-CF-F-161 monthlyGrossOfSource
-MK-CF-F-189 essentialsFromLoggedSpending
-MK-CF-F-190 essentialsMonthly
 MK-CF-F-194 monthOutflow
 MK-CF-F-205 COMING
 MK-CF-F-212 receivedInMonth
 MK-CF-O-008 whatsComing
 MK-CF-O-017 futurePaycheck
-MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -4122,7 +4138,6 @@
 MK-NW-F-094 ledgerGroups
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
-MK-NW-F-107 propertyUses
 MK-NW-F-127 gainOfRow
 MK-NW-F-128 heldValueOf
 MK-NW-F-129 gainRowName
@@ -4130,7 +4145,6 @@
 MK-NW-F-135 earmarkLeavesOut
 MK-NW-F-136 earmarkLeavesOutWords
 MK-NW-F-138 knownHoldingsReturn
-MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -4208,7 +4222,10 @@
 MK-ST-F-078 dateShown
 MK-XS-F-002 dataGaps
 MK-XS-F-004 buildDatedGrid
+MK-XS-F-005 trendPoints
 MK-XS-F-007 makeMonthlySnapshot
+MK-XS-F-008 normalizeSnapshot
+MK-XS-F-009 readHistory
 MK-XS-F-011 buildChangeWalk
 MK-XS-F-018 yearsToRetirement
 MK-XS-F-019 retirementHorizonYears
@@ -4226,6 +4243,7 @@
 MK-XS-F-118 prettyDate
 MK-XS-F-119 namesFor
 MK-XS-F-120 nameOf
+MK-XS-F-121 isYm
 MK-XS-F-131 toInt
 MK-XS-F-170 daysSince
 MK-XS-F-182 figureSpec
@@ -4276,10 +4294,10 @@
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-072, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-120, MK-NW-F-124, MK-ST-F-010
-MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003
-MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
+MK-XS-I-014 debt balance — read by MK-CF-F-027, MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-003, MK
+MK-XS-I-015 debt interest rate — read by MK-CF-F-036, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-004
 MK-XS-I-016 debt minimum payment — read by MK-CF-F-023
-MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-025, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010
+MK-XS-I-016 debt minimum payment — read by MK-CF-F-023, MK-CF-F-025, MK-CF-F-038, MK-CF-F-157, MK-CF-O-010, MK-NW-O-004
 MK-XS-I-017 birth year — read by MK-CF-F-089
 MK-XS-I-017 birth year — read by MK-CF-F-089, MK-CF-F-197, MK-NW-F-041, MK-PL-F-057, MK-PL-F-058, MK-PL-F-060, MK
 MK-XS-I-017 birth year — read by MK-PL-F-026
@@ -4302,10 +4320,11 @@
 MK-XS-I-024 logged expenses — read by MK-CF-F-067, MK-CF-F-068, MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002, MK
 MK-XS-I-024 logged expenses — read by MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002
 MK-XS-I-024 logged expenses — read by MK-CF-F-150, MK-CF-F-151, MK-CF-F-153, MK-CF-O-002, MK-NW-F-115
+MK-XS-I-025 typical monthly essentials — read by MK-CF-F-009, MK-CF-F-010, MK-NW-O-004
 MK-XS-I-026 big costs (amount and year) — read by MK-PL-F-065, MK-PL-F-067
 MK-XS-I-026 big costs (amount and year) — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-027 goals (target, saved, date) — read by MK-CF-F-204, MK-HM-F-006, MK-PL-F-012, MK-PL-F-013, MK-XS-F-174, MK-XS-F-175
-MK-XS-I-028 assumed return — read by MK-NW-F-039, MK-NW-F-040, MK-NW-O-001
+MK-XS-I-028 assumed return — read by MK-NW-F-039, MK-NW-F-040, MK-NW-O-001, MK-NW-O-004
 MK-XS-I-028 assumed return — read by MK-PL-F-049
 MK-XS-I-028 assumed return — read by MK-PL-F-049, MK-PL-F-050, MK-PL-F-067
 MK-XS-I-028 assumed return — read by MK-PL-F-050, MK-PL-F-055
@@ -4316,8 +4335,7 @@
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-097, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK-CF-F-102, MK
 MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-035, MK-ST-F-036, MK-ST-F-072, MK-ST-F-073, MK
-MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-036
-MK-XS-I-032 expenses categories the person set up — read by MK-CF-F-004, MK-CF-F-008</t>
+MK-XS-I-031 dail</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4427,7 +4445,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Nothing for you. 8 functions, and they nest: basePay inside incomeSummary, basePay inside theNetWorth, expenses inside basePay, expenses inside thisMonth, expenses inside incomeSummary, expenses inside theMonth, expenses inside incomeSources, expenses inside theNetWorth, thisMonth inside basePay, thisMonth inside incomeSummary, thisMonth inside theMonth, thisMonth inside theNetWorth, incomeSummary inside theNetWorth, theMonth inside basePay, theMonth inside thisMonth, theMonth inside incomeSummary, theMonth inside theNetWorth, incomeSources inside theNetWorth, theBonds inside basePay, theBonds inside thisMonth, theBonds inside incomeSummary, theBonds inside theMonth and theBonds inside theNetWorth. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
+          <t>Nothing for you. 10 functions, and they nest: basePay inside incomeSummary, basePay inside theNetWorth, basePay inside theEmergencyFund, expenses inside basePay, expenses inside thisMonth, expenses inside incomeSummary, expenses inside theMonth, expenses inside incomeSources, expenses inside theBudgetCounted, expenses inside theNetWorth, expenses inside theEmergencyFund, thisMonth inside basePay, thisMonth inside incomeSummary, thisMonth inside theMonth, thisMonth inside theNetWorth, thisMonth inside theEmergencyFund, incomeSummary inside theNetWorth, incomeSummary inside theEmergencyFund, theMonth inside basePay, theMonth inside thisMonth, theMonth inside incomeSummary, theMonth inside theNetWorth, theMonth inside theEmergencyFund, incomeSources inside theNetWorth, theBudgetCounted inside theNetWorth, theBudgetCounted inside theEmergencyFund, theBonds inside basePay, theBonds inside thisMonth, theBonds inside incomeSummary, theBonds inside theMonth, theBonds inside theNetWorth, theBonds inside theEmergencyFund and theEmergencyFund inside theNetWorth. A function that is a part of a bigger one is the right shape, not a disagreement — I read the code to be sure.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -4572,6 +4590,7 @@
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
@@ -4647,11 +4666,13 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-014 budgetVsActual
 MK-CF-F-019 upcomingBills
 MK-CF-F-037 inferDebtType
@@ -4690,20 +4711,27 @@
 MK-CF-F-178 wageMatchMonthly
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-194 monthOutflow
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-205 COMING
 MK-CF-F-212 receivedInMonth
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-008 whatsComing
 MK-CF-O-017 futurePaycheck
 MK-CF-O-020 theBudgetCounted
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-012 taxTreatmentOf
+MK-NW-F-016 cashTotal
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
+MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-034 benchmarkReturn
 MK-NW-F-035 blendedVolatility
 MK-NW-F-036 benchmarkInfo
@@ -4714,11 +4742,13 @@
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
 MK-NW-F-135 earmarkLeavesOut
 MK-NW-F-136 earmarkLeavesOutWords
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -4826,7 +4856,8 @@
 MK-CF-O-010 theMonth
 MK-CF-O-017 futurePaycheck
 MK-CF-O-020 theBudgetCounted
-MK-NW-O-001 theBonds</t>
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -5001,7 +5032,15 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-021 defaultPaymentType
+          <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-003 categoryMonthly
+MK-CF-F-004 spendBuckets
+MK-CF-F-005 actualMonthFlow
+MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
+MK-CF-F-011 savingsByMonth
+MK-CF-F-021 defaultPaymentType
 MK-CF-F-022 paymentShape
 MK-CF-F-023 requiredPayment
 MK-CF-F-037 inferDebtType
@@ -5010,6 +5049,7 @@
 MK-CF-F-060 salaryGrossByMonth
 MK-CF-F-062 equityRowValue
 MK-CF-F-063 rowVestYear
+MK-CF-F-065 equityVestWeights
 MK-CF-F-066 rsuAnnual
 MK-CF-F-067 rentalList
 MK-CF-F-068 rentalNetAnnual
@@ -5017,21 +5057,29 @@
 MK-CF-F-070 benefitAnnual
 MK-CF-F-071 extraIncome
 MK-CF-F-072 currentRetirementIncomeMonthly
+MK-CF-F-073 otherIncomeMonth
 MK-CF-F-074 tipsAnnual
 MK-CF-F-075 retirementIncomeMonthly
 MK-CF-F-076 guaranteedOutsideStreams
+MK-CF-F-077 scholarshipByCalendarMonth
 MK-CF-F-078 employerMatchMonthly
 MK-CF-F-081 salaryActiveMonths
 MK-CF-F-082 salaryAnnual
 MK-CF-F-083 totalGrossAnnual
+MK-CF-F-084 taxableAnnual
 MK-CF-F-085 filingStatusOf
 MK-CF-F-086 stateRateOf
+MK-CF-F-087 monthlyTaxRates
+MK-CF-F-088 taxableByCalendarMonth
 MK-CF-F-089 over65CountOf
+MK-CF-F-090 effectiveRate
+MK-CF-F-092 incomeMonthlyGrid
 MK-CF-F-097 grossFromNet
 MK-CF-F-099 deductionFor
 MK-CF-F-100 taxableIncomeFor
 MK-CF-F-101 taxOwedFor
 MK-CF-F-102 effectiveRateOnGrossFor
+MK-CF-F-103 marginalBracketFor
 MK-CF-F-108 isMoneyOut
 MK-CF-F-109 reviewTransactions
 MK-CF-F-111 applyTransaction
@@ -5040,6 +5088,8 @@
 MK-CF-F-114 undoSnapshot
 MK-CF-F-115 restoreUndo
 MK-CF-F-116 inverseOf
+MK-CF-F-120 pctBaseMonthly
+MK-CF-F-128 grossByMonth
 MK-CF-F-130 enteredMonthlyRaw
 MK-CF-F-131 normPayee
 MK-CF-F-132 map
@@ -5049,6 +5099,13 @@
 MK-CF-F-137 findPos
 MK-CF-F-138 addLot
 MK-CF-F-139 removeShares
+MK-CF-F-140 periodsAYear
+MK-CF-F-141 perMonth
+MK-CF-F-142 monthsOf
+MK-CF-F-143 annualisedGross
+MK-CF-F-144 takeHomeAsEntered
+MK-CF-F-145 deductionsFromPay
+MK-CF-F-146 payFiguresAgree
 MK-CF-F-148 inMonth
 MK-CF-F-149 recurringDebtPayments
 MK-CF-F-150 debtPaymentsCountedAsExpenses
@@ -5056,32 +5113,59 @@
 MK-CF-F-152 isRadarItem
 MK-CF-F-153 radar
 MK-CF-F-155 cash
+MK-CF-F-156 plannedMonthFlow
+MK-CF-F-157 debtPaymentsByDebt
 MK-CF-F-162 daysApart
 MK-CF-F-165 salaryMonths
 MK-CF-F-166 hasMonthlySalaryTable
 MK-CF-F-167 salaryCalendarYear
+MK-CF-F-171 earnerPay
 MK-CF-F-172 hasWage
 MK-CF-F-173 earnerWages
 MK-CF-F-175 sumOverEarners
 MK-CF-F-176 sumMonthsOverEarners
 MK-CF-F-177 wageGrossByMonth
 MK-CF-F-178 wageMatchMonthly
+MK-CF-F-179 entryFromWage
+MK-CF-F-180 enteredLandsAnnual
+MK-CF-F-181 rateInForce
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
+MK-CF-F-192 inflowLabel
+MK-CF-F-193 inflowSourceWord
 MK-CF-F-197 ageAttainedInYear
+MK-CF-F-198 payrollTaxWithheld
+MK-CF-F-203 MONTH
+MK-CF-F-204 line
+MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
+MK-CF-O-001 basePay
 MK-CF-O-002 expenses
+MK-CF-O-003 thisMonth
+MK-CF-O-004 incomeSummary
+MK-CF-O-010 theMonth
+MK-CF-O-020 theBudgetCounted
+MK-HM-F-005 pctTxt
+MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-012 taxTreatmentOf
+MK-NW-F-016 cashTotal
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
+MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -5093,19 +5177,42 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-055 isBond
+MK-NW-F-056 bondInfo
+MK-NW-F-057 annualCoupon
+MK-NW-F-058 yearsToMaturity
+MK-NW-F-059 currentYield
+MK-NW-F-060 approxYTM
+MK-NW-F-061 bondSummary
+MK-NW-F-064 bondRateSensitivity
 MK-NW-F-067 plural
+MK-NW-F-069 priceAtYield
+MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-072 rowOf
+MK-NW-F-077 ALL
+MK-NW-F-078 ONE
+MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
 MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5115,6 +5222,7 @@
 MK-PF-F-034 closeOnOrBefore
 MK-PF-F-035 unknownFigure
 MK-PL-F-001 taxBucketSplit
+MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-047 colFactor
 MK-PL-F-049 retirementSpendMonthly
@@ -5170,6 +5278,7 @@
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
+MK-XS-F-027 takeHomeMonthly
 MK-XS-F-033 resolveNetWorthRows
 MK-XS-F-064 currentIdToken
 MK-XS-F-083 fetchPriceSeries
@@ -5180,12 +5289,20 @@
 MK-XS-F-147 call
 MK-XS-F-174 recomputeBalances
 MK-XS-F-175 uid
-MK-XS-F-179 ageToday</t>
+MK-XS-F-179 ageToday
+MK-XS-F-180 declareFigures</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-002 expenses</t>
+          <t>MK-CF-O-001 basePay
+MK-CF-O-002 expenses
+MK-CF-O-003 thisMonth
+MK-CF-O-004 incomeSummary
+MK-CF-O-010 theMonth
+MK-CF-O-020 theBudgetCounted
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5305,6 +5422,7 @@
 MK-CF-F-153 radar
 MK-CF-F-155 cash
 MK-CF-F-191 ym
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
@@ -5455,7 +5573,15 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-021 defaultPaymentType
+          <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-003 categoryMonthly
+MK-CF-F-004 spendBuckets
+MK-CF-F-005 actualMonthFlow
+MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
+MK-CF-F-011 savingsByMonth
+MK-CF-F-021 defaultPaymentType
 MK-CF-F-022 paymentShape
 MK-CF-F-023 requiredPayment
 MK-CF-F-037 inferDebtType
@@ -5464,6 +5590,7 @@
 MK-CF-F-060 salaryGrossByMonth
 MK-CF-F-062 equityRowValue
 MK-CF-F-063 rowVestYear
+MK-CF-F-065 equityVestWeights
 MK-CF-F-066 rsuAnnual
 MK-CF-F-067 rentalList
 MK-CF-F-068 rentalNetAnnual
@@ -5471,21 +5598,29 @@
 MK-CF-F-070 benefitAnnual
 MK-CF-F-071 extraIncome
 MK-CF-F-072 currentRetirementIncomeMonthly
+MK-CF-F-073 otherIncomeMonth
 MK-CF-F-074 tipsAnnual
 MK-CF-F-075 retirementIncomeMonthly
 MK-CF-F-076 guaranteedOutsideStreams
+MK-CF-F-077 scholarshipByCalendarMonth
 MK-CF-F-078 employerMatchMonthly
 MK-CF-F-081 salaryActiveMonths
 MK-CF-F-082 salaryAnnual
 MK-CF-F-083 totalGrossAnnual
+MK-CF-F-084 taxableAnnual
 MK-CF-F-085 filingStatusOf
 MK-CF-F-086 stateRateOf
+MK-CF-F-087 monthlyTaxRates
+MK-CF-F-088 taxableByCalendarMonth
 MK-CF-F-089 over65CountOf
+MK-CF-F-090 effectiveRate
+MK-CF-F-092 incomeMonthlyGrid
 MK-CF-F-097 grossFromNet
 MK-CF-F-099 deductionFor
 MK-CF-F-100 taxableIncomeFor
 MK-CF-F-101 taxOwedFor
 MK-CF-F-102 effectiveRateOnGrossFor
+MK-CF-F-103 marginalBracketFor
 MK-CF-F-108 isMoneyOut
 MK-CF-F-109 reviewTransactions
 MK-CF-F-111 applyTransaction
@@ -5494,6 +5629,8 @@
 MK-CF-F-114 undoSnapshot
 MK-CF-F-115 restoreUndo
 MK-CF-F-116 inverseOf
+MK-CF-F-120 pctBaseMonthly
+MK-CF-F-128 grossByMonth
 MK-CF-F-130 enteredMonthlyRaw
 MK-CF-F-131 normPayee
 MK-CF-F-132 map
@@ -5503,6 +5640,13 @@
 MK-CF-F-137 findPos
 MK-CF-F-138 addLot
 MK-CF-F-139 removeShares
+MK-CF-F-140 periodsAYear
+MK-CF-F-141 perMonth
+MK-CF-F-142 monthsOf
+MK-CF-F-143 annualisedGross
+MK-CF-F-144 takeHomeAsEntered
+MK-CF-F-145 deductionsFromPay
+MK-CF-F-146 payFiguresAgree
 MK-CF-F-148 inMonth
 MK-CF-F-149 recurringDebtPayments
 MK-CF-F-150 debtPaymentsCountedAsExpenses
@@ -5510,32 +5654,59 @@
 MK-CF-F-152 isRadarItem
 MK-CF-F-153 radar
 MK-CF-F-155 cash
+MK-CF-F-156 plannedMonthFlow
+MK-CF-F-157 debtPaymentsByDebt
 MK-CF-F-162 daysApart
 MK-CF-F-165 salaryMonths
 MK-CF-F-166 hasMonthlySalaryTable
 MK-CF-F-167 salaryCalendarYear
+MK-CF-F-171 earnerPay
 MK-CF-F-172 hasWage
 MK-CF-F-173 earnerWages
 MK-CF-F-175 sumOverEarners
 MK-CF-F-176 sumMonthsOverEarners
 MK-CF-F-177 wageGrossByMonth
 MK-CF-F-178 wageMatchMonthly
+MK-CF-F-179 entryFromWage
+MK-CF-F-180 enteredLandsAnnual
+MK-CF-F-181 rateInForce
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
+MK-CF-F-192 inflowLabel
+MK-CF-F-193 inflowSourceWord
 MK-CF-F-197 ageAttainedInYear
+MK-CF-F-198 payrollTaxWithheld
+MK-CF-F-203 MONTH
+MK-CF-F-204 line
+MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
+MK-CF-O-001 basePay
 MK-CF-O-002 expenses
+MK-CF-O-003 thisMonth
+MK-CF-O-004 incomeSummary
+MK-CF-O-010 theMonth
+MK-CF-O-020 theBudgetCounted
+MK-HM-F-005 pctTxt
+MK-HM-F-006 money0
 MK-NW-F-004 portfolioActualReturn
 MK-NW-F-007 assetKind
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
 MK-NW-F-012 taxTreatmentOf
+MK-NW-F-016 cashTotal
 MK-NW-F-023 wrapperWord
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
+MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-030 earmarkDefault
 MK-NW-F-031 primaryCarIdOf
 MK-NW-F-032 earmarkedAmount
@@ -5547,18 +5718,42 @@
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
+MK-NW-F-055 isBond
+MK-NW-F-056 bondInfo
+MK-NW-F-057 annualCoupon
+MK-NW-F-058 yearsToMaturity
+MK-NW-F-059 currentYield
+MK-NW-F-060 approxYTM
+MK-NW-F-061 bondSummary
+MK-NW-F-064 bondRateSensitivity
+MK-NW-F-067 plural
+MK-NW-F-069 priceAtYield
+MK-NW-F-070 accruedInterestCaveat
+MK-NW-F-072 rowOf
+MK-NW-F-077 ALL
+MK-NW-F-078 ONE
+MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
+MK-NW-F-112 yearlyInterest
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
+MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
 MK-NW-F-124 maturityParts
+MK-NW-F-125 isPastMaturity
+MK-NW-F-126 yearlyInterestNow
+MK-NW-F-131 pricedLikeBond
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -5570,6 +5765,7 @@
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
+MK-PL-F-012 waterfall
 MK-PL-F-013 goalsFromOnboarding
 MK-PL-F-032 rothConversionCost
 MK-PL-F-047 colFactor
@@ -5627,6 +5823,7 @@
 MK-XS-F-006 pruneDaily
 MK-XS-F-017 currentAge
 MK-XS-F-024 resolveLens
+MK-XS-F-027 takeHomeMonthly
 MK-XS-F-033 resolveNetWorthRows
 MK-XS-F-064 currentIdToken
 MK-XS-F-083 fetchPriceSeries
@@ -5635,12 +5832,20 @@
 MK-XS-F-147 call
 MK-XS-F-174 recomputeBalances
 MK-XS-F-175 uid
-MK-XS-F-179 ageToday</t>
+MK-XS-F-179 ageToday
+MK-XS-F-180 declareFigures</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-002 expenses</t>
+          <t>MK-CF-O-001 basePay
+MK-CF-O-002 expenses
+MK-CF-O-003 thisMonth
+MK-CF-O-004 incomeSummary
+MK-CF-O-010 theMonth
+MK-CF-O-020 theBudgetCounted
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -5809,6 +6014,7 @@
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-203 MONTH
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-010 theMonth
@@ -5907,12 +6113,14 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-002 plannedMonthlySpend
 MK-CF-F-006 allocatableThisMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-014 budgetVsActual
 MK-CF-F-018 equityByMonth
 MK-CF-F-019 upcomingBills
@@ -5963,6 +6171,8 @@
 MK-CF-F-179 entryFromWage
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-194 monthOutflow
 MK-CF-F-198 payrollTaxWithheld
 MK-CF-F-201 INCOME
@@ -5970,6 +6180,8 @@
 MK-CF-F-205 COMING
 MK-CF-F-207 SOURCE
 MK-CF-F-212 receivedInMonth
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-008 whatsComing
@@ -5978,14 +6190,19 @@
 MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
+MK-NW-F-016 cashTotal
+MK-NW-F-027 accountClassBreakdown
+MK-NW-F-029 assetAllocation
 MK-NW-F-040 assetsFromOnboarding
 MK-NW-F-053 correctClassOf
 MK-NW-F-054 reclassifyAccounts
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
+MK-NW-F-109 holdingClassOf
 MK-NW-F-121 holdingTagClass
 MK-NW-F-122 holdingTagFor
 MK-NW-F-123 holdingNameEvidence
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -6060,7 +6277,8 @@
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
 MK-CF-O-020 theBudgetCounted
-MK-NW-O-001 theBonds</t>
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -6370,6 +6588,7 @@
 MK-CF-F-176 sumMonthsOverEarners
 MK-CF-F-177 wageGrossByMonth
 MK-CF-F-191 ym
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
@@ -6593,6 +6812,7 @@
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
@@ -6649,12 +6869,14 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
 MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
 MK-CF-F-018 equityByMonth
@@ -6714,12 +6936,16 @@
 MK-CF-F-184 incomeFromAccounts
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-194 monthOutflow
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-201 INCOME
 MK-CF-F-205 COMING
 MK-CF-F-207 SOURCE
 MK-CF-F-212 receivedInMonth
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-008 whatsComing
 MK-CF-O-016 incomeSources
 MK-CF-O-017 futurePaycheck
@@ -6782,6 +7008,7 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -6878,7 +7105,6 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
@@ -6923,6 +7149,7 @@
 MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance</t>
         </is>
       </c>
@@ -7218,6 +7445,7 @@
 MK-CF-F-194 monthOutflow
 MK-CF-F-203 MONTH
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-010 theMonth
@@ -7268,11 +7496,13 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-001 buildBudgetState
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-018 equityByMonth
 MK-CF-F-019 upcomingBills
@@ -7339,6 +7569,8 @@
 MK-CF-F-179 entryFromWage
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-198 payrollTaxWithheld
 MK-CF-F-201 INCOME
@@ -7346,6 +7578,8 @@
 MK-CF-F-205 COMING
 MK-CF-F-207 SOURCE
 MK-CF-F-212 receivedInMonth
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-008 whatsComing
@@ -7409,6 +7643,7 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -7507,7 +7742,6 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-XS-F-004 buildDatedGrid
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
@@ -7550,6 +7784,7 @@
 MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance</t>
         </is>
       </c>
@@ -7808,6 +8043,7 @@
 MK-CF-F-193 inflowSourceWord
 MK-CF-F-203 MONTH
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-008 whatsComing
@@ -7859,11 +8095,13 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-014 budgetVsActual
 MK-CF-F-018 equityByMonth
 MK-CF-F-037 inferDebtType
@@ -7909,12 +8147,16 @@
 MK-CF-F-179 entryFromWage
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-194 monthOutflow
 MK-CF-F-197 ageAttainedInYear
 MK-CF-F-198 payrollTaxWithheld
 MK-CF-F-204 line
 MK-CF-F-205 COMING
 MK-CF-F-212 receivedInMonth
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-004 incomeSummary
 MK-CF-O-017 futurePaycheck
@@ -7955,6 +8197,7 @@
 MK-NW-F-123 holdingNameEvidence
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-O-004 theEmergencyFund
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
 MK-PF-F-004 marketValue
@@ -8041,7 +8284,8 @@
 MK-CF-O-010 theMonth
 MK-CF-O-017 futurePaycheck
 MK-CF-O-020 theBudgetCounted
-MK-NW-O-001 theBonds</t>
+MK-NW-O-001 theBonds
+MK-NW-O-004 theEmergencyFund</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8197,6 +8441,8 @@
 MK-CF-F-004 spendBuckets
 MK-CF-F-005 actualMonthFlow
 MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-011 savingsByMonth
 MK-CF-F-013 budgetFromOnboarding
 MK-CF-F-014 budgetVsActual
@@ -8310,6 +8556,8 @@
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
 MK-CF-F-188 householdPreTaxContributionsAnnual
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
 MK-CF-F-192 inflowLabel
 MK-CF-F-193 inflowSourceWord
@@ -8320,6 +8568,9 @@
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
@@ -8328,6 +8579,7 @@
 MK-CF-O-007 theTaxOrganizer
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-002 milestoneLabel
 MK-HM-F-003 milestoneFloor
 MK-HM-F-004 milestoneCrossed
@@ -8384,6 +8636,7 @@
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
@@ -8409,6 +8662,7 @@
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -8514,7 +8768,6 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-ST-F-085 rentFigure
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
@@ -8558,8 +8811,10 @@
 MK-CF-O-007 theTaxOrganizer
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance</t>
         </is>
       </c>
@@ -8699,6 +8954,7 @@
 MK-CF-F-188 householdPreTaxContributionsAnnual
 MK-CF-F-191 ym
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-PL-F-031 taxOrganizer
 MK-PL-F-082 taxableIncomeSteps
@@ -8711,7 +8967,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -8913,6 +9169,7 @@
 MK-CF-F-203 MONTH
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
+MK-CF-F-216 typed
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
 MK-CF-O-006 theCreditLine
@@ -8964,7 +9221,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -9230,6 +9487,9 @@
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
@@ -9433,7 +9693,6 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-ST-F-085 rentFigure
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
 MK-XS-F-007 makeMonthlySnapshot
 MK-XS-F-008 normalizeSnapshot
@@ -9567,10 +9826,13 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-003 categoryMonthly
+          <t>MK-CF-F-002 plannedMonthlySpend
+MK-CF-F-003 categoryMonthly
 MK-CF-F-004 spendBuckets
 MK-CF-F-005 actualMonthFlow
 MK-CF-F-008 spendByMonth
+MK-CF-F-009 monthlyEssentials
+MK-CF-F-010 emergencyTest
 MK-CF-F-011 savingsByMonth
 MK-CF-F-021 defaultPaymentType
 MK-CF-F-022 paymentShape
@@ -9663,6 +9925,8 @@
 MK-CF-F-185 needsTakeHomeConversion
 MK-CF-F-186 convertTakeHomeMode
 MK-CF-F-187 seniorDeductionFor
+MK-CF-F-189 essentialsFromLoggedSpending
+MK-CF-F-190 essentialsMonthly
 MK-CF-F-191 ym
 MK-CF-F-192 inflowLabel
 MK-CF-F-193 inflowSourceWord
@@ -9673,6 +9937,9 @@
 MK-CF-F-204 line
 MK-CF-F-206 householdK401ByMonth
 MK-CF-F-207 SOURCE
+MK-CF-F-216 typed
+MK-CF-F-217 hasOldRentFigure
+MK-CF-F-218 moveOldRentFigure
 MK-CF-O-001 basePay
 MK-CF-O-002 expenses
 MK-CF-O-003 thisMonth
@@ -9680,6 +9947,7 @@
 MK-CF-O-006 theCreditLine
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-HM-F-005 pctTxt
 MK-HM-F-006 money0
 MK-NW-F-001 isAlternative
@@ -9723,6 +9991,7 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-106 mortgagesByProperty
+MK-NW-F-107 propertyUses
 MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-112 yearlyInterest
@@ -9745,6 +10014,7 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook
 MK-PF-F-001 totalShares
 MK-PF-F-002 costBasis
@@ -9793,10 +10063,7 @@
 MK-ST-F-083 accountValuesOn
 MK-ST-F-084 fillBetweenObservations
 MK-ST-F-085 rentFigure
-MK-XS-F-005 trendPoints
 MK-XS-F-006 pruneDaily
-MK-XS-F-008 normalizeSnapshot
-MK-XS-F-009 readHistory
 MK-XS-F-024 resolveLens
 MK-XS-F-025 tabOrder
 MK-XS-F-027 takeHomeMonthly
@@ -9804,7 +10071,6 @@
 MK-XS-F-083 fetchPriceSeries
 MK-XS-F-112 relayUrl
 MK-XS-F-120 nameOf
-MK-XS-F-121 isYm
 MK-XS-F-122 n
 MK-XS-F-147 call
 MK-XS-F-174 recomputeBalances
@@ -9823,8 +10089,10 @@
 MK-CF-O-006 theCreditLine
 MK-CF-O-010 theMonth
 MK-CF-O-016 incomeSources
+MK-CF-O-020 theBudgetCounted
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
+MK-NW-O-004 theEmergencyFund
 MK-NW-O-005 theAlternativesOutlook</t>
         </is>
       </c>
@@ -16285,22 +16553,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16328,22 +16596,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -26211,7 +26479,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26297,7 +26565,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26340,7 +26608,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26469,7 +26737,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -27964,7 +28232,7 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>$1,900</t>
+          <t>$300, $1,900</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
@@ -28103,7 +28371,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28146,7 +28414,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28189,7 +28457,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28232,7 +28500,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28275,7 +28543,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28318,7 +28586,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28361,7 +28629,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28533,7 +28801,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29350,7 +29618,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29393,7 +29661,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29436,7 +29704,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29479,7 +29747,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29522,7 +29790,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -30855,7 +31123,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -30898,7 +31166,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26393,7 +26393,7 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26737,7 +26737,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27898,7 +27898,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28457,7 +28457,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28500,7 +28500,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -30908,7 +30908,7 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -30994,7 +30994,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -4270,6 +4270,7 @@
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>MK-XS-I-001 account balance — read by MK-CF-F-111, MK-CF-F-133, MK-CF-F-134, MK-CF-F-136, MK-NW-F-016, MK-NW-F-027, MK
+MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-037, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-PL-F-026, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-CF-F-134, MK-CF-F-136, MK-NW-F-011, MK-NW-F-027, MK-NW-F-040, MK-NW-F-054, MK
@@ -4334,8 +4335,7 @@
 MK-XS-I-029 inflation rate — read by MK-XS-F-174, MK-XS-F-175
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-097, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK
 MK-XS-I-030 tax filing status and age — read by MK-CF-F-085, MK-CF-F-089, MK-CF-F-099, MK-CF-F-100, MK-CF-F-101, MK-CF-F-102, MK
-MK-XS-I-031 daily and monthly snapshots — read by MK-ST-F-028, MK-ST-F-030, MK-ST-F-035, MK-ST-F-036, MK-ST-F-072, MK-ST-F-073, MK
-MK-XS-I-031 dail</t>
+MK-XS-I-031 daily and monthly snapshots — rea</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -4345,7 +4345,6 @@
 MK-CF-F-083 — Turns a monthly figure into a year by multiplying by twelve.
 MK-CF-F-083 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-089 — Uses today's date from the device clock, so the answer changes by itself overnight.
-MK-CF-F-101 — Never lets state rate fall below 0.
 MK-CF-F-150 — Uses a built-in s h o w f i r s t of 5.
 MK-CF-F-197 — The IRS convention for limits: a person attains an age at any point in the calendar year, so this year − birth year — not the birthday-aware age used for display (G1 / G9).
 MK-CF-F-197 — Uses today's date from the device clock, so the answer changes by itself overnight.
@@ -4354,6 +4353,7 @@
 MK-NW-F-032 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-NW-F-034 — If return is missing it uses 6%.
 MK-NW-F-035 — If v is missing it uses 12%.
+MK-NW-F-037 — Uses a built-in d e f a u l t r e t u r n of 7%.
 MK-PL-F-026 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-PL-F-050 — Founder ruling 2026-09-08 (G17): one count, 1,000 futures, on every surface; the guard test simulation_paths.test.ts fails on any other number.
 MK-PL-F-050 — If contrib by year[y] is missing it counts as zero, so nothing recorded and a real zero look the same.
@@ -4399,7 +4399,7 @@
 The recommended pot is 25× the yearly expenses NOT covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator (his ruling).
 [Built in] The assumed rate of return, which the person can change on the cockpit.
 [Founder] Each stream grows on its own rule: Social Security rises with inflation, a fixed pension stays flat. They are never inflated together (fix B1).
-[Founder] One thousan</t>
+[Founder</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5499,6 +5499,7 @@
 MK-NW-F-032 — Caps percent at 100.
 MK-NW-F-032 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-NW-F-034 — If return is missing it uses 6%.
+MK-NW-F-037 — Uses a built-in d e f a u l t r e t u r n of 7%.
 MK-ST-F-049 — Rounds the answer to a whole number.
 No function on record — assumptions unknown
 [Founder] G8, 2026-09-08: the year's figure stands on last 31 December's balance when the person enters it; until then today's balance, stated in those words on the screen.
@@ -6283,7 +6284,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-133, MK-ST-F-027
+          <t>MK-XS-I-001 account balance — read by MK-NW-F-031, MK-NW-F-032, MK-NW-F-037, MK-NW-F-133, MK-ST-F-027
 MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-004, MK-NW-F-011, MK-NW-F-012, MK-NW-F-025, MK-NW-F-120, MK-PL-F-086
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-120, MK-NW-O-001
@@ -6349,7 +6350,7 @@
 MK-XS-I-047 money to leave behind — read by MK-PL-F-067
 MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
-MK-XS-I-050 the share of an account earmarked for retirement — read by MK</t>
+MK-XS-I-050 the share of an account earmarked for retirement</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6357,7 +6358,6 @@
           <t>MK-CF-F-083 — Turns a monthly figure into a year by multiplying by twelve.
 MK-CF-F-083 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-CF-F-089 — Uses today's date from the device clock, so the answer changes by itself overnight.
-MK-CF-F-101 — Never lets state rate fall below 0.
 MK-CF-F-197 — The IRS convention for limits: a person attains an age at any point in the calendar year, so this year − birth year — not the birthday-aware age used for display (G1 / G9).
 MK-CF-F-197 — Uses today's date from the device clock, so the answer changes by itself overnight.
 MK-NW-F-031 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
@@ -6365,6 +6365,7 @@
 MK-NW-F-032 — If balance is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-NW-F-034 — If return is missing it uses 6%.
 MK-NW-F-035 — If v is missing it uses 12%.
+MK-NW-F-037 — Uses a built-in d e f a u l t r e t u r n of 7%.
 MK-PL-F-060 — If statement monthly is missing it counts as zero, so nothing recorded and a real zero look the same.
 MK-PL-F-065 — Never lets the answer fall below 5% or rise above 20%.
 MK-PL-F-067 — If monthly is missing it uses 0.
@@ -6381,7 +6382,7 @@
 MK-XS-F-179 — Uses today's date from the device clock, so the answer changes by itself overnight.
 NONE RECORDED — the declaration names none.
 No function on record — assumptions unknown
-… and 44 more, on the functions tab</t>
+… and 45 more, on the functions tab</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16596,7 +16597,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>evening | ava | your &lt;name&gt;: $#</t>
+          <t>morning | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -26479,7 +26480,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26565,7 +26566,7 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26608,7 +26609,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26737,7 +26738,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -27319,7 +27320,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:355</t>
+          <t>src/domain/planning/hub.ts:357</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -27812,7 +27813,7 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -27898,7 +27899,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -27941,7 +27942,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -28156,7 +28157,7 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -28371,7 +28372,7 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -28414,7 +28415,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28457,7 +28458,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28500,7 +28501,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28543,7 +28544,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28586,7 +28587,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28629,7 +28630,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28801,7 +28802,7 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -29618,7 +29619,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29661,7 +29662,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29747,7 +29748,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29790,7 +29791,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -31123,7 +31124,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -31166,7 +31167,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26480,7 +26480,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="I418" s="2" t="n"/>
     </row>
-    <row r="419" ht="45" customHeight="1">
+    <row r="419" ht="60" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26695,7 +26695,7 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -28501,7 +28501,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29662,7 +29662,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29748,7 +29748,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Map'!$A$1:$U$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$538</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$540</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conflicts'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="n"/>
     </row>
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-046 · MK-NW-M-047 · MK-NW-M-048 · MK-NW-M-049 · MK-NW-M-050 · MK-NW-M-051 · MK-NW-M-052 · MK-NW-M-053 · MK-NW-M-054 · MK-NW-M-055 · MK-NW-M-056 · MK-NW-M-057 · MK-NW-M-058 · MK-NW-M-059 · MK-NW-M-060 · MK-NW-M-061 · MK-NW-M-062 · MK-NW-M-063 · MK-NW-M-064 · MK-PF-M-013 · MK-PF-M-014 · MK-PF-M-015 · MK-PF-M-016 · MK-PF-M-017 · MK-PF-M-018 · MK-PF-M-019 · MK-PF-M-020 · MK-CF-M-055 · MK-CF-M-056 · MK-CF-M-057 · MK-CF-M-058 · MK-CF-M-059 · MK-CF-M-060 · MK-CF-M-061 · MK-CF-M-062 · MK-CF-M-063 · MK-CF-M-066 · MK-CF-M-069 · MK-CF-M-070 · MK-CF-M-071 · MK-CF-M-072 · MK-CF-M-073 · MK-CF-M-074 · MK-CF-M-075</t>
+          <t>MK-NW-M-046 · MK-NW-M-047 · MK-NW-M-048 · MK-NW-M-049 · MK-NW-M-050 · MK-NW-M-051 · MK-NW-M-052 · MK-NW-M-053 · MK-NW-M-054 · MK-NW-M-055 · MK-NW-M-056 · MK-NW-M-057 · MK-NW-M-058 · MK-NW-M-059 · MK-NW-M-060 · MK-NW-M-061 · MK-NW-M-062 · MK-NW-M-063 · MK-NW-M-064 · MK-PF-M-013 · MK-PF-M-014 · MK-PF-M-015 · MK-PF-M-016 · MK-PF-M-017 · MK-PF-M-018 · MK-PF-M-019 · MK-PF-M-020 · MK-PF-M-021 · MK-PF-M-022 · MK-CF-M-055 · MK-CF-M-056 · MK-CF-M-057 · MK-CF-M-058 · MK-CF-M-059 · MK-CF-M-060 · MK-CF-M-061 · MK-CF-M-062 · MK-CF-M-063 · MK-CF-M-066 · MK-CF-M-069 · MK-CF-M-070 · MK-CF-M-071 · MK-CF-M-072 · MK-CF-M-073 · MK-CF-M-074 · MK-CF-M-075</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9213</v>
+        <v>9199</v>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" s="2" t="n"/>
     </row>
@@ -1323,6 +1323,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -1790,6 +1791,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2420,6 +2422,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3215,6 +3218,7 @@
 MK-NW-F-130 notIncludedSentence
 MK-NW-F-131 pricedLikeBond
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3255,6 +3259,8 @@
 MK-ST-F-047 activeCurrency
 MK-ST-F-048 currencySymbol
 MK-ST-F-049 formatMoney
+MK-ST-F-050 formatMoneyCents
+MK-ST-F-051 moneyCompact
 MK-ST-F-052 toNum
 MK-ST-F-053 money
 MK-ST-F-056 has
@@ -3274,11 +3280,12 @@
 MK-XS-F-112 relayUrl
 MK-XS-F-122 n
 MK-XS-F-147 call
-MK-XS-F-180 declareFigures</t>
+MK-XS-F-180 declareFigures
+MK-XS-F-183 writeFigure</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3441,8 +3448,6 @@
 MK-ST-F-035 covers
 MK-ST-F-043 newEntityId
 MK-ST-F-044 setMoneyFormat
-MK-ST-F-050 formatMoneyCents
-MK-ST-F-051 moneyCompact
 MK-ST-F-055 round2
 MK-ST-F-066 isDayKey
 MK-ST-F-067 utcOfDay
@@ -3487,8 +3492,7 @@
 MK-XS-F-174 recomputeBalances
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
-MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-182 figureSpec</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3516,7 +3520,7 @@
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
 MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-009, MK-PF-F-011, MK-PF-F-014, MK-PF-F-029, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
-MK-XS-I-007 purchase price and date (per lot) — read by MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK-PF-F-014, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-139, MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-ST-F-082
 MK-XS-I-009 transaction date — read by MK-NW-O-008
@@ -3557,7 +3561,7 @@
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
-MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078
+MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078, MK-XS-F-183
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
         </is>
@@ -4145,6 +4149,7 @@
 MK-NW-F-135 earmarkLeavesOut
 MK-NW-F-136 earmarkLeavesOutWords
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -7008,6 +7013,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
@@ -7643,6 +7649,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
@@ -8661,6 +8668,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -8741,6 +8749,7 @@
 MK-ST-F-047 activeCurrency
 MK-ST-F-048 currencySymbol
 MK-ST-F-049 formatMoney
+MK-ST-F-050 formatMoneyCents
 MK-ST-F-051 moneyCompact
 MK-ST-F-052 toNum
 MK-ST-F-053 money
@@ -8799,7 +8808,8 @@
 MK-XS-F-174 recomputeBalances
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
-MK-XS-F-180 declareFigures</t>
+MK-XS-F-180 declareFigures
+MK-XS-F-183 writeFigure</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -9579,6 +9589,7 @@
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
+MK-NW-F-139 leftOutValueOf
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -10144,7 +10155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I538"/>
+  <dimension ref="A1:I540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10223,7 +10234,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 7 rows not found on screen</t>
+          <t>11 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 9 rows not found on screen</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -10748,7 +10759,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8 rows on the master · 21 places in the code print a dollar figure · 6 of them have no row · 12 rows not found on screen</t>
+          <t>8 rows on the master · 21 places in the code print a dollar figure · 6 of them have no row · 14 rows not found on screen</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -11028,7 +11039,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 11 rows not found on screen</t>
+          <t>10 rows on the master · 1 places in the code print a dollar figure · 0 of them have no row · 13 rows not found on screen</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -12757,7 +12768,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>retiree, rich|account:bond, rich|account:savings, rich|account:trad_ira, worker</t>
+          <t>retiree, rich|account:trad_ira, worker</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -21508,7 +21519,7 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>% | Add your actual 12-month return on each holding to see how you compare to the benchmark.</t>
+          <t>% | Add historic 12-month return on each holding to see how you compare to the benchmark.</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -24126,20 +24137,20 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/invest · /account-detail · /home</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr"/>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-007 — SAVED SCENARIOS (n)</t>
+          <t>MK-PF-M-021 — the value the return is on (with a price history)</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
       <c r="F346" s="2" t="inlineStr"/>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>words looked for: saved scenarios</t>
+          <t>words looked for: value return price history</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -24157,20 +24168,20 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/invest · /account-detail · /home</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr"/>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-011 — Monthly saving until then</t>
+          <t>MK-PF-M-022 — the value left out (no price history)</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr"/>
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>words looked for: monthly saving until then</t>
+          <t>words looked for: value left out price history</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -24188,20 +24199,20 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>/required-withdrawals</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr"/>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-014 — Taken so far $X · still to take</t>
+          <t>MK-PL-M-007 — SAVED SCENARIOS (n)</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr"/>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>words looked for: taken / still take</t>
+          <t>words looked for: saved scenarios</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -24219,20 +24230,20 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/will-it-last</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr"/>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-017 — Monthly check (today's dollars)</t>
+          <t>MK-PL-M-011 — Monthly saving until then</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr"/>
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>words looked for: monthly check today dollars</t>
+          <t>words looked for: monthly saving until then</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -24250,20 +24261,20 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr"/>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-023 — Extra tax next April (calculated) — about $X</t>
+          <t>MK-PL-M-014 — Taken so far $X · still to take</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr"/>
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>words looked for: extra tax next april calculated / about</t>
+          <t>words looked for: taken / still take</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -24281,20 +24292,20 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr"/>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-025 — +$X/mo (the saving dial)</t>
+          <t>MK-PL-M-017 — Monthly check (today's dollars)</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr"/>
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>words looked for: saving dial</t>
+          <t>words looked for: monthly check today dollars</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -24312,20 +24323,20 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/roth</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-026 — $X → $Y (nest egg before and after)</t>
+          <t>MK-PL-M-023 — Extra tax next April (calculated) — about $X</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr"/>
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>words looked for: nest egg before after</t>
+          <t>words looked for: extra tax next april calculated / about</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -24349,14 +24360,14 @@
       <c r="C353" s="2" t="inlineStr"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-027 — the difference the change makes</t>
+          <t>MK-PL-M-025 — +$X/mo (the saving dial)</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr"/>
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>words looked for: difference change makes</t>
+          <t>words looked for: saving dial</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -24374,20 +24385,20 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>/multi-goal</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr"/>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-031 — paid off &lt;month&gt; · saves $X</t>
+          <t>MK-PL-M-026 — $X → $Y (nest egg before and after)</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr"/>
       <c r="F354" s="2" t="inlineStr"/>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>words looked for: paid off / saves</t>
+          <t>words looked for: nest egg before after</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -24405,20 +24416,20 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr"/>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-033 — your $X grows to $Y by age N at Z%/yr</t>
+          <t>MK-PL-M-027 — the difference the change makes</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr"/>
       <c r="F355" s="2" t="inlineStr"/>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>words looked for: grows age</t>
+          <t>words looked for: difference change makes</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -24436,20 +24447,20 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/multi-goal</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr"/>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-034 — At Z% return, your money lasts past age N</t>
+          <t>MK-PL-M-031 — paid off &lt;month&gt; · saves $X</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr"/>
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>words looked for: return money lasts past age</t>
+          <t>words looked for: paid off / saves</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -24473,14 +24484,14 @@
       <c r="C357" s="2" t="inlineStr"/>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-035 — Retire at age (the dial)</t>
+          <t>MK-PL-M-033 — your $X grows to $Y by age N at Z%/yr</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr"/>
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>words looked for: retire age dial</t>
+          <t>words looked for: grows age</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -24498,20 +24509,20 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr"/>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-036 — the future total cost of school</t>
+          <t>MK-PL-M-034 — At Z% return, your money lasts past age N</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr"/>
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>words looked for: future total cost school</t>
+          <t>words looked for: return money lasts past age</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -24529,20 +24540,20 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /home</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr"/>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-002 — = Planned surplus</t>
+          <t>MK-PL-M-035 — Retire at age (the dial)</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr"/>
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>words looked for: planned surplus</t>
+          <t>words looked for: retire age dial</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -24560,20 +24571,20 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /income-manager</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr"/>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-008 — YOUR SOURCES — Bonus</t>
+          <t>MK-PL-M-036 — the future total cost of school</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr"/>
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>words looked for: sources / bonus</t>
+          <t>words looked for: future total cost school</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -24591,20 +24602,20 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /income-manager</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr"/>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-009 — YOUR SOURCES — Stock vesting (equity)</t>
+          <t>MK-CF-M-002 — = Planned surplus</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>words looked for: sources / stock vesting equity</t>
+          <t>words looked for: planned surplus</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -24628,14 +24639,14 @@
       <c r="C362" s="2" t="inlineStr"/>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-010 — YOUR SOURCES — Rental property</t>
+          <t>MK-CF-M-008 — YOUR SOURCES — Bonus</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr"/>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>words looked for: sources / rental property</t>
+          <t>words looked for: sources / bonus</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
@@ -24659,14 +24670,14 @@
       <c r="C363" s="2" t="inlineStr"/>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-012 — RECEIVED · &lt;month&gt; — each payment</t>
+          <t>MK-CF-M-009 — YOUR SOURCES — Stock vesting (equity)</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr"/>
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>words looked for: received / payment</t>
+          <t>words looked for: sources / stock vesting equity</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -24684,20 +24695,20 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /bill-calendar</t>
+          <t>/cashflow · /income-manager</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr"/>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-016 — BIG-TICKET RADAR — &lt;bill&gt; · due &lt;month&gt;</t>
+          <t>MK-CF-M-010 — YOUR SOURCES — Rental property</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr"/>
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>words looked for: big ticket radar / due</t>
+          <t>words looked for: sources / rental property</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -24715,20 +24726,20 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>/base-pay · /cashflow · /income-manager</t>
+          <t>/cashflow · /income-manager</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr"/>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-031 — Take-home</t>
+          <t>MK-CF-M-012 — RECEIVED · &lt;month&gt; — each payment</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr"/>
       <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>words looked for: take home</t>
+          <t>words looked for: received / payment</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -24746,20 +24757,20 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>/income-summary · /income-manager</t>
+          <t>/cashflow · /bill-calendar</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr"/>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-037 — Take-home each month</t>
+          <t>MK-CF-M-016 — BIG-TICKET RADAR — &lt;bill&gt; · due &lt;month&gt;</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr"/>
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>words looked for: take home month</t>
+          <t>words looked for: big ticket radar / due</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -24777,20 +24788,20 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>/income-summary · /income-manager</t>
+          <t>/base-pay · /cashflow · /income-manager</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr"/>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-039 — its own month, never spread</t>
+          <t>MK-CF-M-031 — Take-home</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr"/>
       <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>words looked for: own month never spread</t>
+          <t>words looked for: take home</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -24808,20 +24819,20 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>/income-summary</t>
+          <t>/income-summary · /income-manager</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr"/>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-040 — is not here — it is reinvested where it is earned</t>
+          <t>MK-CF-M-037 — Take-home each month</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
       <c r="F368" s="2" t="inlineStr"/>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>words looked for: not here / reinvested where earned</t>
+          <t>words looked for: take home month</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -24839,20 +24850,20 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>/base-pay</t>
+          <t>/income-summary · /income-manager</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr"/>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-046 — Medicare 1.45% of everything, 0.9% more above</t>
+          <t>MK-CF-M-039 — its own month, never spread</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr"/>
       <c r="F369" s="2" t="inlineStr"/>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>words looked for: medicare everything more above</t>
+          <t>words looked for: own month never spread</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -24870,20 +24881,20 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/income-summary</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr"/>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-047 — Expected inflow</t>
+          <t>MK-CF-M-040 — is not here — it is reinvested where it is earned</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
       <c r="F370" s="2" t="inlineStr"/>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>words looked for: expected inflow</t>
+          <t>words looked for: not here / reinvested where earned</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
@@ -24901,20 +24912,20 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/base-pay</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr"/>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-048 — Planned outflow (expenses + debt)</t>
+          <t>MK-CF-M-046 — Medicare 1.45% of everything, 0.9% more above</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr"/>
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>words looked for: planned outflow expenses debt</t>
+          <t>words looked for: medicare everything more above</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
@@ -24932,20 +24943,20 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /home</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr"/>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-051 — Inflow</t>
+          <t>MK-CF-M-047 — Expected inflow</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr"/>
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>words looked for: inflow</t>
+          <t>words looked for: expected inflow</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -24963,20 +24974,20 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /home</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr"/>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
+          <t>MK-CF-M-048 — Planned outflow (expenses + debt)</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr"/>
       <c r="F373" s="2" t="inlineStr"/>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>words looked for: outflow expenses debt</t>
+          <t>words looked for: planned outflow expenses debt</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -25000,14 +25011,14 @@
       <c r="C374" s="2" t="inlineStr"/>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-053 — = Surplus</t>
+          <t>MK-CF-M-051 — Inflow</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr"/>
       <c r="F374" s="2" t="inlineStr"/>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>words looked for: surplus</t>
+          <t>words looked for: inflow</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
@@ -25025,20 +25036,20 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr"/>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-056 — left of your budget</t>
+          <t>MK-CF-M-052 — Outflow (expenses + debt)</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr"/>
       <c r="F375" s="2" t="inlineStr"/>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>words looked for: left budget</t>
+          <t>words looked for: outflow expenses debt</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
@@ -25056,20 +25067,20 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>/bill-calendar</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr"/>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-063 — Covered — about $X there by &lt;date&gt;</t>
+          <t>MK-CF-M-053 — = Surplus</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>words looked for: covered / about there</t>
+          <t>words looked for: surplus</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
@@ -25087,20 +25098,20 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>/income-manager</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr"/>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-066 — Dividends, interest &amp; coupons</t>
+          <t>MK-CF-M-056 — left of your budget</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr"/>
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>words looked for: dividends interest coupons</t>
+          <t>words looked for: left budget</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
@@ -25118,20 +25129,20 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /bill-calendar</t>
+          <t>/bill-calendar</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr"/>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-073 — /month</t>
+          <t>MK-CF-M-063 — Covered — about $X there by &lt;date&gt;</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
       <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>words looked for: month</t>
+          <t>words looked for: covered / about there</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
@@ -25149,20 +25160,20 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/income-manager</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr"/>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-074 — paid down since &lt;month&gt;</t>
+          <t>MK-CF-M-066 — Dividends, interest &amp; coupons</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr"/>
       <c r="F379" s="2" t="inlineStr"/>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>words looked for: paid down since</t>
+          <t>words looked for: dividends interest coupons</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
@@ -25180,20 +25191,20 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/cashflow · /bill-calendar</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr"/>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-075 — % of where you started</t>
+          <t>MK-CF-M-073 — /month</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
       <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>words looked for: where started</t>
+          <t>words looked for: month</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -25211,20 +25222,20 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>/big-costs</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr"/>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-002 — the total of your big costs</t>
+          <t>MK-CF-M-074 — paid down since &lt;month&gt;</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr"/>
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>words looked for: total big costs</t>
+          <t>words looked for: paid down since</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -25242,20 +25253,20 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr"/>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-017 — the life-cover gap</t>
+          <t>MK-CF-M-075 — % of where you started</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
       <c r="F382" s="2" t="inlineStr"/>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>words looked for: life cover gap</t>
+          <t>words looked for: where started</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
@@ -25273,20 +25284,20 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>/contribution-room · /home</t>
+          <t>/big-costs</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr"/>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-003 — $X left / up to $Y</t>
+          <t>MK-MN-M-002 — the total of your big costs</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr"/>
       <c r="F383" s="2" t="inlineStr"/>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>words looked for: left</t>
+          <t>words looked for: total big costs</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
@@ -25304,20 +25315,20 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>/credit</t>
+          <t>/insurance</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr"/>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-006 — $X of $Y used — the line marks 30%</t>
+          <t>MK-MN-M-017 — the life-cover gap</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
       <c r="F384" s="2" t="inlineStr"/>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>words looked for: used / line marks</t>
+          <t>words looked for: life cover gap</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
@@ -25335,20 +25346,20 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>/insights</t>
+          <t>/contribution-room · /home</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr"/>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-016 — Total invested · Cash total · Investable total</t>
+          <t>MK-MN-M-003 — $X left / up to $Y</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>words looked for: total invested / cash total / investable total</t>
+          <t>words looked for: left</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -25366,20 +25377,20 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>/jobsafety</t>
+          <t>/credit</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr"/>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-021 — Using $X/month from your logged expenses</t>
+          <t>MK-MN-M-006 — $X of $Y used — the line marks 30%</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>words looked for: using month logged expenses</t>
+          <t>words looked for: used / line marks</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -25392,34 +25403,30 @@
     <row r="387" ht="60" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>function inside no question</t>
+          <t>row not seen on its screen</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>src/domain/budget/index.ts</t>
+          <t>/insights</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr"/>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-012 annualCashflow</t>
-        </is>
-      </c>
-      <c r="E387" s="2" t="inlineStr">
-        <is>
-          <t>2 · DISPLAYED</t>
-        </is>
-      </c>
+          <t>MK-MN-M-016 — Total invested · Cash total · Investable total</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr"/>
       <c r="F387" s="2" t="inlineStr"/>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>reaches a screen: Yes</t>
+          <t>words looked for: total invested / cash total / investable total</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>This calculation exists in the code, but none of the 22 questions leads to it. Either it prints a figure that has no row, or the map is missing a question, or the code is dead. Claude reads each one and says which; you rule on any that need a new question.</t>
+          <t>The master file has a row for this figure, but the words on the row were not found on the screen. Either the words on the row are out of date, or the figure only appears after a tap the census cannot make. Claude reads each one and fixes the row or the census; nothing for you to decide yet.</t>
         </is>
       </c>
       <c r="I387" s="2" t="n"/>
@@ -25427,34 +25434,30 @@
     <row r="388" ht="60" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>function inside no question</t>
+          <t>row not seen on its screen</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>src/domain/debt/mortgageOdds.ts</t>
+          <t>/jobsafety</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr"/>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-042 mortgageOddsEffect</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>2 · DISPLAYED</t>
-        </is>
-      </c>
+          <t>MK-MN-M-021 — Using $X/month from your logged expenses</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr"/>
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>reaches a screen: Yes</t>
+          <t>words looked for: using month logged expenses</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>This calculation exists in the code, but none of the 22 questions leads to it. Either it prints a figure that has no row, or the map is missing a question, or the code is dead. Claude reads each one and says which; you rule on any that need a new question.</t>
+          <t>The master file has a row for this figure, but the words on the row were not found on the screen. Either the words on the row are out of date, or the figure only appears after a tap the census cannot make. Claude reads each one and fixes the row or the census; nothing for you to decide yet.</t>
         </is>
       </c>
       <c r="I388" s="2" t="n"/>
@@ -25467,13 +25470,13 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>src/domain/debt/mortgageVsTreasury.ts</t>
+          <t>src/domain/budget/index.ts</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr"/>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-043 compareMortgageToTreasury</t>
+          <t>MK-CF-F-012 annualCashflow</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -25502,18 +25505,18 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>src/domain/debt/mortgageVsTreasury.ts</t>
+          <t>src/domain/debt/mortgageOdds.ts</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr"/>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-125 amortise</t>
+          <t>MK-CF-F-042 mortgageOddsEffect</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>3 · DEPENDENT</t>
+          <t>2 · DISPLAYED</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr"/>
@@ -25543,12 +25546,12 @@
       <c r="C391" s="2" t="inlineStr"/>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-F-126 futureValue</t>
+          <t>MK-CF-F-043 compareMortgageToTreasury</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>3 · DEPENDENT</t>
+          <t>2 · DISPLAYED</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr"/>
@@ -25572,18 +25575,18 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
+          <t>src/domain/debt/mortgageVsTreasury.ts</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr"/>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-018 theDebts</t>
+          <t>MK-CF-F-125 amortise</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>2 · DISPLAYED</t>
+          <t>3 · DEPENDENT</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr"/>
@@ -25607,18 +25610,18 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts</t>
+          <t>src/domain/debt/mortgageVsTreasury.ts</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr"/>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-F-101 PLAN</t>
+          <t>MK-CF-F-126 futureValue</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>2 · DISPLAYED</t>
+          <t>3 · DEPENDENT</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr"/>
@@ -25642,13 +25645,13 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>src/domain/retirement/index.ts</t>
+          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr"/>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-F-048 capitalNeeded</t>
+          <t>MK-CF-O-018 theDebts</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -25677,18 +25680,18 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Calculation Module code/engines/holding-class.ts</t>
+          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr"/>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>MK-ST-F-011 classifyHoldingClass</t>
+          <t>MK-NW-F-101 PLAN</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>3 · DEPENDENT</t>
+          <t>2 · DISPLAYED</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
@@ -25712,13 +25715,13 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Calculation Module code/engines/money.ts</t>
+          <t>src/domain/retirement/index.ts</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr"/>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>MK-ST-F-019 signed</t>
+          <t>MK-PL-F-048 capitalNeeded</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -25747,18 +25750,18 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>src/domain/completeness/index.ts</t>
+          <t>Calculation Module code/engines/holding-class.ts</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr"/>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-F-001 planCompleteness</t>
+          <t>MK-ST-F-011 classifyHoldingClass</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>2 · DISPLAYED</t>
+          <t>3 · DEPENDENT</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr"/>
@@ -25777,16 +25780,86 @@
     <row r="398" ht="60" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>plumbing categorised as calculation (rule 8)</t>
+          <t>function inside no question</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>services · import parsing · store hooks · sign-in</t>
+          <t>Calculation Module code/engines/money.ts</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr"/>
       <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>MK-ST-F-019 signed</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>2 · DISPLAYED</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr"/>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>reaches a screen: Yes</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>This calculation exists in the code, but none of the 22 questions leads to it. Either it prints a figure that has no row, or the map is missing a question, or the code is dead. Claude reads each one and says which; you rule on any that need a new question.</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="n"/>
+    </row>
+    <row r="399" ht="60" customHeight="1">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>function inside no question</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/completeness/index.ts</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr"/>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-F-001 planCompleteness</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>2 · DISPLAYED</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr"/>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>reaches a screen: Yes</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>This calculation exists in the code, but none of the 22 questions leads to it. Either it prints a figure that has no row, or the map is missing a question, or the code is dead. Claude reads each one and says which; you rule on any that need a new question.</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="n"/>
+    </row>
+    <row r="400" ht="60" customHeight="1">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>plumbing categorised as calculation (rule 8)</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>services · import parsing · store hooks · sign-in</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr"/>
+      <c r="D400" s="2" t="inlineStr">
         <is>
           <t>MK-XS-F-012 decodeCsvBase64 (holdingsImport.ts)
 MK-XS-F-013 parseCsv (holdingsImport.ts)
@@ -25840,94 +25913,16 @@
 MK-XS-F-178 useLevel (useStore.ts)</t>
         </is>
       </c>
-      <c r="E398" s="2" t="inlineStr">
+      <c r="E400" s="2" t="inlineStr">
         <is>
           <t>50 functions</t>
         </is>
       </c>
-      <c r="F398" s="2" t="inlineStr"/>
-      <c r="G398" s="2" t="inlineStr"/>
-      <c r="H398" s="2" t="inlineStr">
-        <is>
-          <t>rule 8: an action or bring-data-in function is listed as such; the build categorised these as DISPLAYED or DEPENDENT because their return reaches a screen (a lock state, a sync status, a parsed file). Recommend: re-categorise in the build, one rule for the lot — your ruling</t>
-        </is>
-      </c>
-      <c r="I398" s="2" t="n"/>
-    </row>
-    <row r="399" ht="60" customHeight="1">
-      <c r="A399" s="2" t="inlineStr">
-        <is>
-          <t>orchestrator orphan</t>
-        </is>
-      </c>
-      <c r="B399" s="2" t="inlineStr">
-        <is>
-          <t>no screen imports it</t>
-        </is>
-      </c>
-      <c r="C399" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/functions/cashflow/expenses.ts</t>
-        </is>
-      </c>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>MK-CF-O-002 expenses</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>named by 0 row(s)</t>
-        </is>
-      </c>
-      <c r="F399" s="2" t="inlineStr">
-        <is>
-          <t>imported by 0 screen(s)</t>
-        </is>
-      </c>
-      <c r="G399" s="2" t="inlineStr"/>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
-        </is>
-      </c>
-      <c r="I399" s="2" t="n"/>
-    </row>
-    <row r="400" ht="60" customHeight="1">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>orchestrator orphan</t>
-        </is>
-      </c>
-      <c r="B400" s="2" t="inlineStr">
-        <is>
-          <t>no screen imports it</t>
-        </is>
-      </c>
-      <c r="C400" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
-        </is>
-      </c>
-      <c r="D400" s="2" t="inlineStr">
-        <is>
-          <t>MK-CF-O-003 thisMonth</t>
-        </is>
-      </c>
-      <c r="E400" s="2" t="inlineStr">
-        <is>
-          <t>named by 8 row(s)</t>
-        </is>
-      </c>
-      <c r="F400" s="2" t="inlineStr">
-        <is>
-          <t>imported by 0 screen(s)</t>
-        </is>
-      </c>
+      <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
+          <t>rule 8: an action or bring-data-in function is listed as such; the build categorised these as DISPLAYED or DEPENDENT because their return reaches a screen (a lock state, a sync status, a parsed file). Recommend: re-categorise in the build, one rule for the lot — your ruling</t>
         </is>
       </c>
       <c r="I400" s="2" t="n"/>
@@ -25940,17 +25935,17 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>/contribution-room</t>
+          <t>no screen imports it</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/contribution-room.ts</t>
+          <t>MoneyKeel/functions/cashflow/expenses.ts</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-005 theContributionRoom</t>
+          <t>MK-CF-O-002 expenses</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -25960,7 +25955,7 @@
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>imported by 1 screen(s)</t>
+          <t>imported by 0 screen(s)</t>
         </is>
       </c>
       <c r="G401" s="2" t="inlineStr"/>
@@ -25979,27 +25974,27 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>/tax-organizer</t>
+          <t>no screen imports it</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/tax-organizer.ts</t>
+          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-007 theTaxOrganizer</t>
+          <t>MK-CF-O-003 thisMonth</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>named by 0 row(s)</t>
+          <t>named by 8 row(s)</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>imported by 1 screen(s)</t>
+          <t>imported by 0 screen(s)</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr"/>
@@ -26018,17 +26013,17 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>no screen imports it</t>
+          <t>/contribution-room</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
+          <t>MoneyKeel/functions/cashflow/contribution-room.ts</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-011 PAY</t>
+          <t>MK-CF-O-005 theContributionRoom</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -26038,7 +26033,7 @@
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>imported by 0 screen(s)</t>
+          <t>imported by 1 screen(s)</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr"/>
@@ -26057,17 +26052,17 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>no screen imports it</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
+          <t>MoneyKeel/functions/cashflow/tax-organizer.ts</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-012 PAY_ESTIMATED</t>
+          <t>MK-CF-O-007 theTaxOrganizer</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -26077,7 +26072,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>imported by 0 screen(s)</t>
+          <t>imported by 1 screen(s)</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -26106,7 +26101,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-013 PAY_LANDS_TYPED</t>
+          <t>MK-CF-O-011 PAY</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -26140,12 +26135,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-014 M</t>
+          <t>MK-CF-O-012 PAY_ESTIMATED</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -26179,12 +26174,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-015 workedLineAmount</t>
+          <t>MK-CF-O-013 PAY_LANDS_TYPED</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -26218,12 +26213,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
+          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-016 incomeSources</t>
+          <t>MK-CF-O-014 M</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -26257,17 +26252,17 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
+          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-018 theDebts</t>
+          <t>MK-CF-O-015 workedLineAmount</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>named by 8 row(s)</t>
+          <t>named by 0 row(s)</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -26291,7 +26286,7 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>/income-manager</t>
+          <t>no screen imports it</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -26301,7 +26296,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-019 theIncomeManager</t>
+          <t>MK-CF-O-016 incomeSources</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -26311,7 +26306,7 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>imported by 1 screen(s)</t>
+          <t>imported by 0 screen(s)</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr"/>
@@ -26330,27 +26325,27 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>/plan · /cashflow</t>
+          <t>no screen imports it</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/budget-counted.ts</t>
+          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-020 theBudgetCounted</t>
+          <t>MK-CF-O-018 theDebts</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>named by 0 row(s)</t>
+          <t>named by 8 row(s)</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>imported by 2 screen(s)</t>
+          <t>imported by 0 screen(s)</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr"/>
@@ -26364,85 +26359,77 @@
     <row r="412" ht="60" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>orchestrator orphan</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/account-detail · /analytics · /base-pay · /bill-calendar · /bonds · /cashflow · /holding-detail · /home · /income-manager · /income-summary · /insights · /invest · /itemize · /monthly-income · /other-investments</t>
+          <t>/income-manager</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:74</t>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>spec.unit === 'money' ? formatMoney(value)</t>
+          <t>MK-CF-O-019 theIncomeManager</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>$420, $600, $151,000, $165,000 … (1279 renders)</t>
+          <t>named by 0 row(s)</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>inside writeFigure</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
-        </is>
-      </c>
+          <t>imported by 1 screen(s)</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr"/>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
         </is>
       </c>
       <c r="I412" s="2" t="n"/>
     </row>
-    <row r="413" ht="45" customHeight="1">
+    <row r="413" ht="60" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>orchestrator orphan</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
+          <t>/plan · /cashflow</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:76</t>
+          <t>MoneyKeel/functions/cashflow/budget-counted.ts</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>: spec.unit === 'money-cents' ? formatMoneyCents(value)</t>
+          <t>MK-CF-O-020 theBudgetCounted</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>$90.00 … (3 renders)</t>
+          <t>named by 0 row(s)</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>inside writeFigure</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average), MK-NW-M-029 CURRENT PRICE · LIVE</t>
-        </is>
-      </c>
+          <t>imported by 2 screen(s)</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr"/>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
         </is>
       </c>
       <c r="I413" s="2" t="n"/>
@@ -26455,32 +26442,32 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
+          <t>/account-detail · /analytics · /base-pay · /bill-calendar · /bonds · /cashflow · /holding-detail · /home · /income-manager · /income-summary · /insights · /invest · /itemize · /monthly-income · /other-investments</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:80</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
+          <t>spec.unit === 'money' ? formatMoney(value)</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
+          <t>$420, $600, $165,000, $151,000 … (1292 renders)</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>inside basePay</t>
+          <t>inside writeFigure</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26490,45 +26477,45 @@
       </c>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="60" customHeight="1">
+    <row r="415" ht="45" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>src/components/DrawSteerSheet.tsx:137 (+1 spoken/visible twin)</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:82</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
+          <t>: spec.unit === 'money-cents' ? formatMoneyCents(value)</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>$250,000 … (10 renders)</t>
+          <t>$90.00 … (3 renders)</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>inside DrawSteerSheet</t>
+          <t>inside writeFigure</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average), MK-NW-M-029 CURRENT PRICE · LIVE</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I415" s="2" t="n"/>
@@ -26541,32 +26528,32 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:285</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
+          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>$0 … (14 renders)</t>
+          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>inside AllocateSavings</t>
+          <t>inside basePay</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -26579,42 +26566,42 @@
     <row r="417" ht="60" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:324</t>
+          <t>src/components/DrawSteerSheet.tsx:137 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>$0 … (7 renders)</t>
+          <t>$250,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>inside AllocateSavings</t>
+          <t>inside DrawSteerSheet</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I417" s="2" t="n"/>
@@ -26627,32 +26614,32 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>src/components/MortgageRateCompare.tsx:56 (+1 spoken/visible twin)</t>
+          <t>src/components/MoneySheets.tsx:285</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">accessibilityLabel={`${rates} A dollar into your mortgage saves you ${c.direction === 'paying-down-wins' ? 'more' : 'less'} than the same dollar would earn in Treasuries, about ${spokenMoney(yearly)} </t>
+          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>$5,320 … (4 renders)</t>
+          <t>$0 … (14 renders)</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>inside MortgageRateCompare</t>
+          <t>inside AllocateSavings</t>
         </is>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26670,32 +26657,32 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/cashflow · /home</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
+          <t>src/components/MoneySheets.tsx:324</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
+          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>$4,795 … (14 renders)</t>
+          <t>$0 … (7 renders)</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>inside PaycheckCard</t>
+          <t>inside AllocateSavings</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26713,123 +26700,123 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
+          <t>/cashflow</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>src/components/MortgageRateCompare.tsx:56 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accessibilityLabel={`${rates} A dollar into your mortgage saves you ${c.direction === 'paying-down-wins' ? 'more' : 'less'} than the same dollar would earn in Treasuries, about ${spokenMoney(yearly)} </t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>$5,320 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>inside MortgageRateCompare</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="n"/>
+    </row>
+    <row r="421" ht="45" customHeight="1">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
           <t>/cashflow · /home</t>
         </is>
       </c>
-      <c r="C420" s="2" t="inlineStr">
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>$4,795 … (14 renders)</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>inside PaycheckCard</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="n"/>
+    </row>
+    <row r="422" ht="60" customHeight="1">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow · /home</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
         <is>
           <t>src/components/PaycheckCard.tsx:49</t>
         </is>
       </c>
-      <c r="D420" s="2" t="inlineStr">
+      <c r="D422" s="2" t="inlineStr">
         <is>
           <t>&lt;Row key={i} label={g.source + (g.day ? ` (day ${g.day})` : '')} value={maskedMoney(g.amount)} /&gt;</t>
         </is>
       </c>
-      <c r="E420" s="2" t="inlineStr">
+      <c r="E422" s="2" t="inlineStr">
         <is>
           <t>$2,200, $1,300 … (14 renders)</t>
         </is>
       </c>
-      <c r="F420" s="2" t="inlineStr">
+      <c r="F422" s="2" t="inlineStr">
         <is>
           <t>inside PaycheckCard</t>
         </is>
       </c>
-      <c r="G420" s="2" t="inlineStr">
+      <c r="G422" s="2" t="inlineStr">
         <is>
           <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
-      <c r="H420" s="2" t="inlineStr">
+      <c r="H422" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="n"/>
-    </row>
-    <row r="421" ht="60" customHeight="1">
-      <c r="A421" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B421" s="2" t="inlineStr">
-        <is>
-          <t>/cashflow · /home</t>
-        </is>
-      </c>
-      <c r="C421" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PaycheckCard.tsx:54</t>
-        </is>
-      </c>
-      <c r="D421" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={[styles.rowValue, { fontWeight: '800' }]}&gt;{maskedMoney(m.guaranteedTotal)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E421" s="2" t="inlineStr">
-        <is>
-          <t>$3,500 … (7 renders)</t>
-        </is>
-      </c>
-      <c r="F421" s="2" t="inlineStr">
-        <is>
-          <t>inside PaycheckCard</t>
-        </is>
-      </c>
-      <c r="G421" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
-        </is>
-      </c>
-      <c r="H421" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I421" s="2" t="n"/>
-    </row>
-    <row r="422" ht="30" customHeight="1">
-      <c r="A422" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B422" s="2" t="inlineStr">
-        <is>
-          <t>/cashflow · /home</t>
-        </is>
-      </c>
-      <c r="C422" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PaycheckCard.tsx:59</t>
-        </is>
-      </c>
-      <c r="D422" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.rowValue}&gt;{maskedMoney(m.safeDraw)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr">
-        <is>
-          <t>$1,295 … (7 renders)</t>
-        </is>
-      </c>
-      <c r="F422" s="2" t="inlineStr">
-        <is>
-          <t>inside PaycheckCard</t>
-        </is>
-      </c>
-      <c r="G422" s="2" t="inlineStr">
-        <is>
-          <t>MK-CF-M-055 Draw from savings</t>
-        </is>
-      </c>
-      <c r="H422" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I422" s="2" t="n"/>
@@ -26837,7 +26824,7 @@
     <row r="423" ht="60" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -26847,17 +26834,17 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:65</t>
+          <t>src/components/PaycheckCard.tsx:54</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.year}&gt;This year ~{maskedMoney(year.thisYear)} &lt;EstimateTag /&gt; &lt;Text style={styles.yearNote}&gt;— varies month to month&lt;/Text&gt;&lt;/Text&gt;</t>
+          <t>&lt;Text style={[styles.rowValue, { fontWeight: '800' }]}&gt;{maskedMoney(m.guaranteedTotal)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>$55,140 … (7 renders)</t>
+          <t>$3,500 … (7 renders)</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -26867,17 +26854,17 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I423" s="2" t="n"/>
     </row>
-    <row r="424" ht="45" customHeight="1">
+    <row r="424" ht="30" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -26885,32 +26872,32 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:124</t>
+          <t>src/components/PaycheckCard.tsx:59</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>We're including your {maskedMoney(mortgageMonthly)}/month mortgage until it's paid off in {mortgagePayoffYear}, from your loan.</t>
+          <t>&lt;Text style={styles.rowValue}&gt;{maskedMoney(m.safeDraw)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>$1,900</t>
+          <t>$1,295 … (7 renders)</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>inside PlanInputs</t>
+          <t>inside PaycheckCard</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
+          <t>MK-CF-M-055 Draw from savings</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -26928,27 +26915,27 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:146</t>
+          <t>src/components/PaycheckCard.tsx:65</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
+          <t>&lt;Text style={styles.year}&gt;This year ~{maskedMoney(year.thisYear)} &lt;EstimateTag /&gt; &lt;Text style={styles.yearNote}&gt;— varies month to month&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>$1,080,000, $1,160,000, $130,000 … (4 renders)</t>
+          <t>$55,140 … (7 renders)</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>inside PlanInputs</t>
+          <t>inside PaycheckCard</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -26976,17 +26963,17 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:153</t>
+          <t>src/components/PlanInputs.tsx:124</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
+          <t>We're including your {maskedMoney(mortgageMonthly)}/month mortgage until it's paid off in {mortgagePayoffYear}, from your loan.</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
+          <t>$1,900</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
@@ -27019,17 +27006,17 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:165 (+1 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:146</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
+          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
+          <t>$1,080,000, $1,160,000, $130,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
@@ -27049,10 +27036,10 @@
       </c>
       <c r="I427" s="2" t="n"/>
     </row>
-    <row r="428" ht="60" customHeight="1">
+    <row r="428" ht="45" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -27062,17 +27049,17 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:183 (+2 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:153</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
+          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>$25,000 … (3 renders)</t>
+          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
@@ -27082,12 +27069,12 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I428" s="2" t="n"/>
@@ -27105,22 +27092,22 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:253</t>
+          <t>src/components/PlanInputs.tsx:165 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>$0 … (5 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>inside Stepper</t>
+          <t>inside PlanInputs</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
@@ -27148,22 +27135,22 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>src/components/SpendMoreControl.tsx:61</t>
+          <t>src/components/PlanInputs.tsx:183 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.amt} accessibilityLabel={`${spokenMoney(extra)} more in expenses each month`}&gt;{maskedMoney(extra)}&lt;/Text&gt;</t>
+          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>$0 … (4 renders)</t>
+          <t>$25,000 … (3 renders)</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>inside SpendMoreControl</t>
+          <t>inside PlanInputs</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -27178,10 +27165,10 @@
       </c>
       <c r="I430" s="2" t="n"/>
     </row>
-    <row r="431" ht="45" customHeight="1">
+    <row r="431" ht="60" customHeight="1">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -27191,32 +27178,32 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>src/components/SpendMoreControl.tsx:73</t>
+          <t>src/components/PlanInputs.tsx:253</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>? &lt;&gt;You'd spend &lt;Text style={s.b}&gt;{maskedMoney(total)}&lt;/Text&gt;/month — the same as now.&lt;/&gt;</t>
+          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>$3,800 … (2 renders)</t>
+          <t>$0 … (5 renders)</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>inside SpendMoreControl</t>
+          <t>inside Stepper</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I431" s="2" t="n"/>
@@ -27229,27 +27216,27 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>/tips</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>src/components/UI.tsx:179</t>
+          <t>src/components/SpendMoreControl.tsx:61</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
+          <t>&lt;Text style={s.amt} accessibilityLabel={`${spokenMoney(extra)} more in expenses each month`}&gt;{maskedMoney(extra)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>$0 … (12 renders)</t>
+          <t>$0 … (4 renders)</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>inside AmountText</t>
+          <t>inside SpendMoreControl</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
@@ -27264,45 +27251,45 @@
       </c>
       <c r="I432" s="2" t="n"/>
     </row>
-    <row r="433" ht="60" customHeight="1">
+    <row r="433" ht="45" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>/income-detail · /tax-organizer</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>src/domain/income/from-accounts.ts:176</t>
+          <t>src/components/SpendMoreControl.tsx:73</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
+          <t>? &lt;&gt;You'd spend &lt;Text style={s.b}&gt;{maskedMoney(total)}&lt;/Text&gt;/month — the same as now.&lt;/&gt;</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>$10,000 … (2 renders)</t>
+          <t>$3,800 … (2 renders)</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>inside incomeFromAccounts</t>
+          <t>inside SpendMoreControl</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I433" s="2" t="n"/>
@@ -27315,27 +27302,27 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /plan</t>
+          <t>/tips</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:357</t>
+          <t>src/components/UI.tsx:179</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
+          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>$439,000 … (10 renders)</t>
+          <t>$0 … (12 renders)</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>inside onCourseSentence</t>
+          <t>inside AmountText</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
@@ -27358,27 +27345,27 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/big-costs</t>
+          <t>/income-detail · /tax-organizer</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>src/screens/BigCostsScreen.tsx:46</t>
+          <t>src/domain/income/from-accounts.ts:176</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
+          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>$0 … (3 renders)</t>
+          <t>$10,000 … (2 renders)</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>inside BigCostsScreen</t>
+          <t>inside incomeFromAccounts</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
@@ -27401,80 +27388,80 @@
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
+          <t>/analytics · /plan</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:357</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>$439,000 … (10 renders)</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>inside onCourseSentence</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="n"/>
+    </row>
+    <row r="437" ht="60" customHeight="1">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
           <t>/big-costs</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/BigCostsScreen.tsx:61 (+2 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D436" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`${c.label}, ${spokenMoney(c.amount)} in ${c.year}. Opens the editor.`}</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr">
-        <is>
-          <t>$25,000 … (3 renders)</t>
-        </is>
-      </c>
-      <c r="F436" s="2" t="inlineStr">
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/BigCostsScreen.tsx:46</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (3 renders)</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
         <is>
           <t>inside BigCostsScreen</t>
         </is>
       </c>
-      <c r="G436" s="2" t="inlineStr">
+      <c r="G437" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H436" s="2" t="inlineStr">
+      <c r="H437" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
-      <c r="I436" s="2" t="n"/>
-    </row>
-    <row r="437" ht="45" customHeight="1">
-      <c r="A437" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B437" s="2" t="inlineStr">
-        <is>
-          <t>/contribution-room</t>
-        </is>
-      </c>
-      <c r="C437" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/ContributionRoomScreen.tsx:30</t>
-        </is>
-      </c>
-      <c r="D437" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.room}&gt;{knownUsed ? `${money(room)} left` : `up to ${money(limit)}`}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>$14,900, $1,500, $4,400, $32,500 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F437" s="2" t="inlineStr">
-        <is>
-          <t>inside RoomCard</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-004 about $X of the $Y limit</t>
-        </is>
-      </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I437" s="2" t="n"/>
@@ -27482,42 +27469,42 @@
     <row r="438" ht="60" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>/contribution-room</t>
+          <t>/big-costs</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ContributionRoomScreen.tsx:34</t>
+          <t>src/screens/BigCostsScreen.tsx:61 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>{knownUsed ? `That is about ${money(used)} of the ${money(limit)} limit — calculated from what you entered you contribute each month, not from your payroll, so check it against your latest statement.`</t>
+          <t>accessibilityLabel={`${c.label}, ${spokenMoney(c.amount)} in ${c.year}. Opens the editor.`}</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $24,500, $6,000, $7,500 … (18 renders)</t>
+          <t>$25,000 … (3 renders)</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>inside RoomCard</t>
+          <t>inside BigCostsScreen</t>
         </is>
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-004 about $X of the $Y limit</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I438" s="2" t="n"/>
@@ -27525,7 +27512,7 @@
     <row r="439" ht="45" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -27535,32 +27522,32 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ContributionRoomScreen.tsx:74 (+1 spoken/visible twin)</t>
+          <t>src/screens/ContributionRoomScreen.tsx:30</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Try it in a what-if: about ${money(perMonth)} a month for the rest of the year`}&gt;</t>
+          <t>&lt;Text style={s.room}&gt;{knownUsed ? `${money(room)} left` : `up to ${money(limit)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>$5,000, $10,800, $8,200 … (8 renders)</t>
+          <t>$14,900, $1,500, $4,400, $32,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>inside ContributionRoomScreen</t>
+          <t>inside RoomCard</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-005 about $X for the rest of the year, MK-MN-M-004 about $X of the $Y limit</t>
+          <t>MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I439" s="2" t="n"/>
@@ -27568,85 +27555,85 @@
     <row r="440" ht="60" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/contribution-room</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
+          <t>src/screens/ContributionRoomScreen.tsx:34</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
+          <t>{knownUsed ? `That is about ${money(used)} of the ${money(limit)} limit — calculated from what you entered you contribute each month, not from your payroll, so check it against your latest statement.`</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>$210,622 … (8 renders)</t>
+          <t>$9,600, $24,500, $6,000, $7,500 … (18 renders)</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>inside EducationScreen</t>
+          <t>inside RoomCard</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I440" s="2" t="n"/>
     </row>
-    <row r="441" ht="60" customHeight="1">
+    <row r="441" ht="45" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/contribution-room</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>src/screens/EducationScreen.tsx:74</t>
+          <t>src/screens/ContributionRoomScreen.tsx:74 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`Try it in a what-if: about ${money(perMonth)} a month for the rest of the year`}&gt;</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>$1,285 … (4 renders)</t>
+          <t>$5,000, $10,800, $8,200 … (8 renders)</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>inside EducationScreen</t>
+          <t>inside ContributionRoomScreen</t>
         </is>
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-005 about $X for the rest of the year, MK-MN-M-004 about $X of the $Y limit</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I441" s="2" t="n"/>
@@ -27659,27 +27646,27 @@
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>/expense</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ExpenseScreen.tsx:225</t>
+          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>$60.00, $120.00</t>
+          <t>$210,622 … (8 renders)</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>inside ExpenseScreen</t>
+          <t>inside EducationScreen</t>
         </is>
       </c>
       <c r="G442" s="2" t="inlineStr">
@@ -27702,27 +27689,27 @@
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>/goals</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:92</t>
+          <t>src/screens/EducationScreen.tsx:74</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>$1,880, $100 … (4 renders)</t>
+          <t>$1,285 … (4 renders)</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>inside GoalsScreen</t>
+          <t>inside EducationScreen</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -27740,85 +27727,85 @@
     <row r="444" ht="60" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
+          <t>/expense</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/ExpenseScreen.tsx:225</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>$60.00, $120.00</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>inside ExpenseScreen</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="n"/>
+    </row>
+    <row r="445" ht="60" customHeight="1">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C444" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:93</t>
-        </is>
-      </c>
-      <c r="D444" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.capLab}&gt;typical free cash to save{capacity.lumpy ? ` · ranges ${money(capacity.min)}–${money(capacity.max)} (some months free up more)` : ''}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr">
-        <is>
-          <t>-$1,420, $2,180, -$3,200, $400 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F444" s="2" t="inlineStr">
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:92</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>$1,880, $100 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-008 typical free cash to save $X/mo</t>
-        </is>
-      </c>
-      <c r="H444" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="n"/>
-    </row>
-    <row r="445" ht="45" customHeight="1">
-      <c r="A445" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B445" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C445" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:101</t>
-        </is>
-      </c>
-      <c r="D445" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget comes to {money(0)}/year.&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (2 renders)</t>
-        </is>
-      </c>
-      <c r="F445" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I445" s="2" t="n"/>
@@ -27836,118 +27823,118 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
+          <t>src/screens/GoalsScreen.tsx:93</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.capLab}&gt;typical free cash to save{capacity.lumpy ? ` · ranges ${money(capacity.min)}–${money(capacity.max)} (some months free up more)` : ''}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>-$1,420, $2,180, -$3,200, $400 … (8 renders)</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>inside GoalsScreen</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-008 typical free cash to save $X/mo</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="n"/>
+    </row>
+    <row r="447" ht="45" customHeight="1">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:101</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget comes to {money(0)}/year.&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>inside GoalsScreen</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="n"/>
+    </row>
+    <row r="448" ht="60" customHeight="1">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
           <t>src/screens/GoalsScreen.tsx:108</t>
         </is>
       </c>
-      <c r="D446" s="2" t="inlineStr">
+      <c r="D448" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget{sinkBasis.allPct ? ` (${sinkBasis.pct}% of take-home pay)` : ''} comes to ~{money(sink.annual)}/year. Set aside {money(sink.monthly)}/month so n</t>
         </is>
       </c>
-      <c r="E446" s="2" t="inlineStr">
+      <c r="E448" s="2" t="inlineStr">
         <is>
           <t>$3,600, $300, $2,400, $200 … (12 renders)</t>
         </is>
       </c>
-      <c r="F446" s="2" t="inlineStr">
+      <c r="F448" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G446" s="2" t="inlineStr">
+      <c r="G448" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
-      <c r="H446" s="2" t="inlineStr">
+      <c r="H448" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="n"/>
-    </row>
-    <row r="447" ht="60" customHeight="1">
-      <c r="A447" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B447" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C447" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:142</t>
-        </is>
-      </c>
-      <c r="D447" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.goalSub}&gt;{money(g.saved)} of {money(g.target)} · {money(remaining)} to go{perMonth &gt; 0 ? ` · need ~${money(perMonth)}/month${mo &gt; 0 ? ` for ${mo} mo` : ''}` : ''}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr">
-        <is>
-          <t>$0, $60,000, $1,538, $20,000 … (16 renders)</t>
-        </is>
-      </c>
-      <c r="F447" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
-        </is>
-      </c>
-      <c r="H447" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I447" s="2" t="n"/>
-    </row>
-    <row r="448" ht="45" customHeight="1">
-      <c r="A448" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B448" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C448" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:145</t>
-        </is>
-      </c>
-      <c r="D448" s="2" t="inlineStr">
-        <is>
-          <t>This month: funded {money(fundedMo)} of {money(perMonth)}/month{behind ? ' — allocate more to catch up.' : ' ✓'}</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>$0, $1,538, $1,333 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F448" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
-        </is>
-      </c>
-      <c r="H448" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I448" s="2" t="n"/>
@@ -27955,7 +27942,7 @@
     <row r="449" ht="60" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -27965,17 +27952,17 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:151</t>
+          <t>src/screens/GoalsScreen.tsx:142</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.goalSub}&gt;{money(g.saved)} of {money(g.target)} · {money(remaining)} to go{perMonth &gt; 0 ? ` · need ~${money(perMonth)}/month${mo &gt; 0 ? ` for ${mo} mo` : ''}` : ''}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>$7,200 … (4 renders)</t>
+          <t>$0, $60,000, $1,538, $20,000 … (16 renders)</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
@@ -27985,20 +27972,20 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I449" s="2" t="n"/>
     </row>
-    <row r="450" ht="60" customHeight="1">
+    <row r="450" ht="45" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -28008,17 +27995,17 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:207</t>
+          <t>src/screens/GoalsScreen.tsx:145</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
+          <t>This month: funded {money(fundedMo)} of {money(perMonth)}/month{behind ? ' — allocate more to catch up.' : ' ✓'}</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>$420, $9,000, $2,200 … (8 renders)</t>
+          <t>$0, $1,538, $1,333 … (8 renders)</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -28028,12 +28015,12 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I450" s="2" t="n"/>
@@ -28051,17 +28038,17 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:234</t>
+          <t>src/screens/GoalsScreen.tsx:151</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {plural(liabilities.length, 'debt')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>$14,000, $284,200 … (4 renders)</t>
+          <t>$7,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
@@ -28094,17 +28081,17 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:235</t>
+          <t>src/screens/GoalsScreen.tsx:207</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>$1,228, $236,683 … (4 renders)</t>
+          <t>$420, $9,000, $2,200 … (8 renders)</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
@@ -28127,7 +28114,7 @@
     <row r="453" ht="60" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -28137,17 +28124,17 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:303</t>
+          <t>src/screens/GoalsScreen.tsx:234</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {plural(liabilities.length, 'debt')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500, $0 … (8 renders)</t>
+          <t>$14,000, $284,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
@@ -28157,12 +28144,12 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I453" s="2" t="n"/>
@@ -28180,17 +28167,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:305</t>
+          <t>src/screens/GoalsScreen.tsx:235</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
+          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (12 renders)</t>
+          <t>$1,228, $236,683 … (4 renders)</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -28213,42 +28200,42 @@
     <row r="455" ht="60" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/goals</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:135</t>
+          <t>src/screens/GoalsScreen.tsx:303</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
+          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>$300, $1,900</t>
+          <t>$7,200, $3,500, $0 … (8 renders)</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>inside HomeScreen</t>
+          <t>inside GoalsScreen</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
@@ -28256,42 +28243,42 @@
     <row r="456" ht="60" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/goals</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:309 (+1 spoken/visible twin)</t>
+          <t>src/screens/GoalsScreen.tsx:305</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
+          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $709,800 … (10 renders)</t>
+          <t>$7,200, $3,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>inside HomeScreen</t>
+          <t>inside GoalsScreen</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I456" s="2" t="n"/>
@@ -28309,17 +28296,17 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:426 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:135</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
+          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
+          <t>$300, $1,900</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
@@ -28342,7 +28329,7 @@
     <row r="458" ht="60" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -28352,17 +28339,17 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:513</t>
+          <t>src/screens/HomeScreen.tsx:309 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
+          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $0, $3,500 … (21 renders)</t>
+          <t>$165,000, $709,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -28372,12 +28359,12 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I458" s="2" t="n"/>
@@ -28385,7 +28372,7 @@
     <row r="459" ht="60" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -28395,17 +28382,17 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:526 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:426 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
+          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (14 renders)</t>
+          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
@@ -28415,12 +28402,12 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I459" s="2" t="n"/>
@@ -28438,113 +28425,113 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
+          <t>src/screens/HomeScreen.tsx:513</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>$7,200, $0, $3,500 … (21 renders)</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>inside HomeScreen</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="n"/>
+    </row>
+    <row r="461" ht="60" customHeight="1">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/HomeScreen.tsx:526 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>$7,200, $3,500 … (14 renders)</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>inside HomeScreen</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="n"/>
+    </row>
+    <row r="462" ht="60" customHeight="1">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
           <t>src/screens/HomeScreen.tsx:527</t>
         </is>
       </c>
-      <c r="D460" s="2" t="inlineStr">
+      <c r="D462" s="2" t="inlineStr">
         <is>
           <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Actual expenses so far&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(bva.spent_total))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
-      <c r="E460" s="2" t="inlineStr">
+      <c r="E462" s="2" t="inlineStr">
         <is>
           <t>$0 … (7 renders)</t>
         </is>
       </c>
-      <c r="F460" s="2" t="inlineStr">
+      <c r="F462" s="2" t="inlineStr">
         <is>
           <t>inside HomeScreen</t>
         </is>
       </c>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
-        </is>
-      </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I460" s="2" t="n"/>
-    </row>
-    <row r="461" ht="45" customHeight="1">
-      <c r="A461" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B461" s="2" t="inlineStr">
-        <is>
-          <t>/income-detail</t>
-        </is>
-      </c>
-      <c r="C461" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/IncomeDetailScreen.tsx:68</t>
-        </is>
-      </c>
-      <c r="D461" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E461" s="2" t="inlineStr">
-        <is>
-          <t>$86,400, $86,720, $42,000</t>
-        </is>
-      </c>
-      <c r="F461" s="2" t="inlineStr">
-        <is>
-          <t>inside IncomeDetailScreen</t>
-        </is>
-      </c>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
-        </is>
-      </c>
-      <c r="H461" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I461" s="2" t="n"/>
-    </row>
-    <row r="462" ht="45" customHeight="1">
-      <c r="A462" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B462" s="2" t="inlineStr">
-        <is>
-          <t>/income-detail</t>
-        </is>
-      </c>
-      <c r="C462" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/IncomeDetailScreen.tsx:69</t>
-        </is>
-      </c>
-      <c r="D462" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
-        </is>
-      </c>
-      <c r="E462" s="2" t="inlineStr">
-        <is>
-          <t>$108,000, $108,400, $42,000</t>
-        </is>
-      </c>
-      <c r="F462" s="2" t="inlineStr">
-        <is>
-          <t>inside IncomeDetailScreen</t>
-        </is>
-      </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28567,17 +28554,17 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:72</t>
+          <t>src/screens/IncomeDetailScreen.tsx:68</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
+          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $7,227, $3,500</t>
+          <t>$86,400, $86,720, $42,000</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -28587,7 +28574,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28610,17 +28597,17 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:73</t>
+          <t>src/screens/IncomeDetailScreen.tsx:69</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
+          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>$4,800 … (2 renders)</t>
+          <t>$108,000, $108,400, $42,000</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -28630,7 +28617,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28653,118 +28640,118 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
+          <t>src/screens/IncomeDetailScreen.tsx:72</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>$7,200, $7,227, $3,500</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>inside IncomeDetailScreen</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="n"/>
+    </row>
+    <row r="466" ht="45" customHeight="1">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/IncomeDetailScreen.tsx:73</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>$4,800 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>inside IncomeDetailScreen</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="n"/>
+    </row>
+    <row r="467" ht="45" customHeight="1">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
           <t>src/screens/IncomeDetailScreen.tsx:85</t>
         </is>
       </c>
-      <c r="D465" s="2" t="inlineStr">
+      <c r="D467" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={styles.srcAmt}&gt;{money(src.gross_amount)}&lt;Text style={styles.per}&gt;{CADENCE[src.frequency]}&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E465" s="2" t="inlineStr">
+      <c r="E467" s="2" t="inlineStr">
         <is>
           <t>$9,000, $400, $3,500 … (4 renders)</t>
         </is>
       </c>
-      <c r="F465" s="2" t="inlineStr">
+      <c r="F467" s="2" t="inlineStr">
         <is>
           <t>inside IncomeDetailScreen</t>
         </is>
       </c>
-      <c r="G465" s="2" t="inlineStr">
+      <c r="G467" s="2" t="inlineStr">
         <is>
           <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
-      <c r="H465" s="2" t="inlineStr">
+      <c r="H467" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="n"/>
-    </row>
-    <row r="466" ht="60" customHeight="1">
-      <c r="A466" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B466" s="2" t="inlineStr">
-        <is>
-          <t>/home · /insights</t>
-        </is>
-      </c>
-      <c r="C466" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/InsightsScreen.tsx:76</t>
-        </is>
-      </c>
-      <c r="D466" s="2" t="inlineStr">
-        <is>
-          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="inlineStr">
-        <is>
-          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
-        </is>
-      </c>
-      <c r="F466" s="2" t="inlineStr">
-        <is>
-          <t>inside useInsights</t>
-        </is>
-      </c>
-      <c r="G466" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
-        </is>
-      </c>
-      <c r="H466" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I466" s="2" t="n"/>
-    </row>
-    <row r="467" ht="60" customHeight="1">
-      <c r="A467" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B467" s="2" t="inlineStr">
-        <is>
-          <t>/home · /insights</t>
-        </is>
-      </c>
-      <c r="C467" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/InsightsScreen.tsx:155</t>
-        </is>
-      </c>
-      <c r="D467" s="2" t="inlineStr">
-        <is>
-          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
-        </is>
-      </c>
-      <c r="E467" s="2" t="inlineStr">
-        <is>
-          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F467" s="2" t="inlineStr">
-        <is>
-          <t>inside useInsights</t>
-        </is>
-      </c>
-      <c r="G467" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H467" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I467" s="2" t="n"/>
@@ -28772,7 +28759,7 @@
     <row r="468" ht="60" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -28782,17 +28769,17 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:161</t>
+          <t>src/screens/InsightsScreen.tsx:76</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
+          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>$0 … (6 renders)</t>
+          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -28802,12 +28789,12 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I468" s="2" t="n"/>
@@ -28825,17 +28812,17 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:162</t>
+          <t>src/screens/InsightsScreen.tsx:155</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
+          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>$4,520, $3,800 … (6 renders)</t>
+          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
@@ -28858,7 +28845,7 @@
     <row r="470" ht="60" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -28868,17 +28855,17 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:172</t>
+          <t>src/screens/InsightsScreen.tsx:161</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
+          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
+          <t>$0 … (6 renders)</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -28888,12 +28875,12 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I470" s="2" t="n"/>
@@ -28911,17 +28898,17 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:177</t>
+          <t>src/screens/InsightsScreen.tsx:162</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
+          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>$4,200 … (2 renders)</t>
+          <t>$4,520, $3,800 … (6 renders)</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
@@ -28949,32 +28936,32 @@
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/home · /insights</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
+          <t>src/screens/InsightsScreen.tsx:172</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
+          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
+          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>inside InsuranceScreen</t>
+          <t>inside useInsights</t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -28987,42 +28974,42 @@
     <row r="473" ht="60" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/home · /insights</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:70</t>
+          <t>src/screens/InsightsScreen.tsx:177</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
+          <t>$4,200 … (2 renders)</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>inside InsuranceScreen</t>
+          <t>inside useInsights</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I473" s="2" t="n"/>
@@ -29040,17 +29027,17 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:71</t>
+          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
+          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
@@ -29083,17 +29070,17 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:72</t>
+          <t>src/screens/InsuranceScreen.tsx:70</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
+          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
@@ -29103,7 +29090,7 @@
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>MK-MN-M-018 Income replacement (N yrs)</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
@@ -29126,17 +29113,17 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:73</t>
+          <t>src/screens/InsuranceScreen.tsx:71</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;− Savings &amp; existing coverage&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;−{money(need.covered)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000, $0</t>
+          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -29146,7 +29133,7 @@
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
@@ -29156,7 +29143,7 @@
       </c>
       <c r="I476" s="2" t="n"/>
     </row>
-    <row r="477" ht="45" customHeight="1">
+    <row r="477" ht="60" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29164,32 +29151,32 @@
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>/jobsafety</t>
+          <t>/insurance</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:117</t>
+          <t>src/screens/InsuranceScreen.tsx:72</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[s.hero, { color: covered ? Colors.gainText : Colors.amber }]}&gt;{covered ? '✓ Covered' : money(gap)}&lt;/Text&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>$3,600, $31,320, $18,600</t>
+          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>inside JobSafetyScreen</t>
+          <t>inside InsuranceScreen</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -29207,65 +29194,65 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
+          <t>/insurance</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/InsuranceScreen.tsx:73</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;− Savings &amp; existing coverage&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;−{money(need.covered)}&lt;/Text&gt;&lt;/View&gt;</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>$165,000, $729,800, $250,000, $0</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>inside InsuranceScreen</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="n"/>
+    </row>
+    <row r="479" ht="45" customHeight="1">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
           <t>/jobsafety</t>
         </is>
       </c>
-      <c r="C478" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/JobSafetyScreen.tsx:119</t>
-        </is>
-      </c>
-      <c r="D478" s="2" t="inlineStr">
-        <is>
-          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
-        </is>
-      </c>
-      <c r="E478" s="2" t="inlineStr">
-        <is>
-          <t>$3,600, $600, $0, $31,320 … (9 renders)</t>
-        </is>
-      </c>
-      <c r="F478" s="2" t="inlineStr">
-        <is>
-          <t>inside JobSafetyScreen</t>
-        </is>
-      </c>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
-        </is>
-      </c>
-      <c r="H478" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I478" s="2" t="n"/>
-    </row>
-    <row r="479" ht="60" customHeight="1">
-      <c r="A479" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B479" s="2" t="inlineStr">
-        <is>
-          <t>/jobsafety</t>
-        </is>
-      </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:132</t>
+          <t>src/screens/JobSafetyScreen.tsx:117</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
+          <t>&lt;Text style={[s.hero, { color: covered ? Colors.gainText : Colors.amber }]}&gt;{covered ? '✓ Covered' : money(gap)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>$600, $5,220, $3,100</t>
+          <t>$3,600, $31,320, $18,600</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
@@ -29288,252 +29275,252 @@
     <row r="480" ht="60" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>/jobsafety</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/JobSafetyScreen.tsx:119</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>$3,600, $600, $0, $31,320 … (9 renders)</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>inside JobSafetyScreen</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="n"/>
+    </row>
+    <row r="481" ht="60" customHeight="1">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>/jobsafety</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/JobSafetyScreen.tsx:132</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>$600, $5,220, $3,100</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>inside JobSafetyScreen</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="n"/>
+    </row>
+    <row r="482" ht="60" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B480" s="2" t="inlineStr">
+      <c r="B482" s="2" t="inlineStr">
         <is>
           <t>/jobsafety</t>
         </is>
       </c>
-      <c r="C480" s="2" t="inlineStr">
+      <c r="C482" s="2" t="inlineStr">
         <is>
           <t>src/screens/JobSafetyScreen.tsx:175</t>
         </is>
       </c>
-      <c r="D480" s="2" t="inlineStr">
+      <c r="D482" s="2" t="inlineStr">
         <is>
           <t>Setting aside &lt;Text style={s.bold}&gt;{money(EXAMPLE_PACE)}/month&lt;/Text&gt; closes the gap in &lt;Text style={s.bold}&gt;{monthsToClose} months&lt;/Text&gt; — an example pace, set your own.</t>
         </is>
       </c>
-      <c r="E480" s="2" t="inlineStr">
+      <c r="E482" s="2" t="inlineStr">
         <is>
           <t>$300 … (3 renders)</t>
         </is>
       </c>
-      <c r="F480" s="2" t="inlineStr">
+      <c r="F482" s="2" t="inlineStr">
         <is>
           <t>inside JobSafetyScreen</t>
         </is>
       </c>
-      <c r="G480" s="2" t="inlineStr">
+      <c r="G482" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H480" s="2" t="inlineStr">
+      <c r="H482" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I480" s="2" t="n"/>
-    </row>
-    <row r="481" ht="45" customHeight="1">
-      <c r="A481" s="2" t="inlineStr">
+      <c r="I482" s="2" t="n"/>
+    </row>
+    <row r="483" ht="45" customHeight="1">
+      <c r="A483" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
         </is>
       </c>
-      <c r="B481" s="2" t="inlineStr">
+      <c r="B483" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C481" s="2" t="inlineStr">
+      <c r="C483" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:81</t>
         </is>
       </c>
-      <c r="D481" s="2" t="inlineStr">
+      <c r="D483" s="2" t="inlineStr">
         <is>
           <t>{ label: 'Retirement saving', from: `${maskedMoney(A.contribMonthly ?? 0)}/month`, to: `${maskedMoney(retirementMonthly)}/month` },</t>
         </is>
       </c>
-      <c r="E481" s="2" t="inlineStr">
+      <c r="E483" s="2" t="inlineStr">
         <is>
           <t>$0, $500 … (8 renders)</t>
         </is>
       </c>
-      <c r="F481" s="2" t="inlineStr">
+      <c r="F483" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G481" s="2" t="inlineStr">
+      <c r="G483" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo, MK-PL-M-030 Extra on debt $X/mo</t>
         </is>
       </c>
-      <c r="H481" s="2" t="inlineStr">
+      <c r="H483" s="2" t="inlineStr">
         <is>
           <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
-      <c r="I481" s="2" t="n"/>
-    </row>
-    <row r="482" ht="45" customHeight="1">
-      <c r="A482" s="2" t="inlineStr">
+      <c r="I483" s="2" t="n"/>
+    </row>
+    <row r="484" ht="45" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B482" s="2" t="inlineStr">
+      <c r="B484" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C482" s="2" t="inlineStr">
+      <c r="C484" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:135 (+1 spoken/visible twin)</t>
         </is>
       </c>
-      <c r="D482" s="2" t="inlineStr">
+      <c r="D484" s="2" t="inlineStr">
         <is>
           <t>accessibilityLabel={`Extra on debt at ${spokenMoney(extraDebt)} a month`} /&gt;</t>
         </is>
       </c>
-      <c r="E482" s="2" t="inlineStr">
+      <c r="E484" s="2" t="inlineStr">
         <is>
           <t>$0 … (4 renders)</t>
         </is>
       </c>
-      <c r="F482" s="2" t="inlineStr">
+      <c r="F484" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr">
+      <c r="G484" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-030 Extra on debt $X/mo</t>
         </is>
       </c>
-      <c r="H482" s="2" t="inlineStr">
+      <c r="H484" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I482" s="2" t="n"/>
-    </row>
-    <row r="483" ht="30" customHeight="1">
-      <c r="A483" s="2" t="inlineStr">
+      <c r="I484" s="2" t="n"/>
+    </row>
+    <row r="485" ht="30" customHeight="1">
+      <c r="A485" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B483" s="2" t="inlineStr">
+      <c r="B485" s="2" t="inlineStr">
         <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="C483" s="2" t="inlineStr">
+      <c r="C485" s="2" t="inlineStr">
         <is>
           <t>src/screens/MultiGoalScreen.tsx:155</t>
         </is>
       </c>
-      <c r="D483" s="2" t="inlineStr">
+      <c r="D485" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.dialAmt}&gt;{maskedMoney(retirementMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
-      <c r="E483" s="2" t="inlineStr">
+      <c r="E485" s="2" t="inlineStr">
         <is>
           <t>$500 … (4 renders)</t>
         </is>
       </c>
-      <c r="F483" s="2" t="inlineStr">
+      <c r="F485" s="2" t="inlineStr">
         <is>
           <t>inside MultiGoalScreen</t>
         </is>
       </c>
-      <c r="G483" s="2" t="inlineStr">
+      <c r="G485" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
-        </is>
-      </c>
-      <c r="H483" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I483" s="2" t="n"/>
-    </row>
-    <row r="484" ht="60" customHeight="1">
-      <c r="A484" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B484" s="2" t="inlineStr">
-        <is>
-          <t>/multi-goal</t>
-        </is>
-      </c>
-      <c r="C484" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/MultiGoalScreen.tsx:168 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D484" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`Can you do it all? ${weighed.covered ? `Covered, with ${spokenMoney(weighed.spare)} a month to spare` : `Short ${spokenMoney(Math.abs(weighed.spare))} a month`}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>$1,380, $400, $500 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F484" s="2" t="inlineStr">
-        <is>
-          <t>inside MultiGoalScreen</t>
-        </is>
-      </c>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
-        </is>
-      </c>
-      <c r="H484" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I484" s="2" t="n"/>
-    </row>
-    <row r="485" ht="45" customHeight="1">
-      <c r="A485" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B485" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C485" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/PlanHubScreen.tsx:234</t>
-        </is>
-      </c>
-      <c r="D485" s="2" t="inlineStr">
-        <is>
-          <t>Your {maskedMoney(planSpend)}/month expenses{onCourse ? ` — ${onCourse}` : ` — ${oddsLine(lens, wil.chance!, wil.horizonAge)}`}.</t>
-        </is>
-      </c>
-      <c r="E485" s="2" t="inlineStr">
-        <is>
-          <t>$3,800 … (2 renders)</t>
-        </is>
-      </c>
-      <c r="F485" s="2" t="inlineStr">
-        <is>
-          <t>inside PlanHubScreen</t>
-        </is>
-      </c>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -29551,80 +29538,80 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
+          <t>/multi-goal</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/MultiGoalScreen.tsx:168 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>accessibilityLabel={`Can you do it all? ${weighed.covered ? `Covered, with ${spokenMoney(weighed.spare)} a month to spare` : `Short ${spokenMoney(Math.abs(weighed.spare))} a month`}`}&gt;</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>$1,380, $400, $500 … (8 renders)</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>inside MultiGoalScreen</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="n"/>
+    </row>
+    <row r="487" ht="45" customHeight="1">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C486" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/PlanHubScreen.tsx:274</t>
-        </is>
-      </c>
-      <c r="D486" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {plural(door.credit.accounts, 'account', `${door.credit.accounts}${accounts.some((a: any) =&gt; a.source === 'connected') ? ' connected' : ''</t>
-        </is>
-      </c>
-      <c r="E486" s="2" t="inlineStr">
-        <is>
-          <t>$165,000, $729,800</t>
-        </is>
-      </c>
-      <c r="F486" s="2" t="inlineStr">
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PlanHubScreen.tsx:234</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>Your {maskedMoney(planSpend)}/month expenses{onCourse ? ` — ${onCourse}` : ` — ${oddsLine(lens, wil.chance!, wil.horizonAge)}`}.</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>$3,800 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
         <is>
           <t>inside PlanHubScreen</t>
         </is>
       </c>
-      <c r="G486" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
-        </is>
-      </c>
-      <c r="H486" s="2" t="inlineStr">
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I486" s="2" t="n"/>
-    </row>
-    <row r="487" ht="60" customHeight="1">
-      <c r="A487" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B487" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C487" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/PlanHubScreen.tsx:309</t>
-        </is>
-      </c>
-      <c r="D487" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
-        </is>
-      </c>
-      <c r="E487" s="2" t="inlineStr">
-        <is>
-          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
-        </is>
-      </c>
-      <c r="F487" s="2" t="inlineStr">
-        <is>
-          <t>inside PlanHubScreen</t>
-        </is>
-      </c>
-      <c r="G487" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
-        </is>
-      </c>
-      <c r="H487" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I487" s="2" t="n"/>
@@ -29632,7 +29619,7 @@
     <row r="488" ht="60" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -29642,17 +29629,17 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:315</t>
+          <t>src/screens/PlanHubScreen.tsx:274</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {plural(door.credit.accounts, 'account', `${door.credit.accounts}${accounts.some((a: any) =&gt; a.source === 'connected') ? ' connected' : ''</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>$2,200, $1,300 … (4 renders)</t>
+          <t>$165,000, $729,800</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
@@ -29662,12 +29649,12 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I488" s="2" t="n"/>
@@ -29685,17 +29672,17 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:317</t>
+          <t>src/screens/PlanHubScreen.tsx:309</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
+          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
@@ -29705,7 +29692,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29728,17 +29715,17 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:318 (+1 spoken/visible twin)</t>
+          <t>src/screens/PlanHubScreen.tsx:315</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
+          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>$1,295 … (4 renders)</t>
+          <t>$2,200, $1,300 … (4 renders)</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
@@ -29748,7 +29735,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29771,17 +29758,17 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:319</t>
+          <t>src/screens/PlanHubScreen.tsx:317</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.payRow, styles.payTotal]}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;Your paycheck&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(paycheckTotal))}/</t>
+          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>$4,795 … (2 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
@@ -29791,7 +29778,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -29801,10 +29788,10 @@
       </c>
       <c r="I491" s="2" t="n"/>
     </row>
-    <row r="492" ht="45" customHeight="1">
+    <row r="492" ht="60" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -29814,17 +29801,17 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:328</t>
+          <t>src/screens/PlanHubScreen.tsx:318 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>✓ covers your {maskedMoney(planSpend)}/month expenses. You're drawing {maskedMoney(Math.round(drawUsed))}/month</t>
+          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>$3,800, $300 … (4 renders)</t>
+          <t>$1,295 … (4 renders)</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
@@ -29834,12 +29821,12 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I492" s="2" t="n"/>
@@ -29847,123 +29834,123 @@
     <row r="493" ht="60" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PlanHubScreen.tsx:319</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>&lt;View style={[styles.payRow, styles.payTotal]}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;Your paycheck&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(paycheckTotal))}/</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>$4,795 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>inside PlanHubScreen</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="n"/>
+    </row>
+    <row r="494" ht="45" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B493" s="2" t="inlineStr">
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PlanHubScreen.tsx:328</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>✓ covers your {maskedMoney(planSpend)}/month expenses. You're drawing {maskedMoney(Math.round(drawUsed))}/month</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>$3,800, $300 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>inside PlanHubScreen</t>
+        </is>
+      </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="n"/>
+    </row>
+    <row r="495" ht="60" customHeight="1">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
         <is>
           <t>/required-withdrawals</t>
         </is>
       </c>
-      <c r="C493" s="2" t="inlineStr">
+      <c r="C495" s="2" t="inlineStr">
         <is>
           <t>src/screens/RequiredWithdrawalsScreen.tsx:102</t>
         </is>
       </c>
-      <c r="D493" s="2" t="inlineStr">
+      <c r="D495" s="2" t="inlineStr">
         <is>
           <t>&lt;Text style={s.line}&gt;Yours starts in &lt;Text style={s.strong}&gt;{startYear}&lt;/Text&gt; (age {rmdStartAgeFor(age)}). Estimated first withdrawal: &lt;Text style={s.strong}&gt;~{maskedMoney(Math.round(schedule[0]?.amo</t>
         </is>
       </c>
-      <c r="E493" s="2" t="inlineStr">
+      <c r="E495" s="2" t="inlineStr">
         <is>
           <t>$41,528, $138,428</t>
         </is>
       </c>
-      <c r="F493" s="2" t="inlineStr">
+      <c r="F495" s="2" t="inlineStr">
         <is>
           <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
-      <c r="G493" s="2" t="inlineStr">
+      <c r="G495" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
-        </is>
-      </c>
-      <c r="H493" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I493" s="2" t="n"/>
-    </row>
-    <row r="494" ht="60" customHeight="1">
-      <c r="A494" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B494" s="2" t="inlineStr">
-        <is>
-          <t>/required-withdrawals</t>
-        </is>
-      </c>
-      <c r="C494" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:189 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D494" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`${r.year}, age ${r.age}: about ${spokenMoney(Math.round(r.amount))}${r.isCurrent ? ', this year' : ''}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>$41,528, $43,628, $45,625, $47,916 … (32 renders)</t>
-        </is>
-      </c>
-      <c r="F494" s="2" t="inlineStr">
-        <is>
-          <t>inside RequiredWithdrawalsScreen</t>
-        </is>
-      </c>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
-        </is>
-      </c>
-      <c r="H494" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I494" s="2" t="n"/>
-    </row>
-    <row r="495" ht="45" customHeight="1">
-      <c r="A495" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B495" s="2" t="inlineStr">
-        <is>
-          <t>/required-withdrawals</t>
-        </is>
-      </c>
-      <c r="C495" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:205 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D495" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`${a.label}, ${spokenMoney(Math.round(a.balance || 0))}, marked pre-tax. Opens its page to edit.`}&gt;</t>
-        </is>
-      </c>
-      <c r="E495" s="2" t="inlineStr">
-        <is>
-          <t>$120,000, $400,000 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F495" s="2" t="inlineStr">
-        <is>
-          <t>inside RequiredWithdrawalsScreen</t>
-        </is>
-      </c>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-016 BASED ON THESE ACCOUNTS — each balance</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
@@ -29976,85 +29963,85 @@
     <row r="496" ht="60" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:39</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:189 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
+          <t>accessibilityLabel={`${r.year}, age ${r.age}: about ${spokenMoney(Math.round(r.amount))}${r.isCurrent ? ', this year' : ''}`}&gt;</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
+          <t>$41,528, $43,628, $45,625, $47,916 … (32 renders)</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>inside big</t>
+          <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I496" s="2" t="n"/>
     </row>
-    <row r="497" ht="60" customHeight="1">
+    <row r="497" ht="45" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:503</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:205 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`${a.label}, ${spokenMoney(Math.round(a.balance || 0))}, marked pre-tax. Opens its page to edit.`}&gt;</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>$250K … (2 renders)</t>
+          <t>$120,000, $400,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>inside RetirementCockpit</t>
+          <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-016 BASED ON THESE ACCOUNTS — each balance</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I497" s="2" t="n"/>
@@ -30072,22 +30059,22 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:533</t>
+          <t>src/screens/RetirementCockpit.tsx:39</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
+          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
+          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>inside RetirementCockpit</t>
+          <t>inside big</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -30115,17 +30102,17 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:568</t>
+          <t>src/screens/RetirementCockpit.tsx:504</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$250K … (2 renders)</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
@@ -30158,17 +30145,17 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:645</t>
+          <t>src/screens/RetirementCockpit.tsx:534</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
+          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
+          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -30201,17 +30188,17 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:654</t>
+          <t>src/screens/RetirementCockpit.tsx:569</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -30244,17 +30231,17 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:664</t>
+          <t>src/screens/RetirementCockpit.tsx:646</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
+          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>$0 … (2 renders)</t>
+          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -30287,17 +30274,17 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:688</t>
+          <t>src/screens/RetirementCockpit.tsx:655</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>$10K, $250K … (4 renders)</t>
+          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -30330,17 +30317,17 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:689</t>
+          <t>src/screens/RetirementCockpit.tsx:665</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source}${info.period ? ` · ${info.period}`</t>
+          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $400K, $300K … (10 renders)</t>
+          <t>$0 … (2 renders)</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -30373,17 +30360,17 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:750</t>
+          <t>src/screens/RetirementCockpit.tsx:689</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
+          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$10K, $250K … (4 renders)</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -30416,17 +30403,17 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:767</t>
+          <t>src/screens/RetirementCockpit.tsx:690</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
+          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source}${info.period ? ` · ${info.period}`</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>$5,000, $3,800 … (8 renders)</t>
+          <t>$120K, $45K, $400K, $300K … (10 renders)</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
@@ -30459,17 +30446,17 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:789</t>
+          <t>src/screens/RetirementCockpit.tsx:751</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
+          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>$14,900, $24,500 … (12 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -30502,17 +30489,17 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:791</t>
+          <t>src/screens/RetirementCockpit.tsx:768</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>$7,500 … (6 renders)</t>
+          <t>$5,000, $3,800 … (8 renders)</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
@@ -30545,17 +30532,17 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:806</t>
+          <t>src/screens/RetirementCockpit.tsx:790</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
+          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$14,900, $24,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -30588,22 +30575,22 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:979</t>
+          <t>src/screens/RetirementCockpit.tsx:792</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
+          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
+          <t>$7,500 … (6 renders)</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>inside EarmarkSheet</t>
+          <t>inside RetirementCockpit</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
@@ -30631,22 +30618,22 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:984</t>
+          <t>src/screens/RetirementCockpit.tsx:807</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}&lt;/Text&gt;</t>
+          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>inside EarmarkSheet</t>
+          <t>inside RetirementCockpit</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
@@ -30669,27 +30656,27 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RothScreen.tsx:85 (+1 spoken/visible twin)</t>
+          <t>src/screens/RetirementCockpit.tsx:980</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
+          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>$0 … (12 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
-          <t>inside RothScreen</t>
+          <t>inside EarmarkSheet</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
@@ -30707,85 +30694,85 @@
     <row r="513" ht="60" customHeight="1">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RetirementCockpit.tsx:985</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>inside EarmarkSheet</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="n"/>
+    </row>
+    <row r="514" ht="60" customHeight="1">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
           <t>/roth</t>
         </is>
       </c>
-      <c r="C513" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:135</t>
-        </is>
-      </c>
-      <c r="D513" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.note}&gt;from your pre-tax {maskedMoney(Math.round(preTax))}{num(amount) &gt; preTax ? ' — capped at your balance' : ''}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E513" s="2" t="inlineStr">
-        <is>
-          <t>$120,000, $400,000</t>
-        </is>
-      </c>
-      <c r="F513" s="2" t="inlineStr">
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:85 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
         <is>
           <t>inside RothScreen</t>
         </is>
       </c>
-      <c r="G513" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-024 from your pre-tax $X</t>
-        </is>
-      </c>
-      <c r="H513" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I513" s="2" t="n"/>
-    </row>
-    <row r="514" ht="45" customHeight="1">
-      <c r="A514" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B514" s="2" t="inlineStr">
-        <is>
-          <t>/roth</t>
-        </is>
-      </c>
-      <c r="C514" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:142 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D514" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`Set ${spokenMoney(v)}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr">
-        <is>
-          <t>$10,000, $25,000, $50,000 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F514" s="2" t="inlineStr">
-        <is>
-          <t>inside RothScreen</t>
-        </is>
-      </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-024 from your pre-tax $X</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I514" s="2" t="n"/>
@@ -30793,7 +30780,7 @@
     <row r="515" ht="60" customHeight="1">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -30803,17 +30790,17 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RothScreen.tsx:195</t>
+          <t>src/screens/RothScreen.tsx:135</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>title={`Convert ${maskedMoney(amt)} to Roth this year`}</t>
+          <t>&lt;Text style={s.note}&gt;from your pre-tax {maskedMoney(Math.round(preTax))}{num(amount) &gt; preTax ? ' — capped at your balance' : ''}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>$0 … (2 renders)</t>
+          <t>$120,000, $400,000</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
@@ -30823,17 +30810,17 @@
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-024 from your pre-tax $X</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I515" s="2" t="n"/>
     </row>
-    <row r="516" ht="30" customHeight="1">
+    <row r="516" ht="45" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -30841,32 +30828,32 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/roth</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:103</t>
+          <t>src/screens/RothScreen.tsx:142 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.receiveHead}&gt;You receive {maskedMoney(num(op.ri_ss))}/month ✓&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`Set ${spokenMoney(v)}`}&gt;</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>$2,200</t>
+          <t>$10,000, $25,000, $50,000 … (12 renders)</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>inside SsTimingScreen</t>
+          <t>inside RothScreen</t>
         </is>
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-018 You receive $X/mo ✓</t>
+          <t>MK-PL-M-024 from your pre-tax $X</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
@@ -30879,85 +30866,85 @@
     <row r="517" ht="60" customHeight="1">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:195</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>title={`Convert ${maskedMoney(amt)} to Roth this year`}</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>inside RothScreen</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="n"/>
+    </row>
+    <row r="518" ht="30" customHeight="1">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
           <t>/ss-timing</t>
         </is>
       </c>
-      <c r="C517" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/SsTimingScreen.tsx:137</t>
-        </is>
-      </c>
-      <c r="D517" s="2" t="inlineStr">
-        <is>
-          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr">
-        <is>
-          <t>$2,600 … (3 renders)</t>
-        </is>
-      </c>
-      <c r="F517" s="2" t="inlineStr">
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/SsTimingScreen.tsx:103</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.receiveHead}&gt;You receive {maskedMoney(num(op.ri_ss))}/month ✓&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>$2,200</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
         <is>
           <t>inside SsTimingScreen</t>
         </is>
       </c>
-      <c r="G517" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
-        </is>
-      </c>
-      <c r="H517" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
-        </is>
-      </c>
-      <c r="I517" s="2" t="n"/>
-    </row>
-    <row r="518" ht="60" customHeight="1">
-      <c r="A518" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B518" s="2" t="inlineStr">
-        <is>
-          <t>/ss-timing</t>
-        </is>
-      </c>
-      <c r="C518" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/SsTimingScreen.tsx:151</t>
-        </is>
-      </c>
-      <c r="D518" s="2" t="inlineStr">
-        <is>
-          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
-        </is>
-      </c>
-      <c r="F518" s="2" t="inlineStr">
-        <is>
-          <t>inside SsTimingScreen</t>
-        </is>
-      </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-018 You receive $X/mo ✓</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I518" s="2" t="n"/>
@@ -30975,17 +30962,17 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:153</t>
+          <t>src/screens/SsTimingScreen.tsx:137</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
+          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
+          <t>$2,600 … (3 renders)</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -31018,17 +31005,17 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:154</t>
+          <t>src/screens/SsTimingScreen.tsx:151</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
+          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
+          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -31038,7 +31025,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -31051,42 +31038,42 @@
     <row r="521" ht="60" customHeight="1">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>/stress-test</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:74 (+1 spoken/visible twin)</t>
+          <t>src/screens/SsTimingScreen.tsx:153</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
+          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>$3,000 … (10 renders)</t>
+          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>inside StressTestScreen</t>
+          <t>inside SsTimingScreen</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I521" s="2" t="n"/>
@@ -31099,32 +31086,32 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>/stress-test</t>
+          <t>/ss-timing</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:78</t>
+          <t>src/screens/SsTimingScreen.tsx:154</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
+          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>$17,000, $5,220</t>
+          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>inside StressTestScreen</t>
+          <t>inside SsTimingScreen</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -31137,7 +31124,7 @@
     <row r="523" ht="60" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -31147,17 +31134,17 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:104</t>
+          <t>src/screens/StressTestScreen.tsx:74 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
+          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>$600, $5,220, $3,100</t>
+          <t>$3,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -31167,12 +31154,12 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I523" s="2" t="n"/>
@@ -31180,7 +31167,7 @@
     <row r="524" ht="60" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -31190,17 +31177,17 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:108</t>
+          <t>src/screens/StressTestScreen.tsx:78</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
+          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$17,000, $5,220</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
@@ -31210,12 +31197,12 @@
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I524" s="2" t="n"/>
@@ -31223,7 +31210,7 @@
     <row r="525" ht="60" customHeight="1">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -31233,17 +31220,17 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:118</t>
+          <t>src/screens/StressTestScreen.tsx:104</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.fundTxt}&gt;3 months of essentials{rent &gt; 0 ? ', less the rent that keeps arriving,' : ''} is &lt;Text style={styles.bold}&gt;{money(r.recommendedFund)}&lt;/Text&gt;. You're &lt;Text style={[styles.</t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>$1,800, $9,300 … (4 renders)</t>
+          <t>$600, $5,220, $3,100</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -31253,55 +31240,55 @@
       </c>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I525" s="2" t="n"/>
     </row>
-    <row r="526" ht="45" customHeight="1">
+    <row r="526" ht="60" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>/tax-organizer</t>
+          <t>/stress-test</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:90</t>
+          <t>src/screens/StressTestScreen.tsx:108</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.rowV}&gt;{money(l.amount)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>$108,000, $400, $42,000 … (4 renders)</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>inside TaxOrganizerScreen</t>
+          <t>inside StressTestScreen</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I526" s="2" t="n"/>
@@ -31314,65 +31301,65 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
+          <t>/stress-test</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/StressTestScreen.tsx:118</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.fundTxt}&gt;3 months of essentials{rent &gt; 0 ? ', less the rent that keeps arriving,' : ''} is &lt;Text style={styles.bold}&gt;{money(r.recommendedFund)}&lt;/Text&gt;. You're &lt;Text style={[styles.</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>$1,800, $9,300 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>inside StressTestScreen</t>
+        </is>
+      </c>
+      <c r="G527" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-026 your $X/month of essentials</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="n"/>
+    </row>
+    <row r="528" ht="45" customHeight="1">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
           <t>/tax-organizer</t>
         </is>
       </c>
-      <c r="C527" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
-        </is>
-      </c>
-      <c r="D527" s="2" t="inlineStr">
-        <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
-        </is>
-      </c>
-      <c r="E527" s="2" t="inlineStr">
-        <is>
-          <t>$108,000, $108,400, $42,000, $0</t>
-        </is>
-      </c>
-      <c r="F527" s="2" t="inlineStr">
-        <is>
-          <t>inside TaxOrganizerScreen</t>
-        </is>
-      </c>
-      <c r="G527" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
-        </is>
-      </c>
-      <c r="H527" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I527" s="2" t="n"/>
-    </row>
-    <row r="528" ht="60" customHeight="1">
-      <c r="A528" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B528" s="2" t="inlineStr">
-        <is>
-          <t>/tax-organizer</t>
-        </is>
-      </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:90</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={styles.rowV}&gt;{money(l.amount)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $0 … (4 renders)</t>
+          <t>$108,000, $400, $42,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
@@ -31405,17 +31392,17 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
+          <t>$108,000, $108,400, $42,000, $0</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
@@ -31448,17 +31435,17 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>$66,200, $66,600, $17,850, $0</t>
+          <t>$9,600, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
@@ -31491,17 +31478,17 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $6,000 … (4 renders)</t>
+          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
@@ -31524,7 +31511,7 @@
     <row r="532" ht="60" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -31534,17 +31521,17 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000</t>
+          <t>$66,200, $66,600, $17,850, $0</t>
         </is>
       </c>
       <c r="F532" s="2" t="inlineStr">
@@ -31554,12 +31541,12 @@
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
         </is>
       </c>
       <c r="H532" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I532" s="2" t="n"/>
@@ -31567,42 +31554,42 @@
     <row r="533" ht="60" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:105</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
+          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>$500 … (3 renders)</t>
+          <t>$9,600, $6,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>inside WhatIfScreen</t>
+          <t>inside TaxOrganizerScreen</t>
         </is>
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I533" s="2" t="n"/>
@@ -31615,27 +31602,27 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:146 (+1 spoken/visible twin)</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
+          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>inside WhatIfScreen</t>
+          <t>inside TaxOrganizerScreen</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
@@ -31663,17 +31650,17 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:150</t>
+          <t>src/screens/WhatIfScreen.tsx:105</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
+          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>$756,665, $651,067, $6,000</t>
+          <t>$500 … (3 renders)</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -31696,42 +31683,42 @@
     <row r="536" ht="60" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:51</t>
+          <t>src/screens/WhatIfScreen.tsx:146 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
+          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>$250,000</t>
+          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>inside WillItLastScreen</t>
+          <t>inside WhatIfScreen</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-008 What you have (nest egg)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I536" s="2" t="n"/>
@@ -31739,42 +31726,42 @@
     <row r="537" ht="60" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:52</t>
+          <t>src/screens/WhatIfScreen.tsx:150</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
+          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$756,665, $651,067, $6,000</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>inside WillItLastScreen</t>
+          <t>inside WhatIfScreen</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-009 Monthly expenses in retirement</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I537" s="2" t="n"/>
@@ -31792,38 +31779,124 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
+          <t>src/screens/WillItLastScreen.tsx:51</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>$250,000</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>inside WillItLastScreen</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-008 What you have (nest egg)</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="n"/>
+    </row>
+    <row r="539" ht="60" customHeight="1">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/WillItLastScreen.tsx:52</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>$3,800</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>inside WillItLastScreen</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-009 Monthly expenses in retirement</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="n"/>
+    </row>
+    <row r="540" ht="60" customHeight="1">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
           <t>src/screens/WillItLastScreen.tsx:53</t>
         </is>
       </c>
-      <c r="D538" s="2" t="inlineStr">
+      <c r="D540" s="2" t="inlineStr">
         <is>
           <t>{ label: 'Guaranteed income', value: `${maskedMoney(inp.guaranteed_monthly_income)}/month from age ${inp.guaranteed_start_age ?? inp.retire_age}`, source: A.ssMonthly != null || A.ssClaimAge != null ?</t>
         </is>
       </c>
-      <c r="E538" s="2" t="inlineStr">
+      <c r="E540" s="2" t="inlineStr">
         <is>
           <t>$3,500</t>
         </is>
       </c>
-      <c r="F538" s="2" t="inlineStr">
+      <c r="F540" s="2" t="inlineStr">
         <is>
           <t>inside WillItLastScreen</t>
         </is>
       </c>
-      <c r="G538" s="2" t="inlineStr">
+      <c r="G540" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-010 Guaranteed income — $X/mo from age Y</t>
         </is>
       </c>
-      <c r="H538" s="2" t="inlineStr">
+      <c r="H540" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I538" s="2" t="n"/>
+      <c r="I540" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I538"/>
+  <autoFilter ref="A1:I540"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Map'!$A$1:$U$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$540</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Census'!$A$1:$I$539</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Conflicts'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="2" t="n"/>
     </row>
@@ -1345,6 +1345,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -1386,6 +1390,7 @@
 MK-ST-F-003 dayWords
 MK-ST-F-005 measuredFromLabel
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
@@ -1426,7 +1431,8 @@
 MK-XS-F-131 toInt
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1792,6 +1798,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-141 holdingBondFacts
+MK-NW-F-142 classReturnOf
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -1818,10 +1826,15 @@
 MK-PF-F-041 isoDay
 MK-PF-F-042 windowTotal
 MK-PF-F-045 priceHistoryShortSentence
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-012 waterfall
 MK-ST-F-002 monthWords
 MK-ST-F-003 dayWords
 MK-ST-F-004 coverageFor
+MK-ST-F-019 signed
 MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
@@ -1855,7 +1868,8 @@
 MK-XS-F-170 daysSince
 MK-XS-F-180 declareFigures
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2072,6 +2086,8 @@
 MK-NW-F-008 incomeBearingClassOf
 MK-NW-F-009 maturityClass
 MK-NW-F-011 assetClassOf
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-055 isBond
 MK-NW-F-056 bondInfo
 MK-NW-F-057 annualCoupon
@@ -2087,9 +2103,13 @@
 MK-NW-F-077 ALL
 MK-NW-F-078 ONE
 MK-NW-F-090 windowStartKey
+MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
@@ -2116,11 +2136,15 @@
 MK-PF-F-041 isoDay
 MK-PF-F-045 priceHistoryShortSentence
 MK-PF-F-046 saleShortOfPurchasesSentence
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
 MK-PL-F-012 waterfall
 MK-ST-F-002 monthWords
 MK-ST-F-003 dayWords
 MK-ST-F-004 coverageFor
 MK-ST-F-010 nameEvidence
+MK-ST-F-019 signed
 MK-ST-F-030 record
 MK-ST-F-034 firstDate
 MK-ST-F-036 reconcile
@@ -2149,7 +2173,8 @@
 MK-XS-F-170 daysSince
 MK-XS-F-180 declareFigures
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2423,6 +2448,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-141 holdingBondFacts
+MK-NW-F-142 classReturnOf
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2449,11 +2476,16 @@
 MK-PF-F-041 isoDay
 MK-PF-F-042 windowTotal
 MK-PF-F-045 priceHistoryShortSentence
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-012 waterfall
 MK-ST-F-002 monthWords
 MK-ST-F-003 dayWords
 MK-ST-F-004 coverageFor
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-028 buildDayFromAccounts
 MK-ST-F-030 record
@@ -2488,7 +2520,8 @@
 MK-XS-F-170 daysSince
 MK-XS-F-180 declareFigures
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2938,7 +2971,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3187,6 +3221,8 @@
 MK-NW-F-024 accountLastFour
 MK-NW-F-025 accountDisplayName
 MK-NW-F-026 accountDisplayNames
+MK-NW-F-053 correctClassOf
+MK-NW-F-054 reclassifyAccounts
 MK-NW-F-055 isBond
 MK-NW-F-056 bondInfo
 MK-NW-F-057 annualCoupon
@@ -3206,9 +3242,13 @@
 MK-NW-F-091 pricedGainOf
 MK-NW-F-104 closedWith
 MK-NW-F-105 whyNoReturn
+MK-NW-F-109 holdingClassOf
 MK-NW-F-112 yearlyInterest
 MK-NW-F-119 estimatedAccrued
 MK-NW-F-120 classEvidenceOf
+MK-NW-F-121 holdingTagClass
+MK-NW-F-122 holdingTagFor
+MK-NW-F-123 holdingNameEvidence
 MK-NW-F-124 maturityParts
 MK-NW-F-125 isPastMaturity
 MK-NW-F-126 yearlyInterestNow
@@ -3244,9 +3284,14 @@
 MK-PF-F-040 returnSincePurchases
 MK-PF-F-041 isoDay
 MK-PF-F-042 windowTotal
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-012 waterfall
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-027 accountId
 MK-ST-F-028 buildDayFromAccounts
@@ -3281,11 +3326,12 @@
 MK-XS-F-122 n
 MK-XS-F-147 call
 MK-XS-F-180 declareFigures
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3389,8 +3435,6 @@
 MK-NW-F-040 assetsFromOnboarding
 MK-NW-F-041 monthlyContributionsFromOnboarding
 MK-NW-F-046 historyCoverage
-MK-NW-F-053 correctClassOf
-MK-NW-F-054 reclassifyAccounts
 MK-NW-F-065 buildNetWorth
 MK-NW-F-066 sumWhere
 MK-NW-F-068 prettyDay
@@ -3399,17 +3443,14 @@
 MK-NW-F-103 investmentRecordDates
 MK-NW-F-106 mortgagesByProperty
 MK-NW-F-107 propertyUses
-MK-NW-F-109 holdingClassOf
 MK-NW-F-110 primaryHomeIdOf
 MK-NW-F-114 rentAmount
 MK-NW-F-115 liveRent
 MK-NW-F-116 rentedIdsOf
 MK-NW-F-117 propertyUseMap
-MK-NW-F-121 holdingTagClass
-MK-NW-F-122 holdingTagFor
-MK-NW-F-123 holdingNameEvidence
 MK-NW-F-133 valueEntered
 MK-NW-F-134 carValueNotEnteredNotes
+MK-NW-F-142 classReturnOf
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-PF-F-020 portfolioBenchReturn
@@ -3514,7 +3555,7 @@
         <is>
           <t>MK-XS-I-001 account balance — read by MK-NW-F-056, MK-NW-F-078, MK-NW-O-001, MK-NW-O-008, MK-ST-F-027, MK-ST-F-028
 MK-XS-I-001 account balance — read by MK-ST-F-027
-MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-012, MK-NW-F-025, MK-NW-F-120, MK-NW-O-001
+MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-012, MK-NW-F-025, MK-NW-F-054, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-025, MK-NW-F-026, MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
 MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-NW-F-091, MK-NW-F-128, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
@@ -3522,9 +3563,9 @@
 MK-XS-I-005 holding price — read by MK-ST-F-027
 MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-139, MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
-MK-XS-I-008 transaction amount — read by MK-ST-F-082
-MK-XS-I-009 transaction date — read by MK-NW-O-008
-MK-XS-I-010 transaction words (the institution's own wording) — read by MK-ST-F-013
+MK-XS-I-008 transaction amount — read by MK-PF-F-048, MK-ST-F-082
+MK-XS-I-009 transaction date — read by MK-NW-O-008, MK-PF-F-048
+MK-XS-I-010 transaction words (the institution's own wording) — read by MK-NW-F-123, MK-ST-F-013
 MK-XS-I-011 bond face value — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK-NW-F-069, MK
 MK-XS-I-012 bond coupon rate — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-060, MK-NW-F-064, MK-NW-F-070, MK-NW-F-071, MK
 MK-XS-I-013 bond maturity date — read by MK-NW-F-056, MK-NW-F-058, MK-NW-F-060, MK-NW-F-061, MK-NW-F-069, MK-NW-F-071, MK
@@ -3552,12 +3593,12 @@
 MK-XS-I-041 the payment the person chose to make on a debt — read by MK-CF-F-023
 MK-XS-I-042 how a stream is paid — monthly, yearly or one lump — read by MK-CF-F-021, MK-CF-F-022, MK-CF-F-023, MK-CF-F-149, MK-CF-F-150, MK-CF-F-152, MK
 MK-XS-I-043 their own retirement contribution — read by MK-CF-F-092, MK-CF-F-181, MK-CF-F-206
-MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-091, MK-NW-F-127, MK-PF-F-013, MK-ST-F-027, MK-ST-F-028, MK
+MK-XS-I-048 the person’s own asset-class answer — read by MK-NW-F-011, MK-NW-F-053, MK-NW-F-054, MK-NW-F-091, MK-NW-F-109, MK-NW-F-127, MK
 MK-XS-I-048 the person’s own asset-class answer — read by MK-ST-F-027
 MK-XS-I-049 bond price — what the bond is worth today — read by MK-NW-F-056, MK-NW-F-057, MK-NW-F-059, MK-NW-F-060, MK-NW-F-061, MK-NW-F-064, MK
 MK-XS-I-052 the day of the month a debt payment is due — read by MK-CF-F-005
 MK-XS-I-055 the wrapper an account sits in — ISA, 401(k), IRA and the rest — read by MK-CF-F-005, MK-CF-F-075, MK-CF-F-156, MK-NW-F-011, MK-NW-F-012, MK-NW-F-023, MK
-MK-XS-I-056 how a holding was classified, and by whom — read by MK-PF-F-013
+MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-PF-F-013
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
 MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
@@ -3687,7 +3728,8 @@
 MK-XS-F-025 tabOrder
 MK-XS-F-122 n
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -4169,6 +4211,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-002 withdrawalPlan
 MK-PL-F-003 depletionAge
 MK-PL-F-004 withdrawalOrder
@@ -4212,6 +4258,7 @@
 MK-ST-F-003 dayWords
 MK-ST-F-005 measuredFromLabel
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-031 valueOn
 MK-ST-F-033 onOrBefore
@@ -4252,7 +4299,8 @@
 MK-XS-F-131 toInt
 MK-XS-F-170 daysSince
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -4848,7 +4896,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -6269,7 +6318,8 @@
 MK-XS-F-174 recomputeBalances
 MK-XS-F-175 uid
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -7043,6 +7093,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
@@ -7077,6 +7131,7 @@
 MK-PL-F-086 splitBucketOf
 MK-PL-F-087 taxTypeNotStated
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
@@ -7139,7 +7194,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -7679,6 +7735,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-004 withdrawalOrder
 MK-PL-F-005 rmdStartAgeFor
@@ -7713,6 +7773,7 @@
 MK-PL-F-086 splitBucketOf
 MK-PL-F-087 taxTypeNotStated
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
@@ -7776,7 +7837,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -8279,7 +8341,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -8699,6 +8762,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-011 buildGoalsState
 MK-PL-F-012 waterfall
@@ -8731,6 +8798,7 @@
 MK-PL-F-087 taxTypeNotStated
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
@@ -8809,7 +8877,8 @@
 MK-XS-F-175 uid
 MK-XS-F-179 ageToday
 MK-XS-F-180 declareFigures
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -9621,6 +9690,10 @@
 MK-PF-F-042 windowTotal
 MK-PF-F-043 windowTotalOfRow
 MK-PF-F-044 startValues
+MK-PF-F-047 isIndividualBondOrCD
+MK-PF-F-048 bondInterestInWindow
+MK-PF-F-049 returnWithInterest
+MK-PF-F-050 worthWithInterest
 MK-PL-F-001 taxBucketSplit
 MK-PL-F-005 rmdStartAgeFor
 MK-PL-F-007 rmdAtAge
@@ -9658,6 +9731,7 @@
 MK-PL-F-087 taxTypeNotStated
 MK-ST-F-010 nameEvidence
 MK-ST-F-013 personalFlowTotals
+MK-ST-F-019 signed
 MK-ST-F-021 toNumber
 MK-ST-F-024 rmdStartAge
 MK-ST-F-025 rmdStartAgeFromAge
@@ -9739,7 +9813,8 @@
 MK-XS-F-179 ageToday
 MK-XS-F-180 declareFigures
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -10089,7 +10164,8 @@
 MK-XS-F-175 uid
 MK-XS-F-180 declareFigures
 MK-XS-F-182 figureSpec
-MK-XS-F-183 writeFigure</t>
+MK-XS-F-183 writeFigure
+MK-XS-F-185 percentDigits</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -10155,7 +10231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I540"/>
+  <dimension ref="A1:I539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16565,22 +16641,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>afternoon | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16608,22 +16684,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morning | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -25785,13 +25861,13 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Calculation Module code/engines/money.ts</t>
+          <t>src/domain/completeness/index.ts</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr"/>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>MK-ST-F-019 signed</t>
+          <t>MK-XS-F-001 planCompleteness</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -25815,51 +25891,16 @@
     <row r="399" ht="60" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>function inside no question</t>
+          <t>plumbing categorised as calculation (rule 8)</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>src/domain/completeness/index.ts</t>
+          <t>services · import parsing · store hooks · sign-in</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr"/>
       <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>MK-XS-F-001 planCompleteness</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>2 · DISPLAYED</t>
-        </is>
-      </c>
-      <c r="F399" s="2" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>reaches a screen: Yes</t>
-        </is>
-      </c>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>This calculation exists in the code, but none of the 22 questions leads to it. Either it prints a figure that has no row, or the map is missing a question, or the code is dead. Claude reads each one and says which; you rule on any that need a new question.</t>
-        </is>
-      </c>
-      <c r="I399" s="2" t="n"/>
-    </row>
-    <row r="400" ht="60" customHeight="1">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>plumbing categorised as calculation (rule 8)</t>
-        </is>
-      </c>
-      <c r="B400" s="2" t="inlineStr">
-        <is>
-          <t>services · import parsing · store hooks · sign-in</t>
-        </is>
-      </c>
-      <c r="C400" s="2" t="inlineStr"/>
-      <c r="D400" s="2" t="inlineStr">
         <is>
           <t>MK-XS-F-012 decodeCsvBase64 (holdingsImport.ts)
 MK-XS-F-013 parseCsv (holdingsImport.ts)
@@ -25913,16 +25954,55 @@
 MK-XS-F-178 useLevel (useStore.ts)</t>
         </is>
       </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>50 functions</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr"/>
+      <c r="G399" s="2" t="inlineStr"/>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>rule 8: an action or bring-data-in function is listed as such; the build categorised these as DISPLAYED or DEPENDENT because their return reaches a screen (a lock state, a sync status, a parsed file). Recommend: re-categorise in the build, one rule for the lot — your ruling</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="n"/>
+    </row>
+    <row r="400" ht="60" customHeight="1">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>orchestrator orphan</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>no screen imports it</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/expenses.ts</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>MK-CF-O-002 expenses</t>
+        </is>
+      </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>50 functions</t>
-        </is>
-      </c>
-      <c r="F400" s="2" t="inlineStr"/>
+          <t>named by 0 row(s)</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>imported by 0 screen(s)</t>
+        </is>
+      </c>
       <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>rule 8: an action or bring-data-in function is listed as such; the build categorised these as DISPLAYED or DEPENDENT because their return reaches a screen (a lock state, a sync status, a parsed file). Recommend: re-categorise in the build, one rule for the lot — your ruling</t>
+          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
         </is>
       </c>
       <c r="I400" s="2" t="n"/>
@@ -25940,17 +26020,17 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/expenses.ts</t>
+          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-002 expenses</t>
+          <t>MK-CF-O-003 thisMonth</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>named by 0 row(s)</t>
+          <t>named by 8 row(s)</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
@@ -25974,27 +26054,27 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>no screen imports it</t>
+          <t>/contribution-room</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
+          <t>MoneyKeel/functions/cashflow/contribution-room.ts</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-003 thisMonth</t>
+          <t>MK-CF-O-005 theContributionRoom</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>named by 8 row(s)</t>
+          <t>named by 0 row(s)</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>imported by 0 screen(s)</t>
+          <t>imported by 1 screen(s)</t>
         </is>
       </c>
       <c r="G402" s="2" t="inlineStr"/>
@@ -26013,17 +26093,17 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>/contribution-room</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/contribution-room.ts</t>
+          <t>MoneyKeel/functions/cashflow/tax-organizer.ts</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-005 theContributionRoom</t>
+          <t>MK-CF-O-007 theTaxOrganizer</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -26052,17 +26132,17 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>/tax-organizer</t>
+          <t>no screen imports it</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/tax-organizer.ts</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-007 theTaxOrganizer</t>
+          <t>MK-CF-O-011 PAY</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -26072,7 +26152,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>imported by 1 screen(s)</t>
+          <t>imported by 0 screen(s)</t>
         </is>
       </c>
       <c r="G404" s="2" t="inlineStr"/>
@@ -26101,7 +26181,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-011 PAY</t>
+          <t>MK-CF-O-012 PAY_ESTIMATED</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -26140,7 +26220,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-012 PAY_ESTIMATED</t>
+          <t>MK-CF-O-013 PAY_LANDS_TYPED</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -26174,12 +26254,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts</t>
+          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-013 PAY_LANDS_TYPED</t>
+          <t>MK-CF-O-014 M</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -26218,7 +26298,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-014 M</t>
+          <t>MK-CF-O-015 workedLineAmount</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -26252,12 +26332,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/this-month.ts</t>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-015 workedLineAmount</t>
+          <t>MK-CF-O-016 incomeSources</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -26291,17 +26371,17 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
+          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-016 incomeSources</t>
+          <t>MK-CF-O-018 theDebts</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>named by 0 row(s)</t>
+          <t>named by 8 row(s)</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -26325,27 +26405,27 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>no screen imports it</t>
+          <t>/income-manager</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/the-debts.ts</t>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-018 theDebts</t>
+          <t>MK-CF-O-019 theIncomeManager</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>named by 8 row(s)</t>
+          <t>named by 0 row(s)</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>imported by 0 screen(s)</t>
+          <t>imported by 1 screen(s)</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr"/>
@@ -26364,17 +26444,17 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>/income-manager</t>
+          <t>/plan · /cashflow</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/income-summary.ts</t>
+          <t>MoneyKeel/functions/cashflow/budget-counted.ts</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-019 theIncomeManager</t>
+          <t>MK-CF-O-020 theBudgetCounted</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -26384,7 +26464,7 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>imported by 1 screen(s)</t>
+          <t>imported by 2 screen(s)</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr"/>
@@ -26398,43 +26478,47 @@
     <row r="413" ht="60" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>orchestrator orphan</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>/plan · /cashflow</t>
+          <t>/account-detail · /analytics · /base-pay · /bill-calendar · /bonds · /cashflow · /holding-detail · /home · /income-manager · /income-summary · /insights · /invest · /itemize · /monthly-income · /other-investments</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/budget-counted.ts</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:146</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-O-020 theBudgetCounted</t>
+          <t>spec.unit === 'money' ? formatMoney(value)</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>named by 0 row(s)</t>
+          <t>$420, $600, $165,000, $151,000 … (1292 renders)</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>imported by 2 screen(s)</t>
-        </is>
-      </c>
-      <c r="G413" s="2" t="inlineStr"/>
+          <t>inside writeFigure</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-017 Return</t>
+        </is>
+      </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>This door exists in the code, but either no row on the master file names it, or no screen walks through it — the screen reaches the parts behind the door instead. The rows and the screen must both point at the door.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I413" s="2" t="n"/>
     </row>
-    <row r="414" ht="60" customHeight="1">
+    <row r="414" ht="45" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26442,22 +26526,22 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>/account-detail · /analytics · /base-pay · /bill-calendar · /bonds · /cashflow · /holding-detail · /home · /income-manager · /income-summary · /insights · /invest · /itemize · /monthly-income · /other-investments</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:80</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:148</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>spec.unit === 'money' ? formatMoney(value)</t>
+          <t>: spec.unit === 'money-cents' ? formatMoneyCents(value)</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>$420, $600, $165,000, $151,000 … (1292 renders)</t>
+          <t>$90.00 … (3 renders)</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -26467,7 +26551,7 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
+          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average), MK-NW-M-029 CURRENT PRICE · LIVE</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -26477,7 +26561,7 @@
       </c>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="45" customHeight="1">
+    <row r="415" ht="60" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26485,32 +26569,32 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
+          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:82</t>
+          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>: spec.unit === 'money-cents' ? formatMoneyCents(value)</t>
+          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>$90.00 … (3 renders)</t>
+          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>inside writeFigure</t>
+          <t>inside basePay</t>
         </is>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-NW-M-031 Quantity — n shares, MK-NW-M-032 Price paid (average), MK-NW-M-029 CURRENT PRICE · LIVE</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -26523,42 +26607,42 @@
     <row r="416" ht="60" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /base-pay · /cashflow · /home · /income-manager · /income-summary · /insights · /jobsafety · /stress-test</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/cashflow/base-pay.ts:962</t>
+          <t>src/components/DrawSteerSheet.tsx:137 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>const money0 = (n: number) =&gt; money(Math.round(n));</t>
+          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>$9,000, $1,800, $800, $6,400 … (92 renders)</t>
+          <t>$250,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>inside basePay</t>
+          <t>inside DrawSteerSheet</t>
         </is>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I416" s="2" t="n"/>
@@ -26566,42 +26650,42 @@
     <row r="417" ht="60" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>src/components/DrawSteerSheet.tsx:137 (+1 spoken/visible twin)</t>
+          <t>src/components/MoneySheets.tsx:285</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${BUCKET_LABEL[b]}, ${empty ? 'nothing here yet' : spokenMoney(Math.round(bal))}, ${i + 1} of ${order.length}.`}&gt;</t>
+          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>$250,000 … (10 renders)</t>
+          <t>$0 … (14 renders)</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>inside DrawSteerSheet</t>
+          <t>inside AllocateSavings</t>
         </is>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I417" s="2" t="n"/>
@@ -26619,17 +26703,17 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:285</t>
+          <t>src/components/MoneySheets.tsx:324</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[sh.allocHead, over &amp;&amp; { color: Colors.red }]}&gt;{money(Math.max(0, available - total))} of {money(available)} left to assign&lt;/Text&gt;</t>
+          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>$0 … (14 renders)</t>
+          <t>$0 … (7 renders)</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -26639,7 +26723,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26657,32 +26741,32 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/cashflow</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>src/components/MoneySheets.tsx:324</t>
+          <t>src/components/MortgageRateCompare.tsx:56 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={sh.saveTxt}&gt;{over ? 'Over available' : `Assign ${money(total)}`}&lt;/Text&gt;</t>
+          <t xml:space="preserve">accessibilityLabel={`${rates} A dollar into your mortgage saves you ${c.direction === 'paying-down-wins' ? 'more' : 'less'} than the same dollar would earn in Treasuries, about ${spokenMoney(yearly)} </t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>$0 … (7 renders)</t>
+          <t>$5,320 … (4 renders)</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>inside AllocateSavings</t>
+          <t>inside MortgageRateCompare</t>
         </is>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-CF-M-004 each row of the month — what it is and w, MK-CF-M-059 total interest</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -26692,7 +26776,7 @@
       </c>
       <c r="I419" s="2" t="n"/>
     </row>
-    <row r="420" ht="60" customHeight="1">
+    <row r="420" ht="45" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26700,32 +26784,32 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>/cashflow</t>
+          <t>/cashflow · /home</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>src/components/MortgageRateCompare.tsx:56 (+1 spoken/visible twin)</t>
+          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">accessibilityLabel={`${rates} A dollar into your mortgage saves you ${c.direction === 'paying-down-wins' ? 'more' : 'less'} than the same dollar would earn in Treasuries, about ${spokenMoney(yearly)} </t>
+          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>$5,320 … (4 renders)</t>
+          <t>$4,795 … (14 renders)</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>inside MortgageRateCompare</t>
+          <t>inside PaycheckCard</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-059 total interest, MK-CF-M-004 each row of the month — what it is and w</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26735,7 +26819,7 @@
       </c>
       <c r="I420" s="2" t="n"/>
     </row>
-    <row r="421" ht="45" customHeight="1">
+    <row r="421" ht="60" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26748,17 +26832,17 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:26 (+1 spoken/visible twin)</t>
+          <t>src/components/PaycheckCard.tsx:49</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>: `Surplus in ${m.label}: an estimate. ${maskedMoney(m.netSafeToSpend)}`}&gt;</t>
+          <t>&lt;Row key={i} label={g.source + (g.day ? ` (day ${g.day})` : '')} value={maskedMoney(g.amount)} /&gt;</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>$4,795 … (14 renders)</t>
+          <t>$2,200, $1,300 … (14 renders)</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
@@ -26768,7 +26852,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -26791,17 +26875,17 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:49</t>
+          <t>src/components/PaycheckCard.tsx:54</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row key={i} label={g.source + (g.day ? ` (day ${g.day})` : '')} value={maskedMoney(g.amount)} /&gt;</t>
+          <t>&lt;Text style={[styles.rowValue, { fontWeight: '800' }]}&gt;{maskedMoney(m.guaranteedTotal)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>$2,200, $1,300 … (14 renders)</t>
+          <t>$3,500 … (7 renders)</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
@@ -26811,7 +26895,7 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -26821,10 +26905,10 @@
       </c>
       <c r="I422" s="2" t="n"/>
     </row>
-    <row r="423" ht="60" customHeight="1">
+    <row r="423" ht="30" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -26834,17 +26918,17 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>src/components/PaycheckCard.tsx:54</t>
+          <t>src/components/PaycheckCard.tsx:59</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.rowValue, { fontWeight: '800' }]}&gt;{maskedMoney(m.guaranteedTotal)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.rowValue}&gt;{maskedMoney(m.safeDraw)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (7 renders)</t>
+          <t>$1,295 … (7 renders)</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -26854,227 +26938,227 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-055 Draw from savings</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I423" s="2" t="n"/>
     </row>
-    <row r="424" ht="30" customHeight="1">
+    <row r="424" ht="60" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
+          <t>money figure with NO row</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>/cashflow · /home</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PaycheckCard.tsx:65</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.year}&gt;This year ~{maskedMoney(year.thisYear)} &lt;EstimateTag /&gt; &lt;Text style={styles.yearNote}&gt;— varies month to month&lt;/Text&gt;&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>$55,140 … (7 renders)</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>inside PaycheckCard</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="n"/>
+    </row>
+    <row r="425" ht="45" customHeight="1">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B424" s="2" t="inlineStr">
-        <is>
-          <t>/cashflow · /home</t>
-        </is>
-      </c>
-      <c r="C424" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PaycheckCard.tsx:59</t>
-        </is>
-      </c>
-      <c r="D424" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.rowValue}&gt;{maskedMoney(m.safeDraw)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E424" s="2" t="inlineStr">
-        <is>
-          <t>$1,295 … (7 renders)</t>
-        </is>
-      </c>
-      <c r="F424" s="2" t="inlineStr">
-        <is>
-          <t>inside PaycheckCard</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>MK-CF-M-055 Draw from savings</t>
-        </is>
-      </c>
-      <c r="H424" s="2" t="inlineStr">
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PlanInputs.tsx:124</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>We're including your {maskedMoney(mortgageMonthly)}/month mortgage until it's paid off in {mortgagePayoffYear}, from your loan.</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>$1,900</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>inside PlanInputs</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I424" s="2" t="n"/>
-    </row>
-    <row r="425" ht="60" customHeight="1">
-      <c r="A425" s="2" t="inlineStr">
+      <c r="I425" s="2" t="n"/>
+    </row>
+    <row r="426" ht="60" customHeight="1">
+      <c r="A426" s="2" t="inlineStr">
         <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B425" s="2" t="inlineStr">
-        <is>
-          <t>/cashflow · /home</t>
-        </is>
-      </c>
-      <c r="C425" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PaycheckCard.tsx:65</t>
-        </is>
-      </c>
-      <c r="D425" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.year}&gt;This year ~{maskedMoney(year.thisYear)} &lt;EstimateTag /&gt; &lt;Text style={styles.yearNote}&gt;— varies month to month&lt;/Text&gt;&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E425" s="2" t="inlineStr">
-        <is>
-          <t>$55,140 … (7 renders)</t>
-        </is>
-      </c>
-      <c r="F425" s="2" t="inlineStr">
-        <is>
-          <t>inside PaycheckCard</t>
-        </is>
-      </c>
-      <c r="G425" s="2" t="inlineStr">
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PlanInputs.tsx:146</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>$1,080,000, $1,160,000, $130,000 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>inside PlanInputs</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H425" s="2" t="inlineStr">
+      <c r="H426" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I425" s="2" t="n"/>
-    </row>
-    <row r="426" ht="45" customHeight="1">
-      <c r="A426" s="2" t="inlineStr">
+      <c r="I426" s="2" t="n"/>
+    </row>
+    <row r="427" ht="45" customHeight="1">
+      <c r="A427" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B426" s="2" t="inlineStr">
+      <c r="B427" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C426" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PlanInputs.tsx:124</t>
-        </is>
-      </c>
-      <c r="D426" s="2" t="inlineStr">
-        <is>
-          <t>We're including your {maskedMoney(mortgageMonthly)}/month mortgage until it's paid off in {mortgagePayoffYear}, from your loan.</t>
-        </is>
-      </c>
-      <c r="E426" s="2" t="inlineStr">
-        <is>
-          <t>$1,900</t>
-        </is>
-      </c>
-      <c r="F426" s="2" t="inlineStr">
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PlanInputs.tsx:153</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
         <is>
           <t>inside PlanInputs</t>
         </is>
       </c>
-      <c r="G426" s="2" t="inlineStr">
+      <c r="G427" s="2" t="inlineStr">
         <is>
           <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
         </is>
       </c>
-      <c r="H426" s="2" t="inlineStr">
+      <c r="H427" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I426" s="2" t="n"/>
-    </row>
-    <row r="427" ht="60" customHeight="1">
-      <c r="A427" s="2" t="inlineStr">
+      <c r="I427" s="2" t="n"/>
+    </row>
+    <row r="428" ht="60" customHeight="1">
+      <c r="A428" s="2" t="inlineStr">
         <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B427" s="2" t="inlineStr">
+      <c r="B428" s="2" t="inlineStr">
         <is>
           <t>/plan</t>
         </is>
       </c>
-      <c r="C427" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PlanInputs.tsx:146</t>
-        </is>
-      </c>
-      <c r="D427" s="2" t="inlineStr">
-        <is>
-          <t>{maskedMoney(suggestedTarget)} — our starting figure, not yours. Change it to your own number.</t>
-        </is>
-      </c>
-      <c r="E427" s="2" t="inlineStr">
-        <is>
-          <t>$1,080,000, $1,160,000, $130,000 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F427" s="2" t="inlineStr">
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>src/components/PlanInputs.tsx:165 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
         <is>
           <t>inside PlanInputs</t>
         </is>
       </c>
-      <c r="G427" s="2" t="inlineStr">
+      <c r="G428" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H427" s="2" t="inlineStr">
+      <c r="H428" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
-      <c r="I427" s="2" t="n"/>
-    </row>
-    <row r="428" ht="45" customHeight="1">
-      <c r="A428" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B428" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C428" s="2" t="inlineStr">
-        <is>
-          <t>src/components/PlanInputs.tsx:153</t>
-        </is>
-      </c>
-      <c r="D428" s="2" t="inlineStr">
-        <is>
-          <t>&lt;SectionBand title="WHAT COUNTS TOWARD RETIREMENT" value={counted &gt; 0 ? maskedMoney(counted) : '—'} /&gt;</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr">
-        <is>
-          <t>$165,000, $729,800, $250,000 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F428" s="2" t="inlineStr">
-        <is>
-          <t>inside PlanInputs</t>
-        </is>
-      </c>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
-        </is>
-      </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I428" s="2" t="n"/>
@@ -27092,17 +27176,17 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:165 (+1 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:183 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${names.get(a.asset_id)}, ${spokenMoney(Math.round(a.balance ?? 0))}. ${counts ? 'Counts toward retirement' : "Doesn't count"}. Tap to change.`}</t>
+          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (16 renders)</t>
+          <t>$25,000 … (3 renders)</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr">
@@ -27135,22 +27219,22 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:183 (+2 spoken/visible twin)</t>
+          <t>src/components/PlanInputs.tsx:253</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>value={bigCosts.length ? maskedMoney(bigCosts.reduce((t: number, c: any) =&gt; t + c.amount, 0)) : 'None yet'} /&gt;</t>
+          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>$25,000 … (3 renders)</t>
+          <t>$0 … (5 renders)</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>inside PlanInputs</t>
+          <t>inside Stepper</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -27178,22 +27262,22 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>src/components/PlanInputs.tsx:253</t>
+          <t>src/components/SpendMoreControl.tsx:61</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.stepVal}&gt;{money ? `+${maskedMoney(value)}` : value}&lt;/Text&gt;</t>
+          <t>&lt;Text style={s.amt} accessibilityLabel={`${spokenMoney(extra)} more in expenses each month`}&gt;{maskedMoney(extra)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>$0 … (5 renders)</t>
+          <t>$0 … (4 renders)</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>inside Stepper</t>
+          <t>inside SpendMoreControl</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
@@ -27208,88 +27292,88 @@
       </c>
       <c r="I431" s="2" t="n"/>
     </row>
-    <row r="432" ht="60" customHeight="1">
+    <row r="432" ht="45" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>/plan</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>src/components/SpendMoreControl.tsx:73</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>? &lt;&gt;You'd spend &lt;Text style={s.b}&gt;{maskedMoney(total)}&lt;/Text&gt;/month — the same as now.&lt;/&gt;</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>$3,800 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>inside SpendMoreControl</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="n"/>
+    </row>
+    <row r="433" ht="60" customHeight="1">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B432" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C432" s="2" t="inlineStr">
-        <is>
-          <t>src/components/SpendMoreControl.tsx:61</t>
-        </is>
-      </c>
-      <c r="D432" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.amt} accessibilityLabel={`${spokenMoney(extra)} more in expenses each month`}&gt;{maskedMoney(extra)}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (4 renders)</t>
-        </is>
-      </c>
-      <c r="F432" s="2" t="inlineStr">
-        <is>
-          <t>inside SpendMoreControl</t>
-        </is>
-      </c>
-      <c r="G432" s="2" t="inlineStr">
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>/tips</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>src/components/UI.tsx:179</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>inside AmountText</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H432" s="2" t="inlineStr">
+      <c r="H433" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
-      <c r="I432" s="2" t="n"/>
-    </row>
-    <row r="433" ht="45" customHeight="1">
-      <c r="A433" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B433" s="2" t="inlineStr">
-        <is>
-          <t>/plan</t>
-        </is>
-      </c>
-      <c r="C433" s="2" t="inlineStr">
-        <is>
-          <t>src/components/SpendMoreControl.tsx:73</t>
-        </is>
-      </c>
-      <c r="D433" s="2" t="inlineStr">
-        <is>
-          <t>? &lt;&gt;You'd spend &lt;Text style={s.b}&gt;{maskedMoney(total)}&lt;/Text&gt;/month — the same as now.&lt;/&gt;</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr">
-        <is>
-          <t>$3,800 … (2 renders)</t>
-        </is>
-      </c>
-      <c r="F433" s="2" t="inlineStr">
-        <is>
-          <t>inside SpendMoreControl</t>
-        </is>
-      </c>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
-        </is>
-      </c>
-      <c r="H433" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I433" s="2" t="n"/>
@@ -27302,27 +27386,27 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>/tips</t>
+          <t>/income-detail · /tax-organizer</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>src/components/UI.tsx:179</t>
+          <t>src/domain/income/from-accounts.ts:176</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>const fmt = hide ? '••••' : formatMoney(safeAmt);</t>
+          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>$0 … (12 renders)</t>
+          <t>$10,000 … (2 renders)</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>inside AmountText</t>
+          <t>inside incomeFromAccounts</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
@@ -27345,27 +27429,27 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>/income-detail · /tax-organizer</t>
+          <t>/analytics · /plan</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>src/domain/income/from-accounts.ts:176</t>
+          <t>src/domain/planning/hub.ts:357</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>lines.push({ label, why: `${asPercent(rate)} coupon on ${money(face)} face`, annual: (rate * face), assumed: false });</t>
+          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>$10,000 … (2 renders)</t>
+          <t>$439,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>inside incomeFromAccounts</t>
+          <t>inside onCourseSentence</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
@@ -27388,27 +27472,27 @@
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>/analytics · /plan</t>
+          <t>/big-costs</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:357</t>
+          <t>src/screens/BigCostsScreen.tsx:46</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>const near = (n: number) =&gt; money(Math.max(1000, Math.round(n / 1000) * 1000));</t>
+          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>$439,000 … (10 renders)</t>
+          <t>$0 … (3 renders)</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>inside onCourseSentence</t>
+          <t>inside BigCostsScreen</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr">
@@ -27436,17 +27520,17 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>src/screens/BigCostsScreen.tsx:46</t>
+          <t>src/screens/BigCostsScreen.tsx:61 (+2 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>&lt;SectionBand inCard inset={20} title="YOUR BIG ONE-TIME COSTS" value={costs.length === 0 ? money(0) : undefined} /&gt;</t>
+          <t>accessibilityLabel={`${c.label}, ${spokenMoney(c.amount)} in ${c.year}. Opens the editor.`}</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>$0 … (3 renders)</t>
+          <t>$25,000 … (3 renders)</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
@@ -27466,174 +27550,174 @@
       </c>
       <c r="I437" s="2" t="n"/>
     </row>
-    <row r="438" ht="60" customHeight="1">
+    <row r="438" ht="45" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>/contribution-room</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/ContributionRoomScreen.tsx:30</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.room}&gt;{knownUsed ? `${money(room)} left` : `up to ${money(limit)}`}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>$14,900, $1,500, $4,400, $32,500 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>inside RoomCard</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-004 about $X of the $Y limit</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="n"/>
+    </row>
+    <row r="439" ht="60" customHeight="1">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>/contribution-room</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/ContributionRoomScreen.tsx:34</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>{knownUsed ? `That is about ${money(used)} of the ${money(limit)} limit — calculated from what you entered you contribute each month, not from your payroll, so check it against your latest statement.`</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>$9,600, $24,500, $6,000, $7,500 … (18 renders)</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>inside RoomCard</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-004 about $X of the $Y limit</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="n"/>
+    </row>
+    <row r="440" ht="45" customHeight="1">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>/contribution-room</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/ContributionRoomScreen.tsx:74 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>accessibilityLabel={`Try it in a what-if: about ${money(perMonth)} a month for the rest of the year`}&gt;</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>$5,000, $10,800, $8,200 … (8 renders)</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>inside ContributionRoomScreen</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-005 about $X for the rest of the year, MK-MN-M-004 about $X of the $Y limit</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="n"/>
+    </row>
+    <row r="441" ht="60" customHeight="1">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B438" s="2" t="inlineStr">
-        <is>
-          <t>/big-costs</t>
-        </is>
-      </c>
-      <c r="C438" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/BigCostsScreen.tsx:61 (+2 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D438" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`${c.label}, ${spokenMoney(c.amount)} in ${c.year}. Opens the editor.`}</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>$25,000 … (3 renders)</t>
-        </is>
-      </c>
-      <c r="F438" s="2" t="inlineStr">
-        <is>
-          <t>inside BigCostsScreen</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>/education</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>$210,622 … (8 renders)</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>inside EducationScreen</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H438" s="2" t="inlineStr">
+      <c r="H441" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
-      <c r="I438" s="2" t="n"/>
-    </row>
-    <row r="439" ht="45" customHeight="1">
-      <c r="A439" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B439" s="2" t="inlineStr">
-        <is>
-          <t>/contribution-room</t>
-        </is>
-      </c>
-      <c r="C439" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/ContributionRoomScreen.tsx:30</t>
-        </is>
-      </c>
-      <c r="D439" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.room}&gt;{knownUsed ? `${money(room)} left` : `up to ${money(limit)}`}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="inlineStr">
-        <is>
-          <t>$14,900, $1,500, $4,400, $32,500 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F439" s="2" t="inlineStr">
-        <is>
-          <t>inside RoomCard</t>
-        </is>
-      </c>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-004 about $X of the $Y limit</t>
-        </is>
-      </c>
-      <c r="H439" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I439" s="2" t="n"/>
-    </row>
-    <row r="440" ht="60" customHeight="1">
-      <c r="A440" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B440" s="2" t="inlineStr">
-        <is>
-          <t>/contribution-room</t>
-        </is>
-      </c>
-      <c r="C440" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/ContributionRoomScreen.tsx:34</t>
-        </is>
-      </c>
-      <c r="D440" s="2" t="inlineStr">
-        <is>
-          <t>{knownUsed ? `That is about ${money(used)} of the ${money(limit)} limit — calculated from what you entered you contribute each month, not from your payroll, so check it against your latest statement.`</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr">
-        <is>
-          <t>$9,600, $24,500, $6,000, $7,500 … (18 renders)</t>
-        </is>
-      </c>
-      <c r="F440" s="2" t="inlineStr">
-        <is>
-          <t>inside RoomCard</t>
-        </is>
-      </c>
-      <c r="G440" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-004 about $X of the $Y limit</t>
-        </is>
-      </c>
-      <c r="H440" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I440" s="2" t="n"/>
-    </row>
-    <row r="441" ht="45" customHeight="1">
-      <c r="A441" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B441" s="2" t="inlineStr">
-        <is>
-          <t>/contribution-room</t>
-        </is>
-      </c>
-      <c r="C441" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/ContributionRoomScreen.tsx:74 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D441" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`Try it in a what-if: about ${money(perMonth)} a month for the rest of the year`}&gt;</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr">
-        <is>
-          <t>$5,000, $10,800, $8,200 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F441" s="2" t="inlineStr">
-        <is>
-          <t>inside ContributionRoomScreen</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-005 about $X for the rest of the year, MK-MN-M-004 about $X of the $Y limit</t>
-        </is>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I441" s="2" t="n"/>
@@ -27651,17 +27735,17 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>src/screens/EducationScreen.tsx:63 (+1 spoken/visible twin)</t>
+          <t>src/screens/EducationScreen.tsx:74</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(plan.futureTotalCost)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>$210,622 … (8 renders)</t>
+          <t>$1,285 … (4 renders)</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
@@ -27689,27 +27773,27 @@
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/expense</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>src/screens/EducationScreen.tsx:74</t>
+          <t>src/screens/ExpenseScreen.tsx:225</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.gapHero}&gt;{money(plan.monthlyNeeded)}/month&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>$1,285 … (4 renders)</t>
+          <t>$60.00, $120.00</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>inside EducationScreen</t>
+          <t>inside ExpenseScreen</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
@@ -27732,27 +27816,27 @@
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>/expense</t>
+          <t>/goals</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>src/screens/ExpenseScreen.tsx:225</t>
+          <t>src/screens/GoalsScreen.tsx:92</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.entryAmt}&gt;-{money2((item as any).amount)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>$60.00, $120.00</t>
+          <t>$1,880, $100 … (4 renders)</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>inside ExpenseScreen</t>
+          <t>inside GoalsScreen</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
@@ -27770,7 +27854,7 @@
     <row r="445" ht="60" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -27780,17 +27864,17 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:92</t>
+          <t>src/screens/GoalsScreen.tsx:93</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.capVal}&gt;{money(capacity.avg)}/month&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.capLab}&gt;typical free cash to save{capacity.lumpy ? ` · ranges ${money(capacity.min)}–${money(capacity.max)} (some months free up more)` : ''}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>$1,880, $100 … (4 renders)</t>
+          <t>-$1,420, $2,180, -$3,200, $400 … (8 renders)</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
@@ -27800,98 +27884,98 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-008 typical free cash to save $X/mo</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I445" s="2" t="n"/>
     </row>
-    <row r="446" ht="60" customHeight="1">
+    <row r="446" ht="45" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
+          <t>money figure — more than one row could be it</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:101</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget comes to {money(0)}/year.&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>inside GoalsScreen</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="n"/>
+    </row>
+    <row r="447" ht="60" customHeight="1">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B446" s="2" t="inlineStr">
+      <c r="B447" s="2" t="inlineStr">
         <is>
           <t>/goals</t>
         </is>
       </c>
-      <c r="C446" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:93</t>
-        </is>
-      </c>
-      <c r="D446" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.capLab}&gt;typical free cash to save{capacity.lumpy ? ` · ranges ${money(capacity.min)}–${money(capacity.max)} (some months free up more)` : ''}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>-$1,420, $2,180, -$3,200, $400 … (8 renders)</t>
-        </is>
-      </c>
-      <c r="F446" s="2" t="inlineStr">
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/GoalsScreen.tsx:108</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget{sinkBasis.allPct ? ` (${sinkBasis.pct}% of take-home pay)` : ''} comes to ~{money(sink.annual)}/year. Set aside {money(sink.monthly)}/month so n</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>$3,600, $300, $2,400, $200 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
         <is>
           <t>inside GoalsScreen</t>
         </is>
       </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-008 typical free cash to save $X/mo</t>
-        </is>
-      </c>
-      <c r="H446" s="2" t="inlineStr">
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010 your non-monthly budget</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="n"/>
-    </row>
-    <row r="447" ht="45" customHeight="1">
-      <c r="A447" s="2" t="inlineStr">
-        <is>
-          <t>money figure — more than one row could be it</t>
-        </is>
-      </c>
-      <c r="B447" s="2" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="C447" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/GoalsScreen.tsx:101</t>
-        </is>
-      </c>
-      <c r="D447" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget comes to {money(0)}/year.&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (2 renders)</t>
-        </is>
-      </c>
-      <c r="F447" s="2" t="inlineStr">
-        <is>
-          <t>inside GoalsScreen</t>
-        </is>
-      </c>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
-        </is>
-      </c>
-      <c r="H447" s="2" t="inlineStr">
-        <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I447" s="2" t="n"/>
@@ -27899,7 +27983,7 @@
     <row r="448" ht="60" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -27909,17 +27993,17 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:108</t>
+          <t>src/screens/GoalsScreen.tsx:142</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.suggestSub}&gt;Your non-monthly budget{sinkBasis.allPct ? ` (${sinkBasis.pct}% of take-home pay)` : ''} comes to ~{money(sink.annual)}/year. Set aside {money(sink.monthly)}/month so n</t>
+          <t>&lt;Text style={styles.goalSub}&gt;{money(g.saved)} of {money(g.target)} · {money(remaining)} to go{perMonth &gt; 0 ? ` · need ~${money(perMonth)}/month${mo &gt; 0 ? ` for ${mo} mo` : ''}` : ''}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>$3,600, $300, $2,400, $200 … (12 renders)</t>
+          <t>$0, $60,000, $1,538, $20,000 … (16 renders)</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
@@ -27929,17 +28013,17 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I448" s="2" t="n"/>
     </row>
-    <row r="449" ht="60" customHeight="1">
+    <row r="449" ht="45" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -27952,17 +28036,17 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:142</t>
+          <t>src/screens/GoalsScreen.tsx:145</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.goalSub}&gt;{money(g.saved)} of {money(g.target)} · {money(remaining)} to go{perMonth &gt; 0 ? ` · need ~${money(perMonth)}/month${mo &gt; 0 ? ` for ${mo} mo` : ''}` : ''}&lt;/Text&gt;</t>
+          <t>This month: funded {money(fundedMo)} of {money(perMonth)}/month{behind ? ' — allocate more to catch up.' : ' ✓'}</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>$0, $60,000, $1,538, $20,000 … (16 renders)</t>
+          <t>$0, $1,538, $1,333 … (8 renders)</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
@@ -27982,10 +28066,10 @@
       </c>
       <c r="I449" s="2" t="n"/>
     </row>
-    <row r="450" ht="45" customHeight="1">
+    <row r="450" ht="60" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -27995,17 +28079,17 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:145</t>
+          <t>src/screens/GoalsScreen.tsx:151</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>This month: funded {money(fundedMo)} of {money(perMonth)}/month{behind ? ' — allocate more to catch up.' : ' ✓'}</t>
+          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>$0, $1,538, $1,333 … (8 renders)</t>
+          <t>$7,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -28015,12 +28099,12 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I450" s="2" t="n"/>
@@ -28038,17 +28122,17 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:151</t>
+          <t>src/screens/GoalsScreen.tsx:207</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.goalAllocate}&gt;Surplus this month: {money(availableSurplus)} — &lt;Text style={styles.goalAllocateCta}&gt;Allocate to this goal ›&lt;/Text&gt;&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>$7,200 … (4 renders)</t>
+          <t>$420, $9,000, $2,200 … (8 renders)</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
@@ -28081,17 +28165,17 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:207</t>
+          <t>src/screens/GoalsScreen.tsx:234</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.dtiSub}&gt;{money(dti.monthlyDebt)}/month in debt payments ÷ {money(dti.grossMonthly)}/month income&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {plural(liabilities.length, 'debt')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>$420, $9,000, $2,200 … (8 renders)</t>
+          <t>$14,000, $284,200 … (4 renders)</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
@@ -28124,17 +28208,17 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:234</t>
+          <t>src/screens/GoalsScreen.tsx:235</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;around {monthsToDate(plan.months)} · {money(totalDebt)} across {plural(liabilities.length, 'debt')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>$14,000, $284,200 … (4 renders)</t>
+          <t>$1,228, $236,683 … (4 renders)</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
@@ -28157,7 +28241,7 @@
     <row r="454" ht="60" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -28167,17 +28251,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:235</t>
+          <t>src/screens/GoalsScreen.tsx:303</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.resultSub}&gt;Total interest: {money(plan.totalInterest)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>$1,228, $236,683 … (4 renders)</t>
+          <t>$7,200, $3,500, $0 … (8 renders)</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
@@ -28187,12 +28271,12 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I454" s="2" t="n"/>
@@ -28200,7 +28284,7 @@
     <row r="455" ht="60" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -28210,17 +28294,17 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:303</t>
+          <t>src/screens/GoalsScreen.tsx:305</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Surplus this month: {money(availableSurplus)}. What you allocate is set aside for this goal and flips it 🟢 On track.&lt;/Text&gt;</t>
+          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500, $0 … (8 renders)</t>
+          <t>$7,200, $3,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
@@ -28230,12 +28314,12 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I455" s="2" t="n"/>
@@ -28248,27 +28332,27 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>/goals</t>
+          <t>/home</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>src/screens/GoalsScreen.tsx:305</t>
+          <t>src/screens/HomeScreen.tsx:135</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>{availableSurplus &gt; 0 &amp;&amp; &lt;TouchableOpacity accessibilityRole="button" accessibilityLabel={`Use all available surplus, ${money(availableSurplus)}`} onPress={() =&gt; setAllocAmt(String(Math.round(availabl</t>
+          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (12 renders)</t>
+          <t>$300, $1,900</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>inside GoalsScreen</t>
+          <t>inside HomeScreen</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
@@ -28286,7 +28370,7 @@
     <row r="457" ht="60" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -28296,17 +28380,17 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:135</t>
+          <t>src/screens/HomeScreen.tsx:312 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>if (due.length) Alert.alert('Debt due soon', due.map((d: any) =&gt; `${d.label} — ${maskedMoney(requiredPayment(d))} due day ${d.due_day}`).join('\n'), [{ text: 'OK' }]);</t>
+          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>$300, $1,900</t>
+          <t>$165,000, $709,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
@@ -28316,12 +28400,12 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I457" s="2" t="n"/>
@@ -28329,7 +28413,7 @@
     <row r="458" ht="60" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -28339,17 +28423,17 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:309 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:429 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Your investments: ${spokenMoney(investTotal)}${youReturn != null ? `, ${youReturn &gt;= 0 ? 'up' : 'down'} ${Math.abs(Math.round(youReturn * 1000) / 10)} percent this month` : ''}${f</t>
+          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $709,800 … (10 renders)</t>
+          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -28359,12 +28443,12 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I458" s="2" t="n"/>
@@ -28372,7 +28456,7 @@
     <row r="459" ht="60" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -28382,17 +28466,17 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:426 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:516</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Net worth ${spokenMoney(netWorth)}${nwDir ? `, ${nwDir} since last month` : ''}. Opens the Net worth tab.`}&gt;</t>
+          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>$151,000, $445,600, $250,000 … (14 renders)</t>
+          <t>$7,200, $0, $3,500 … (21 renders)</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr">
@@ -28402,12 +28486,12 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I459" s="2" t="n"/>
@@ -28425,17 +28509,17 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:513</t>
+          <t>src/screens/HomeScreen.tsx:529 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`This month's cash flow, ${pace.word.replace('✓ ', '')}: income ${spokenMoney(Math.round(thisMonthNet))}, spent so far ${spokenMoney(Math.round(bva.spent_total))}, ${left &gt;= 0 ? `$</t>
+          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $0, $3,500 … (21 renders)</t>
+          <t>$7,200, $3,500 … (14 renders)</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -28445,7 +28529,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28468,17 +28552,17 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:526 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:530</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Income&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(thisMonthNet))}&lt;/Text&gt;{thisMonthNet === 0 &amp;&amp; !hasIncomeEntered &amp;&amp; &lt;EmptyNote do</t>
+          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Actual expenses so far&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(bva.spent_total))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $3,500 … (14 renders)</t>
+          <t>$0 … (7 renders)</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -28488,7 +28572,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28498,7 +28582,7 @@
       </c>
       <c r="I461" s="2" t="n"/>
     </row>
-    <row r="462" ht="60" customHeight="1">
+    <row r="462" ht="45" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -28506,32 +28590,32 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>/home</t>
+          <t>/income-detail</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:527</t>
+          <t>src/screens/IncomeDetailScreen.tsx:68</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.cfCell}&gt;&lt;Text style={styles.cfLabel}&gt;Actual expenses so far&lt;/Text&gt;&lt;Text style={styles.cfNum}&gt;{maskedMoney(Math.round(bva.spent_total))}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>$0 … (7 renders)</t>
+          <t>$86,400, $86,720, $42,000</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>inside HomeScreen</t>
+          <t>inside IncomeDetailScreen</t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28554,17 +28638,17 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:68</t>
+          <t>src/screens/IncomeDetailScreen.tsx:69</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroV}&gt;{money(state.total_net_annual)}&lt;/Text&gt;</t>
+          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>$86,400, $86,720, $42,000</t>
+          <t>$108,000, $108,400, $42,000</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -28574,7 +28658,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28597,17 +28681,17 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:69</t>
+          <t>src/screens/IncomeDetailScreen.tsx:72</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row label="Gross / year" value={money(state.total_gross_annual)} bold /&gt;</t>
+          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>$108,000, $108,400, $42,000</t>
+          <t>$7,200, $7,227, $3,500</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -28617,7 +28701,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -28640,17 +28724,17 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:72</t>
+          <t>src/screens/IncomeDetailScreen.tsx:73</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>&lt;Row label="Take-home / month" value={`${money(state.net_monthly_income)}/month`} /&gt;</t>
+          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>$7,200, $7,227, $3,500</t>
+          <t>$4,800 … (2 renders)</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -28660,7 +28744,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28683,17 +28767,17 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:73</t>
+          <t>src/screens/IncomeDetailScreen.tsx:85</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>{state.employer_match_annual &gt; 0 &amp;&amp; &lt;Row label="Employer 401(k) match" value={`${money(state.employer_match_annual)}/year`} /&gt;}</t>
+          <t>&lt;Text style={styles.srcAmt}&gt;{money(src.gross_amount)}&lt;Text style={styles.per}&gt;{CADENCE[src.frequency]}&lt;/Text&gt;&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>$4,800 … (2 renders)</t>
+          <t>$9,000, $400, $3,500 … (4 renders)</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -28703,7 +28787,7 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -28713,45 +28797,45 @@
       </c>
       <c r="I466" s="2" t="n"/>
     </row>
-    <row r="467" ht="45" customHeight="1">
+    <row r="467" ht="60" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>/income-detail</t>
+          <t>/home · /insights</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>src/screens/IncomeDetailScreen.tsx:85</t>
+          <t>src/screens/InsightsScreen.tsx:76</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.srcAmt}&gt;{money(src.gross_amount)}&lt;Text style={styles.per}&gt;{CADENCE[src.frequency]}&lt;/Text&gt;&lt;/Text&gt;</t>
+          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>$9,000, $400, $3,500 … (4 renders)</t>
+          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>inside IncomeDetailScreen</t>
+          <t>inside useInsights</t>
         </is>
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I467" s="2" t="n"/>
@@ -28759,7 +28843,7 @@
     <row r="468" ht="60" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -28769,17 +28853,17 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:76</t>
+          <t>src/screens/InsightsScreen.tsx:155</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>const shareOf = (v: number) =&gt; (investable &gt; 0 ? `${money(v)} · ${Math.round((v / investable) * 100)}%` : money(v));</t>
+          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $400,000, $300,000 … (15 renders)</t>
+          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -28789,12 +28873,12 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I468" s="2" t="n"/>
@@ -28802,7 +28886,7 @@
     <row r="469" ht="60" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -28812,17 +28896,17 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:155</t>
+          <t>src/screens/InsightsScreen.tsx:161</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>.concat([{ label: 'Total invested', value: money(investable) }]),</t>
+          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000 … (8 renders)</t>
+          <t>$0 … (6 renders)</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
@@ -28832,12 +28916,12 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I469" s="2" t="n"/>
@@ -28845,7 +28929,7 @@
     <row r="470" ht="60" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -28855,17 +28939,17 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:161</t>
+          <t>src/screens/InsightsScreen.tsx:162</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>runway: () =&gt; [{ label: 'Cash on hand', value: money(ef.cash) },</t>
+          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>$0 … (6 renders)</t>
+          <t>$4,520, $3,800 … (6 renders)</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -28875,12 +28959,12 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I470" s="2" t="n"/>
@@ -28888,7 +28972,7 @@
     <row r="471" ht="60" customHeight="1">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -28898,17 +28982,17 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:162</t>
+          <t>src/screens/InsightsScreen.tsx:172</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>{ label: `Expenses/month (${essentialsLabel})`, value: money(ef.plannedSpendMonthly) },</t>
+          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>$4,520, $3,800 … (6 renders)</t>
+          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
@@ -28918,12 +29002,12 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I471" s="2" t="n"/>
@@ -28931,7 +29015,7 @@
     <row r="472" ht="60" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -28941,17 +29025,17 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:172</t>
+          <t>src/screens/InsightsScreen.tsx:177</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>{ label: `${IRS_LIMITS.year} 401(k) limit`, value: money(h.limit) }, { label: "You've contributed", value: money(h.used) }, { label: 'Room left', value: money(h.remaining) }]; },</t>
+          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>$24,500, $9,600, $14,900 … (15 renders)</t>
+          <t>$4,200 … (2 renders)</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr">
@@ -28961,12 +29045,12 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-007 Left / Over · left to spend this month</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I472" s="2" t="n"/>
@@ -28974,42 +29058,42 @@
     <row r="473" ht="60" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>/home · /insights</t>
+          <t>/insurance</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsightsScreen.tsx:177</t>
+          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>'toxic-debt': () =&gt; toxic ? [{ label: toxic.label, value: `${pct(toxic.interest_rate_apr)} APR` }, { label: 'Balance', value: money(toxic.remaining_balance || 0) }] : [],</t>
+          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>$4,200 … (2 renders)</t>
+          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>inside useInsights</t>
+          <t>inside InsuranceScreen</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I473" s="2" t="n"/>
@@ -29027,17 +29111,17 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:65 (+1 spoken/visible twin)</t>
+          <t>src/screens/InsuranceScreen.tsx:70</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.heroVal}&gt;{money(need.gap)}&lt;/Text&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>$944,000, $649,400, $185,000, $15,000 … (8 renders)</t>
+          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
@@ -29047,7 +29131,7 @@
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>MK-MN-M-018 Income replacement (N yrs)</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
@@ -29070,17 +29154,17 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:70</t>
+          <t>src/screens/InsuranceScreen.tsx:71</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Income replacement ({num(years)} yrs)&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>$1,080,000, $420,000, $0 … (4 renders)</t>
+          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
@@ -29090,7 +29174,7 @@
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
@@ -29113,17 +29197,17 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:71</t>
+          <t>src/screens/InsuranceScreen.tsx:72</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;+ Debts, goals &amp; final expenses&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;{money(need.totalNeed - need.incomeReplacement)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>$29,000, $299,200, $15,000 … (4 renders)</t>
+          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -29156,17 +29240,17 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:72</t>
+          <t>src/screens/InsuranceScreen.tsx:73</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;Total need&lt;/Text&gt;&lt;Text style={[styles.bdV, styles.bold]}&gt;{money(need.totalNeed)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;− Savings &amp; existing coverage&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;−{money(need.covered)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>$1,109,000, $1,379,200, $435,000, $15,000</t>
+          <t>$165,000, $729,800, $250,000, $0</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
@@ -29176,7 +29260,7 @@
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MK-MN-M-019 + Debts, goals &amp; final expenses · Total </t>
+          <t>MK-MN-M-018 Income replacement (N yrs)</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -29186,7 +29270,7 @@
       </c>
       <c r="I477" s="2" t="n"/>
     </row>
-    <row r="478" ht="60" customHeight="1">
+    <row r="478" ht="45" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29194,32 +29278,32 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>/insurance</t>
+          <t>/jobsafety</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>src/screens/InsuranceScreen.tsx:73</t>
+          <t>src/screens/JobSafetyScreen.tsx:117</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.bd}&gt;&lt;Text style={styles.bdL}&gt;− Savings &amp; existing coverage&lt;/Text&gt;&lt;Text style={styles.bdV}&gt;−{money(need.covered)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;Text style={[s.hero, { color: covered ? Colors.gainText : Colors.amber }]}&gt;{covered ? '✓ Covered' : money(gap)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800, $250,000, $0</t>
+          <t>$3,600, $31,320, $18,600</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>inside InsuranceScreen</t>
+          <t>inside JobSafetyScreen</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-018 Income replacement (N yrs)</t>
+          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -29229,7 +29313,7 @@
       </c>
       <c r="I478" s="2" t="n"/>
     </row>
-    <row r="479" ht="45" customHeight="1">
+    <row r="479" ht="60" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29242,17 +29326,17 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:117</t>
+          <t>src/screens/JobSafetyScreen.tsx:119</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[s.hero, { color: covered ? Colors.gainText : Colors.amber }]}&gt;{covered ? '✓ Covered' : money(gap)}&lt;/Text&gt;</t>
+          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>$3,600, $31,320, $18,600</t>
+          <t>$3,600, $600, $0, $31,320 … (9 renders)</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
@@ -29285,17 +29369,17 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:119</t>
+          <t>src/screens/JobSafetyScreen.tsx:132</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>{months} months of essentials is {money(target)} ({money(ess)}/month{rent &gt; 0 ? ` − ${figPer('MK-NW-M-064', rent)} rent from your property, which keeps arriving` : ''}) — your {basisWord} cover {money</t>
+          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>$3,600, $600, $0, $31,320 … (9 renders)</t>
+          <t>$600, $5,220, $3,100</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
@@ -29318,7 +29402,7 @@
     <row r="481" ht="60" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -29328,17 +29412,17 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:132</t>
+          <t>src/screens/JobSafetyScreen.tsx:175</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.baselineNote}&gt;Using {money(monthSpend)}/month — {emergencyFund.essentialsBasis} of your logged expenses — type your own if a typical month differs.&lt;/Text&gt;</t>
+          <t>Setting aside &lt;Text style={s.bold}&gt;{money(EXAMPLE_PACE)}/month&lt;/Text&gt; closes the gap in &lt;Text style={s.bold}&gt;{monthsToClose} months&lt;/Text&gt; — an example pace, set your own.</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>$600, $5,220, $3,100</t>
+          <t>$300 … (3 renders)</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
@@ -29348,55 +29432,55 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-020 N months of essentials is $X ($Y/month)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I481" s="2" t="n"/>
     </row>
-    <row r="482" ht="60" customHeight="1">
+    <row r="482" ht="45" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>/jobsafety</t>
+          <t>/multi-goal</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>src/screens/JobSafetyScreen.tsx:175</t>
+          <t>src/screens/MultiGoalScreen.tsx:81</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Setting aside &lt;Text style={s.bold}&gt;{money(EXAMPLE_PACE)}/month&lt;/Text&gt; closes the gap in &lt;Text style={s.bold}&gt;{monthsToClose} months&lt;/Text&gt; — an example pace, set your own.</t>
+          <t>{ label: 'Retirement saving', from: `${maskedMoney(A.contribMonthly ?? 0)}/month`, to: `${maskedMoney(retirementMonthly)}/month` },</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>$300 … (3 renders)</t>
+          <t>$0, $500 … (8 renders)</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>inside JobSafetyScreen</t>
+          <t>inside MultiGoalScreen</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo, MK-PL-M-030 Extra on debt $X/mo</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I482" s="2" t="n"/>
@@ -29404,7 +29488,7 @@
     <row r="483" ht="45" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -29414,17 +29498,17 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>src/screens/MultiGoalScreen.tsx:81</t>
+          <t>src/screens/MultiGoalScreen.tsx:135 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'Retirement saving', from: `${maskedMoney(A.contribMonthly ?? 0)}/month`, to: `${maskedMoney(retirementMonthly)}/month` },</t>
+          <t>accessibilityLabel={`Extra on debt at ${spokenMoney(extraDebt)} a month`} /&gt;</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>$0, $500 … (8 renders)</t>
+          <t>$0 … (4 renders)</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
@@ -29434,17 +29518,17 @@
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo, MK-PL-M-030 Extra on debt $X/mo</t>
+          <t>MK-PL-M-030 Extra on debt $X/mo</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I483" s="2" t="n"/>
     </row>
-    <row r="484" ht="45" customHeight="1">
+    <row r="484" ht="30" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29457,17 +29541,17 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>src/screens/MultiGoalScreen.tsx:135 (+1 spoken/visible twin)</t>
+          <t>src/screens/MultiGoalScreen.tsx:155</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Extra on debt at ${spokenMoney(extraDebt)} a month`} /&gt;</t>
+          <t>&lt;Text style={s.dialAmt}&gt;{maskedMoney(retirementMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>$0 … (4 renders)</t>
+          <t>$500 … (4 renders)</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
@@ -29477,7 +29561,7 @@
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-030 Extra on debt $X/mo</t>
+          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -29487,7 +29571,7 @@
       </c>
       <c r="I484" s="2" t="n"/>
     </row>
-    <row r="485" ht="30" customHeight="1">
+    <row r="485" ht="60" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29500,17 +29584,17 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>src/screens/MultiGoalScreen.tsx:155</t>
+          <t>src/screens/MultiGoalScreen.tsx:168 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.dialAmt}&gt;{maskedMoney(retirementMonthly)}/month&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`Can you do it all? ${weighed.covered ? `Covered, with ${spokenMoney(weighed.spare)} a month to spare` : `Short ${spokenMoney(Math.abs(weighed.spare))} a month`}`}&gt;</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>$500 … (4 renders)</t>
+          <t>$1,380, $400, $500 … (8 renders)</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -29530,7 +29614,7 @@
       </c>
       <c r="I485" s="2" t="n"/>
     </row>
-    <row r="486" ht="60" customHeight="1">
+    <row r="486" ht="45" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29538,32 +29622,32 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>/multi-goal</t>
+          <t>/plan</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>src/screens/MultiGoalScreen.tsx:168 (+1 spoken/visible twin)</t>
+          <t>src/screens/PlanHubScreen.tsx:234</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Can you do it all? ${weighed.covered ? `Covered, with ${spokenMoney(weighed.spare)} a month to spare` : `Short ${spokenMoney(Math.abs(weighed.spare))} a month`}`}&gt;</t>
+          <t>Your {maskedMoney(planSpend)}/month expenses{onCourse ? ` — ${onCourse}` : ` — ${oddsLine(lens, wil.chance!, wil.horizonAge)}`}.</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>$1,380, $400, $500 … (8 renders)</t>
+          <t>$3,800 … (2 renders)</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>inside MultiGoalScreen</t>
+          <t>inside PlanHubScreen</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-029 Retirement saving — $X/mo now → $Y/mo</t>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -29573,7 +29657,7 @@
       </c>
       <c r="I486" s="2" t="n"/>
     </row>
-    <row r="487" ht="45" customHeight="1">
+    <row r="487" ht="60" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29586,17 +29670,17 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:234</t>
+          <t>src/screens/PlanHubScreen.tsx:274</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Your {maskedMoney(planSpend)}/month expenses{onCourse ? ` — ${onCourse}` : ` — ${oddsLine(lens, wil.chance!, wil.horizonAge)}`}.</t>
+          <t>&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {plural(door.credit.accounts, 'account', `${door.credit.accounts}${accounts.some((a: any) =&gt; a.source === 'connected') ? ' connected' : ''</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>$3,800 … (2 renders)</t>
+          <t>$165,000, $729,800</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
@@ -29606,7 +29690,7 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -29619,7 +29703,7 @@
     <row r="488" ht="60" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -29629,17 +29713,17 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:274</t>
+          <t>src/screens/PlanHubScreen.tsx:309</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.doorCredit}&gt;✓ What you have — already in: {plural(door.credit.accounts, 'account', `${door.credit.accounts}${accounts.some((a: any) =&gt; a.source === 'connected') ? ' connected' : ''</t>
+          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>$165,000, $729,800</t>
+          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
@@ -29649,12 +29733,12 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-001 ✓ What you have — already in: N accounts</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I488" s="2" t="n"/>
@@ -29672,17 +29756,17 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:309</t>
+          <t>src/screens/PlanHubScreen.tsx:315</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Your retirement paycheck: guaranteed ${spokenMoney(Math.round(payMonth.guaranteedTotal))}, draw from savings ${spokenMoney(Math.round(payMonth.safeDraw))}, total ${spokenMoney(Mat</t>
+          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>$3,500, $1,295, $4,795 … (6 renders)</t>
+          <t>$2,200, $1,300 … (4 renders)</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
@@ -29692,7 +29776,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29715,17 +29799,17 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:315</t>
+          <t>src/screens/PlanHubScreen.tsx:317</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>&lt;View key={i} style={styles.payRow}&gt;&lt;Text style={styles.payL}&gt;{g.source}&lt;/Text&gt;&lt;Text style={styles.payV}&gt;{maskedMoney(Math.round(g.amount))}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>$2,200, $1,300 … (4 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
@@ -29735,7 +29819,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29758,17 +29842,17 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:317</t>
+          <t>src/screens/PlanHubScreen.tsx:318 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;= Guaranteed&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(payMonth.guaranteedTotal))}&lt;/Text&gt;&lt;/V</t>
+          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$1,295 … (4 renders)</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
@@ -29778,7 +29862,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -29801,17 +29885,17 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:318 (+1 spoken/visible twin)</t>
+          <t>src/screens/PlanHubScreen.tsx:319</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.payRow}&gt;&lt;View style={{ flexDirection: 'row', alignItems: 'center', gap: 4 }}&gt;&lt;Text style={styles.payL}&gt;+ Draw from savings&lt;/Text&gt;&lt;InfoDot term="safeDraw" /&gt;&lt;/View&gt;&lt;Text style={styl</t>
+          <t>&lt;View style={[styles.payRow, styles.payTotal]}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;Your paycheck&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(paycheckTotal))}/</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>$1,295 … (4 renders)</t>
+          <t>$4,795 … (2 renders)</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
@@ -29821,7 +29905,7 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
@@ -29831,10 +29915,10 @@
       </c>
       <c r="I492" s="2" t="n"/>
     </row>
-    <row r="493" ht="60" customHeight="1">
+    <row r="493" ht="45" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -29844,17 +29928,17 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:319</t>
+          <t>src/screens/PlanHubScreen.tsx:328</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.payRow, styles.payTotal]}&gt;&lt;Text style={[styles.payL, styles.payStrong]}&gt;Your paycheck&lt;/Text&gt;&lt;Text style={[styles.payV, styles.payStrong]}&gt;{maskedMoney(Math.round(paycheckTotal))}/</t>
+          <t>✓ covers your {maskedMoney(planSpend)}/month expenses. You're drawing {maskedMoney(Math.round(drawUsed))}/month</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>$4,795 … (2 renders)</t>
+          <t>$3,800, $300 … (4 renders)</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
@@ -29864,17 +29948,17 @@
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I493" s="2" t="n"/>
     </row>
-    <row r="494" ht="45" customHeight="1">
+    <row r="494" ht="60" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29882,32 +29966,32 @@
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>/plan</t>
+          <t>/required-withdrawals</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>src/screens/PlanHubScreen.tsx:328</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:102</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>✓ covers your {maskedMoney(planSpend)}/month expenses. You're drawing {maskedMoney(Math.round(drawUsed))}/month</t>
+          <t>&lt;Text style={s.line}&gt;Yours starts in &lt;Text style={s.strong}&gt;{startYear}&lt;/Text&gt; (age {rmdStartAgeFor(age)}). Estimated first withdrawal: &lt;Text style={s.strong}&gt;~{maskedMoney(Math.round(schedule[0]?.amo</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>$3,800, $300 … (4 renders)</t>
+          <t>$41,528, $138,428</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>inside PlanHubScreen</t>
+          <t>inside RequiredWithdrawalsScreen</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-002 Your odds — can't work them out yet. Add</t>
+          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
         </is>
       </c>
       <c r="H494" s="2" t="inlineStr">
@@ -29930,17 +30014,17 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:102</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:189 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.line}&gt;Yours starts in &lt;Text style={s.strong}&gt;{startYear}&lt;/Text&gt; (age {rmdStartAgeFor(age)}). Estimated first withdrawal: &lt;Text style={s.strong}&gt;~{maskedMoney(Math.round(schedule[0]?.amo</t>
+          <t>accessibilityLabel={`${r.year}, age ${r.age}: about ${spokenMoney(Math.round(r.amount))}${r.isCurrent ? ', this year' : ''}`}&gt;</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>$41,528, $138,428</t>
+          <t>$41,528, $43,628, $45,625, $47,916 … (32 renders)</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
@@ -29960,7 +30044,7 @@
       </c>
       <c r="I495" s="2" t="n"/>
     </row>
-    <row r="496" ht="60" customHeight="1">
+    <row r="496" ht="45" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -29973,17 +30057,17 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:189 (+1 spoken/visible twin)</t>
+          <t>src/screens/RequiredWithdrawalsScreen.tsx:205 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${r.year}, age ${r.age}: about ${spokenMoney(Math.round(r.amount))}${r.isCurrent ? ', this year' : ''}`}&gt;</t>
+          <t>accessibilityLabel={`${a.label}, ${spokenMoney(Math.round(a.balance || 0))}, marked pre-tax. Opens its page to edit.`}&gt;</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>$41,528, $43,628, $45,625, $47,916 … (32 renders)</t>
+          <t>$120,000, $400,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -29993,7 +30077,7 @@
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-015 YEAR BY YEAR (ESTIMATES) — each year and</t>
+          <t>MK-PL-M-016 BASED ON THESE ACCOUNTS — each balance</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
@@ -30003,45 +30087,45 @@
       </c>
       <c r="I496" s="2" t="n"/>
     </row>
-    <row r="497" ht="45" customHeight="1">
+    <row r="497" ht="60" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>/required-withdrawals</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RequiredWithdrawalsScreen.tsx:205 (+1 spoken/visible twin)</t>
+          <t>src/screens/RetirementCockpit.tsx:39</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`${a.label}, ${spokenMoney(Math.round(a.balance || 0))}, marked pre-tax. Opens its page to edit.`}&gt;</t>
+          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $400,000 … (4 renders)</t>
+          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>inside RequiredWithdrawalsScreen</t>
+          <t>inside big</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-016 BASED ON THESE ACCOUNTS — each balance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I497" s="2" t="n"/>
@@ -30059,22 +30143,22 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:39</t>
+          <t>src/screens/RetirementCockpit.tsx:504</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>const big = (n: number) =&gt; moneyCompact(n, 'M');</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>$165K, $2.03M, $480K, $1.38M … (66 renders)</t>
+          <t>$250K … (2 renders)</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>inside big</t>
+          <t>inside RetirementCockpit</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
@@ -30102,17 +30186,17 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:504</t>
+          <t>src/screens/RetirementCockpit.tsx:534</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>$250K … (2 renders)</t>
+          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
@@ -30145,17 +30229,17 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:534</t>
+          <t>src/screens/RetirementCockpit.tsx:569</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.verdictSub}&gt;Each year you spend {money(dPlan.spendAnnual)}{dPlan.guaranteedAnnual &gt; 0 ? `: Social Security / pension covers ${money(dPlan.guaranteedAnnual)}, and you take ${money(d</t>
+          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>$45,600, $26,400, $19,200 … (6 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
@@ -30188,17 +30272,17 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:569</t>
+          <t>src/screens/RetirementCockpit.tsx:646</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.planStmt}&gt;▸ Everything below assumes your plan: retire at {Math.round(planRetireAge)}{planSave &gt; 0 ? `, keep saving ${money(planSave)}/month` : ''}.&lt;/Text&gt;</t>
+          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -30231,17 +30315,17 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:646</t>
+          <t>src/screens/RetirementCockpit.tsx:655</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>label={`Retirement nest egg ${big(nestEgg)}, by account type: ${segs.map((s) =&gt; `${s.label} ${money(s.amt)}`).join(', ') || 'none yet'}`}&gt;</t>
+          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>$45,000, $120,000, $20,000, $309,800 … (10 renders)</t>
+          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -30274,17 +30358,17 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:655</t>
+          <t>src/screens/RetirementCockpit.tsx:665</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.lgV}&gt;{moneyCompact(s.amt, 'M')}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>$45K, $120K, $20K, $310K … (10 renders)</t>
+          <t>$0 … (2 renders)</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -30317,17 +30401,17 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:665</t>
+          <t>src/screens/RetirementCockpit.tsx:689</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.donutAmt}&gt;{money(0)}&lt;/Text&gt;</t>
+          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>$0 … (2 renders)</t>
+          <t>$10K, $250K … (4 renders)</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -30360,17 +30444,17 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:689</t>
+          <t>src/screens/RetirementCockpit.tsx:690</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.instWarn} numberOfLines={1}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')} · ⚠ Set a type ›&lt;/Text&gt;</t>
+          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source}${info.period ? ` · ${info.period}`</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>$10K, $250K … (4 renders)</t>
+          <t>$120K, $45K, $400K, $300K … (10 renders)</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -30403,17 +30487,17 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:690</t>
+          <t>src/screens/RetirementCockpit.tsx:751</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>: &lt;Text style={styles.instSrc} numberOfLines={2}&gt;{assetKind(a.kind)?.label} · {moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}{simple ? '' : ` · ${info.source}${info.period ? ` · ${info.period}`</t>
+          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $400K, $300K … (10 renders)</t>
+          <t>$2,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
@@ -30446,17 +30530,17 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:751</t>
+          <t>src/screens/RetirementCockpit.tsx:768</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;If your {big(nestEgg)} grows at {(planGrowth * 100).toFixed(1)}% ({basisLabel}){planSave &gt; 0 ? ` and you keep saving ${money(planSave)}/month` : ''}.{hasRetireBar ? ` Amber b</t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>$2,000 … (4 renders)</t>
+          <t>$5,000, $3,800 … (8 renders)</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -30489,17 +30573,17 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:768</t>
+          <t>src/screens/RetirementCockpit.tsx:790</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;You plan to spend &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(planSpend)}/month&lt;/Text&gt; in today's dollars → about &lt;Text style={{ fontWeight: '800', </t>
+          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>$5,000, $3,800 … (8 renders)</t>
+          <t>$14,900, $24,500 … (12 renders)</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
@@ -30532,17 +30616,17 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:790</t>
+          <t>src/screens/RetirementCockpit.tsx:792</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>? &lt;Text style={styles.note}&gt;💼 You can still add &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(k401.remaining)}&lt;/Text&gt; to your 401(k) this year{k401.catchUp ? ' (incl. the $8,0</t>
+          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>$14,900, $24,500 … (12 renders)</t>
+          <t>$7,500 … (6 renders)</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -30575,17 +30659,17 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:792</t>
+          <t>src/screens/RetirementCockpit.tsx:807</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={[styles.note, { marginTop: 6 }]}&gt;🏦 You can also contribute up to &lt;Text style={{ fontWeight: '800', color: Colors.textPrimary }}&gt;{money(annualIraLimit(age))}&lt;/Text&gt; to an IRA{age &gt;= 50 ? </t>
+          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>$7,500 … (6 renders)</t>
+          <t>$3,500 … (2 renders)</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
@@ -30618,22 +30702,22 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:807</t>
+          <t>src/screens/RetirementCockpit.tsx:980</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>? `${money(guarRowMonthly)}/month${claimAge &gt; age &amp;&amp; ssIncome &gt; 0 ? ` · Social Security part starts at ${claimAge}` : ''} · today's $${A.ssEligible == null ? ' · from your setup' : ''}`</t>
+          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>$3,500 … (2 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>inside RetirementCockpit</t>
+          <t>inside EarmarkSheet</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
@@ -30661,17 +30745,17 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:980</t>
+          <t>src/screens/RetirementCockpit.tsx:985</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.accBal}&gt;{isProp ? 'excluded — you live in it' : `${assetKind(a.kind)?.label ?? 'Other'} · ${money(a.balance)}`}&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000 … (14 renders)</t>
+          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr">
@@ -30699,27 +30783,27 @@
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/roth</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>src/screens/RetirementCockpit.tsx:985</t>
+          <t>src/screens/RothScreen.tsx:85 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.counts}&gt;{moneyCompact(earmarkedAmount(a, carId, homeId), 'M')}&lt;/Text&gt;</t>
+          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>$120K, $45K, $300K, $20K … (14 renders)</t>
+          <t>$0 … (12 renders)</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>inside EarmarkSheet</t>
+          <t>inside RothScreen</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
@@ -30737,179 +30821,179 @@
     <row r="514" ht="60" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:135</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={s.note}&gt;from your pre-tax {maskedMoney(Math.round(preTax))}{num(amount) &gt; preTax ? ' — capped at your balance' : ''}&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>$120,000, $400,000</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>inside RothScreen</t>
+        </is>
+      </c>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-024 from your pre-tax $X</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="n"/>
+    </row>
+    <row r="515" ht="45" customHeight="1">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>money figure — a row describes it</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:142 (+1 spoken/visible twin)</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>accessibilityLabel={`Set ${spokenMoney(v)}`}&gt;</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>$10,000, $25,000, $50,000 … (12 renders)</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>inside RothScreen</t>
+        </is>
+      </c>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-024 from your pre-tax $X</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>Nothing to do.</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="n"/>
+    </row>
+    <row r="516" ht="60" customHeight="1">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
           <t>money figure with NO row</t>
         </is>
       </c>
-      <c r="B514" s="2" t="inlineStr">
+      <c r="B516" s="2" t="inlineStr">
         <is>
           <t>/roth</t>
         </is>
       </c>
-      <c r="C514" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:85 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D514" s="2" t="inlineStr">
-        <is>
-          <t>{ label: `Convert to Roth this year (${nowYear})`, from: adopted ? maskedMoney(Number(A.rothConversionThisYear)) : 'nothing planned', to: maskedMoney(amt) },</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F514" s="2" t="inlineStr">
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RothScreen.tsx:195</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>title={`Convert ${maskedMoney(amt)} to Roth this year`}</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>$0 … (2 renders)</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
         <is>
           <t>inside RothScreen</t>
         </is>
       </c>
-      <c r="G514" s="2" t="inlineStr">
+      <c r="G516" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H514" s="2" t="inlineStr">
+      <c r="H516" s="2" t="inlineStr">
         <is>
           <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
-      <c r="I514" s="2" t="n"/>
-    </row>
-    <row r="515" ht="60" customHeight="1">
-      <c r="A515" s="2" t="inlineStr">
+      <c r="I516" s="2" t="n"/>
+    </row>
+    <row r="517" ht="30" customHeight="1">
+      <c r="A517" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
         </is>
       </c>
-      <c r="B515" s="2" t="inlineStr">
-        <is>
-          <t>/roth</t>
-        </is>
-      </c>
-      <c r="C515" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:135</t>
-        </is>
-      </c>
-      <c r="D515" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Text style={s.note}&gt;from your pre-tax {maskedMoney(Math.round(preTax))}{num(amount) &gt; preTax ? ' — capped at your balance' : ''}&lt;/Text&gt;</t>
-        </is>
-      </c>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>$120,000, $400,000</t>
-        </is>
-      </c>
-      <c r="F515" s="2" t="inlineStr">
-        <is>
-          <t>inside RothScreen</t>
-        </is>
-      </c>
-      <c r="G515" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-024 from your pre-tax $X</t>
-        </is>
-      </c>
-      <c r="H515" s="2" t="inlineStr">
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/SsTimingScreen.tsx:103</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Text style={styles.receiveHead}&gt;You receive {maskedMoney(num(op.ri_ss))}/month ✓&lt;/Text&gt;</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>$2,200</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>inside SsTimingScreen</t>
+        </is>
+      </c>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-018 You receive $X/mo ✓</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="inlineStr">
         <is>
           <t>Nothing to do.</t>
         </is>
       </c>
-      <c r="I515" s="2" t="n"/>
-    </row>
-    <row r="516" ht="45" customHeight="1">
-      <c r="A516" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B516" s="2" t="inlineStr">
-        <is>
-          <t>/roth</t>
-        </is>
-      </c>
-      <c r="C516" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:142 (+1 spoken/visible twin)</t>
-        </is>
-      </c>
-      <c r="D516" s="2" t="inlineStr">
-        <is>
-          <t>accessibilityLabel={`Set ${spokenMoney(v)}`}&gt;</t>
-        </is>
-      </c>
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>$10,000, $25,000, $50,000 … (12 renders)</t>
-        </is>
-      </c>
-      <c r="F516" s="2" t="inlineStr">
-        <is>
-          <t>inside RothScreen</t>
-        </is>
-      </c>
-      <c r="G516" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-024 from your pre-tax $X</t>
-        </is>
-      </c>
-      <c r="H516" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I516" s="2" t="n"/>
-    </row>
-    <row r="517" ht="60" customHeight="1">
-      <c r="A517" s="2" t="inlineStr">
-        <is>
-          <t>money figure with NO row</t>
-        </is>
-      </c>
-      <c r="B517" s="2" t="inlineStr">
-        <is>
-          <t>/roth</t>
-        </is>
-      </c>
-      <c r="C517" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/RothScreen.tsx:195</t>
-        </is>
-      </c>
-      <c r="D517" s="2" t="inlineStr">
-        <is>
-          <t>title={`Convert ${maskedMoney(amt)} to Roth this year`}</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr">
-        <is>
-          <t>$0 … (2 renders)</t>
-        </is>
-      </c>
-      <c r="F517" s="2" t="inlineStr">
-        <is>
-          <t>inside RothScreen</t>
-        </is>
-      </c>
-      <c r="G517" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H517" s="2" t="inlineStr">
-        <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
-        </is>
-      </c>
       <c r="I517" s="2" t="n"/>
     </row>
-    <row r="518" ht="30" customHeight="1">
+    <row r="518" ht="60" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -30919,17 +31003,17 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:103</t>
+          <t>src/screens/SsTimingScreen.tsx:137</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.receiveHead}&gt;You receive {maskedMoney(num(op.ri_ss))}/month ✓&lt;/Text&gt;</t>
+          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>$2,200</t>
+          <t>$2,600 … (3 renders)</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -30939,12 +31023,12 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-018 You receive $X/mo ✓</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I518" s="2" t="n"/>
@@ -30962,17 +31046,17 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:137</t>
+          <t>src/screens/SsTimingScreen.tsx:151</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>{usingExample &amp;&amp; &lt;Text style={styles.exampleBanner}&gt;Showing example numbers (a {maskedMoney(exampleStmt)}/month statement) — type yours above to see your own.&lt;/Text&gt;}</t>
+          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>$2,600 … (3 renders)</t>
+          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -30982,7 +31066,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -31005,17 +31089,17 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:151</t>
+          <t>src/screens/SsTimingScreen.tsx:153</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>: `Claiming at ${r.claimAge} pays ${maskedMoney(r.monthly)}/month, about ${maskedMoney(r.lifetime)} in total by age ${liveTo}${usingExample ? ', example numbers' : ''}`}&gt;</t>
+          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>$1,820, $611,520, $2,600, $717,600 … (18 renders)</t>
+          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
@@ -31025,7 +31109,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -31048,17 +31132,17 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:153</t>
+          <t>src/screens/SsTimingScreen.tsx:154</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tdMonthly, styles.tRight, { width: 104 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.monthly)}&lt;/Text&gt;</t>
+          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>$1,820, $2,600, $3,224 … (9 renders)</t>
+          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
@@ -31068,7 +31152,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">
@@ -31081,42 +31165,42 @@
     <row r="522" ht="60" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/stress-test</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>src/screens/SsTimingScreen.tsx:154</t>
+          <t>src/screens/StressTestScreen.tsx:74 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={[styles.td, styles.tRight, { width: 110 }, r.passed &amp;&amp; styles.passed, usingExample &amp;&amp; styles.example]}&gt;{maskedMoney(r.lifetime)}&lt;/Text&gt;</t>
+          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>$611,520, $717,600, $773,760 … (9 renders)</t>
+          <t>$3,000 … (10 renders)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>inside SsTimingScreen</t>
+          <t>inside StressTestScreen</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I522" s="2" t="n"/>
@@ -31124,7 +31208,7 @@
     <row r="523" ht="60" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure — more than one row could be it</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -31134,17 +31218,17 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:74 (+1 spoken/visible twin)</t>
+          <t>src/screens/StressTestScreen.tsx:78</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>{r.coversIt ? `✓ You could cover a ${money(shock)} hit` : `⚠ A ${money(shock)} hit would put you ${money(Math.abs(r.cashAfter))} in the red`}</t>
+          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>$3,000 … (10 renders)</t>
+          <t>$17,000, $5,220</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -31154,12 +31238,12 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
         </is>
       </c>
       <c r="I523" s="2" t="n"/>
@@ -31177,17 +31261,17 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:78</t>
+          <t>src/screens/StressTestScreen.tsx:104</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>? `You'd have ${money(r.cashAfter)} left${rentPaysForIt ? ', and rent from your property pays for your essentials' : ` — about ${r.runwayAfter.toFixed(1)} months of essentials`} (${money(ess)}/month —</t>
+          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>$17,000, $5,220</t>
+          <t>$600, $5,220, $3,100</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
@@ -31197,7 +31281,7 @@
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">
@@ -31210,7 +31294,7 @@
     <row r="525" ht="60" customHeight="1">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>money figure — more than one row could be it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -31220,17 +31304,17 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:104</t>
+          <t>src/screens/StressTestScreen.tsx:108</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;Text style={styles.note}&gt;Covering your {money(ess)}/month of essentials ({essLabel}) with no paycheck coming in{rentLine ? `, counting ${rentLine} of rent from your property, which keeps arriving` : </t>
+          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>$600, $5,220, $3,100</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -31240,12 +31324,12 @@
       </c>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H525" s="2" t="inlineStr">
         <is>
-          <t>Claude reads the screen and says which row owns it; only a genuine second figure comes to you.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I525" s="2" t="n"/>
@@ -31253,7 +31337,7 @@
     <row r="526" ht="60" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -31263,17 +31347,17 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:108</t>
+          <t>src/screens/StressTestScreen.tsx:118</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.note}&gt;Your essential expenses come to {money(0)}/month.&lt;/Text&gt;</t>
+          <t>&lt;Text style={styles.fundTxt}&gt;3 months of essentials{rent &gt; 0 ? ', less the rent that keeps arriving,' : ''} is &lt;Text style={styles.bold}&gt;{money(r.recommendedFund)}&lt;/Text&gt;. You're &lt;Text style={[styles.</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1,800, $9,300 … (4 renders)</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
@@ -31283,17 +31367,17 @@
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-MN-M-026 your $X/month of essentials</t>
         </is>
       </c>
       <c r="H526" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I526" s="2" t="n"/>
     </row>
-    <row r="527" ht="60" customHeight="1">
+    <row r="527" ht="45" customHeight="1">
       <c r="A527" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -31301,32 +31385,32 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>/stress-test</t>
+          <t>/tax-organizer</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>src/screens/StressTestScreen.tsx:118</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:90</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.fundTxt}&gt;3 months of essentials{rent &gt; 0 ? ', less the rent that keeps arriving,' : ''} is &lt;Text style={styles.bold}&gt;{money(r.recommendedFund)}&lt;/Text&gt;. You're &lt;Text style={[styles.</t>
+          <t>&lt;Text style={styles.rowV}&gt;{money(l.amount)}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
         <is>
-          <t>$1,800, $9,300 … (4 renders)</t>
+          <t>$108,000, $400, $42,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>inside StressTestScreen</t>
+          <t>inside TaxOrganizerScreen</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
@@ -31336,7 +31420,7 @@
       </c>
       <c r="I527" s="2" t="n"/>
     </row>
-    <row r="528" ht="45" customHeight="1">
+    <row r="528" ht="60" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
           <t>money figure — a row describes it</t>
@@ -31349,17 +31433,17 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:90</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={styles.rowV}&gt;{money(l.amount)}&lt;/Text&gt;</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>$108,000, $400, $42,000 … (4 renders)</t>
+          <t>$108,000, $108,400, $42,000, $0</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
@@ -31392,17 +31476,17 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:94</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Gross income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.grossIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>$108,000, $108,400, $42,000, $0</t>
+          <t>$9,600, $0 … (4 renders)</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
@@ -31435,17 +31519,17 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:95</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;401(k) contribution&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;− {money(org.steps.preTaxContributions)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $0 … (4 renders)</t>
+          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
@@ -31478,17 +31562,17 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:96</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;Standard deduction{org.steps.deductionIncludes.length ? &lt;Text style={styles.tag}&gt;  includes {org.steps.deductionIncludes.join(' and ')}&lt;/Text&gt; : null</t>
+          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>$32,200, $24,150, $16,100 … (4 renders)</t>
+          <t>$66,200, $66,600, $17,850, $0</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
@@ -31521,17 +31605,17 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:97</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>&lt;View style={[styles.row, styles.total]}&gt;&lt;Text style={styles.totalL}&gt;Taxable income&lt;/Text&gt;&lt;Text style={styles.totalV}&gt;{money(org.steps.taxableIncome)}&lt;/Text&gt;&lt;/View&gt;</t>
+          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>$66,200, $66,600, $17,850, $0</t>
+          <t>$9,600, $6,000 … (4 renders)</t>
         </is>
       </c>
       <c r="F532" s="2" t="inlineStr">
@@ -31554,7 +31638,7 @@
     <row r="533" ht="60" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>money figure — a row describes it</t>
+          <t>money figure with NO row</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -31564,17 +31648,17 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:107</t>
+          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>{org.contributions.map((c) =&gt; &lt;View key={c.label} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{c.label}&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(c.amount)}&lt;/Text&gt;&lt;/View&gt;)}</t>
+          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>$9,600, $6,000 … (4 renders)</t>
+          <t>$120,000, $45,000, $300,000, $20,000</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
@@ -31584,12 +31668,12 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-028 Gross income · 401(k) contribution · Sta</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>Nothing to do.</t>
+          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
         </is>
       </c>
       <c r="I533" s="2" t="n"/>
@@ -31602,27 +31686,27 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>/tax-organizer</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>src/screens/TaxOrganizerScreen.tsx:117</t>
+          <t>src/screens/WhatIfScreen.tsx:105</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>{org.accounts.map((ac, i) =&gt; &lt;View key={i} style={styles.row}&gt;&lt;Text style={styles.rowL}&gt;{ac.label} &lt;Text style={styles.tag}&gt;{ac.kind}&lt;/Text&gt;&lt;/Text&gt;&lt;Text style={styles.rowV}&gt;{money(ac.balance)}&lt;/Text&gt;&lt;</t>
+          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>$120,000, $45,000, $300,000, $20,000</t>
+          <t>$500 … (3 renders)</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>inside TaxOrganizerScreen</t>
+          <t>inside WhatIfScreen</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
@@ -31650,17 +31734,17 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:105</t>
+          <t>src/screens/WhatIfScreen.tsx:146 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.dial}&gt;+{maskedMoney(addMonthly)}/month&lt;/Text&gt;</t>
+          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>$500 … (3 renders)</t>
+          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -31693,17 +31777,17 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:146 (+1 spoken/visible twin)</t>
+          <t>src/screens/WhatIfScreen.tsx:150</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>accessibilityLabel={`Estimates at age ${result.retireAge}: nest egg ${spokenMoney(result.before.egg)} becomes ${spokenMoney(result.after.egg)}; the chance your money lasts ${result.before.chance} perc</t>
+          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>$4,977,392, $5,734,057, $9,483,181, $10,134,248 … (12 renders)</t>
+          <t>$756,665, $651,067, $6,000</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
@@ -31726,42 +31810,42 @@
     <row r="537" ht="60" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>money figure with NO row</t>
+          <t>money figure — a row describes it</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/will-it-last</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WhatIfScreen.tsx:150</t>
+          <t>src/screens/WillItLastScreen.tsx:51</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>&lt;Text style={s.deltaHero}&gt;{result.after.egg - result.before.egg &gt;= 0 ? '+' : '\u2212'}{maskedMoney(Math.abs(result.after.egg - result.before.egg))}&lt;/Text&gt;</t>
+          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>$756,665, $651,067, $6,000</t>
+          <t>$250,000</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>inside WhatIfScreen</t>
+          <t>inside WillItLastScreen</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-PL-M-008 What you have (nest egg)</t>
         </is>
       </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>This place in the code prints a dollar figure that no row on the master file describes. Claude reads the code line and proposes a row, with the figure, the screen and the section named; you confirm or correct the proposal.</t>
+          <t>Nothing to do.</t>
         </is>
       </c>
       <c r="I537" s="2" t="n"/>
@@ -31779,17 +31863,17 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:51</t>
+          <t>src/screens/WillItLastScreen.tsx:52</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'What you have (nest egg)', value: maskedMoney(inp.start_balance), source: 'your live account balances', route: '/(tabs)/analytics' },</t>
+          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>$250,000</t>
+          <t>$3,800</t>
         </is>
       </c>
       <c r="F538" s="2" t="inlineStr">
@@ -31799,7 +31883,7 @@
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-008 What you have (nest egg)</t>
+          <t>MK-PL-M-009 Monthly expenses in retirement</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
@@ -31822,17 +31906,17 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>src/screens/WillItLastScreen.tsx:52</t>
+          <t>src/screens/WillItLastScreen.tsx:53</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>{ label: 'Monthly expenses in retirement', value: maskedMoney(inp.retire_monthly_spend_today), source: A.spendMonthly != null ? 'you entered' : 'calculated from your data', route: '/retirement' },</t>
+          <t>{ label: 'Guaranteed income', value: `${maskedMoney(inp.guaranteed_monthly_income)}/month from age ${inp.guaranteed_start_age ?? inp.retire_age}`, source: A.ssMonthly != null || A.ssClaimAge != null ?</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="F539" s="2" t="inlineStr">
@@ -31842,7 +31926,7 @@
       </c>
       <c r="G539" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-009 Monthly expenses in retirement</t>
+          <t>MK-PL-M-010 Guaranteed income — $X/mo from age Y</t>
         </is>
       </c>
       <c r="H539" s="2" t="inlineStr">
@@ -31852,51 +31936,8 @@
       </c>
       <c r="I539" s="2" t="n"/>
     </row>
-    <row r="540" ht="60" customHeight="1">
-      <c r="A540" s="2" t="inlineStr">
-        <is>
-          <t>money figure — a row describes it</t>
-        </is>
-      </c>
-      <c r="B540" s="2" t="inlineStr">
-        <is>
-          <t>/will-it-last</t>
-        </is>
-      </c>
-      <c r="C540" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/WillItLastScreen.tsx:53</t>
-        </is>
-      </c>
-      <c r="D540" s="2" t="inlineStr">
-        <is>
-          <t>{ label: 'Guaranteed income', value: `${maskedMoney(inp.guaranteed_monthly_income)}/month from age ${inp.guaranteed_start_age ?? inp.retire_age}`, source: A.ssMonthly != null || A.ssClaimAge != null ?</t>
-        </is>
-      </c>
-      <c r="E540" s="2" t="inlineStr">
-        <is>
-          <t>$3,500</t>
-        </is>
-      </c>
-      <c r="F540" s="2" t="inlineStr">
-        <is>
-          <t>inside WillItLastScreen</t>
-        </is>
-      </c>
-      <c r="G540" s="2" t="inlineStr">
-        <is>
-          <t>MK-PL-M-010 Guaranteed income — $X/mo from age Y</t>
-        </is>
-      </c>
-      <c r="H540" s="2" t="inlineStr">
-        <is>
-          <t>Nothing to do.</t>
-        </is>
-      </c>
-      <c r="I540" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I540"/>
+  <autoFilter ref="A1:I539"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -26488,7 +26488,7 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:146</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:115</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-017 Return</t>
+          <t>MK-PF-M-014 Wealth generated, MK-PF-M-002 Wealth generated, MK-PF-M-006 WHAT EACH CATEGORY EARNED — RETURN</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/_figure-spec.ts:148</t>
+          <t>MoneyKeel/functions/_figure-spec.ts:117</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26776,7 +26776,7 @@
       </c>
       <c r="I419" s="2" t="n"/>
     </row>
-    <row r="420" ht="45" customHeight="1">
+    <row r="420" ht="60" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26809,7 +26809,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26852,7 +26852,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -28013,7 +28013,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
+          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28615,7 +28615,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-013 Take-home / month, MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match</t>
+          <t>MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month, MK-MN-M-014 Employer 401(k) match</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29819,7 +29819,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29862,7 +29862,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
@@ -31238,7 +31238,7 @@
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H523" s="2" t="inlineStr">
@@ -31281,7 +31281,7 @@
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-024 You could cover a $X hit, MK-MN-M-026 your $X/month of essentials</t>
+          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
         </is>
       </c>
       <c r="H524" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-19</t>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · census 2026-10-20</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -1324,6 +1324,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-005 theAlternativesOutlook
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
@@ -1800,6 +1802,8 @@
 MK-NW-F-139 leftOutValueOf
 MK-NW-F-141 holdingBondFacts
 MK-NW-F-142 classReturnOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2450,6 +2454,8 @@
 MK-NW-F-139 leftOutValueOf
 MK-NW-F-141 holdingBondFacts
 MK-NW-F-142 classReturnOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-002 theAccount
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -2946,6 +2952,7 @@
 MK-ST-F-073 rebuildDays
 MK-ST-F-076 ageLabel
 MK-ST-F-077 isStale
+MK-ST-F-078 dateShown
 MK-ST-F-079 dailyWindowStart
 MK-ST-F-080 isDay
 MK-ST-F-081 timeWeightedReturn
@@ -3259,6 +3266,8 @@
 MK-NW-F-131 pricedLikeBond
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-001 theBonds
 MK-NW-O-008 thePerformance
 MK-PF-F-001 totalShares
@@ -3331,7 +3340,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -3557,11 +3566,11 @@
 MK-XS-I-001 account balance — read by MK-ST-F-027
 MK-XS-I-002 account type (taxable, pre-tax, Roth) — read by MK-NW-F-011, MK-NW-F-012, MK-NW-F-025, MK-NW-F-054, MK-NW-F-120, MK-NW-O-001
 MK-XS-I-003 institution name — read by MK-NW-F-025, MK-NW-F-026, MK-NW-F-071, MK-NW-F-072, MK-NW-O-001
-MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-NW-F-091, MK-NW-F-128, MK-PF-F-001, MK-PF-F-002, MK-PF-F-004, MK
+MK-XS-I-004 holding quantity (shares) — read by MK-CF-F-062, MK-NW-F-091, MK-NW-F-128, MK-NW-F-143, MK-PF-F-001, MK-PF-F-002, MK
 MK-XS-I-004 holding quantity (shares) — read by MK-ST-F-027
-MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-009, MK-PF-F-011, MK-PF-F-014, MK-PF-F-029, MK
+MK-XS-I-005 holding price — read by MK-NW-F-091, MK-NW-F-128, MK-NW-F-143, MK-NW-O-008, MK-PF-F-009, MK-PF-F-011, MK
 MK-XS-I-005 holding price — read by MK-ST-F-027
-MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-139, MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK-PF-F-013, MK
+MK-XS-I-007 purchase price and date (per lot) — read by MK-NW-F-139, MK-NW-F-143, MK-PF-F-002, MK-PF-F-005, MK-PF-F-007, MK-PF-F-012, MK
 MK-XS-I-007 purchase price and date (per lot) — read by MK-ST-F-027
 MK-XS-I-008 transaction amount — read by MK-PF-F-048, MK-ST-F-082
 MK-XS-I-009 transaction date — read by MK-NW-O-008, MK-PF-F-048
@@ -3601,7 +3610,7 @@
 MK-XS-I-056 how a holding was classified, and by whom — read by MK-NW-F-053, MK-NW-F-054, MK-NW-F-109, MK-PF-F-013
 MK-XS-I-059 the month a bonus lands — read by MK-CF-F-088, MK-CF-F-092
 MK-XS-I-060 how a person is paid — weekly, fortnightly, monthly — read by MK-CF-F-130
-MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-F-091, MK-NW-F-128, MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
+MK-XS-I-063 option contract multiplier — 100 unless the broker or the person states otherwise — read by MK-NW-F-091, MK-NW-F-128, MK-NW-F-143, MK-PF-F-002, MK-PF-F-004, MK-PF-F-031
 MK-XS-I-064 the unit beside a quantity — shares, coins, contracts, ounces or units — read by MK-CF-F-003, MK-CF-F-008, MK-CF-F-204, MK-NW-F-078, MK-XS-F-183
 MK-XS-I-065 accrued interest on a bond — interest earned since the last coupon — read by MK-NW-F-056, MK-NW-F-060, MK-NW-F-070, MK-NW-F-072
 [the code's record, this build — evidence for the ruling, not the row's statement: it cannot see inputs handed in as arguments, and it counts every branch below the producer]</t>
@@ -4192,6 +4201,8 @@
 MK-NW-F-136 earmarkLeavesOutWords
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-008 thePerformance
 MK-PF-F-005 unrealizedGain
 MK-PF-F-007 totalROI
@@ -7064,6 +7075,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
@@ -7706,6 +7719,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
 MK-NW-O-008 thePerformance
@@ -8732,6 +8747,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -9659,6 +9676,8 @@
 MK-NW-F-134 carValueNotEnteredNotes
 MK-NW-F-138 knownHoldingsReturn
 MK-NW-F-139 leftOutValueOf
+MK-NW-F-143 gainRowBetween
+MK-NW-F-144 beforeTheRecordSentence
 MK-NW-O-001 theBonds
 MK-NW-O-003 theNetWorth
 MK-NW-O-004 theEmergencyFund
@@ -16641,22 +16660,22 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>afternoon | ava | your &lt;name&gt;: $#</t>
+          <t>estimate | social security | $#</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>retiree</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>spoken, visible</t>
+          <t>visible</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>$4,795 | this month</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -16684,22 +16703,22 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>estimate | social security | $#</t>
+          <t>evening | ava | your &lt;name&gt;: $#</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>retiree</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>visible</t>
+          <t>spoken, visible</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>$4,795 | this month</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -26594,7 +26613,7 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-034 Your 401(k)s, MK-CF-M-020 THIS MONTH — free to use, MK-XS-M-006 Income · In (received) · In (take-home)</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -26680,7 +26699,7 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -26723,7 +26742,7 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -26776,7 +26795,7 @@
       </c>
       <c r="I419" s="2" t="n"/>
     </row>
-    <row r="420" ht="60" customHeight="1">
+    <row r="420" ht="45" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>money figure — more than one row could be it</t>
@@ -26809,7 +26828,7 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-XS-M-005 Spent so far · Spent $X of $Y left to sp, MK-CF-M-001 Expenses, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -26852,7 +26871,7 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
+          <t>MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-020 THIS MONTH — free to use</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -27927,7 +27946,7 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -28013,7 +28032,7 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -28056,7 +28075,7 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -28271,7 +28290,7 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-009 each goal — $X of $Y · $Z to go, MK-MN-M-010 your non-monthly budget</t>
+          <t>MK-MN-M-010 your non-monthly budget, MK-MN-M-009 each goal — $X of $Y · $Z to go</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -28380,7 +28399,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:312 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:314 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -28423,7 +28442,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:429 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:431 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -28466,7 +28485,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:516</t>
+          <t>src/screens/HomeScreen.tsx:518</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -28486,7 +28505,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -28509,7 +28528,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:529 (+1 spoken/visible twin)</t>
+          <t>src/screens/HomeScreen.tsx:531 (+1 spoken/visible twin)</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -28529,7 +28548,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -28552,7 +28571,7 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>src/screens/HomeScreen.tsx:530</t>
+          <t>src/screens/HomeScreen.tsx:532</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
@@ -28572,7 +28591,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -28916,7 +28935,7 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-007 Left / Over · left to spend this month</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -29733,7 +29752,7 @@
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -29776,7 +29795,7 @@
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -29819,7 +29838,7 @@
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -29862,7 +29881,7 @@
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -31023,7 +31042,7 @@
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H518" s="2" t="inlineStr">
@@ -31066,7 +31085,7 @@
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H519" s="2" t="inlineStr">
@@ -31109,7 +31128,7 @@
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H520" s="2" t="inlineStr">
@@ -31152,7 +31171,7 @@
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
+          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
         </is>
       </c>
       <c r="H521" s="2" t="inlineStr">

--- a/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
+++ b/MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx
@@ -29692,7 +29692,7 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-CF-M-023 YOUR FUTURE PAYCHECK — Social Security ·, MK-CF-M-011 YOUR SOURCES — Social Security · pension, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon, MK-CF-M-020 THIS MONTH — free to use</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-CF-M-020 THIS MONTH — free to use, MK-CF-M-022 YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X/mon</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -31412,7 +31412,7 @@
       </c>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
@@ -31455,7 +31455,7 @@
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
@@ -31627,7 +31627,7 @@
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -31670,7 +31670,7 @@
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
@@ -31713,7 +31713,7 @@
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-013 Take-home / month, MK-MN-M-012 Gross / year</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-012 Gross / year, MK-MN-M-013 Take-home / month</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-013 Take-home / month</t>
+          <t>MK-MN-M-011 TAKE-HOME / YEAR, MK-MN-M-014 Employer 401(k) match, MK-MN-M-012 Gross / year</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -31928,7 +31928,7 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>MK-HM-M-001 prices updated &lt;when&gt;, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-HM-M-001 prices updated &lt;when&gt;</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -31971,7 +31971,7 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-XS-M-007 Left / Over · left to spend this month, MK-HM-M-004 &lt;n&gt;% spent · day n of m</t>
+          <t>MK-XS-M-006 Income · In (received) · In (take-home), MK-HM-M-004 &lt;n&gt;% spent · day n of m, MK-XS-M-005 Spent so far · Spent $X of $Y left to sp</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -32788,7 +32788,7 @@
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H527" s="2" t="inlineStr">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H528" s="2" t="inlineStr">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-006 Your paycheck $X/mo</t>
         </is>
       </c>
       <c r="H529" s="2" t="inlineStr">
@@ -32917,7 +32917,7 @@
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
+          <t>MK-PL-M-005 + Draw from savings, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H530" s="2" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante, MK-PL-M-005 + Draw from savings</t>
+          <t>MK-PL-M-006 Your paycheck $X/mo, MK-PL-M-004 = Guaranteed, MK-PL-M-003 YOUR RETIREMENT PAYCHECK — each guarante</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
@@ -34078,7 +34078,7 @@
       </c>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H557" s="2" t="inlineStr">
@@ -34121,7 +34121,7 @@
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="G559" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N, MK-PL-M-021 Showing example numbers (a $X/mo stateme</t>
         </is>
       </c>
       <c r="H559" s="2" t="inlineStr">
@@ -34207,7 +34207,7 @@
       </c>
       <c r="G560" s="2" t="inlineStr">
         <is>
-          <t>MK-PL-M-020 about $X in total by age N, MK-PL-M-019 Claiming at N pays $X a month</t>
+          <t>MK-PL-M-019 Claiming at N pays $X a month, MK-PL-M-020 about $X in total by age N</t>
         </is>
       </c>
       <c r="H560" s="2" t="inlineStr">
@@ -34293,7 +34293,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>MK-MN-M-025 You'd have $X left — about N months of e, MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit</t>
+          <t>MK-MN-M-026 your $X/month of essentials, MK-MN-M-024 You could cover a $X hit, MK-MN-M-025 You'd have $X left — about N months of e</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
